--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -164,7 +164,7 @@
     <numFmt numFmtId="170" formatCode="0.000000000"/>
     <numFmt numFmtId="171" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -265,6 +265,27 @@
       <b val="1"/>
       <color rgb="FF0000FF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF7030A0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="14">
@@ -370,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -461,6 +482,31 @@
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,6 +790,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="51">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -795,6 +842,28 @@
       <c r="D10" t="inlineStr">
         <is>
           <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Value font:</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>variable (set/measure)</t>
+        </is>
+      </c>
+      <c r="C11" s="59" t="inlineStr">
+        <is>
+          <t>fixed data / constant</t>
+        </is>
+      </c>
+      <c r="D11" s="60" t="inlineStr">
+        <is>
+          <t>formula</t>
         </is>
       </c>
     </row>
@@ -852,7 +921,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="61" t="inlineStr">
         <is>
           <t>AEP0.1.1</t>
         </is>
@@ -879,7 +948,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="61" t="inlineStr">
         <is>
           <t>Tube</t>
         </is>
@@ -906,7 +975,7 @@
           <t>0-5</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="61" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="17" t="inlineStr">
@@ -931,7 +1000,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="61" t="inlineStr">
         <is>
           <t>AEP0.1.1</t>
         </is>
@@ -958,7 +1027,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="61" t="inlineStr">
         <is>
           <t>AEP0.2</t>
         </is>
@@ -985,7 +1054,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="61" t="inlineStr">
         <is>
           <t>Tube</t>
         </is>
@@ -1012,7 +1081,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="61" t="inlineStr">
         <is>
           <t>Sintered</t>
         </is>
@@ -1023,6 +1092,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="51">
       <c r="A22" s="9" t="inlineStr">
         <is>
@@ -1077,7 +1147,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D24" s="19" t="n">
+      <c r="D24" s="55" t="n">
         <v>27.48</v>
       </c>
       <c r="E24" s="17" t="inlineStr">
@@ -1102,7 +1172,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="55" t="n">
         <v>27.48</v>
       </c>
       <c r="E25" s="52" t="inlineStr">
@@ -1127,7 +1197,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="62" t="n">
         <v>55</v>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -1152,7 +1222,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="62" t="n">
         <v>95</v>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -1177,7 +1247,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="62" t="n">
         <v>16</v>
       </c>
       <c r="E28" s="17" t="inlineStr">
@@ -1202,7 +1272,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D29" s="21" t="n">
+      <c r="D29" s="62" t="n">
         <v>30</v>
       </c>
       <c r="E29" s="17" t="inlineStr">
@@ -1227,7 +1297,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D30" s="21" t="n">
+      <c r="D30" s="62" t="n">
         <v>24</v>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -1252,7 +1322,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="62" t="n">
         <v>42</v>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -1261,6 +1331,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33" ht="15" customHeight="1" s="51">
       <c r="A33" s="9" t="inlineStr">
         <is>
@@ -1315,7 +1386,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="63">
         <f>IF(rx_ver=ver_name_1,vial_OD_1,IF(rx_ver=ver_name_2,vial_OD_2,NA()))</f>
         <v/>
       </c>
@@ -1341,7 +1412,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D36" s="24" t="n">
+      <c r="D36" s="55" t="n">
         <v>1.1</v>
       </c>
       <c r="E36" s="25" t="inlineStr">
@@ -1366,7 +1437,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="63">
         <f>vial_OD-2*vial_wall</f>
         <v/>
       </c>
@@ -1392,7 +1463,7 @@
           <t>mm²</t>
         </is>
       </c>
-      <c r="D38" s="21">
+      <c r="D38" s="64">
         <f>PI()/4*vial_ID^2</f>
         <v/>
       </c>
@@ -1418,7 +1489,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D39" s="21">
+      <c r="D39" s="64">
         <f>IF(rx_ver=ver_name_1,D_int_1,IF(rx_ver=ver_name_2,D_int_2,NA()))</f>
         <v/>
       </c>
@@ -1444,7 +1515,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D40" s="21">
+      <c r="D40" s="64">
         <f>IF(rx_ver=ver_name_1,Vmax_1,IF(rx_ver=ver_name_2,Vmax_2,NA()))</f>
         <v/>
       </c>
@@ -1470,7 +1541,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D41" s="21">
+      <c r="D41" s="64">
         <f>IF(rx_ver=ver_name_1,Vtot_1,IF(rx_ver=ver_name_2,Vtot_2,NA()))</f>
         <v/>
       </c>
@@ -1496,7 +1567,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="63">
         <f>V_max*1000/A_x</f>
         <v/>
       </c>
@@ -1522,7 +1593,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D43" s="26" t="n">
+      <c r="D43" s="62" t="n">
         <v>6</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
@@ -1547,7 +1618,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D44" s="15" t="n">
+      <c r="D44" s="61" t="n">
         <v>2</v>
       </c>
       <c r="E44" s="23" t="inlineStr">
@@ -1572,7 +1643,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D45" s="26" t="n">
+      <c r="D45" s="62" t="n">
         <v>22</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
@@ -1597,7 +1668,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D46" s="28">
+      <c r="D46" s="64">
         <f>D_int-elec_clear</f>
         <v/>
       </c>
@@ -1623,7 +1694,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="65" t="n">
         <v>3.175</v>
       </c>
       <c r="E47" s="23" t="inlineStr">
@@ -1648,7 +1719,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D48" s="30" t="n">
+      <c r="D48" s="66" t="n">
         <v>1.5875</v>
       </c>
       <c r="E48" s="23" t="inlineStr">
@@ -1673,7 +1744,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D49" s="21">
+      <c r="D49" s="64">
         <f>elec_clear</f>
         <v/>
       </c>
@@ -1699,7 +1770,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="65" t="n">
         <v>3.175</v>
       </c>
       <c r="E50" s="23" t="inlineStr">
@@ -1724,7 +1795,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D51" s="30" t="n">
+      <c r="D51" s="66" t="n">
         <v>1.5875</v>
       </c>
       <c r="E51" s="23" t="inlineStr">
@@ -1749,7 +1820,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="63">
         <f>MAX(0,h_datum-elec_clear)</f>
         <v/>
       </c>
@@ -1775,7 +1846,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="67">
         <f>rod_n*(PI()/4*rod_d^2)*elec_sub_L/1000</f>
         <v/>
       </c>
@@ -1801,7 +1872,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D54" s="31">
+      <c r="D54" s="67">
         <f>(PI()/4*spg_OD^2)*MAX(0,h_datum-spg_tip_h)/1000</f>
         <v/>
       </c>
@@ -1827,7 +1898,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D55" s="31">
+      <c r="D55" s="67">
         <f>(eff_OD+eff_ID)/2</f>
         <v/>
       </c>
@@ -1853,7 +1924,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="68">
         <f>(PI()/4*(eff_OD^2-eff_ID^2))*eff_sub_L/1000</f>
         <v/>
       </c>
@@ -1879,7 +1950,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="67">
         <f>elec_disp+spg_disp+eff_disp</f>
         <v/>
       </c>
@@ -1905,7 +1976,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D58" s="33">
+      <c r="D58" s="69">
         <f>ROUND(V_max-disp_tot,0)</f>
         <v/>
       </c>
@@ -1931,7 +2002,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="63">
         <f>(V_charge+disp_tot)*1000/A_x</f>
         <v/>
       </c>
@@ -1957,7 +2028,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D60" s="34">
+      <c r="D60" s="63">
         <f>MAX(0,h_actual-spg_tip_h)</f>
         <v/>
       </c>
@@ -1983,7 +2054,7 @@
           <t>mm²</t>
         </is>
       </c>
-      <c r="D61" s="28">
+      <c r="D61" s="64">
         <f>A_x-(rod_n*(PI()/4*rod_d^2)+(PI()/4*spg_OD^2)+(PI()/4*eff_OD^2))</f>
         <v/>
       </c>
@@ -2009,7 +2080,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D62" s="29" t="n">
+      <c r="D62" s="65" t="n">
         <v>3.175</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
@@ -2034,7 +2105,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D63" s="15" t="n">
+      <c r="D63" s="61" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
@@ -2059,7 +2130,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D64" s="26" t="n">
+      <c r="D64" s="62" t="n">
         <v>5</v>
       </c>
       <c r="E64" s="25" t="inlineStr">
@@ -2084,7 +2155,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="67">
         <f>(rod_n*(PI()/4*rod_d^2)*elec_ins+(PI()/4*spg_OD^2)*spg_len+(PI()/4*(eff_OD^2-eff_ID^2))*(D_int-h_actual)+xtube_n*(PI()/4*xtube_OD^2)*xtube_pro)/1000</f>
         <v/>
       </c>
@@ -2110,7 +2181,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D66" s="34">
+      <c r="D66" s="63">
         <f>V_vial_total-V_charge-V_inserts</f>
         <v/>
       </c>
@@ -2120,6 +2191,7 @@
         </is>
       </c>
     </row>
+    <row r="67"/>
     <row r="68" ht="15" customHeight="1" s="51">
       <c r="A68" s="9" t="inlineStr">
         <is>
@@ -2174,7 +2246,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D70" s="35" t="n">
+      <c r="D70" s="70" t="n">
         <v>3</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
@@ -2199,7 +2271,7 @@
           <t>mA/%</t>
         </is>
       </c>
-      <c r="D71" s="19" t="n">
+      <c r="D71" s="71" t="n">
         <v>1.03</v>
       </c>
       <c r="E71" s="17" t="inlineStr">
@@ -2224,7 +2296,7 @@
           <t>mA</t>
         </is>
       </c>
-      <c r="D72" s="21" t="n">
+      <c r="D72" s="72" t="n">
         <v>2.6</v>
       </c>
       <c r="E72" s="17" t="inlineStr">
@@ -2249,7 +2321,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D73" s="36" t="n">
+      <c r="D73" s="73" t="n">
         <v>3</v>
       </c>
       <c r="E73" s="17" t="inlineStr">
@@ -2274,7 +2346,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D74" s="36" t="n">
+      <c r="D74" s="73" t="n">
         <v>25</v>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -2299,7 +2371,7 @@
           <t>C/mol</t>
         </is>
       </c>
-      <c r="D75" s="37" t="n">
+      <c r="D75" s="74" t="n">
         <v>96485.33212000001</v>
       </c>
       <c r="E75" s="38" t="inlineStr">
@@ -2324,7 +2396,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D76" s="18" t="n">
+      <c r="D76" s="75" t="n">
         <v>2</v>
       </c>
       <c r="E76" s="23" t="inlineStr">
@@ -2349,7 +2421,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D77" s="18" t="n">
+      <c r="D77" s="75" t="n">
         <v>4</v>
       </c>
       <c r="E77" s="23" t="inlineStr">
@@ -2374,7 +2446,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D78" s="24" t="n">
+      <c r="D78" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E78" s="22" t="inlineStr">
@@ -2399,7 +2471,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D79" s="32">
+      <c r="D79" s="68">
         <f>(gerrit_slope*intensity+gerrit_int)/1000</f>
         <v/>
       </c>
@@ -2425,7 +2497,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="18">
+      <c r="D80" s="76">
         <f>IF(AND(intensity&gt;=gerrit_min,intensity&lt;=gerrit_max),"OK","OUT OF FITTED RANGE")</f>
         <v/>
       </c>
@@ -2451,7 +2523,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D81" s="39">
+      <c r="D81" s="53">
         <f>I_app*etaF/(z_e_H2*F_const)*3600</f>
         <v/>
       </c>
@@ -2477,7 +2549,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D82" s="39">
+      <c r="D82" s="53">
         <f>I_app*etaF_OER/(z_e_O2*F_const)*3600</f>
         <v/>
       </c>
@@ -2487,6 +2559,7 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
     <row r="84" ht="15" customHeight="1" s="51">
       <c r="A84" s="9" t="inlineStr">
         <is>
@@ -2541,7 +2614,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D86" s="15" t="n">
+      <c r="D86" s="61" t="n">
         <v>6</v>
       </c>
       <c r="E86" s="40" t="inlineStr">
@@ -2566,7 +2639,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D87" s="15" t="n">
+      <c r="D87" s="61" t="n">
         <v>2</v>
       </c>
       <c r="E87" s="40" t="inlineStr">
@@ -2591,7 +2664,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D88" s="15" t="n">
+      <c r="D88" s="61" t="n">
         <v>1</v>
       </c>
       <c r="E88" s="40" t="inlineStr">
@@ -2616,7 +2689,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D89" s="39">
+      <c r="D89" s="53">
         <f>rH2_gen</f>
         <v/>
       </c>
@@ -2642,7 +2715,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D90" s="39">
+      <c r="D90" s="53">
         <f>H2_cons*bio_O2/bio_H2</f>
         <v/>
       </c>
@@ -2668,7 +2741,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D91" s="39">
+      <c r="D91" s="53">
         <f>H2_cons*bio_CO2/bio_H2</f>
         <v/>
       </c>
@@ -2694,7 +2767,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D92" s="41">
+      <c r="D92" s="53">
         <f>O2_net_gen-O2_cons</f>
         <v/>
       </c>
@@ -2704,6 +2777,7 @@
         </is>
       </c>
     </row>
+    <row r="93"/>
     <row r="94" ht="15" customHeight="1" s="51">
       <c r="A94" s="9" t="inlineStr">
         <is>
@@ -2758,7 +2832,7 @@
           <t>°C</t>
         </is>
       </c>
-      <c r="D96" s="26" t="n">
+      <c r="D96" s="62" t="n">
         <v>30</v>
       </c>
       <c r="E96" s="16" t="inlineStr">
@@ -2783,7 +2857,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D97" s="19">
+      <c r="D97" s="63">
         <f>T_C+273.15</f>
         <v/>
       </c>
@@ -2809,7 +2883,7 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D98" s="15" t="n">
+      <c r="D98" s="61" t="n">
         <v>101325</v>
       </c>
       <c r="E98" s="16" t="inlineStr">
@@ -2834,7 +2908,7 @@
           <t>Pa/atm</t>
         </is>
       </c>
-      <c r="D99" s="18" t="n">
+      <c r="D99" s="75" t="n">
         <v>101325</v>
       </c>
       <c r="E99" s="23" t="inlineStr">
@@ -2859,7 +2933,7 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D100" s="18" t="n">
+      <c r="D100" s="75" t="n">
         <v>1.3e-05</v>
       </c>
       <c r="E100" s="17" t="inlineStr">
@@ -2884,7 +2958,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D101" s="18" t="n">
+      <c r="D101" s="75" t="n">
         <v>1500</v>
       </c>
       <c r="E101" s="17" t="inlineStr">
@@ -2909,7 +2983,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D102" s="18" t="n">
+      <c r="D102" s="75" t="n">
         <v>298.15</v>
       </c>
       <c r="E102" s="23" t="inlineStr">
@@ -2934,7 +3008,7 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D103" s="42">
+      <c r="D103" s="77">
         <f>H_O2ref*EXP(H_O2T*(1/T_K-1/T_ref))</f>
         <v/>
       </c>
@@ -2960,7 +3034,7 @@
           <t>atm</t>
         </is>
       </c>
-      <c r="D104" s="18" t="n">
+      <c r="D104" s="75" t="n">
         <v>0.3</v>
       </c>
       <c r="E104" s="17" t="inlineStr">
@@ -3003,7 +3077,7 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D106" s="21">
+      <c r="D106" s="64">
         <f>O2_ceil_atm*Pa_per_atm</f>
         <v/>
       </c>
@@ -3029,7 +3103,7 @@
           <t>mol/m³</t>
         </is>
       </c>
-      <c r="D107" s="32">
+      <c r="D107" s="68">
         <f>H_O2_T*O2_ceil_Pa</f>
         <v/>
       </c>
@@ -3055,7 +3129,7 @@
           <t>µM</t>
         </is>
       </c>
-      <c r="D108" s="28">
+      <c r="D108" s="64">
         <f>O2_ceil_C*1000</f>
         <v/>
       </c>
@@ -3065,6 +3139,7 @@
         </is>
       </c>
     </row>
+    <row r="109"/>
     <row r="110" ht="15" customHeight="1" s="51">
       <c r="A110" s="9" t="inlineStr">
         <is>
@@ -3119,7 +3194,7 @@
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D112" s="26" t="n">
+      <c r="D112" s="62" t="n">
         <v>10</v>
       </c>
       <c r="E112" s="16" t="inlineStr">
@@ -3144,7 +3219,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D113" s="24" t="n">
+      <c r="D113" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E113" s="16" t="inlineStr">
@@ -3169,7 +3244,7 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D114" s="24" t="n">
+      <c r="D114" s="55" t="n">
         <v>1</v>
       </c>
       <c r="E114" s="16" t="inlineStr">
@@ -3194,7 +3269,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D115" s="24" t="n">
+      <c r="D115" s="55" t="n">
         <v>0.5</v>
       </c>
       <c r="E115" s="25" t="inlineStr">
@@ -3219,7 +3294,7 @@
           <t>J/mol/K</t>
         </is>
       </c>
-      <c r="D116" s="39" t="n">
+      <c r="D116" s="78" t="n">
         <v>8.314462618</v>
       </c>
       <c r="E116" s="38" t="inlineStr">
@@ -3244,7 +3319,7 @@
           <t>g/mol</t>
         </is>
       </c>
-      <c r="D117" s="32" t="n">
+      <c r="D117" s="79" t="n">
         <v>44.0095</v>
       </c>
       <c r="E117" s="38" t="inlineStr">
@@ -3269,7 +3344,7 @@
           <t>mol/s</t>
         </is>
       </c>
-      <c r="D118" s="44">
+      <c r="D118" s="80">
         <f>P_atm*(Q_CO2/1000000/60)/(R_gas*T_K)</f>
         <v/>
       </c>
@@ -3295,7 +3370,7 @@
           <t>mol</t>
         </is>
       </c>
-      <c r="D119" s="42">
+      <c r="D119" s="77">
         <f>nCO2_rate*spg_dur</f>
         <v/>
       </c>
@@ -3321,7 +3396,7 @@
           <t>1/h</t>
         </is>
       </c>
-      <c r="D120" s="19">
+      <c r="D120" s="63">
         <f>60/spg_int</f>
         <v/>
       </c>
@@ -3347,7 +3422,7 @@
           <t>1/d</t>
         </is>
       </c>
-      <c r="D121" s="21">
+      <c r="D121" s="64">
         <f>pulses_h*24</f>
         <v/>
       </c>
@@ -3369,7 +3444,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D122" s="41">
+      <c r="D122" s="53">
         <f>CO2_pulse*pulses_h</f>
         <v/>
       </c>
@@ -3395,7 +3470,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D123" s="34">
+      <c r="D123" s="63">
         <f>IF(CO2_cons&gt;0,CO2_supply/CO2_cons,NA())</f>
         <v/>
       </c>
@@ -3421,7 +3496,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D124" s="45">
+      <c r="D124" s="68">
         <f>spg_dur/(spg_int*60)</f>
         <v/>
       </c>
@@ -3431,6 +3506,7 @@
         </is>
       </c>
     </row>
+    <row r="125"/>
     <row r="126" ht="15" customHeight="1" s="51">
       <c r="A126" s="9" t="inlineStr">
         <is>
@@ -3485,7 +3561,7 @@
           <t>N/m</t>
         </is>
       </c>
-      <c r="D128" s="32" t="n">
+      <c r="D128" s="79" t="n">
         <v>0.0712</v>
       </c>
       <c r="E128" s="17" t="inlineStr">
@@ -3510,7 +3586,7 @@
           <t>kg/m³</t>
         </is>
       </c>
-      <c r="D129" s="19" t="n">
+      <c r="D129" s="71" t="n">
         <v>995.65</v>
       </c>
       <c r="E129" s="17" t="inlineStr">
@@ -3535,7 +3611,7 @@
           <t>m/s²</t>
         </is>
       </c>
-      <c r="D130" s="37" t="n">
+      <c r="D130" s="74" t="n">
         <v>9.806649999999999</v>
       </c>
       <c r="E130" s="38" t="inlineStr">
@@ -3560,7 +3636,7 @@
           <t>m²/s</t>
         </is>
       </c>
-      <c r="D131" s="18" t="n">
+      <c r="D131" s="75" t="n">
         <v>2.4e-09</v>
       </c>
       <c r="E131" s="16" t="inlineStr">
@@ -3585,7 +3661,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D132" s="18" t="n">
+      <c r="D132" s="75" t="n">
         <v>205</v>
       </c>
       <c r="E132" s="17" t="inlineStr">
@@ -3610,7 +3686,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D133" s="18" t="n">
+      <c r="D133" s="75" t="n">
         <v>130</v>
       </c>
       <c r="E133" s="17" t="inlineStr">
@@ -3635,7 +3711,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D134" s="18" t="n">
+      <c r="D134" s="75" t="n">
         <v>70</v>
       </c>
       <c r="E134" s="17" t="inlineStr">
@@ -3660,7 +3736,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D135" s="18" t="n">
+      <c r="D135" s="75" t="n">
         <v>28</v>
       </c>
       <c r="E135" s="17" t="inlineStr">
@@ -3685,7 +3761,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D136" s="18" t="n">
+      <c r="D136" s="75" t="n">
         <v>13</v>
       </c>
       <c r="E136" s="17" t="inlineStr">
@@ -3710,7 +3786,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D137" s="21" t="n">
+      <c r="D137" s="72" t="n">
         <v>1.3</v>
       </c>
       <c r="E137" s="17" t="inlineStr">
@@ -3735,7 +3811,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D138" s="46">
+      <c r="D138" s="81">
         <f>CHOOSE(por_grade+1,por0_um,por1_um,por2_um,por3_um,por4_um,por5_um)/1000000</f>
         <v/>
       </c>
@@ -3761,7 +3837,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D139" s="46">
+      <c r="D139" s="81">
         <f>spg_ID/1000</f>
         <v/>
       </c>
@@ -3787,7 +3863,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D140" s="46">
+      <c r="D140" s="81">
         <f>IF(sparger=spg_name_1,tube_d_m,IF(sparger=spg_name_2,por_pore,NA()))</f>
         <v/>
       </c>
@@ -3813,7 +3889,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D141" s="41">
+      <c r="D141" s="53">
         <f>(6*d_orifice*sigma/(rho_L*g_const))^(1/3)</f>
         <v/>
       </c>
@@ -3839,7 +3915,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D142" s="48">
+      <c r="D142" s="67">
         <f>d_bubble*1000</f>
         <v/>
       </c>
@@ -3861,7 +3937,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D143" s="19" t="n">
+      <c r="D143" s="71" t="n">
         <v>2.14</v>
       </c>
       <c r="E143" s="47" t="inlineStr">
@@ -3886,7 +3962,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D144" s="31" t="n">
+      <c r="D144" s="82" t="n">
         <v>0.505</v>
       </c>
       <c r="E144" s="47" t="inlineStr">
@@ -3911,7 +3987,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D145" s="32">
+      <c r="D145" s="68">
         <f>SQRT(mend_a*sigma/(rho_L*d_bubble)+mend_b*g_const*d_bubble)</f>
         <v/>
       </c>
@@ -3921,6 +3997,7 @@
         </is>
       </c>
     </row>
+    <row r="146"/>
     <row r="147" ht="15" customHeight="1" s="51">
       <c r="A147" s="9" t="inlineStr">
         <is>
@@ -3975,7 +4052,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D149" s="39">
+      <c r="D149" s="53">
         <f>(Q_CO2/1000000/60)/(A_x/1000000)</f>
         <v/>
       </c>
@@ -4001,7 +4078,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D150" s="39">
+      <c r="D150" s="53">
         <f>u_sg/u_rise</f>
         <v/>
       </c>
@@ -4027,7 +4104,7 @@
           <t>1/m</t>
         </is>
       </c>
-      <c r="D151" s="19">
+      <c r="D151" s="63">
         <f>6*holdup/d_bubble</f>
         <v/>
       </c>
@@ -4053,7 +4130,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D152" s="32">
+      <c r="D152" s="68">
         <f>d_bubble/u_rise</f>
         <v/>
       </c>
@@ -4079,7 +4156,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D153" s="39">
+      <c r="D153" s="53">
         <f>2*SQRT(D_O2/(PI()*t_contact))</f>
         <v/>
       </c>
@@ -4105,7 +4182,7 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D154" s="41">
+      <c r="D154" s="53">
         <f>kL*a_int</f>
         <v/>
       </c>
@@ -4131,7 +4208,7 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D155" s="42">
+      <c r="D155" s="77">
         <f>kLa_sparge*duty</f>
         <v/>
       </c>
@@ -4157,7 +4234,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D156" s="39">
+      <c r="D156" s="53">
         <f>kLa_sparge*(V_charge/1000000)*O2_ceil_C*3600</f>
         <v/>
       </c>
@@ -4183,7 +4260,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D157" s="41">
+      <c r="D157" s="53">
         <f>strip_sparge*duty</f>
         <v/>
       </c>
@@ -4209,7 +4286,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D158" s="48">
+      <c r="D158" s="67">
         <f>IF(O2_excess&gt;0,strip_avg/O2_excess,NA())</f>
         <v/>
       </c>
@@ -4235,7 +4312,7 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D159" s="39">
+      <c r="D159" s="53">
         <f>IF(O2_excess&gt;0,O2_excess/3600/((V_charge/1000000)*O2_ceil_C),NA())</f>
         <v/>
       </c>
@@ -4245,6 +4322,7 @@
         </is>
       </c>
     </row>
+    <row r="160"/>
     <row r="161" ht="15" customHeight="1" s="51">
       <c r="A161" s="9" t="inlineStr">
         <is>
@@ -4299,7 +4377,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D163" s="29" t="n">
+      <c r="D163" s="65" t="n">
         <v>0.05</v>
       </c>
       <c r="E163" s="47" t="inlineStr">
@@ -4324,7 +4402,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D164" s="49">
+      <c r="D164" s="76">
         <f>IF(u_sg&gt;u_g_max,"RISK - reduce flow","OK")</f>
         <v/>
       </c>
@@ -4334,6 +4412,7 @@
         </is>
       </c>
     </row>
+    <row r="165"/>
     <row r="166" ht="15" customHeight="1" s="51">
       <c r="A166" s="9" t="inlineStr">
         <is>
@@ -4388,7 +4467,7 @@
           <t>mol</t>
         </is>
       </c>
-      <c r="D168" s="42">
+      <c r="D168" s="77">
         <f>O2_excess/60*spg_int</f>
         <v/>
       </c>
@@ -4414,7 +4493,7 @@
           <t>mol</t>
         </is>
       </c>
-      <c r="D169" s="42">
+      <c r="D169" s="77">
         <f>strip_sparge/3600*spg_dur</f>
         <v/>
       </c>
@@ -4440,7 +4519,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D170" s="48">
+      <c r="D170" s="67">
         <f>IF(O2_accum&gt;0,O2_strip_pulse/O2_accum,NA())</f>
         <v/>
       </c>
@@ -4466,7 +4545,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D171" s="49">
+      <c r="D171" s="76">
         <f>IF(spg_dur&gt;=pulse_floor,"OK","BELOW SOLENOID FLOOR")</f>
         <v/>
       </c>
@@ -4492,7 +4571,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D172" s="49">
+      <c r="D172" s="76">
         <f>IF(dur_ok="BELOW SOLENOID FLOOR","Increase duration",IF(carry_flag&lt;&gt;"OK","Reduce flow (carryover)",IF(AND(ISNUMBER(strip_ratio),strip_ratio&gt;=1),"Stripping sufficient - prefer shorter interval for smoother DO","Stripping alone insufficient - rely on bubble knock-off / raise flow or duty / accept higher DO")))</f>
         <v/>
       </c>
@@ -4502,6 +4581,7 @@
         </is>
       </c>
     </row>
+    <row r="173"/>
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -775,7 +775,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="59">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
           <t>DATA GAP - need to measure</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="33" t="inlineStr">
@@ -1078,7 +1076,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="59">
       <c r="A24" s="9" t="inlineStr">
         <is>
@@ -1317,7 +1314,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="15" customHeight="1" s="59">
       <c r="A35" s="9" t="inlineStr">
         <is>
@@ -2178,7 +2174,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70" ht="15" customHeight="1" s="59">
       <c r="A70" s="9" t="inlineStr">
         <is>
@@ -2438,7 +2433,7 @@
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>Clean water electrolysis FE approaches 100% (Nat. Commun. 2022). But in this neutral-pH cell, cathodic O₂ reduction competes with H₂ evolution, so true H₂ FE is likely &lt;1 and UNMEASURED. 1.0 = optimistic upper bound; measure by gas collection.</t>
+          <t>Clean-water electrolysis FE approaches 100%, but in this neutral-pH cell cathodic O₂ reduction competes with H₂ evolution, so true H₂ FE is likely &lt;1 and UNMEASURED. 1.0 = optimistic upper bound; measure by gas collection. Audit: the 'Nat. Commun. 2022' citation is unidentified — identify the specific paper or drop it.</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2619,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="59"/>
+    <row r="88" ht="15" customHeight="1" s="59">
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://journals.asm.org/doi/10.1128/aem.02007-22</t>
+        </is>
+      </c>
+    </row>
     <row r="89" ht="15" customHeight="1" s="59">
       <c r="A89" s="9" t="inlineStr">
         <is>
@@ -2634,7 +2635,11 @@
       <c r="B89" s="10" t="n"/>
       <c r="C89" s="10" t="n"/>
       <c r="D89" s="10" t="n"/>
-      <c r="E89" s="10" t="n"/>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>https://journals.asm.org/doi/10.1128/aem.02007-22</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="59">
       <c r="A90" s="11" t="inlineStr">
@@ -2684,7 +2689,7 @@
       </c>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>H₂:O₂:CO₂ consumption ratio (starting 6:2:1). NB literature recommends a 7:2:1 FEED mix - feed is not consumption.</t>
+          <t>H₂:O₂:CO₂ uptake ratio — NOT a fixed constant; set by the electron split between energy (O₂) and CO₂ fixation, which varies with cell density/phase (Lu &amp; Yu 2019, Biochem Eng J 152:107369). 6:2:1 ≈ 40% of electrons to biomass; measured biomass stoichiometry (Ishizaki) is leaner on O₂ (~5.2:1.5:1). Audit: earlier aem.02007-22 citation was WRONG (that paper is on lag phase, not stoichiometry). FEED mix is 7:2:1 (Ishizaki 2001); feed ≠ consumption. Top-sensitivity input — measure your rig's uptake.</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3109,7 @@
       </c>
       <c r="E109" s="16" t="inlineStr">
         <is>
-          <t>Whole-cell growth inhibited above ~0.30 atm O₂ - NOT a hydrogenase limit (the [NiFe] enzyme is O₂-tolerant).</t>
+          <t>Whole-cell growth inhibited above ~0.30 atm O₂ — NOT a hydrogenase limit (the [NiFe] enzyme is O₂-tolerant). Audit: ~0.30 atm threshold corroborated for C. necator (elevated-O₂ growth-inhibition reports, e.g. Amer &amp; Kim 2023).</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3576,13 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="15" customHeight="1" s="59"/>
+    <row r="130" ht="15" customHeight="1" s="59">
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://iapws.org/documents/release/Surf-H2O</t>
+        </is>
+      </c>
+    </row>
     <row r="131" ht="15" customHeight="1" s="59">
       <c r="A131" s="9" t="inlineStr">
         <is>
@@ -3581,7 +3592,11 @@
       <c r="B131" s="10" t="n"/>
       <c r="C131" s="10" t="n"/>
       <c r="D131" s="10" t="n"/>
-      <c r="E131" s="10" t="n"/>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>https://iapws.org/relguide/IAPWS-95.html</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="59">
       <c r="A132" s="11" t="inlineStr">
@@ -3702,11 +3717,11 @@
         </is>
       </c>
       <c r="D136" s="50" t="n">
-        <v>2.4e-09</v>
+        <v>2.249e-09</v>
       </c>
       <c r="E136" s="15" t="inlineStr">
         <is>
-          <t>Literature ~2.4e-9 at 30 °C (Han &amp; Bartels 1996). Confirm.</t>
+          <t>O₂ diffusivity in water at 30 °C. Han &amp; Bartels (1996) fit log₁₀(D[cm²/s]) = −4.410 + 773.8/T − (506.4/T)² → 2.25e-9 m²/s at 303.15 K. Audit 2026-06-16: corrected from 2.4e-9, which the cited fit does not give.</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4661,6 @@
         </is>
       </c>
     </row>
-    <row r="178"/>
     <row r="179" ht="24" customHeight="1" s="59">
       <c r="A179" s="9" t="inlineStr">
         <is>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -150,6 +150,8 @@
     <definedName name="V_H2_gen">Model!$D$85</definedName>
     <definedName name="V_O2_gen">Model!$D$86</definedName>
     <definedName name="V_gas_total">Model!$D$87</definedName>
+    <definedName name="t_O2_ceiling">Model!$D$191</definedName>
+    <definedName name="t_O2_ceiling_strip">Model!$D$192</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -751,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E190"/>
+  <dimension ref="A1:E192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" style="59" min="1" max="1"/>
@@ -2433,7 +2435,7 @@
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>Clean-water electrolysis FE approaches 100%, but in this neutral-pH cell cathodic O₂ reduction competes with H₂ evolution, so true H₂ FE is likely &lt;1 and UNMEASURED. 1.0 = optimistic upper bound; measure by gas collection. Audit: the 'Nat. Commun. 2022' citation is unidentified — identify the specific paper or drop it.</t>
+          <t>H₂ faradaic efficiency at the cathode. Clean acidic/alkaline electrolysis reaches ~100% FE, but neutral-pH HER (this cell) is the hard regime — even with catalysts FE tops out ~97% and is proton-source-sensitive (Clary et al. 2020, PNAS 117:32947). Here cathodic O₂ reduction competes with HER, so true H₂ FE is likely &lt;1 and UNMEASURED. 1.0 = optimistic upper bound; measure by gas collection. Audit 2026-06-16: replaced unidentified 'Nat. Commun. 2022'.</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2691,7 @@
       </c>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>H₂:O₂:CO₂ uptake ratio — NOT a fixed constant; set by the electron split between energy (O₂) and CO₂ fixation, which varies with cell density/phase (Lu &amp; Yu 2019, Biochem Eng J 152:107369). 6:2:1 ≈ 40% of electrons to biomass; measured biomass stoichiometry (Ishizaki) is leaner on O₂ (~5.2:1.5:1). Audit: earlier aem.02007-22 citation was WRONG (that paper is on lag phase, not stoichiometry). FEED mix is 7:2:1 (Ishizaki 2001); feed ≠ consumption. Top-sensitivity input — measure your rig's uptake.</t>
+          <t>H₂:O₂:CO₂ UPTAKE ratio (consumption, not feed). Phase-dependent, not a constant (Lu &amp; Yu 2019, Biochem Eng J 152:107369: the electron split between O₂ respiration and CO₂ fixation shifts with cell density). Bounds: knallgas energy reaction caps O₂:H₂ ≤ 0.5; autotrophic growth diverts ~30–40% of reducing power to fixation, giving O₂:H₂ ≈ 0.29–0.35 and CO₂:H₂ ≈ 0.15–0.19. 6:2:1 (O₂:H₂=0.33, CO₂:H₂=0.17) sits mid-range and is the design central estimate. For reaching growth, size O₂ removal at the lean-O₂ end (bio_O₂≈1.8 → larger surplus). FEED optimum is 7:2:1 (Ishizaki 2001; &lt;12 h lag) — feed ≠ consumption. Top-sensitivity input; can't measure pre-growth.</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2716,7 @@
       </c>
       <c r="E92" s="24" t="inlineStr">
         <is>
-          <t>As above.</t>
+          <t>O₂:H₂ uptake. Range 0.29–0.35 (×bio_H₂ → 1.75–2.1). 2 = central. Lean-O₂ end is growth-protective (more surplus to strip).</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2741,7 @@
       </c>
       <c r="E93" s="24" t="inlineStr">
         <is>
-          <t>As above.</t>
+          <t>CO₂:H₂ uptake (carbon demand). Range 0.15–0.19 (×bio_H₂ → 0.9–1.15). 1 = central. Sets CO₂ demand; supply is ~22× this, so carbon is non-limiting across the range.</t>
         </is>
       </c>
     </row>
@@ -4953,6 +4955,58 @@
       <c r="E190" s="29" t="inlineStr">
         <is>
           <t>Tate's law (d_bubble, section 6) assumes quasi-static detachment, valid for We&lt;~2. Flags when flow invalidates it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="12" t="inlineStr">
+        <is>
+          <t>O₂ time-to-ceiling (no removal)</t>
+        </is>
+      </c>
+      <c r="B191" s="13" t="inlineStr">
+        <is>
+          <t>t_O2_ceiling</t>
+        </is>
+      </c>
+      <c r="C191" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D191" s="68">
+        <f>O2_ceil_C*(V_charge/1000000)/O2_excess*60</f>
+        <v/>
+      </c>
+      <c r="E191" s="29" t="inlineStr">
+        <is>
+          <t>Minutes for dissolved O₂ to rise from ~0 to the 0.30 atm inhibition ceiling if nothing removes the surplus (etaF=1). The O₂ problem's operational timescale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="12" t="inlineStr">
+        <is>
+          <t>O₂ time-to-ceiling (with time-avg strip)</t>
+        </is>
+      </c>
+      <c r="B192" s="13" t="inlineStr">
+        <is>
+          <t>t_O2_ceiling_strip</t>
+        </is>
+      </c>
+      <c r="C192" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D192" s="68">
+        <f>IF(O2_excess-strip_avg&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_excess-strip_avg)*60,"stripping clears surplus")</f>
+        <v/>
+      </c>
+      <c r="E192" s="29" t="inlineStr">
+        <is>
+          <t>Same, but crediting time-averaged gas-bubble stripping. ≈ unchanged here — confirms bubble stripping is not the O₂ mechanism at this duty.</t>
         </is>
       </c>
     </row>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -152,6 +152,30 @@
     <definedName name="V_gas_total">Model!$D$87</definedName>
     <definedName name="t_O2_ceiling">Model!$D$191</definedName>
     <definedName name="t_O2_ceiling_strip">Model!$D$192</definedName>
+    <definedName name="stir_rpm">Model!$D$196</definedName>
+    <definedName name="stir_len">Model!$D$197</definedName>
+    <definedName name="tip_speed">Model!$D$198</definedName>
+    <definedName name="s_renew">Model!$D$199</definedName>
+    <definedName name="kL_surf">Model!$D$200</definedName>
+    <definedName name="a_surf">Model!$D$201</definedName>
+    <definedName name="kLa_surf">Model!$D$202</definedName>
+    <definedName name="surf_strip">Model!$D$203</definedName>
+    <definedName name="surf_ratio">Model!$D$204</definedName>
+    <definedName name="y_O2_vent">Model!$D$205</definedName>
+    <definedName name="DO_vent_eq">Model!$D$206</definedName>
+    <definedName name="hs_flush_time">Model!$D$207</definedName>
+    <definedName name="O2_removal_ratio">Model!$D$208</definedName>
+    <definedName name="t_O2_ceiling_lag">Model!$D$209</definedName>
+    <definedName name="t_O2_ceiling_rem">Model!$D$210</definedName>
+    <definedName name="H_CO2_T">Model!$D$216</definedName>
+    <definedName name="p_CO2_sparge">Model!$D$217</definedName>
+    <definedName name="CO2_diss">Model!$D$218</definedName>
+    <definedName name="Km_CO2">Model!$D$219</definedName>
+    <definedName name="CO2_carbon_margin">Model!$D$220</definedName>
+    <definedName name="pH_CO2_unbuf">Model!$D$222</definedName>
+    <definedName name="H_CO2ref">Model!$D$214</definedName>
+    <definedName name="H_CO2T">Model!$D$215</definedName>
+    <definedName name="Ka1_carb">Model!$D$221</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -286,7 +310,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -361,6 +385,11 @@
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -389,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -494,6 +523,13 @@
     <xf numFmtId="164" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -753,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:E222"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" style="59" min="1" max="1"/>
@@ -777,6 +813,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="59">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1078,6 +1115,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="59">
       <c r="A24" s="9" t="inlineStr">
         <is>
@@ -1316,6 +1354,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="15" customHeight="1" s="59">
       <c r="A35" s="9" t="inlineStr">
         <is>
@@ -2176,6 +2215,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70" ht="15" customHeight="1" s="59">
       <c r="A70" s="9" t="inlineStr">
         <is>
@@ -4374,7 +4414,7 @@
       </c>
       <c r="E163" s="26" t="inlineStr">
         <is>
-          <t>&gt;=1 = dissolved-gas stripping holds the ceiling; &lt;1 = relies on bubble knock-off or DO rises.</t>
+          <t>&gt;=1 = dissolved-gas stripping holds the ceiling; &lt;1 = relies on bubble knock-off or DO rises. NB: BUBBLE path only — see §11 for the stirred-surface/headspace route, the likely-dominant O₂ removal path.</t>
         </is>
       </c>
     </row>
@@ -4663,6 +4703,7 @@
         </is>
       </c>
     </row>
+    <row r="178"/>
     <row r="179" ht="24" customHeight="1" s="59">
       <c r="A179" s="9" t="inlineStr">
         <is>
@@ -4980,7 +5021,7 @@
       </c>
       <c r="E191" s="29" t="inlineStr">
         <is>
-          <t>Minutes for dissolved O₂ to rise from ~0 to the 0.30 atm inhibition ceiling if nothing removes the surplus (etaF=1). The O₂ problem's operational timescale.</t>
+          <t>Minutes for dissolved O₂ to rise from ~0 to the 0.30 atm inhibition ceiling if nothing removes the surplus (etaF=1). The O₂ problem's operational timescale. See §11 t_O2_ceiling_lag (worst case) and t_O2_ceiling_rem (with surface+cathode).</t>
         </is>
       </c>
     </row>
@@ -5007,6 +5048,694 @@
       <c r="E192" s="29" t="inlineStr">
         <is>
           <t>Same, but crediting time-averaged gas-bubble stripping. ≈ unchanged here — confirms bubble stripping is not the O₂ mechanism at this duty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193"/>
+    <row r="194">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>11.  O₂ REMOVAL — STIRRED SURFACE TO VENTED HEADSPACE  (likely-dominant path)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C195" s="11" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E195" s="11" t="inlineStr">
+        <is>
+          <t>Source / assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="12" t="inlineStr">
+        <is>
+          <t>Stir-bar speed</t>
+        </is>
+      </c>
+      <c r="B196" s="13" t="inlineStr">
+        <is>
+          <t>stir_rpm</t>
+        </is>
+      </c>
+      <c r="C196" s="14" t="inlineStr">
+        <is>
+          <t>1/min</t>
+        </is>
+      </c>
+      <c r="D196" s="72" t="n">
+        <v>500</v>
+      </c>
+      <c r="E196" s="31" t="inlineStr">
+        <is>
+          <t>Pioreactor stir setpoint. RPM floor ~125 (stalls below). Input/confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="12" t="inlineStr">
+        <is>
+          <t>Stir-bar length</t>
+        </is>
+      </c>
+      <c r="B197" s="13" t="inlineStr">
+        <is>
+          <t>stir_len</t>
+        </is>
+      </c>
+      <c r="C197" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D197" s="72" t="n">
+        <v>12</v>
+      </c>
+      <c r="E197" s="73" t="inlineStr">
+        <is>
+          <t>Magnetic stir bar. Pioreactor max 20 mm; confirm the supplied bar's length. Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="12" t="inlineStr">
+        <is>
+          <t>Stir-bar tip speed</t>
+        </is>
+      </c>
+      <c r="B198" s="13" t="inlineStr">
+        <is>
+          <t>tip_speed</t>
+        </is>
+      </c>
+      <c r="C198" s="14" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D198" s="68">
+        <f>PI()*(stir_len/1000)*stir_rpm/60</f>
+        <v/>
+      </c>
+      <c r="E198" s="29" t="inlineStr">
+        <is>
+          <t>π·d·rpm/60.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="12" t="inlineStr">
+        <is>
+          <t>Surface renewal frequency</t>
+        </is>
+      </c>
+      <c r="B199" s="13" t="inlineStr">
+        <is>
+          <t>s_renew</t>
+        </is>
+      </c>
+      <c r="C199" s="14" t="inlineStr">
+        <is>
+          <t>1/s</t>
+        </is>
+      </c>
+      <c r="D199" s="68">
+        <f>tip_speed/(vial_ID/1000)</f>
+        <v/>
+      </c>
+      <c r="E199" s="73" t="inlineStr">
+        <is>
+          <t>COARSE proxy: tip speed / vial ID (how often stirred flow sweeps the surface). Calibrate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="12" t="inlineStr">
+        <is>
+          <t>Surface liquid-film coeff kL</t>
+        </is>
+      </c>
+      <c r="B200" s="13" t="inlineStr">
+        <is>
+          <t>kL_surf</t>
+        </is>
+      </c>
+      <c r="C200" s="14" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D200" s="68">
+        <f>2*SQRT(D_O2*s_renew/PI())</f>
+        <v/>
+      </c>
+      <c r="E200" s="73" t="inlineStr">
+        <is>
+          <t>Danckwerts surface-renewal. Coarse (rides s_renew); likely high-end — MEASURE by gassing-out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="12" t="inlineStr">
+        <is>
+          <t>Surface area per volume</t>
+        </is>
+      </c>
+      <c r="B201" s="13" t="inlineStr">
+        <is>
+          <t>a_surf</t>
+        </is>
+      </c>
+      <c r="C201" s="14" t="inlineStr">
+        <is>
+          <t>1/m</t>
+        </is>
+      </c>
+      <c r="D201" s="68">
+        <f>interface_A/V_charge</f>
+        <v/>
+      </c>
+      <c r="E201" s="29" t="inlineStr">
+        <is>
+          <t>Free-surface area / liquid volume (mm²/mL = 1/m). Uses interface_A from §1B (was unused).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="12" t="inlineStr">
+        <is>
+          <t>Surface O₂ transfer kLa</t>
+        </is>
+      </c>
+      <c r="B202" s="13" t="inlineStr">
+        <is>
+          <t>kLa_surf</t>
+        </is>
+      </c>
+      <c r="C202" s="14" t="inlineStr">
+        <is>
+          <t>1/s</t>
+        </is>
+      </c>
+      <c r="D202" s="68">
+        <f>kL_surf*a_surf</f>
+        <v/>
+      </c>
+      <c r="E202" s="73" t="inlineStr">
+        <is>
+          <t>kL_surf × a_surf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="12" t="inlineStr">
+        <is>
+          <t>O₂ strip via surface (ceiling)</t>
+        </is>
+      </c>
+      <c r="B203" s="13" t="inlineStr">
+        <is>
+          <t>surf_strip</t>
+        </is>
+      </c>
+      <c r="C203" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D203" s="68">
+        <f>kLa_surf*(V_charge/1000000)*O2_ceil_C*3600</f>
+        <v/>
+      </c>
+      <c r="E203" s="73" t="inlineStr">
+        <is>
+          <t>O₂ removed across the stirred surface at ceiling driving force, headspace ~O₂-free. Best case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="12" t="inlineStr">
+        <is>
+          <t>Surface strip : excess-O₂</t>
+        </is>
+      </c>
+      <c r="B204" s="13" t="inlineStr">
+        <is>
+          <t>surf_ratio</t>
+        </is>
+      </c>
+      <c r="C204" s="14" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D204" s="68">
+        <f>IF(O2_excess&gt;0,surf_strip/O2_excess,NA())</f>
+        <v/>
+      </c>
+      <c r="E204" s="73" t="inlineStr">
+        <is>
+          <t>&gt;=1 = surface path holds the ceiling. Coarse (kL_surf). Compare bubble strip_ratio ~0.04 — surface is ~2 orders larger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="12" t="inlineStr">
+        <is>
+          <t>Headspace O₂ frac. to vent excess</t>
+        </is>
+      </c>
+      <c r="B205" s="13" t="inlineStr">
+        <is>
+          <t>y_O2_vent</t>
+        </is>
+      </c>
+      <c r="C205" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D205" s="68">
+        <f>IF(CO2_supply&gt;0,O2_excess/CO2_supply,NA())</f>
+        <v/>
+      </c>
+      <c r="E205" s="29" t="inlineStr">
+        <is>
+          <t>Headspace O₂ mole fraction at which the vented CO₂ throughput carries the excess O₂ out. Independent of kL — robust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="12" t="inlineStr">
+        <is>
+          <t>DO in equilib. with that headspace</t>
+        </is>
+      </c>
+      <c r="B206" s="13" t="inlineStr">
+        <is>
+          <t>DO_vent_eq</t>
+        </is>
+      </c>
+      <c r="C206" s="14" t="inlineStr">
+        <is>
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="D206" s="68">
+        <f>H_O2_T*y_O2_vent*P_atm*1000</f>
+        <v/>
+      </c>
+      <c r="E206" s="29" t="inlineStr">
+        <is>
+          <t>Dissolved O₂ matching y_O2_vent. If ≪ ceiling (364 µM) the vent can hold DO low → surface path is vent-feasible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="12" t="inlineStr">
+        <is>
+          <t>Headspace flush time</t>
+        </is>
+      </c>
+      <c r="B207" s="13" t="inlineStr">
+        <is>
+          <t>hs_flush_time</t>
+        </is>
+      </c>
+      <c r="C207" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D207" s="68">
+        <f>headspace_V/(Q_CO2*duty)</f>
+        <v/>
+      </c>
+      <c r="E207" s="29" t="inlineStr">
+        <is>
+          <t>Avg CO₂ flow to displace one headspace volume. Surface stripping needs headspace kept O₂-lean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="12" t="inlineStr">
+        <is>
+          <t>Combined O₂ removal : excess</t>
+        </is>
+      </c>
+      <c r="B208" s="13" t="inlineStr">
+        <is>
+          <t>O2_removal_ratio</t>
+        </is>
+      </c>
+      <c r="C208" s="14" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D208" s="68">
+        <f>IF(O2_excess&gt;0,(strip_avg+surf_strip+O2_cathode_ORR)/O2_excess,NA())</f>
+        <v/>
+      </c>
+      <c r="E208" s="73" t="inlineStr">
+        <is>
+          <t>Bubbles + surface + cathode vs excess (steady growth). &gt;=1 = ceiling held.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="12" t="inlineStr">
+        <is>
+          <t>O₂ time-to-ceiling (LAG, no uptake)</t>
+        </is>
+      </c>
+      <c r="B209" s="13" t="inlineStr">
+        <is>
+          <t>t_O2_ceiling_lag</t>
+        </is>
+      </c>
+      <c r="C209" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D209" s="68">
+        <f>O2_ceil_C*(V_charge/1000000)/O2_net_gen*60</f>
+        <v/>
+      </c>
+      <c r="E209" s="29" t="inlineStr">
+        <is>
+          <t>Lag/establishment: cells not yet consuming O₂, so the full net electrolytic O₂ accumulates. Worst case — the regime that matters for reaching growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="12" t="inlineStr">
+        <is>
+          <t>O₂ time-to-ceiling (with all removal)</t>
+        </is>
+      </c>
+      <c r="B210" s="13" t="inlineStr">
+        <is>
+          <t>t_O2_ceiling_rem</t>
+        </is>
+      </c>
+      <c r="C210" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D210" s="68">
+        <f>IF(O2_excess-strip_avg-surf_strip-O2_cathode_ORR&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_excess-strip_avg-surf_strip-O2_cathode_ORR)*60,"removal holds ceiling")</f>
+        <v/>
+      </c>
+      <c r="E210" s="73" t="inlineStr">
+        <is>
+          <t>Crediting bubble+surface+cathode. 'holds ceiling' = removal ≥ production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211"/>
+    <row r="212">
+      <c r="A212" s="9" t="inlineStr">
+        <is>
+          <t>12.  DISSOLVED CO₂ &amp; CARBON AVAILABILITY  (+ pH note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="11" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B213" s="11" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C213" s="11" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D213" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>Source / assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="12" t="inlineStr">
+        <is>
+          <t>Henry solubility CO₂ (ref, 298.15 K)</t>
+        </is>
+      </c>
+      <c r="B214" s="13" t="inlineStr">
+        <is>
+          <t>H_CO2ref</t>
+        </is>
+      </c>
+      <c r="C214" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³/Pa</t>
+        </is>
+      </c>
+      <c r="D214" s="69" t="n">
+        <v>0.00033</v>
+      </c>
+      <c r="E214" s="74" t="inlineStr">
+        <is>
+          <t>Sander (2023) compilation; CO₂ ~25× more soluble than O₂.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="12" t="inlineStr">
+        <is>
+          <t>Henry T-dependence CO₂</t>
+        </is>
+      </c>
+      <c r="B215" s="13" t="inlineStr">
+        <is>
+          <t>H_CO2T</t>
+        </is>
+      </c>
+      <c r="C215" s="14" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D215" s="69" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E215" s="74" t="inlineStr">
+        <is>
+          <t>Sander (2023): d ln(Hcp)/d(1/T) for CO₂.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="12" t="inlineStr">
+        <is>
+          <t>Henry solubility CO₂ at T</t>
+        </is>
+      </c>
+      <c r="B216" s="13" t="inlineStr">
+        <is>
+          <t>H_CO2_T</t>
+        </is>
+      </c>
+      <c r="C216" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³/Pa</t>
+        </is>
+      </c>
+      <c r="D216" s="68">
+        <f>H_CO2ref*EXP(H_CO2T*(1/T_K-1/T_ref))</f>
+        <v/>
+      </c>
+      <c r="E216" s="29" t="inlineStr">
+        <is>
+          <t>van 't Hoff to reactor T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="12" t="inlineStr">
+        <is>
+          <t>CO₂ partial pressure at sparge</t>
+        </is>
+      </c>
+      <c r="B217" s="13" t="inlineStr">
+        <is>
+          <t>p_CO2_sparge</t>
+        </is>
+      </c>
+      <c r="C217" s="14" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D217" s="68">
+        <f>P_atm</f>
+        <v/>
+      </c>
+      <c r="E217" s="31" t="inlineStr">
+        <is>
+          <t>Pure-CO₂ sparge: p_CO₂ ≈ surface pressure during a pulse. Assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="12" t="inlineStr">
+        <is>
+          <t>Dissolved CO₂ (during sparge)</t>
+        </is>
+      </c>
+      <c r="B218" s="13" t="inlineStr">
+        <is>
+          <t>CO2_diss</t>
+        </is>
+      </c>
+      <c r="C218" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³</t>
+        </is>
+      </c>
+      <c r="D218" s="68">
+        <f>H_CO2_T*p_CO2_sparge</f>
+        <v/>
+      </c>
+      <c r="E218" s="29" t="inlineStr">
+        <is>
+          <t>Equilibrium dissolved CO₂ while sparging (mol/m³ = mM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="12" t="inlineStr">
+        <is>
+          <t>RuBisCO Km for CO₂</t>
+        </is>
+      </c>
+      <c r="B219" s="13" t="inlineStr">
+        <is>
+          <t>Km_CO2</t>
+        </is>
+      </c>
+      <c r="C219" s="14" t="inlineStr">
+        <is>
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="D219" s="72" t="n">
+        <v>50</v>
+      </c>
+      <c r="E219" s="73" t="inlineStr">
+        <is>
+          <t>C. necator form-II RuBisCO Km(CO₂) ~ order 50 µM. Coarse — confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="12" t="inlineStr">
+        <is>
+          <t>Carbon margin (dissolved CO₂ : Km)</t>
+        </is>
+      </c>
+      <c r="B220" s="13" t="inlineStr">
+        <is>
+          <t>CO2_carbon_margin</t>
+        </is>
+      </c>
+      <c r="C220" s="14" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D220" s="68">
+        <f>CO2_diss*1000/Km_CO2</f>
+        <v/>
+      </c>
+      <c r="E220" s="29" t="inlineStr">
+        <is>
+          <t>&gt;&gt;1 = CO₂ saturating for fixation during sparge. (Between pulses it falls; duty-averaged is lower.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="12" t="inlineStr">
+        <is>
+          <t>Carbonic-acid Ka1 (apparent)</t>
+        </is>
+      </c>
+      <c r="B221" s="13" t="inlineStr">
+        <is>
+          <t>Ka1_carb</t>
+        </is>
+      </c>
+      <c r="C221" s="14" t="inlineStr">
+        <is>
+          <t>mol/L</t>
+        </is>
+      </c>
+      <c r="D221" s="69" t="n">
+        <v>4.45e-07</v>
+      </c>
+      <c r="E221" s="74" t="inlineStr">
+        <is>
+          <t>CO₂(aq)+H₂O ⇌ H⁺+HCO₃⁻, pKa1 6.35 (25 °C).</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="12" t="inlineStr">
+        <is>
+          <t>pH — UNBUFFERED worst case</t>
+        </is>
+      </c>
+      <c r="B222" s="13" t="inlineStr">
+        <is>
+          <t>pH_CO2_unbuf</t>
+        </is>
+      </c>
+      <c r="C222" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D222" s="68">
+        <f>-LOG10(SQRT(Ka1_carb*(CO2_diss/1000)))</f>
+        <v/>
+      </c>
+      <c r="E222" s="73" t="inlineStr">
+        <is>
+          <t>Pure water saturated with CO₂ at p_CO2_sparge — a LOWER BOUND only. The Sydow (2017) phosphate medium (~36–108 mM) buffers pH near setpoint; true pH needs the buffer model.</t>
         </is>
       </c>
     </row>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -176,6 +176,13 @@
     <definedName name="H_CO2ref">Model!$D$214</definedName>
     <definedName name="H_CO2T">Model!$D$215</definedName>
     <definedName name="Ka1_carb">Model!$D$221</definedName>
+    <definedName name="H_H2ref">Model!$D$226</definedName>
+    <definedName name="H_H2T">Model!$D$227</definedName>
+    <definedName name="H_H2_T">Model!$D$228</definedName>
+    <definedName name="C_H2_sat">Model!$D$229</definedName>
+    <definedName name="t_H2_sat">Model!$D$230</definedName>
+    <definedName name="H2_turnover">Model!$D$231</definedName>
+    <definedName name="H2_safety">Model!$D$232</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -789,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E222"/>
+  <dimension ref="A1:E232"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" style="59" min="1" max="1"/>
@@ -813,7 +820,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="59">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1121,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="59">
       <c r="A24" s="9" t="inlineStr">
         <is>
@@ -1354,7 +1359,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="15" customHeight="1" s="59">
       <c r="A35" s="9" t="inlineStr">
         <is>
@@ -2215,7 +2219,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70" ht="15" customHeight="1" s="59">
       <c r="A70" s="9" t="inlineStr">
         <is>
@@ -2657,7 +2660,7 @@
       </c>
       <c r="E87" s="20" t="inlineStr">
         <is>
-          <t>Total off the electrodes ≈ what you collect over water while etaF=1; if etaF&lt;1, less by the cathodic O₂ (O2_cathode_ORR).</t>
+          <t>Total electrolytic gas (H₂+O₂) off the electrodes — an ABIOTIC calibration check (collect over water, no cells, to verify Gerrit's Law / etaF). With cells, H₂ (and excess O₂) are consumed so you would not collect this. If etaF&lt;1, less by the cathodic O₂ (O2_cathode_ORR).</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2810,7 @@
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Assumption: 100% of evolved H₂ consumed.</t>
+          <t>Assumes 100% of evolved H₂ is consumed. Holds only at active growth; during LAG/low density uptake ≈ 0, so H₂ (and pro-rata O₂/CO₂ consumption) is overstated — see §13 (H₂ saturates/escapes in ~7 min unconsumed) and t_O2_ceiling_lag (§11).</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2836,7 @@
       </c>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>H₂ consumed x (O₂/H₂ ratio).</t>
+          <t>H₂ consumed × (O₂/H₂ ratio). Steady-growth only; ≈ 0 during lag (cells not yet respiring) — the lag O₂ surplus is the full net electrolytic O₂.</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3591,7 @@
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>&gt;1 = carbon non-limiting (before stripping use).</t>
+          <t>&gt;1 = carbon supply exceeds fixation demand. NB ~22× is over-dosing, not headroom — high dissolved CO₂/low pH extends lag (§12). CO₂ also feeds the §11 headspace vent, but only after it saturates the liquid (~1 h), so the vent leg is weak during early/lag operation.</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4706,6 @@
         </is>
       </c>
     </row>
-    <row r="178"/>
     <row r="179" ht="24" customHeight="1" s="59">
       <c r="A179" s="9" t="inlineStr">
         <is>
@@ -5051,7 +5053,6 @@
         </is>
       </c>
     </row>
-    <row r="193"/>
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
@@ -5474,7 +5475,6 @@
         </is>
       </c>
     </row>
-    <row r="211"/>
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
@@ -5736,6 +5736,220 @@
       <c r="E222" s="73" t="inlineStr">
         <is>
           <t>Pure water saturated with CO₂ at p_CO2_sparge — a LOWER BOUND only. The Sydow (2017) phosphate medium (~36–108 mM) buffers pH near setpoint; true pH needs the buffer model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="inlineStr">
+        <is>
+          <t>13.  H₂ AVAILABILITY &amp; UTILISATION  (does the '100% consumed' assumption hold?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="11" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B225" s="11" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C225" s="11" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D225" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E225" s="11" t="inlineStr">
+        <is>
+          <t>Source / assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="12" t="inlineStr">
+        <is>
+          <t>Henry solubility H₂ (ref, 298.15 K)</t>
+        </is>
+      </c>
+      <c r="B226" s="13" t="inlineStr">
+        <is>
+          <t>H_H2ref</t>
+        </is>
+      </c>
+      <c r="C226" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³/Pa</t>
+        </is>
+      </c>
+      <c r="D226" s="69" t="n">
+        <v>7.8e-06</v>
+      </c>
+      <c r="E226" s="74" t="inlineStr">
+        <is>
+          <t>Sander (2023). H₂ is ~6× LESS soluble than O₂.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="12" t="inlineStr">
+        <is>
+          <t>Henry T-dependence H₂</t>
+        </is>
+      </c>
+      <c r="B227" s="13" t="inlineStr">
+        <is>
+          <t>H_H2T</t>
+        </is>
+      </c>
+      <c r="C227" s="14" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D227" s="69" t="n">
+        <v>500</v>
+      </c>
+      <c r="E227" s="74" t="inlineStr">
+        <is>
+          <t>Sander (2023): d ln(Hcp)/d(1/T) for H₂ (weak T-dependence).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="12" t="inlineStr">
+        <is>
+          <t>Henry solubility H₂ at T</t>
+        </is>
+      </c>
+      <c r="B228" s="13" t="inlineStr">
+        <is>
+          <t>H_H2_T</t>
+        </is>
+      </c>
+      <c r="C228" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³/Pa</t>
+        </is>
+      </c>
+      <c r="D228" s="68">
+        <f>H_H2ref*EXP(H_H2T*(1/T_K-1/T_ref))</f>
+        <v/>
+      </c>
+      <c r="E228" s="29" t="inlineStr">
+        <is>
+          <t>van 't Hoff to reactor T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="12" t="inlineStr">
+        <is>
+          <t>Dissolved-H₂ saturation (1 atm)</t>
+        </is>
+      </c>
+      <c r="B229" s="13" t="inlineStr">
+        <is>
+          <t>C_H2_sat</t>
+        </is>
+      </c>
+      <c r="C229" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³</t>
+        </is>
+      </c>
+      <c r="D229" s="68">
+        <f>H_H2_T*P_atm</f>
+        <v/>
+      </c>
+      <c r="E229" s="29" t="inlineStr">
+        <is>
+          <t>Max dissolved H₂ at surface pressure (mol/m³ = mM). The cells' H₂ supply is capped at this concentration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="12" t="inlineStr">
+        <is>
+          <t>Time to saturate dissolved H₂ (LAG)</t>
+        </is>
+      </c>
+      <c r="B230" s="13" t="inlineStr">
+        <is>
+          <t>t_H2_sat</t>
+        </is>
+      </c>
+      <c r="C230" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D230" s="68">
+        <f>C_H2_sat*(V_charge/1000000)/rH2_gen*60</f>
+        <v/>
+      </c>
+      <c r="E230" s="29" t="inlineStr">
+        <is>
+          <t>If cells don't yet consume H₂ (lag), dissolved H₂ reaches saturation this fast; beyond it, evolved H₂ bubbles off — lost AND building an explosive headspace. Mirrors the O₂ lag timescale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="12" t="inlineStr">
+        <is>
+          <t>H₂ pool turnovers per hour</t>
+        </is>
+      </c>
+      <c r="B231" s="13" t="inlineStr">
+        <is>
+          <t>H2_turnover</t>
+        </is>
+      </c>
+      <c r="C231" s="14" t="inlineStr">
+        <is>
+          <t>1/h</t>
+        </is>
+      </c>
+      <c r="D231" s="68">
+        <f>rH2_gen/(V_charge/1000000)/C_H2_sat</f>
+        <v/>
+      </c>
+      <c r="E231" s="73" t="inlineStr">
+        <is>
+          <t>Volumetric H₂ evolution / saturable pool. &gt;&gt;1 means H₂ is generated far faster than the liquid can hold it, so cells must consume it in near-real-time or it escapes. '100% consumed' needs uptake ≥ evolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="12" t="inlineStr">
+        <is>
+          <t>H₂ headspace safety flag</t>
+        </is>
+      </c>
+      <c r="B232" s="13" t="inlineStr">
+        <is>
+          <t>H2_safety</t>
+        </is>
+      </c>
+      <c r="C232" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D232" s="68">
+        <f>IF(rH2_gen&gt;0,"CAUTION: H₂+O₂ headspace is explosive (H₂ 4–94% in O₂) — keep headspace swept &amp; vented, no ignition sources","n/a")</f>
+        <v/>
+      </c>
+      <c r="E232" s="32" t="inlineStr">
+        <is>
+          <t>Electrolysis co-produces H₂ and O₂; any H₂ that bubbles off mixes with headspace O₂ within the explosive range.</t>
         </is>
       </c>
     </row>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -100,7 +100,6 @@
     <definedName name="rod_n">Model!$D$46</definedName>
     <definedName name="rx_ver">Model!$D$16</definedName>
     <definedName name="sched_bal">Model!$D$175</definedName>
-    <definedName name="sched_verdict">Model!$D$177</definedName>
     <definedName name="sigma">Model!$D$133</definedName>
     <definedName name="sparge_depth">Model!$D$62</definedName>
     <definedName name="sparger">Model!$D$17</definedName>
@@ -541,6 +540,32 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF63BE7B"/>
+          <bgColor rgb="FF63BE7B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8696B"/>
+          <bgColor rgb="FFF8696B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB84"/>
+          <bgColor rgb="FFFFEB84"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -802,7 +827,7 @@
     <col width="44" customWidth="1" style="59" min="1" max="1"/>
     <col width="15" customWidth="1" style="59" min="2" max="2"/>
     <col width="11" customWidth="1" style="59" min="3" max="3"/>
-    <col width="16" customWidth="1" style="59" min="4" max="4"/>
+    <col width="12" customWidth="1" style="59" min="4" max="4"/>
     <col width="70" customWidth="1" style="59" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -820,6 +845,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="59">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1121,6 +1147,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="59">
       <c r="A24" s="9" t="inlineStr">
         <is>
@@ -1359,6 +1386,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="15" customHeight="1" s="59">
       <c r="A35" s="9" t="inlineStr">
         <is>
@@ -2219,6 +2247,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70" ht="15" customHeight="1" s="59">
       <c r="A70" s="9" t="inlineStr">
         <is>
@@ -2525,7 +2554,7 @@
         </is>
       </c>
       <c r="D82" s="51">
-        <f>IF(AND(intensity&gt;=gerrit_min,intensity&lt;=gerrit_max),"OK","OUT OF FITTED RANGE")</f>
+        <f>IF(AND(intensity&gt;=gerrit_min,intensity&lt;=gerrit_max),"OK","OUT")</f>
         <v/>
       </c>
       <c r="E82" s="16" t="inlineStr">
@@ -4528,7 +4557,7 @@
         </is>
       </c>
       <c r="D169" s="51">
-        <f>IF(u_sg&gt;u_g_max,"RISK - reduce flow","OK")</f>
+        <f>IF(u_sg&gt;u_g_max,"RISK","OK")</f>
         <v/>
       </c>
       <c r="E169" s="26" t="inlineStr">
@@ -4650,7 +4679,7 @@
       </c>
       <c r="E175" s="26" t="inlineStr">
         <is>
-          <t>&gt;=1 = each pulse clears the interval's O₂ by stripping alone.</t>
+          <t>&gt;=1 = each pulse clears the interval's O₂ by stripping alone. NB bubble-only; the real O₂ route is the §11 surface/headspace path. The schedule verdict cell was removed (it scored bubbles only) — see the optimiser.</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4700,7 @@
         </is>
       </c>
       <c r="D176" s="51">
-        <f>IF(spg_dur&gt;=pulse_floor,"OK","BELOW SOLENOID FLOOR")</f>
+        <f>IF(spg_dur&gt;=pulse_floor,"OK","LOW")</f>
         <v/>
       </c>
       <c r="E176" s="15" t="inlineStr">
@@ -4681,31 +4710,13 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="22" t="inlineStr">
-        <is>
-          <t>Schedule verdict</t>
-        </is>
-      </c>
-      <c r="B177" s="13" t="inlineStr">
-        <is>
-          <t>sched_verdict</t>
-        </is>
-      </c>
-      <c r="C177" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D177" s="51">
-        <f>IF(dur_ok="BELOW SOLENOID FLOOR","Increase duration",IF(carry_flag&lt;&gt;"OK","Reduce flow (carryover)",IF(AND(ISNUMBER(strip_ratio),strip_ratio&gt;=1),"Stripping sufficient - prefer shorter interval for smoother DO","Stripping alone insufficient - rely on bubble knock-off / raise flow or duty / accept higher DO")))</f>
-        <v/>
-      </c>
-      <c r="E177" s="26" t="inlineStr">
-        <is>
-          <t>Synthesised recommendation (Phase 1 logic).</t>
-        </is>
-      </c>
-    </row>
+      <c r="A177" s="22" t="n"/>
+      <c r="B177" s="13" t="n"/>
+      <c r="C177" s="14" t="n"/>
+      <c r="D177" s="51" t="n"/>
+      <c r="E177" s="26" t="n"/>
+    </row>
+    <row r="178"/>
     <row r="179" ht="24" customHeight="1" s="59">
       <c r="A179" s="9" t="inlineStr">
         <is>
@@ -4992,7 +5003,7 @@
         </is>
       </c>
       <c r="D190" s="68">
-        <f>IF(We_orifice&lt;2,"Static (Tate valid)","Dynamic – bubbles larger than modelled")</f>
+        <f>IF(We_orifice&lt;2,"Static","Dynamic")</f>
         <v/>
       </c>
       <c r="E190" s="29" t="inlineStr">
@@ -5044,15 +5055,16 @@
         </is>
       </c>
       <c r="D192" s="68">
-        <f>IF(O2_excess-strip_avg&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_excess-strip_avg)*60,"stripping clears surplus")</f>
+        <f>IF(O2_excess-strip_avg&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_excess-strip_avg)*60,9999)</f>
         <v/>
       </c>
       <c r="E192" s="29" t="inlineStr">
         <is>
-          <t>Same, but crediting time-averaged gas-bubble stripping. ≈ unchanged here — confirms bubble stripping is not the O₂ mechanism at this duty.</t>
-        </is>
-      </c>
-    </row>
+          <t>Same, but crediting time-averaged gas-bubble stripping. ≈ unchanged here — confirms bubble stripping is not the O₂ mechanism at this duty. (9999 = stripping clears the surplus; no finite time-to-ceiling.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193"/>
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
@@ -5466,15 +5478,16 @@
         </is>
       </c>
       <c r="D210" s="68">
-        <f>IF(O2_excess-strip_avg-surf_strip-O2_cathode_ORR&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_excess-strip_avg-surf_strip-O2_cathode_ORR)*60,"removal holds ceiling")</f>
+        <f>IF(O2_excess-strip_avg-surf_strip-O2_cathode_ORR&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_excess-strip_avg-surf_strip-O2_cathode_ORR)*60,9999)</f>
         <v/>
       </c>
       <c r="E210" s="73" t="inlineStr">
         <is>
-          <t>Crediting bubble+surface+cathode. 'holds ceiling' = removal ≥ production.</t>
-        </is>
-      </c>
-    </row>
+          <t>Crediting bubble+surface+cathode. 'holds ceiling' = removal ≥ production. (9999 = combined removal holds the ceiling; no finite time-to-ceiling.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211"/>
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
@@ -5739,6 +5752,7 @@
         </is>
       </c>
     </row>
+    <row r="223"/>
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
@@ -5944,7 +5958,7 @@
         </is>
       </c>
       <c r="D232" s="68">
-        <f>IF(rH2_gen&gt;0,"CAUTION: H₂+O₂ headspace is explosive (H₂ 4–94% in O₂) — keep headspace swept &amp; vented, no ignition sources","n/a")</f>
+        <f>IF(rH2_gen&gt;0,"EXPLOSIVE","n/a")</f>
         <v/>
       </c>
       <c r="E232" s="32" t="inlineStr">
@@ -5957,6 +5971,139 @@
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
+  <conditionalFormatting sqref="D82">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"OUT"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D169">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
+      <formula>"RISK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D190">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
+      <formula>"Static"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+      <formula>"Dynamic"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D176">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
+      <formula>"LOW"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D232">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+      <formula>"EXPLOSIVE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D208">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="3"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D204">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="3"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D163">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D191">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="15"/>
+        <cfvo type="num" val="60"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D209">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="15"/>
+        <cfvo type="num" val="60"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D128">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="20"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D189">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D97">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1.5e-05"/>
+        <cfvo type="num" val="4e-05"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>$D$19:$D$20</formula1>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -182,6 +182,22 @@
     <definedName name="t_H2_sat">Model!$D$230</definedName>
     <definedName name="H2_turnover">Model!$D$231</definedName>
     <definedName name="H2_safety">Model!$D$232</definedName>
+    <definedName name="sched_mode">Model!$D$236</definedName>
+    <definedName name="spg_dur_man">Model!$D$237</definedName>
+    <definedName name="spg_int_man">Model!$D$238</definedName>
+    <definedName name="target_DO_frac">Model!$D$239</definedName>
+    <definedName name="carbon_margin_min">Model!$D$240</definedName>
+    <definedName name="duty_carbon">Model!$D$241</definedName>
+    <definedName name="duty_O2vent">Model!$D$242</definedName>
+    <definedName name="duty_opt">Model!$D$243</definedName>
+    <definedName name="spg_int_max">Model!$D$244</definedName>
+    <definedName name="spg_dur_opt">Model!$D$245</definedName>
+    <definedName name="spg_int_opt">Model!$D$246</definedName>
+    <definedName name="spg_int_opt_s">Model!$D$247</definedName>
+    <definedName name="duty_actual">Model!$D$248</definedName>
+    <definedName name="opt_binding">Model!$D$249</definedName>
+    <definedName name="od_ok">Model!$D$250</definedName>
+    <definedName name="kinetic_caveat">Model!$D$251</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -199,7 +215,7 @@
     <numFmt numFmtId="170" formatCode="0.000000000"/>
     <numFmt numFmtId="171" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -315,8 +331,14 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -396,6 +418,11 @@
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -424,7 +451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -534,6 +561,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -821,7 +852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E232"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" style="59" min="1" max="1"/>
@@ -845,7 +876,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="59">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1147,7 +1177,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="59">
       <c r="A24" s="9" t="inlineStr">
         <is>
@@ -1386,7 +1415,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="15" customHeight="1" s="59">
       <c r="A35" s="9" t="inlineStr">
         <is>
@@ -2247,7 +2275,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70" ht="15" customHeight="1" s="59">
       <c r="A70" s="9" t="inlineStr">
         <is>
@@ -3363,12 +3390,13 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D118" s="30" t="n">
-        <v>1</v>
+      <c r="D118" s="38">
+        <f>IF(sched_mode="Optimal",spg_dur_opt,spg_dur_man)</f>
+        <v/>
       </c>
       <c r="E118" s="15" t="inlineStr">
         <is>
-          <t>Solenoid open time. Input.</t>
+          <t>Pulse duration ACTUALLY USED. Driven by §14: Manual→spg_dur_man, Optimal→computed optimum.</t>
         </is>
       </c>
     </row>
@@ -3388,12 +3416,13 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D119" s="30" t="n">
-        <v>1</v>
+      <c r="D119" s="38">
+        <f>IF(sched_mode="Optimal",spg_int_opt,spg_int_man)</f>
+        <v/>
       </c>
       <c r="E119" s="15" t="inlineStr">
         <is>
-          <t>Time between pulse starts. Input.</t>
+          <t>Sparge interval ACTUALLY USED. Driven by §14: Manual→spg_int_man, Optimal→computed optimum.</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4745,6 @@
       <c r="D177" s="51" t="n"/>
       <c r="E177" s="26" t="n"/>
     </row>
-    <row r="178"/>
     <row r="179" ht="24" customHeight="1" s="59">
       <c r="A179" s="9" t="inlineStr">
         <is>
@@ -5064,7 +5092,6 @@
         </is>
       </c>
     </row>
-    <row r="193"/>
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
@@ -5487,7 +5514,6 @@
         </is>
       </c>
     </row>
-    <row r="211"/>
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
@@ -5752,7 +5778,6 @@
         </is>
       </c>
     </row>
-    <row r="223"/>
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
@@ -5964,6 +5989,453 @@
       <c r="E232" s="32" t="inlineStr">
         <is>
           <t>Electrolysis co-produces H₂ and O₂; any H₂ that bubbles off mixes with headspace O₂ within the explosive range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="9" t="inlineStr">
+        <is>
+          <t>14.  OPTIMAL SPARGE SCHEDULE  (absolute answer: pulse duration &amp; interval for a given CO₂ flow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="11" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B235" s="11" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C235" s="11" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D235" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E235" s="11" t="inlineStr">
+        <is>
+          <t>Source / assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="12" t="inlineStr">
+        <is>
+          <t>Schedule mode</t>
+        </is>
+      </c>
+      <c r="B236" s="13" t="inlineStr">
+        <is>
+          <t>sched_mode</t>
+        </is>
+      </c>
+      <c r="C236" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D236" s="72" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="E236" s="31" t="inlineStr">
+        <is>
+          <t>Manual = use the values you type below; Optimal = the model computes &amp; applies the optimum. Dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="12" t="inlineStr">
+        <is>
+          <t>Manual pulse duration</t>
+        </is>
+      </c>
+      <c r="B237" s="13" t="inlineStr">
+        <is>
+          <t>spg_dur_man</t>
+        </is>
+      </c>
+      <c r="C237" s="14" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D237" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" s="31" t="inlineStr">
+        <is>
+          <t>Your pulse length, used when sched_mode=Manual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="12" t="inlineStr">
+        <is>
+          <t>Manual sparge interval</t>
+        </is>
+      </c>
+      <c r="B238" s="13" t="inlineStr">
+        <is>
+          <t>spg_int_man</t>
+        </is>
+      </c>
+      <c r="C238" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D238" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" s="31" t="inlineStr">
+        <is>
+          <t>Your interval, used when sched_mode=Manual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="12" t="inlineStr">
+        <is>
+          <t>Target dissolved-O₂ ceiling fraction</t>
+        </is>
+      </c>
+      <c r="B239" s="13" t="inlineStr">
+        <is>
+          <t>target_DO_frac</t>
+        </is>
+      </c>
+      <c r="C239" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D239" s="72" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E239" s="31" t="inlineStr">
+        <is>
+          <t>Hold DO at ≤ this × the inhibition ceiling. Lower = safer O₂ margin → needs more flushing. Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="12" t="inlineStr">
+        <is>
+          <t>Min carbon supply margin</t>
+        </is>
+      </c>
+      <c r="B240" s="13" t="inlineStr">
+        <is>
+          <t>carbon_margin_min</t>
+        </is>
+      </c>
+      <c r="C240" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D240" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E240" s="31" t="inlineStr">
+        <is>
+          <t>Required CO₂ supply : fixation demand. Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="12" t="inlineStr">
+        <is>
+          <t>Duty floor — carbon</t>
+        </is>
+      </c>
+      <c r="B241" s="13" t="inlineStr">
+        <is>
+          <t>duty_carbon</t>
+        </is>
+      </c>
+      <c r="C241" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D241" s="68">
+        <f>carbon_margin_min*CO2_cons/(nCO2_rate*3600)</f>
+        <v/>
+      </c>
+      <c r="E241" s="29" t="inlineStr">
+        <is>
+          <t>Duty needed so CO₂ supply ≥ margin × fixation demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="12" t="inlineStr">
+        <is>
+          <t>Duty floor — O₂ venting (lag)</t>
+        </is>
+      </c>
+      <c r="B242" s="13" t="inlineStr">
+        <is>
+          <t>duty_O2vent</t>
+        </is>
+      </c>
+      <c r="C242" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D242" s="68">
+        <f>O2_net_gen/(target_DO_frac*O2_ceil_atm)/(nCO2_rate*3600)</f>
+        <v/>
+      </c>
+      <c r="E242" s="29" t="inlineStr">
+        <is>
+          <t>Duty so the vented CO₂ throughput carries the worst-case (lag, no uptake) net O₂ out at ≤ target DO. Usually the binding floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="12" t="inlineStr">
+        <is>
+          <t>Optimal duty cycle</t>
+        </is>
+      </c>
+      <c r="B243" s="13" t="inlineStr">
+        <is>
+          <t>duty_opt</t>
+        </is>
+      </c>
+      <c r="C243" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D243" s="68">
+        <f>MAX(duty_carbon,duty_O2vent)</f>
+        <v/>
+      </c>
+      <c r="E243" s="29" t="inlineStr">
+        <is>
+          <t>The binding of the two floors — the least CO₂ that stays feasible (minimises over-dose → highest pH → shortest lag).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="12" t="inlineStr">
+        <is>
+          <t>Max interval — O₂ flush frequency</t>
+        </is>
+      </c>
+      <c r="B244" s="13" t="inlineStr">
+        <is>
+          <t>spg_int_max</t>
+        </is>
+      </c>
+      <c r="C244" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D244" s="68">
+        <f>target_DO_frac*t_O2_ceiling_lag</f>
+        <v/>
+      </c>
+      <c r="E244" s="29" t="inlineStr">
+        <is>
+          <t>Pulses must be frequent enough that DO doesn't spike past target between flushes (lag worst-case).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="12" t="inlineStr">
+        <is>
+          <t>► OPTIMAL pulse duration</t>
+        </is>
+      </c>
+      <c r="B245" s="13" t="inlineStr">
+        <is>
+          <t>spg_dur_opt</t>
+        </is>
+      </c>
+      <c r="C245" s="14" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D245" s="75">
+        <f>pulse_floor</f>
+        <v/>
+      </c>
+      <c r="E245" s="76" t="inlineStr">
+        <is>
+          <t>ANSWER. Shortest reliable pulse → most frequent, smoothest DO, best OD-read windows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="12" t="inlineStr">
+        <is>
+          <t>► OPTIMAL sparge interval</t>
+        </is>
+      </c>
+      <c r="B246" s="13" t="inlineStr">
+        <is>
+          <t>spg_int_opt</t>
+        </is>
+      </c>
+      <c r="C246" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D246" s="75">
+        <f>MIN(spg_dur_opt/(60*duty_opt),spg_int_max)</f>
+        <v/>
+      </c>
+      <c r="E246" s="76" t="inlineStr">
+        <is>
+          <t>ANSWER. From optimal duty at the floor pulse, capped by the O₂-flush frequency limit. Set sched_mode=Optimal to apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  optimal interval (seconds)</t>
+        </is>
+      </c>
+      <c r="B247" s="13" t="inlineStr">
+        <is>
+          <t>spg_int_opt_s</t>
+        </is>
+      </c>
+      <c r="C247" s="14" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D247" s="68">
+        <f>spg_int_opt*60</f>
+        <v/>
+      </c>
+      <c r="E247" s="76" t="inlineStr">
+        <is>
+          <t>Convenience: interval in seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  resulting duty / binding constraint</t>
+        </is>
+      </c>
+      <c r="B248" s="13" t="inlineStr">
+        <is>
+          <t>duty_actual</t>
+        </is>
+      </c>
+      <c r="C248" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D248" s="68">
+        <f>spg_dur_opt/(spg_int_opt*60)</f>
+        <v/>
+      </c>
+      <c r="E248" s="29" t="inlineStr">
+        <is>
+          <t>Achieved duty at the optimum (= duty_opt unless the flush-frequency cap binds, raising it).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  binding constraint</t>
+        </is>
+      </c>
+      <c r="B249" s="13" t="inlineStr">
+        <is>
+          <t>opt_binding</t>
+        </is>
+      </c>
+      <c r="C249" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D249" s="68">
+        <f>IF(spg_int_opt&lt;spg_dur_opt/(60*duty_opt)-0.0001,"O2-FREQ",IF(duty_O2vent&gt;=duty_carbon,"O2-VENT","CARBON"))</f>
+        <v/>
+      </c>
+      <c r="E249" s="29" t="inlineStr">
+        <is>
+          <t>Which limit sets the schedule: O2-VENT (O₂ removal), O2-FREQ (flush frequency), or CARBON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OD-window check</t>
+        </is>
+      </c>
+      <c r="B250" s="13" t="inlineStr">
+        <is>
+          <t>od_ok</t>
+        </is>
+      </c>
+      <c r="C250" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D250" s="68">
+        <f>IF(spg_int_opt*60-spg_dur_opt&gt;=5,"OK","TIGHT")</f>
+        <v/>
+      </c>
+      <c r="E250" s="29" t="inlineStr">
+        <is>
+          <t>≥5 s gap between pulses for an OD read. Can't measure OD while sparging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="12" t="inlineStr">
+        <is>
+          <t>ACCURACY LIMIT — no validated kinetics</t>
+        </is>
+      </c>
+      <c r="B251" s="13" t="inlineStr">
+        <is>
+          <t>kinetic_caveat</t>
+        </is>
+      </c>
+      <c r="C251" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D251" s="68">
+        <f>"see note →"</f>
+        <v/>
+      </c>
+      <c r="E251" s="73" t="inlineStr">
+        <is>
+          <t>This optimiser targets a CONSTRAINT PROXY: the least-dosing schedule that holds DO below the O₂ ceiling, keeps carbon non-limiting, respects the solenoid floor and flush frequency. It is NOT a fitted growth model — no validated μ(dissolved-O₂, pH, dissolved-CO₂) or lag kinetics exist for C. necator under in-culture electrolysis. So this is the lag-MINIMISING DIRECTION, not a biologically-exact optimum. Confidence is further bounded by etaF (unmeasured), surface kL (coarse, §11) and the unbuffered-pH simplification (§12). Treat the numbers as a strong starting point to validate empirically, not ground truth.</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6576,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <conditionalFormatting sqref="D250">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="0">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="2">
+      <formula>"TIGHT"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
     <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>$D$19:$D$20</formula1>
       <formula2>0</formula2>
@@ -6116,6 +6596,9 @@
     <dataValidation sqref="D18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"0,1,2,3,4,5"</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D236" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Manual,Optimal"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -2534,7 +2534,7 @@
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>H₂ faradaic efficiency at the cathode. Clean acidic/alkaline electrolysis reaches ~100% FE, but neutral-pH HER (this cell) is the hard regime — even with catalysts FE tops out ~97% and is proton-source-sensitive (Clary et al. 2020, PNAS 117:32947). Here cathodic O₂ reduction competes with HER, so true H₂ FE is likely &lt;1 and UNMEASURED. 1.0 = optimistic upper bound; measure by gas collection. Audit 2026-06-16: replaced unidentified 'Nat. Commun. 2022'.</t>
+          <t>H₂ faradaic efficiency at the cathode. Clean acidic/alkaline electrolysis reaches ~100% FE, but neutral-pH HER (this cell) is the hard regime — even with catalysts FE tops out ~97% and is proton-source-sensitive (Clary et al. 2020, PNAS 117:32947). Here cathodic O₂ reduction competes with HER, so true H₂ FE is likely &lt;1 and UNMEASURED. 1.0 = optimistic upper bound; measure via cathode-gas collection or the H₂:O₂ ratio.</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Anodic OER, gross. Uses etaF_OER (D-row below), not the cathodic H₂ etaF. H₂:O₂(anodic)=2:1.</t>
+          <t>Anodic OER, gross. Uses etaF_OER (anodic), not the cathodic etaF. H₂:O₂(anodic) = 2:1.</t>
         </is>
       </c>
     </row>
@@ -2720,13 +2720,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="59">
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>https://journals.asm.org/doi/10.1128/aem.02007-22</t>
-        </is>
-      </c>
-    </row>
+    <row r="88" ht="15" customHeight="1" s="59"/>
     <row r="89" ht="15" customHeight="1" s="59">
       <c r="A89" s="9" t="inlineStr">
         <is>
@@ -2736,11 +2730,7 @@
       <c r="B89" s="10" t="n"/>
       <c r="C89" s="10" t="n"/>
       <c r="D89" s="10" t="n"/>
-      <c r="E89" s="10" t="inlineStr">
-        <is>
-          <t>https://journals.asm.org/doi/10.1128/aem.02007-22</t>
-        </is>
-      </c>
+      <c r="E89" s="10" t="n"/>
     </row>
     <row r="90" ht="15" customHeight="1" s="59">
       <c r="A90" s="11" t="inlineStr">
@@ -2790,7 +2780,7 @@
       </c>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>H₂:O₂:CO₂ UPTAKE ratio (consumption, not feed). Phase-dependent, not a constant (Lu &amp; Yu 2019, Biochem Eng J 152:107369: the electron split between O₂ respiration and CO₂ fixation shifts with cell density). Bounds: knallgas energy reaction caps O₂:H₂ ≤ 0.5; autotrophic growth diverts ~30–40% of reducing power to fixation, giving O₂:H₂ ≈ 0.29–0.35 and CO₂:H₂ ≈ 0.15–0.19. 6:2:1 (O₂:H₂=0.33, CO₂:H₂=0.17) sits mid-range and is the design central estimate. For reaching growth, size O₂ removal at the lean-O₂ end (bio_O₂≈1.8 → larger surplus). FEED optimum is 7:2:1 (Ishizaki 2001; &lt;12 h lag) — feed ≠ consumption. Top-sensitivity input; can't measure pre-growth.</t>
+          <t>H₂:O₂:CO₂ UPTAKE ratio (consumption, not feed). Phase-dependent, not a constant (Lu &amp; Yu 2019, Biochem Eng J 152:107369: the electron split between O₂ respiration and CO₂ fixation shifts with cell density). Bounds: knallgas energy reaction caps O₂:H₂ ≤ 0.5; autotrophic growth diverts ~30–40% of reducing power to fixation, giving O₂:H₂ ≈ 0.29–0.35 and CO₂:H₂ ≈ 0.15–0.19. 6:2:1 (O₂:H₂=0.33, CO₂:H₂=0.17) sits mid-range and is the design central estimate. For reaching growth, size O₂ removal at the lean-O₂ end (bio_O₂≈1.8 → larger surplus). FEED optimum is 7:2:1 (Ishizaki 2001; gives &lt;12 h lag, Amer &amp; Kim 2023) — feed ≠ consumption. Top-sensitivity input; can't measure pre-growth.</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2830,7 @@
       </c>
       <c r="E93" s="24" t="inlineStr">
         <is>
-          <t>CO₂:H₂ uptake (carbon demand). Range 0.15–0.19 (×bio_H₂ → 0.9–1.15). 1 = central. Sets CO₂ demand; supply is ~22× this, so carbon is non-limiting across the range.</t>
+          <t>CO₂:H₂ uptake (carbon demand). Range 0.15–0.19 (×bio_H₂ → 0.9–1.15). 1 = central. Sets CO₂ demand; supply far exceeds it (~20× at the optimum), so carbon is non-limiting across the range.</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3200,7 @@
       </c>
       <c r="E109" s="16" t="inlineStr">
         <is>
-          <t>Whole-cell growth inhibited above ~0.30 atm O₂ — NOT a hydrogenase limit (the [NiFe] enzyme is O₂-tolerant). Audit: ~0.30 atm threshold corroborated for C. necator (elevated-O₂ growth-inhibition reports, e.g. Amer &amp; Kim 2023).</t>
+          <t>Whole-cell growth inhibited above ~0.30 atm O₂ — NOT a hydrogenase limit (the [NiFe] enzyme is O₂-tolerant). ~0.30 atm reported for C. necator (Amer &amp; Kim 2023).</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3296,7 @@
       </c>
       <c r="E113" s="25" t="inlineStr">
         <is>
-          <t>mol/m³ = mmol/L; x1000 = µM. Practical aim is to MINIMISE dissolved O₂ (cathodic O₂ reduction steals H₂-evolution current); floor set by stripping capacity.</t>
+          <t>mol/m³ = mmol/L; ×1000 = µM. Practical aim is to MINIMISE dissolved O₂ (cathodic O₂ reduction steals H₂-evolution current); floor set by O₂-removal capacity (§11).</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3639,7 @@
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>&gt;1 = carbon supply exceeds fixation demand. NB ~22× is over-dosing, not headroom — high dissolved CO₂/low pH extends lag (§12). CO₂ also feeds the §11 headspace vent, but only after it saturates the liquid (~1 h), so the vent leg is weak during early/lag operation.</t>
+          <t>&gt;1 = carbon supply exceeds fixation demand. NB ~20× is over-dosing, not headroom — high dissolved CO₂/low pH extends lag (§12). CO₂ also feeds the §11 headspace vent, but only after it saturates the liquid (~1 h), so the vent leg is weak during early/lag operation.</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3814,7 @@
       </c>
       <c r="E136" s="15" t="inlineStr">
         <is>
-          <t>O₂ diffusivity in water at 30 °C. Han &amp; Bartels (1996) fit log₁₀(D[cm²/s]) = −4.410 + 773.8/T − (506.4/T)² → 2.25e-9 m²/s at 303.15 K. Audit 2026-06-16: corrected from 2.4e-9, which the cited fit does not give.</t>
+          <t>O₂ diffusivity in water at 30 °C. Han &amp; Bartels (1996) fit log₁₀(D[cm²/s]) = −4.410 + 773.8/T − (506.4/T)² → 2.25e-9 m²/s at 303.15 K.</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4068,7 @@
       </c>
       <c r="E146" s="26" t="inlineStr">
         <is>
-          <t>Static low-flow force balance (buoyancy vs surface tension). Flow-dependence not modelled.</t>
+          <t>Static low-flow force balance (buoyancy vs surface tension); valid in the quasi-static regime — see bubble_regime (§10).</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4698,7 @@
       </c>
       <c r="E175" s="26" t="inlineStr">
         <is>
-          <t>&gt;=1 = each pulse clears the interval's O₂ by stripping alone. NB bubble-only; the real O₂ route is the §11 surface/headspace path. The schedule verdict cell was removed (it scored bubbles only) — see the optimiser.</t>
+          <t>&gt;=1 = each pulse clears the interval's O₂ by stripping alone. Bubble path only — the dominant O₂ route is the §11 surface/headspace path; see §14 optimiser.</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4795,7 @@
       </c>
       <c r="E181" s="29" t="inlineStr">
         <is>
-          <t>Cap underside to release point. Was implicitly = elec_ins; now explicit so it tracks spg_tip_h independently.</t>
+          <t>Cap underside to release point; tracks spg_tip_h.</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5266,7 @@
       </c>
       <c r="E201" s="29" t="inlineStr">
         <is>
-          <t>Free-surface area / liquid volume (mm²/mL = 1/m). Uses interface_A from §1B (was unused).</t>
+          <t>Free-surface area / liquid volume (mm²/mL = 1/m); uses interface_A (§1B).</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5344,7 @@
       </c>
       <c r="E204" s="73" t="inlineStr">
         <is>
-          <t>&gt;=1 = surface path holds the ceiling. Coarse (kL_surf). Compare bubble strip_ratio ~0.04 — surface is ~2 orders larger.</t>
+          <t>&gt;=1 = surface path holds the ceiling. Coarse (kL_surf). Bubble strip_ratio is &lt;&lt;1, so the surface path is ~2 orders larger.</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5687,7 @@
       </c>
       <c r="E219" s="73" t="inlineStr">
         <is>
-          <t>C. necator form-II RuBisCO Km(CO₂) ~ order 50 µM. Coarse — confirm.</t>
+          <t>C. necator RuBisCO Km(CO₂) ~ order 50 µM. Coarse — confirm.</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5823,7 @@
       </c>
       <c r="E226" s="74" t="inlineStr">
         <is>
-          <t>Sander (2023). H₂ is ~6× LESS soluble than O₂.</t>
+          <t>Sander (2023). H₂ is ~1.7× less soluble than O₂.</t>
         </is>
       </c>
     </row>
@@ -6619,24 +6609,23 @@
     <hyperlink ref="E80" r:id="rId15"/>
     <hyperlink ref="E81" r:id="rId16"/>
     <hyperlink ref="E82" r:id="rId17"/>
-    <hyperlink ref="E88" r:id="rId18"/>
-    <hyperlink ref="E89" r:id="rId19"/>
-    <hyperlink ref="E90" r:id="rId20"/>
-    <hyperlink ref="E102" r:id="rId21"/>
-    <hyperlink ref="E103" r:id="rId22"/>
-    <hyperlink ref="E106" r:id="rId23"/>
-    <hyperlink ref="E107" display="C. necator membrane-bound [NiFe]-hydrogenase tolerates O₂, so the enzyme is not the binding constraint." r:id="rId24"/>
-    <hyperlink ref="E118" r:id="rId25"/>
-    <hyperlink ref="E119" r:id="rId26"/>
-    <hyperlink ref="E130" r:id="rId27"/>
-    <hyperlink ref="E131" r:id="rId28"/>
-    <hyperlink ref="E132" r:id="rId29"/>
-    <hyperlink ref="E134" r:id="rId30"/>
-    <hyperlink ref="E135" r:id="rId31"/>
-    <hyperlink ref="E136" r:id="rId32"/>
-    <hyperlink ref="E137" r:id="rId33"/>
-    <hyperlink ref="E138" r:id="rId34"/>
-    <hyperlink ref="E139" r:id="rId35"/>
+    <hyperlink ref="E89" r:id="rId18"/>
+    <hyperlink ref="E90" r:id="rId19"/>
+    <hyperlink ref="E102" r:id="rId20"/>
+    <hyperlink ref="E103" r:id="rId21"/>
+    <hyperlink ref="E106" r:id="rId22"/>
+    <hyperlink ref="E107" display="C. necator membrane-bound [NiFe]-hydrogenase tolerates O₂, so the enzyme is not the binding constraint." r:id="rId23"/>
+    <hyperlink ref="E118" r:id="rId24"/>
+    <hyperlink ref="E119" r:id="rId25"/>
+    <hyperlink ref="E130" r:id="rId26"/>
+    <hyperlink ref="E131" r:id="rId27"/>
+    <hyperlink ref="E132" r:id="rId28"/>
+    <hyperlink ref="E134" r:id="rId29"/>
+    <hyperlink ref="E135" r:id="rId30"/>
+    <hyperlink ref="E136" r:id="rId31"/>
+    <hyperlink ref="E137" r:id="rId32"/>
+    <hyperlink ref="E138" r:id="rId33"/>
+    <hyperlink ref="E139" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -2730,7 +2730,11 @@
       <c r="B89" s="10" t="n"/>
       <c r="C89" s="10" t="n"/>
       <c r="D89" s="10" t="n"/>
-      <c r="E89" s="10" t="n"/>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>https://journals.asm.org/doi/10.1128/aem.02007-22</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="59">
       <c r="A90" s="11" t="inlineStr">
@@ -3639,7 +3643,7 @@
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>&gt;1 = carbon supply exceeds fixation demand. NB ~20× is over-dosing, not headroom — high dissolved CO₂/low pH extends lag (§12). CO₂ also feeds the §11 headspace vent, but only after it saturates the liquid (~1 h), so the vent leg is weak during early/lag operation.</t>
+          <t>&gt;1 = carbon supply exceeds fixation demand (~20× at the optimum → carbon non-limiting). Sparged CO₂ bubbles dissolve only ~1–2% per ~0.04 s rise, so most burst at the surface: the headspace fills with CO₂ and the §11 vent/sweep is active from the first pulse (including lag), building over the hs_flush_time scale. High pCO₂ can still extend lag (Amer &amp; Kim 2023, §12).</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4170,7 @@
       </c>
       <c r="E150" s="26" t="inlineStr">
         <is>
-          <t>Mendelson correlation, mm-scale bubbles.</t>
+          <t>Mendelson wave-theory correlation, valid for inertial bubbles ≈1–10 mm (the tube gives 4.1 mm, in range). Below ~1 mm (fine sinters, Grade ~4–5 ≈ 0.4–0.8 mm by Tate) the σ/(ρ·d_b) term makes it rise UNPHYSICALLY faster as d_b shrinks; real sub-mm bubbles follow Stokes/intermediate flow and rise far slower, so this overestimates u_rise (→ underestimates holdup &amp; bubble-stripping). Bubble-stripping is non-dominant (§11) and the optimiser doesn't use it, so the conclusion is unaffected — flagged for fine-sinter selections.</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4849,7 @@
       </c>
       <c r="E183" s="31" t="inlineStr">
         <is>
-          <t>Cathodic O₂-reduction pathway: 4 = full reduction to water, 2 = peroxide. Assumed 4. Confirm.</t>
+          <t>Electrons per O₂ reduced at the cathode. 4 = full reduction to water (Pt-like); 2 = peroxide (H₂O₂), favoured on non-Pt electrodes at neutral pH. NB z=2 consumes O₂ at TWICE the rate per unit ORR current (each O₂ takes only 2 e⁻), so it makes the surplus SMALLER — z=4 (default) is the higher-excess, conservative choice. H₂O₂ is biocidal — a separate toxicity risk if significant. Inert while etaF=1; set per electrode material.</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6221,7 @@
       </c>
       <c r="E243" s="29" t="inlineStr">
         <is>
-          <t>The binding of the two floors — the least CO₂ that stays feasible (minimises over-dose → highest pH → shortest lag).</t>
+          <t>The binding of the two floors — the least CO₂ that stays feasible. The O₂-vent floor binds here, NOT pH: the Sydow phosphate buffer (~36–108 mM, §12) holds pH near setpoint, so over-dosing is constrained by pCO₂-driven lag (Amer &amp; Kim 2023), not acid shock.</t>
         </is>
       </c>
     </row>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -4165,12 +4165,12 @@
         </is>
       </c>
       <c r="D150" s="65">
-        <f>SQRT(mend_a*sigma/(rho_L*d_bubble)+mend_b*g_const*d_bubble)</f>
+        <f>IF(d_bubble&lt;0.001,NA(),SQRT(mend_a*sigma/(rho_L*d_bubble)+mend_b*g_const*d_bubble))</f>
         <v/>
       </c>
       <c r="E150" s="26" t="inlineStr">
         <is>
-          <t>Mendelson wave-theory correlation, valid for inertial bubbles ≈1–10 mm (the tube gives 4.1 mm, in range). Below ~1 mm (fine sinters, Grade ~4–5 ≈ 0.4–0.8 mm by Tate) the σ/(ρ·d_b) term makes it rise UNPHYSICALLY faster as d_b shrinks; real sub-mm bubbles follow Stokes/intermediate flow and rise far slower, so this overestimates u_rise (→ underestimates holdup &amp; bubble-stripping). Bubble-stripping is non-dominant (§11) and the optimiser doesn't use it, so the conclusion is unaffected — flagged for fine-sinter selections.</t>
+          <t>Mendelson wave-theory correlation, valid for inertial bubbles ≈1–10 mm. Returns #N/A when the selected sparger gives d_bubble &lt; 1 mm — fine sinters (Grade ~4–5) make sub-mm bubbles the correlation cannot model (it rises unphysically as d_b shrinks). The §7 bubble-stripping chain errors with it by design; the §11 surface path and §14 optimiser are independent. Tube = 4.1 mm.</t>
         </is>
       </c>
     </row>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -198,6 +198,8 @@
     <definedName name="opt_binding">Model!$D$249</definedName>
     <definedName name="od_ok">Model!$D$250</definedName>
     <definedName name="kinetic_caveat">Model!$D$251</definedName>
+    <definedName name="kLa_meas">Model!$D$255</definedName>
+    <definedName name="kLa_surf_used">Model!$D$256</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -852,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" style="59" min="1" max="1"/>
@@ -5317,7 +5319,7 @@
         </is>
       </c>
       <c r="D203" s="68">
-        <f>kLa_surf*(V_charge/1000000)*O2_ceil_C*3600</f>
+        <f>kLa_surf_used*(V_charge/1000000)*O2_ceil_C*3600</f>
         <v/>
       </c>
       <c r="E203" s="73" t="inlineStr">
@@ -6430,6 +6432,91 @@
       <c r="E251" s="73" t="inlineStr">
         <is>
           <t>This optimiser targets a CONSTRAINT PROXY: the least-dosing schedule that holds DO below the O₂ ceiling, keeps carbon non-limiting, respects the solenoid floor and flush frequency. It is NOT a fitted growth model — no validated μ(dissolved-O₂, pH, dissolved-CO₂) or lag kinetics exist for C. necator under in-culture electrolysis. So this is the lag-MINIMISING DIRECTION, not a biologically-exact optimum. Confidence is further bounded by etaF (unmeasured), surface kL (coarse, §11) and the unbuffered-pH simplification (§12). Treat the numbers as a strong starting point to validate empirically, not ground truth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="9" t="inlineStr">
+        <is>
+          <t>15.  kLa OVERRIDE / CALIBRATION  (enter a measured surface kLa to replace the §11 estimate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="11" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B254" s="11" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C254" s="11" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D254" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E254" s="11" t="inlineStr">
+        <is>
+          <t>Source / assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="12" t="inlineStr">
+        <is>
+          <t>Measured surface kLa</t>
+        </is>
+      </c>
+      <c r="B255" s="13" t="inlineStr">
+        <is>
+          <t>kLa_meas</t>
+        </is>
+      </c>
+      <c r="C255" s="14" t="inlineStr">
+        <is>
+          <t>1/h</t>
+        </is>
+      </c>
+      <c r="D255" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" s="73" t="inlineStr">
+        <is>
+          <t>Measured surface O₂ transfer coefficient. 0 = use the §11 theoretical estimate (kL_surf). To measure (when you have a DO probe): deoxygenate, then log dissolved-O₂ recovery at operating stir with NO sparging; kLa = slope of −LN(1−DO/DO_sat) vs time (1/h).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="12" t="inlineStr">
+        <is>
+          <t>Surface kLa used downstream</t>
+        </is>
+      </c>
+      <c r="B256" s="13" t="inlineStr">
+        <is>
+          <t>kLa_surf_used</t>
+        </is>
+      </c>
+      <c r="C256" s="14" t="inlineStr">
+        <is>
+          <t>1/s</t>
+        </is>
+      </c>
+      <c r="D256" s="68">
+        <f>IF(kLa_meas&gt;0,kLa_meas/3600,kLa_surf)</f>
+        <v/>
+      </c>
+      <c r="E256" s="29" t="inlineStr">
+        <is>
+          <t>What §11 actually uses: the measured value if entered, otherwise the theoretical estimate. Swap estimate→truth here once measured.</t>
         </is>
       </c>
     </row>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="D118" s="38">
-        <f>IF(sched_mode="Optimal",spg_dur_opt,spg_dur_man)</f>
+        <f>IF(sched_mode="Optimal",spg_dur_opt,IF(sched_mode="Manual",spg_dur_man,NA()))</f>
         <v/>
       </c>
       <c r="E118" s="15" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="D119" s="38">
-        <f>IF(sched_mode="Optimal",spg_int_opt,spg_int_man)</f>
+        <f>IF(sched_mode="Optimal",spg_int_opt,IF(sched_mode="Manual",spg_int_man,NA()))</f>
         <v/>
       </c>
       <c r="E119" s="15" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="E150" s="26" t="inlineStr">
         <is>
-          <t>Mendelson wave-theory correlation, valid for inertial bubbles ≈1–10 mm. Returns #N/A when the selected sparger gives d_bubble &lt; 1 mm — fine sinters (Grade ~4–5) make sub-mm bubbles the correlation cannot model (it rises unphysically as d_b shrinks). The §7 bubble-stripping chain errors with it by design; the §11 surface path and §14 optimiser are independent. Tube = 4.1 mm.</t>
+          <t>Mendelson wave-theory correlation, valid for inertial bubbles ≈1–10 mm. Returns #N/A when the selected sparger gives d_bubble &lt; 1 mm — fine sinters (Grade ~4–5) make sub-mm bubbles the correlation cannot model. By design this #N/A cascades through the §7 bubble-stripping chain and the cells that include it: §9 per-pulse (O2_strip_pulse, sched_bal), §10 t_O2_ceiling_strip, and §11 O2_removal_ratio / t_O2_ceiling_rem. The §14 optimiser and the surface-only cells are independent. Tube = 4.1 mm.</t>
         </is>
       </c>
     </row>
@@ -5449,12 +5449,12 @@
         </is>
       </c>
       <c r="D208" s="68">
-        <f>IF(O2_excess&gt;0,(strip_avg+surf_strip+O2_cathode_ORR)/O2_excess,NA())</f>
+        <f>IF(O2_excess&gt;0,(strip_avg+surf_strip)/O2_excess,NA())</f>
         <v/>
       </c>
       <c r="E208" s="73" t="inlineStr">
         <is>
-          <t>Bubbles + surface + cathode vs excess (steady growth). &gt;=1 = ceiling held.</t>
+          <t>Gas removal (bubble + surface) vs the steady-growth surplus O2_excess (which already nets the cathodic sink and biological uptake). &gt;=1 = ceiling held at steady growth.</t>
         </is>
       </c>
     </row>
@@ -5501,12 +5501,12 @@
         </is>
       </c>
       <c r="D210" s="68">
-        <f>IF(O2_excess-strip_avg-surf_strip-O2_cathode_ORR&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_excess-strip_avg-surf_strip-O2_cathode_ORR)*60,9999)</f>
+        <f>IF(O2_net_gen-strip_avg-surf_strip&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_net_gen-strip_avg-surf_strip)*60,9999)</f>
         <v/>
       </c>
       <c r="E210" s="73" t="inlineStr">
         <is>
-          <t>Crediting bubble+surface+cathode. 'holds ceiling' = removal ≥ production. (9999 = combined removal holds the ceiling; no finite time-to-ceiling.)</t>
+          <t>LAG-with-removal partner to t_O2_ceiling_lag: cells not yet consuming, so removal (bubble + surface) must offset the full net electrolytic O₂ (O2_net_gen, which already nets the cathodic sink), not the steady surplus. 9999 = removal holds the ceiling (no finite time).</t>
         </is>
       </c>
     </row>
@@ -5979,12 +5979,12 @@
         </is>
       </c>
       <c r="D232" s="68">
-        <f>IF(rH2_gen&gt;0,"EXPLOSIVE","n/a")</f>
+        <f>IF(H2_turnover&gt;1,"EXPLOSIVE","watch")</f>
         <v/>
       </c>
       <c r="E232" s="32" t="inlineStr">
         <is>
-          <t>Electrolysis co-produces H₂ and O₂; any H₂ that bubbles off mixes with headspace O₂ within the explosive range.</t>
+          <t>Triggers when H₂ evolves faster than the liquid can hold it (H2_turnover&gt;1) → it escapes to the headspace and mixes with electrolytic O₂ (explosive 4–94% H₂ in O₂). At any useful electrolysis current this is on, so treat headspace inerting/venting as mandatory; 'watch' only if H₂ stays dissolved/consumed.</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="D242" s="68">
-        <f>O2_net_gen/(target_DO_frac*O2_ceil_atm)/(nCO2_rate*3600)</f>
+        <f>O2_net_gen/(target_DO_frac*(O2_ceil_Pa/P_atm))/(nCO2_rate*3600)</f>
         <v/>
       </c>
       <c r="E242" s="29" t="inlineStr">
@@ -6666,19 +6666,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list" errorStyle="stop">
       <formula1>$D$19:$D$20</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list" errorStyle="stop">
       <formula1>$D$21:$D$22</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list" errorStyle="stop">
       <formula1>"0,1,2,3,4,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D236" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list" errorStyle="stop">
       <formula1>"Manual,Optimal"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E27" s="27" t="inlineStr">
         <is>
-          <t>40 mL vial. Pioreactor source (core/pioreactor/models.py) defines the 40 mL with the SAME reactor_diameter_mm (27.0 nominal) as the 20 mL — same-width vial, just taller. Using the measured 20 mL OD (27.48) as the estimate; measure the 40 mL to confirm.</t>
+          <t>40 mL vial — same diameter as 20 mL (Pioreactor source). Using 27.48 mm until measured.</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>40 mL internal usable depth - measure. Same vial diameter as the 20 mL per Pioreactor source, so expect roughly double the 20 mL depth for double the volume.</t>
+          <t>40 mL internal depth — measure. ~double the 20 mL (same diameter, double volume).</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>Held CONSTANT across builds (the OD-measurement clear zone). 22 mm = the 33 mm insertion used in AEP0.1.1 (D_int 55). Raise it (e.g. to 25) if OD is disrupted during electrolysis. Input.</t>
+          <t>Held constant across builds (OD clear zone). 22 mm ↔ 33 mm insertion in AEP0.1.1. Input.</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>All inserts inside the vial. Electrodes &amp; sparge tube counted solid (gas-filled bore displaces); efflux/media-out counted as annular wall only (bore open to the liquid surface); extra tubes solid. Sparge in-vial length via spg_len.</t>
+          <t>In-vial inserts: electrodes &amp; sparge solid; efflux annular (open bore); extra tubes solid.</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
-          <t>Empirical linear fit of current vs LED intensity (constant-current: independent of electrolyte, volume, electrode coverage).</t>
+          <t>Empirical current-vs-intensity fit (constant-current; electrolyte/volume-independent).</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>H₂ faradaic efficiency at the cathode. Clean acidic/alkaline electrolysis reaches ~100% FE, but neutral-pH HER (this cell) is the hard regime — even with catalysts FE tops out ~97% and is proton-source-sensitive (Clary et al. 2020, PNAS 117:32947). Here cathodic O₂ reduction competes with HER, so true H₂ FE is likely &lt;1 and UNMEASURED. 1.0 = optimistic upper bound; measure via cathode-gas collection or the H₂:O₂ ratio.</t>
+          <t>Cathodic H₂ faradaic efficiency. Neutral-pH HER peaks ~97% and competes with O₂ reduction, so true FE is likely &lt;1 and unmeasured (Clary 2020, PNAS 117:32947). 1.0 = optimistic; measure by gas collection.</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="E87" s="20" t="inlineStr">
         <is>
-          <t>Total electrolytic gas (H₂+O₂) off the electrodes — an ABIOTIC calibration check (collect over water, no cells, to verify Gerrit's Law / etaF). With cells, H₂ (and excess O₂) are consumed so you would not collect this. If etaF&lt;1, less by the cathodic O₂ (O2_cathode_ORR).</t>
+          <t>Total electrolytic gas (H₂+O₂) — abiotic check: collect over water, no cells, to verify Gerrit/etaF. Less if etaF&lt;1.</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>H₂:O₂:CO₂ UPTAKE ratio (consumption, not feed). Phase-dependent, not a constant (Lu &amp; Yu 2019, Biochem Eng J 152:107369: the electron split between O₂ respiration and CO₂ fixation shifts with cell density). Bounds: knallgas energy reaction caps O₂:H₂ ≤ 0.5; autotrophic growth diverts ~30–40% of reducing power to fixation, giving O₂:H₂ ≈ 0.29–0.35 and CO₂:H₂ ≈ 0.15–0.19. 6:2:1 (O₂:H₂=0.33, CO₂:H₂=0.17) sits mid-range and is the design central estimate. For reaching growth, size O₂ removal at the lean-O₂ end (bio_O₂≈1.8 → larger surplus). FEED optimum is 7:2:1 (Ishizaki 2001; gives &lt;12 h lag, Amer &amp; Kim 2023) — feed ≠ consumption. Top-sensitivity input; can't measure pre-growth.</t>
+          <t>H₂:O₂:CO₂ UPTAKE ratio (not feed; phase-dependent, Lu &amp; Yu 2019). Knallgas caps O₂:H₂≤0.5; growth gives O₂:H₂≈0.29–0.35, CO₂:H₂≈0.15–0.19. 6:2:1 = mid-range central. Feed optimum 7:2:1 (Ishizaki 2001). Can't measure pre-growth.</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="E92" s="24" t="inlineStr">
         <is>
-          <t>O₂:H₂ uptake. Range 0.29–0.35 (×bio_H₂ → 1.75–2.1). 2 = central. Lean-O₂ end is growth-protective (more surplus to strip).</t>
+          <t>O₂:H₂ uptake, range 0.29–0.35 (×6 → 1.75–2.1). 2 = central; 1.8 (lean) is growth-protective.</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="E93" s="24" t="inlineStr">
         <is>
-          <t>CO₂:H₂ uptake (carbon demand). Range 0.15–0.19 (×bio_H₂ → 0.9–1.15). 1 = central. Sets CO₂ demand; supply far exceeds it (~20× at the optimum), so carbon is non-limiting across the range.</t>
+          <t>CO₂:H₂ uptake, range 0.15–0.19 (×6 → 0.9–1.15). 1 = central. Supply ≫ demand → non-limiting.</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Assumes 100% of evolved H₂ is consumed. Holds only at active growth; during LAG/low density uptake ≈ 0, so H₂ (and pro-rata O₂/CO₂ consumption) is overstated — see §13 (H₂ saturates/escapes in ~7 min unconsumed) and t_O2_ceiling_lag (§11).</t>
+          <t>Assumes 100% of evolved H₂ consumed — steady growth only; ~0 during lag (see §13).</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>H₂ consumed × (O₂/H₂ ratio). Steady-growth only; ≈ 0 during lag (cells not yet respiring) — the lag O₂ surplus is the full net electrolytic O₂.</t>
+          <t>H₂ consumed × O₂:H₂. Steady growth only; ~0 during lag.</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E97" s="20" t="inlineStr">
         <is>
-          <t>Net anodic O₂ (after cathodic ORR) minus biological O₂. Surplus to strip; when etaF&lt;1 the cathode itself removes part of the O₂, shrinking the stripping duty.</t>
+          <t>Net O₂ (after cathode) minus biological uptake — the surplus to strip.</t>
         </is>
       </c>
     </row>
@@ -3206,27 +3206,19 @@
       </c>
       <c r="E109" s="16" t="inlineStr">
         <is>
-          <t>Whole-cell growth inhibited above ~0.30 atm O₂ — NOT a hydrogenase limit (the [NiFe] enzyme is O₂-tolerant). ~0.30 atm reported for C. necator (Amer &amp; Kim 2023).</t>
+          <t>Whole-cell growth inhibited above ~0.30 atm O₂ (Amer &amp; Kim 2023); the [NiFe] hydrogenase itself is O₂-tolerant.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="19.5" customHeight="1" s="59">
-      <c r="A110" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  O₂ ceiling is whole-cell, not enzyme</t>
-        </is>
-      </c>
+      <c r="A110" s="12" t="n"/>
       <c r="C110" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="D110" s="17" t="n"/>
-      <c r="E110" s="16" t="inlineStr">
-        <is>
-          <t>Clarification, not a parameter: the 0.30 atm ceiling above is whole-cell growth inhibition. C. necator's membrane-bound [NiFe]-hydrogenase is O₂-tolerant, so the enzyme is NOT the binding constraint.</t>
-        </is>
-      </c>
+      <c r="E110" s="16" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
@@ -3302,7 +3294,7 @@
       </c>
       <c r="E113" s="25" t="inlineStr">
         <is>
-          <t>mol/m³ = mmol/L; ×1000 = µM. Practical aim is to MINIMISE dissolved O₂ (cathodic O₂ reduction steals H₂-evolution current); floor set by O₂-removal capacity (§11).</t>
+          <t>mol/m³ = mM; ×1000 = µM. Aim: minimise dissolved O₂; floor set by O₂-removal capacity (§11).</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3637,7 @@
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>&gt;1 = carbon supply exceeds fixation demand (~20× at the optimum → carbon non-limiting). Sparged CO₂ bubbles dissolve only ~1–2% per ~0.04 s rise, so most burst at the surface: the headspace fills with CO₂ and the §11 vent/sweep is active from the first pulse (including lag), building over the hs_flush_time scale. High pCO₂ can still extend lag (Amer &amp; Kim 2023, §12).</t>
+          <t>Carbon supply : demand (~20× = over-dosed, non-limiting). CO₂ mostly bursts at the surface → §11 headspace sweep active from pulse 1. High pCO₂ extends lag (Amer &amp; Kim 2023).</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4159,12 @@
         </is>
       </c>
       <c r="D150" s="65">
-        <f>IF(d_bubble&lt;0.001,NA(),SQRT(mend_a*sigma/(rho_L*d_bubble)+mend_b*g_const*d_bubble))</f>
+        <f>SQRT(mend_a*sigma/(rho_L*d_bubble)+mend_b*g_const*d_bubble)</f>
         <v/>
       </c>
       <c r="E150" s="26" t="inlineStr">
         <is>
-          <t>Mendelson wave-theory correlation, valid for inertial bubbles ≈1–10 mm. Returns #N/A when the selected sparger gives d_bubble &lt; 1 mm — fine sinters (Grade ~4–5) make sub-mm bubbles the correlation cannot model. By design this #N/A cascades through the §7 bubble-stripping chain and the cells that include it: §9 per-pulse (O2_strip_pulse, sched_bal), §10 t_O2_ceiling_strip, and §11 O2_removal_ratio / t_O2_ceiling_rem. The §14 optimiser and the surface-only cells are independent. Tube = 4.1 mm.</t>
+          <t>Mendelson rise velocity, valid ~1–10 mm. Sub-mm bubbles (fine sinters) are out of range → bubble strip excluded and flagged (bubble_regime); §11 surface path and §14 optimiser unaffected. Tube = 4.1 mm.</t>
         </is>
       </c>
     </row>
@@ -4414,12 +4406,12 @@
         </is>
       </c>
       <c r="D161" s="68">
-        <f>kLa_sparge*(V_charge/1000000)*O2_ceil_C*3600</f>
+        <f>IF(d_bubble&lt;0.001,0,kLa_sparge*(V_charge/1000000)*O2_ceil_C*3600)</f>
         <v/>
       </c>
       <c r="E161" s="26" t="inlineStr">
         <is>
-          <t>Max while sparging, bulk O₂ at ceiling, CO₂ bubbles ~O₂-free.</t>
+          <t>Bubble O₂ strip at the ceiling driving force (best case). 0 for sub-mm bubbles (fine sinter, bubble model out of range — see bubble_regime).</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4463,7 @@
       </c>
       <c r="E163" s="26" t="inlineStr">
         <is>
-          <t>&gt;=1 = dissolved-gas stripping holds the ceiling; &lt;1 = relies on bubble knock-off or DO rises. NB: BUBBLE path only — see §11 for the stirred-surface/headspace route, the likely-dominant O₂ removal path.</t>
+          <t>Bubble strip : surplus. ≪1 — the §11 surface path is the real route.</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4843,7 @@
       </c>
       <c r="E183" s="31" t="inlineStr">
         <is>
-          <t>Electrons per O₂ reduced at the cathode. 4 = full reduction to water (Pt-like); 2 = peroxide (H₂O₂), favoured on non-Pt electrodes at neutral pH. NB z=2 consumes O₂ at TWICE the rate per unit ORR current (each O₂ takes only 2 e⁻), so it makes the surplus SMALLER — z=4 (default) is the higher-excess, conservative choice. H₂O₂ is biocidal — a separate toxicity risk if significant. Inert while etaF=1; set per electrode material.</t>
+          <t>Electrons per cathodic O₂. 4 = to water; 2 = peroxide (favoured on non-Pt, neutral pH) — consumes 2× the O₂/amp, and H₂O₂ is biocidal. Inert while etaF=1.</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4869,7 @@
       </c>
       <c r="E184" s="29" t="inlineStr">
         <is>
-          <t>The cathodic current NOT making H₂ (1-etaF) reduces dissolved O₂. Zero while etaF=1; rises as the real H₂ efficiency falls.</t>
+          <t>Cathodic current not making H₂ (1−etaF) reduces dissolved O₂. 0 at etaF=1.</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4895,7 @@
       </c>
       <c r="E185" s="29" t="inlineStr">
         <is>
-          <t>Gross anodic O₂ minus cathodic consumption. This is the O₂ the biology and stripping actually have to manage.</t>
+          <t>Anodic O₂ minus cathodic consumption — the O₂ the dissolved pool receives.</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4946,7 @@
       </c>
       <c r="E187" s="32" t="inlineStr">
         <is>
-          <t>Tube = 1. Sinter = unknown active pore count; 1 = worst case (max per-orifice velocity). DATA GAP for the sinter.</t>
+          <t>Tube = 1. Sinter pore count unknown; 1 = worst case. DATA GAP.</t>
         </is>
       </c>
     </row>
@@ -5027,12 +5019,12 @@
         </is>
       </c>
       <c r="D190" s="68">
-        <f>IF(We_orifice&lt;2,"Static","Dynamic")</f>
+        <f>IF(d_bubble&lt;0.001,"Sinter OOR – add fine-bubble model",IF(We_orifice&lt;2,"Static","Dynamic"))</f>
         <v/>
       </c>
       <c r="E190" s="29" t="inlineStr">
         <is>
-          <t>Tate's law (d_bubble, section 6) assumes quasi-static detachment, valid for We&lt;~2. Flags when flow invalidates it.</t>
+          <t>Tate's law assumes quasi-static detachment (We&lt;~2). 'Sinter OOR' = sub-mm bubble; the fine-sinter model isn't built yet.</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5050,7 @@
       </c>
       <c r="E191" s="29" t="inlineStr">
         <is>
-          <t>Minutes for dissolved O₂ to rise from ~0 to the 0.30 atm inhibition ceiling if nothing removes the surplus (etaF=1). The O₂ problem's operational timescale. See §11 t_O2_ceiling_lag (worst case) and t_O2_ceiling_rem (with surface+cathode).</t>
+          <t>Minutes to reach the O₂ ceiling from ~0 with no removal (steady, etaF=1) — the O₂ timescale.</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5076,7 @@
       </c>
       <c r="E192" s="29" t="inlineStr">
         <is>
-          <t>Same, but crediting time-averaged gas-bubble stripping. ≈ unchanged here — confirms bubble stripping is not the O₂ mechanism at this duty. (9999 = stripping clears the surplus; no finite time-to-ceiling.)</t>
+          <t>As above, crediting time-averaged bubble strip (≈unchanged → bubbles aren't the mechanism). 9999 = cleared.</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5212,7 @@
       </c>
       <c r="E199" s="73" t="inlineStr">
         <is>
-          <t>COARSE proxy: tip speed / vial ID (how often stirred flow sweeps the surface). Calibrate.</t>
+          <t>Surface renewal ≈ tip speed / vial ID. Coarse proxy.</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5238,7 @@
       </c>
       <c r="E200" s="73" t="inlineStr">
         <is>
-          <t>Danckwerts surface-renewal. Coarse (rides s_renew); likely high-end — MEASURE by gassing-out.</t>
+          <t>Danckwerts surface-renewal estimate — coarse; measure by gassing-out (§15).</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5342,7 @@
       </c>
       <c r="E204" s="73" t="inlineStr">
         <is>
-          <t>&gt;=1 = surface path holds the ceiling. Coarse (kL_surf). Bubble strip_ratio is &lt;&lt;1, so the surface path is ~2 orders larger.</t>
+          <t>Surface strip : surplus. Coarse (kL_surf). ≫ bubble path — the dominant O₂ route.</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5368,7 @@
       </c>
       <c r="E205" s="29" t="inlineStr">
         <is>
-          <t>Headspace O₂ mole fraction at which the vented CO₂ throughput carries the excess O₂ out. Independent of kL — robust.</t>
+          <t>Headspace O₂ fraction at which the vented CO₂ carries the surplus out. kL-independent.</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5394,7 @@
       </c>
       <c r="E206" s="29" t="inlineStr">
         <is>
-          <t>Dissolved O₂ matching y_O2_vent. If ≪ ceiling (364 µM) the vent can hold DO low → surface path is vent-feasible.</t>
+          <t>Dissolved O₂ matching that headspace fraction. ≪ ceiling → vent-feasible.</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5420,7 @@
       </c>
       <c r="E207" s="29" t="inlineStr">
         <is>
-          <t>Avg CO₂ flow to displace one headspace volume. Surface stripping needs headspace kept O₂-lean.</t>
+          <t>Avg CO₂ flow to displace one headspace volume.</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5472,7 @@
       </c>
       <c r="E209" s="29" t="inlineStr">
         <is>
-          <t>Lag/establishment: cells not yet consuming O₂, so the full net electrolytic O₂ accumulates. Worst case — the regime that matters for reaching growth.</t>
+          <t>Lag/establishment: no biological O₂ uptake yet, so the full net O₂ accumulates. Worst case.</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5685,7 @@
       </c>
       <c r="E219" s="73" t="inlineStr">
         <is>
-          <t>C. necator RuBisCO Km(CO₂) ~ order 50 µM. Coarse — confirm.</t>
+          <t>RuBisCO Km(CO₂) ~ order 50 µM. Coarse — confirm.</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5711,7 @@
       </c>
       <c r="E220" s="29" t="inlineStr">
         <is>
-          <t>&gt;&gt;1 = CO₂ saturating for fixation during sparge. (Between pulses it falls; duty-averaged is lower.)</t>
+          <t>Dissolved CO₂ : RuBisCO Km. ≫1 = saturating (duty-averaged lower).</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5762,7 @@
       </c>
       <c r="E222" s="73" t="inlineStr">
         <is>
-          <t>Pure water saturated with CO₂ at p_CO2_sparge — a LOWER BOUND only. The Sydow (2017) phosphate medium (~36–108 mM) buffers pH near setpoint; true pH needs the buffer model.</t>
+          <t>Unbuffered worst case (pure water + CO₂) — lower bound only; the Sydow phosphate medium holds pH near setpoint.</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5821,7 @@
       </c>
       <c r="E226" s="74" t="inlineStr">
         <is>
-          <t>Sander (2023). H₂ is ~1.7× less soluble than O₂.</t>
+          <t>Sander (2023). H₂ ~1.7× less soluble than O₂.</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5898,7 @@
       </c>
       <c r="E229" s="29" t="inlineStr">
         <is>
-          <t>Max dissolved H₂ at surface pressure (mol/m³ = mM). The cells' H₂ supply is capped at this concentration.</t>
+          <t>Max dissolved H₂ at 1 atm — the cells' H₂ ceiling.</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5924,7 @@
       </c>
       <c r="E230" s="29" t="inlineStr">
         <is>
-          <t>If cells don't yet consume H₂ (lag), dissolved H₂ reaches saturation this fast; beyond it, evolved H₂ bubbles off — lost AND building an explosive headspace. Mirrors the O₂ lag timescale.</t>
+          <t>Lag: dissolved H₂ saturates this fast unconsumed, then bubbles off (lost + explosive headspace). Mirrors the O₂ lag timescale.</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5950,7 @@
       </c>
       <c r="E231" s="73" t="inlineStr">
         <is>
-          <t>Volumetric H₂ evolution / saturable pool. &gt;&gt;1 means H₂ is generated far faster than the liquid can hold it, so cells must consume it in near-real-time or it escapes. '100% consumed' needs uptake ≥ evolution.</t>
+          <t>H₂ evolved ÷ saturable pool. ≫1 → cells must consume in near-real-time or it escapes.</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5976,7 @@
       </c>
       <c r="E232" s="32" t="inlineStr">
         <is>
-          <t>Triggers when H₂ evolves faster than the liquid can hold it (H2_turnover&gt;1) → it escapes to the headspace and mixes with electrolytic O₂ (explosive 4–94% H₂ in O₂). At any useful electrolysis current this is on, so treat headspace inerting/venting as mandatory; 'watch' only if H₂ stays dissolved/consumed.</t>
+          <t>On when H₂ escapes faster than it dissolves (H2_turnover&gt;1) → explosive H₂+O₂ headspace (4–94% in O₂). On at any useful current — headspace venting is mandatory.</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6215,7 @@
       </c>
       <c r="E243" s="29" t="inlineStr">
         <is>
-          <t>The binding of the two floors — the least CO₂ that stays feasible. The O₂-vent floor binds here, NOT pH: the Sydow phosphate buffer (~36–108 mM, §12) holds pH near setpoint, so over-dosing is constrained by pCO₂-driven lag (Amer &amp; Kim 2023), not acid shock.</t>
+          <t>Least feasible CO₂ (binding of the two floors). O₂-venting binds, not pH (buffer holds pH; over-dose limited by pCO₂ lag).</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6423,7 @@
       </c>
       <c r="E251" s="73" t="inlineStr">
         <is>
-          <t>This optimiser targets a CONSTRAINT PROXY: the least-dosing schedule that holds DO below the O₂ ceiling, keeps carbon non-limiting, respects the solenoid floor and flush frequency. It is NOT a fitted growth model — no validated μ(dissolved-O₂, pH, dissolved-CO₂) or lag kinetics exist for C. necator under in-culture electrolysis. So this is the lag-MINIMISING DIRECTION, not a biologically-exact optimum. Confidence is further bounded by etaF (unmeasured), surface kL (coarse, §11) and the unbuffered-pH simplification (§12). Treat the numbers as a strong starting point to validate empirically, not ground truth.</t>
+          <t>Constraint-proxy optimiser, not a fitted growth model — no validated μ(O₂,pH,CO₂) or lag kinetics exist for this system. Gives the lag-minimising direction, not an exact optimum; bounded by etaF, surface kL and the unbuffered-pH simplification. Validate empirically.</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6482,7 @@
       </c>
       <c r="E255" s="73" t="inlineStr">
         <is>
-          <t>Measured surface O₂ transfer coefficient. 0 = use the §11 theoretical estimate (kL_surf). To measure (when you have a DO probe): deoxygenate, then log dissolved-O₂ recovery at operating stir with NO sparging; kLa = slope of −LN(1−DO/DO_sat) vs time (1/h).</t>
+          <t>Measured surface kLa (gassing-out). 0 = use the §11 estimate. kLa = slope of −LN(1−DO/DO_sat) vs time.</t>
         </is>
       </c>
     </row>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -6,7 +6,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="580" windowWidth="20400" windowHeight="18060" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Geometry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Model" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="a_int">Model!$D$156</definedName>
@@ -200,6 +202,11 @@
     <definedName name="kinetic_caveat">Model!$D$251</definedName>
     <definedName name="kLa_meas">Model!$D$255</definedName>
     <definedName name="kLa_surf_used">Model!$D$256</definedName>
+    <definedName name="A_x_in" localSheetId="0">Summary!$D$5</definedName>
+    <definedName name="vial_OD" localSheetId="1">Geometry!$D$3</definedName>
+    <definedName name="vial_wall" localSheetId="1">Geometry!$D$4</definedName>
+    <definedName name="vial_ID" localSheetId="1">Geometry!$D$5</definedName>
+    <definedName name="A_x" localSheetId="1">Geometry!$D$6</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -217,7 +224,7 @@
     <numFmt numFmtId="170" formatCode="0.000000000"/>
     <numFmt numFmtId="171" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -339,8 +346,18 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -425,6 +442,11 @@
         <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -453,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -569,6 +591,12 @@
     <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -849,6 +877,271 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" style="59" min="1" max="1"/>
+    <col width="46" customWidth="1" style="59" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>SUMMARY / CONTROL  (proof slice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="78" t="inlineStr">
+        <is>
+          <t>Imports from other tabs (the only cross-tab references):</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="79" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B4" s="79" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="79" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D4" s="79" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E4" s="79" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>(import) cross-section</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A_x_in</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mm²</t>
+        </is>
+      </c>
+      <c r="D5" s="35">
+        <f>Geometry!$D$6</f>
+        <v/>
+      </c>
+      <c r="E5" s="80" t="inlineStr">
+        <is>
+          <t>IMPORT cell — the one cross-tab link. Local formulas below use this, so their precedents stay on this tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Liquid per mm depth (demo)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mL_per_mm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mL/mm</t>
+        </is>
+      </c>
+      <c r="D6" s="35">
+        <f>A_x_in/1000</f>
+        <v/>
+      </c>
+      <c r="E6" s="81" t="inlineStr">
+        <is>
+          <t>Uses the local import (A_x_in), not Geometry directly → Excel highlights it on this tab.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="59" min="1" max="1"/>
+    <col width="40" customWidth="1" style="59" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>GEOMETRY  (proof slice — formula precedents are all on this tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="79" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B2" s="79" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" s="79" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D2" s="79" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E2" s="79" t="inlineStr">
+        <is>
+          <t>Source / assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Vial outer diameter</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>vial_OD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="E3" s="82" t="inlineStr">
+        <is>
+          <t>Pioreactor 20 mL vial, measured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Vial wall thickness</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>vial_wall</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E4" s="80" t="inlineStr">
+        <is>
+          <t>Borosilicate, estimated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vial internal diameter</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>vial_ID</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D5" s="35">
+        <f>vial_OD-2*vial_wall</f>
+        <v/>
+      </c>
+      <c r="E5" s="81" t="inlineStr">
+        <is>
+          <t>OD − 2 walls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Internal cross-section</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A_x</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mm²</t>
+        </is>
+      </c>
+      <c r="D6" s="35">
+        <f>PI()/4*vial_ID^2</f>
+        <v/>
+      </c>
+      <c r="E6" s="81" t="inlineStr">
+        <is>
+          <t>Uniform-cylinder body.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -8,17 +8,25 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Geometry" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Model" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Electrochemistry" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Biology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mass Transfer" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Model" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="a_int">Model!$D$156</definedName>
+    <definedName name="a_surf">Model!$D$201</definedName>
     <definedName name="A_x">Model!$D$40</definedName>
     <definedName name="bio_CO2">Model!$D$93</definedName>
     <definedName name="bio_H2">Model!$D$91</definedName>
     <definedName name="bio_O2">Model!$D$92</definedName>
     <definedName name="bubble_regime">Model!$D$190</definedName>
+    <definedName name="C_H2_sat">Model!$D$229</definedName>
+    <definedName name="carbon_margin_min">Model!$D$240</definedName>
     <definedName name="carry_flag">Model!$D$169</definedName>
+    <definedName name="CO2_carbon_margin">Model!$D$220</definedName>
     <definedName name="CO2_cons">Model!$D$96</definedName>
+    <definedName name="CO2_diss">Model!$D$218</definedName>
     <definedName name="CO2_pulse">Model!$D$124</definedName>
     <definedName name="CO2_sd_ratio">Model!$D$128</definedName>
     <definedName name="CO2_supply">Model!$D$127</definedName>
@@ -30,8 +38,13 @@
     <definedName name="D_O2">Model!$D$136</definedName>
     <definedName name="d_orifice">Model!$D$145</definedName>
     <definedName name="disp_tot">Model!$D$59</definedName>
+    <definedName name="DO_vent_eq">Model!$D$206</definedName>
     <definedName name="dur_ok">Model!$D$176</definedName>
     <definedName name="duty">Model!$D$129</definedName>
+    <definedName name="duty_actual">Model!$D$248</definedName>
+    <definedName name="duty_carbon">Model!$D$241</definedName>
+    <definedName name="duty_O2vent">Model!$D$242</definedName>
+    <definedName name="duty_opt">Model!$D$243</definedName>
     <definedName name="eff_disp">Model!$D$58</definedName>
     <definedName name="eff_ID">Model!$D$53</definedName>
     <definedName name="eff_OD">Model!$D$52</definedName>
@@ -49,21 +62,37 @@
     <definedName name="gerrit_min">Model!$D$75</definedName>
     <definedName name="gerrit_slope">Model!$D$73</definedName>
     <definedName name="h_actual">Model!$D$61</definedName>
+    <definedName name="H_CO2_T">Model!$D$216</definedName>
+    <definedName name="H_CO2ref">Model!$D$214</definedName>
+    <definedName name="H_CO2T">Model!$D$215</definedName>
     <definedName name="h_datum">Model!$D$44</definedName>
+    <definedName name="H_H2_T">Model!$D$228</definedName>
+    <definedName name="H_H2ref">Model!$D$226</definedName>
+    <definedName name="H_H2T">Model!$D$227</definedName>
     <definedName name="H_O2_T">Model!$D$108</definedName>
     <definedName name="H_O2ref">Model!$D$105</definedName>
     <definedName name="H_O2T">Model!$D$106</definedName>
     <definedName name="H2_cons">Model!$D$94</definedName>
+    <definedName name="H2_safety">Model!$D$232</definedName>
+    <definedName name="H2_turnover">Model!$D$231</definedName>
     <definedName name="headspace_V">Model!$D$68</definedName>
     <definedName name="holdup">Model!$D$155</definedName>
+    <definedName name="hs_flush_time">Model!$D$207</definedName>
     <definedName name="I_app">Model!$D$81</definedName>
     <definedName name="I_valid">Model!$D$82</definedName>
     <definedName name="intensity">Model!$D$72</definedName>
     <definedName name="interface_A">Model!$D$63</definedName>
+    <definedName name="Ka1_carb">Model!$D$221</definedName>
+    <definedName name="kinetic_caveat">Model!$D$251</definedName>
     <definedName name="kL">Model!$D$158</definedName>
+    <definedName name="kL_surf">Model!$D$200</definedName>
     <definedName name="kLa_avg">Model!$D$160</definedName>
+    <definedName name="kLa_meas">Model!$D$255</definedName>
     <definedName name="kLa_req">Model!$D$164</definedName>
     <definedName name="kLa_sparge">Model!$D$159</definedName>
+    <definedName name="kLa_surf">Model!$D$202</definedName>
+    <definedName name="kLa_surf_used">Model!$D$256</definedName>
+    <definedName name="Km_CO2">Model!$D$219</definedName>
     <definedName name="M_CO2">Model!$D$122</definedName>
     <definedName name="mend_a">Model!$D$148</definedName>
     <definedName name="mend_b">Model!$D$149</definedName>
@@ -78,9 +107,14 @@
     <definedName name="O2_cons">Model!$D$95</definedName>
     <definedName name="O2_excess">Model!$D$97</definedName>
     <definedName name="O2_net_gen">Model!$D$185</definedName>
+    <definedName name="O2_removal_ratio">Model!$D$208</definedName>
     <definedName name="O2_strip_pulse">Model!$D$174</definedName>
+    <definedName name="od_ok">Model!$D$250</definedName>
+    <definedName name="opt_binding">Model!$D$249</definedName>
     <definedName name="P_atm">Model!$D$103</definedName>
+    <definedName name="p_CO2_sparge">Model!$D$217</definedName>
     <definedName name="Pa_per_atm">Model!$D$104</definedName>
+    <definedName name="pH_CO2_unbuf">Model!$D$222</definedName>
     <definedName name="por_grade">Model!$D$18</definedName>
     <definedName name="por_pore">Model!$D$143</definedName>
     <definedName name="por0_um">Model!$D$137</definedName>
@@ -101,33 +135,55 @@
     <definedName name="rod_d">Model!$D$45</definedName>
     <definedName name="rod_n">Model!$D$46</definedName>
     <definedName name="rx_ver">Model!$D$16</definedName>
+    <definedName name="s_renew">Model!$D$199</definedName>
     <definedName name="sched_bal">Model!$D$175</definedName>
+    <definedName name="sched_mode">Model!$D$236</definedName>
     <definedName name="sigma">Model!$D$133</definedName>
     <definedName name="sparge_depth">Model!$D$62</definedName>
     <definedName name="sparger">Model!$D$17</definedName>
     <definedName name="spg_disp">Model!$D$56</definedName>
     <definedName name="spg_dur">Model!$D$118</definedName>
+    <definedName name="spg_dur_man">Model!$D$237</definedName>
+    <definedName name="spg_dur_opt">Model!$D$245</definedName>
     <definedName name="spg_ID">Model!$D$50</definedName>
     <definedName name="spg_int">Model!$D$119</definedName>
+    <definedName name="spg_int_man">Model!$D$238</definedName>
+    <definedName name="spg_int_max">Model!$D$244</definedName>
+    <definedName name="spg_int_opt">Model!$D$246</definedName>
+    <definedName name="spg_int_opt_s">Model!$D$247</definedName>
     <definedName name="spg_len">Model!$D$181</definedName>
     <definedName name="spg_name_1">Model!$D$21</definedName>
     <definedName name="spg_name_2">Model!$D$22</definedName>
     <definedName name="spg_OD">Model!$D$49</definedName>
     <definedName name="spg_tip_h">Model!$D$51</definedName>
+    <definedName name="stir_len">Model!$D$197</definedName>
+    <definedName name="stir_rpm">Model!$D$196</definedName>
     <definedName name="strip_avg">Model!$D$162</definedName>
     <definedName name="strip_ratio">Model!$D$163</definedName>
     <definedName name="strip_sparge">Model!$D$161</definedName>
+    <definedName name="surf_ratio">Model!$D$204</definedName>
+    <definedName name="surf_strip">Model!$D$203</definedName>
     <definedName name="T_C">Model!$D$101</definedName>
     <definedName name="t_contact">Model!$D$157</definedName>
+    <definedName name="t_H2_sat">Model!$D$230</definedName>
     <definedName name="T_K">Model!$D$102</definedName>
+    <definedName name="t_O2_ceiling">Model!$D$191</definedName>
+    <definedName name="t_O2_ceiling_lag">Model!$D$209</definedName>
+    <definedName name="t_O2_ceiling_rem">Model!$D$210</definedName>
+    <definedName name="t_O2_ceiling_strip">Model!$D$192</definedName>
     <definedName name="T_ref">Model!$D$107</definedName>
+    <definedName name="target_DO_frac">Model!$D$239</definedName>
+    <definedName name="tip_speed">Model!$D$198</definedName>
     <definedName name="tube_d_m">Model!$D$144</definedName>
     <definedName name="u_g_max">Model!$D$168</definedName>
     <definedName name="u_rise">Model!$D$150</definedName>
     <definedName name="u_sg">Model!$D$154</definedName>
     <definedName name="V_charge">Model!$D$60</definedName>
+    <definedName name="V_gas_total">Model!$D$87</definedName>
+    <definedName name="V_H2_gen">Model!$D$85</definedName>
     <definedName name="V_inserts">Model!$D$67</definedName>
     <definedName name="V_max">Model!$D$42</definedName>
+    <definedName name="V_O2_gen">Model!$D$86</definedName>
     <definedName name="v_orifice">Model!$D$188</definedName>
     <definedName name="V_vial_total">Model!$D$43</definedName>
     <definedName name="ver_name_1">Model!$D$19</definedName>
@@ -145,68 +201,28 @@
     <definedName name="xtube_n">Model!$D$65</definedName>
     <definedName name="xtube_OD">Model!$D$64</definedName>
     <definedName name="xtube_pro">Model!$D$66</definedName>
+    <definedName name="y_O2_vent">Model!$D$205</definedName>
     <definedName name="z_e_H2">Model!$D$78</definedName>
     <definedName name="z_e_O2">Model!$D$79</definedName>
     <definedName name="z_e_ORR">Model!$D$183</definedName>
-    <definedName name="V_H2_gen">Model!$D$85</definedName>
-    <definedName name="V_O2_gen">Model!$D$86</definedName>
-    <definedName name="V_gas_total">Model!$D$87</definedName>
-    <definedName name="t_O2_ceiling">Model!$D$191</definedName>
-    <definedName name="t_O2_ceiling_strip">Model!$D$192</definedName>
-    <definedName name="stir_rpm">Model!$D$196</definedName>
-    <definedName name="stir_len">Model!$D$197</definedName>
-    <definedName name="tip_speed">Model!$D$198</definedName>
-    <definedName name="s_renew">Model!$D$199</definedName>
-    <definedName name="kL_surf">Model!$D$200</definedName>
-    <definedName name="a_surf">Model!$D$201</definedName>
-    <definedName name="kLa_surf">Model!$D$202</definedName>
-    <definedName name="surf_strip">Model!$D$203</definedName>
-    <definedName name="surf_ratio">Model!$D$204</definedName>
-    <definedName name="y_O2_vent">Model!$D$205</definedName>
-    <definedName name="DO_vent_eq">Model!$D$206</definedName>
-    <definedName name="hs_flush_time">Model!$D$207</definedName>
-    <definedName name="O2_removal_ratio">Model!$D$208</definedName>
-    <definedName name="t_O2_ceiling_lag">Model!$D$209</definedName>
-    <definedName name="t_O2_ceiling_rem">Model!$D$210</definedName>
-    <definedName name="H_CO2_T">Model!$D$216</definedName>
-    <definedName name="p_CO2_sparge">Model!$D$217</definedName>
-    <definedName name="CO2_diss">Model!$D$218</definedName>
-    <definedName name="Km_CO2">Model!$D$219</definedName>
-    <definedName name="CO2_carbon_margin">Model!$D$220</definedName>
-    <definedName name="pH_CO2_unbuf">Model!$D$222</definedName>
-    <definedName name="H_CO2ref">Model!$D$214</definedName>
-    <definedName name="H_CO2T">Model!$D$215</definedName>
-    <definedName name="Ka1_carb">Model!$D$221</definedName>
-    <definedName name="H_H2ref">Model!$D$226</definedName>
-    <definedName name="H_H2T">Model!$D$227</definedName>
-    <definedName name="H_H2_T">Model!$D$228</definedName>
-    <definedName name="C_H2_sat">Model!$D$229</definedName>
-    <definedName name="t_H2_sat">Model!$D$230</definedName>
-    <definedName name="H2_turnover">Model!$D$231</definedName>
-    <definedName name="H2_safety">Model!$D$232</definedName>
-    <definedName name="sched_mode">Model!$D$236</definedName>
-    <definedName name="spg_dur_man">Model!$D$237</definedName>
-    <definedName name="spg_int_man">Model!$D$238</definedName>
-    <definedName name="target_DO_frac">Model!$D$239</definedName>
-    <definedName name="carbon_margin_min">Model!$D$240</definedName>
-    <definedName name="duty_carbon">Model!$D$241</definedName>
-    <definedName name="duty_O2vent">Model!$D$242</definedName>
-    <definedName name="duty_opt">Model!$D$243</definedName>
-    <definedName name="spg_int_max">Model!$D$244</definedName>
-    <definedName name="spg_dur_opt">Model!$D$245</definedName>
-    <definedName name="spg_int_opt">Model!$D$246</definedName>
-    <definedName name="spg_int_opt_s">Model!$D$247</definedName>
-    <definedName name="duty_actual">Model!$D$248</definedName>
-    <definedName name="opt_binding">Model!$D$249</definedName>
-    <definedName name="od_ok">Model!$D$250</definedName>
-    <definedName name="kinetic_caveat">Model!$D$251</definedName>
-    <definedName name="kLa_meas">Model!$D$255</definedName>
-    <definedName name="kLa_surf_used">Model!$D$256</definedName>
     <definedName name="A_x_in" localSheetId="0">Summary!$D$5</definedName>
+    <definedName name="I_app_in" localSheetId="0">Summary!$D$7</definedName>
+    <definedName name="O2_per_H2_in" localSheetId="0">Summary!$D$8</definedName>
+    <definedName name="tip_speed_in" localSheetId="0">Summary!$D$9</definedName>
+    <definedName name="A_x" localSheetId="1">Geometry!$D$6</definedName>
+    <definedName name="vial_ID" localSheetId="1">Geometry!$D$5</definedName>
     <definedName name="vial_OD" localSheetId="1">Geometry!$D$3</definedName>
     <definedName name="vial_wall" localSheetId="1">Geometry!$D$4</definedName>
-    <definedName name="vial_ID" localSheetId="1">Geometry!$D$5</definedName>
-    <definedName name="A_x" localSheetId="1">Geometry!$D$6</definedName>
+    <definedName name="intensity" localSheetId="2">Electrochemistry!$D$3</definedName>
+    <definedName name="gerrit_slope" localSheetId="2">Electrochemistry!$D$4</definedName>
+    <definedName name="gerrit_int" localSheetId="2">Electrochemistry!$D$5</definedName>
+    <definedName name="I_app" localSheetId="2">Electrochemistry!$D$6</definedName>
+    <definedName name="bio_H2" localSheetId="3">Biology!$D$3</definedName>
+    <definedName name="bio_O2" localSheetId="3">Biology!$D$4</definedName>
+    <definedName name="O2_per_H2" localSheetId="3">Biology!$D$5</definedName>
+    <definedName name="stir_rpm" localSheetId="4">'Mass Transfer'!$D$3</definedName>
+    <definedName name="stir_len" localSheetId="4">'Mass Transfer'!$D$4</definedName>
+    <definedName name="tip_speed" localSheetId="4">'Mass Transfer'!$D$5</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -224,7 +240,7 @@
     <numFmt numFmtId="170" formatCode="0.000000000"/>
     <numFmt numFmtId="171" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -347,14 +363,27 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <i val="1"/>
     </font>
   </fonts>
   <fills count="17">
@@ -448,7 +477,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -471,11 +500,82 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="7"/>
+      </left>
+      <right style="medium">
+        <color theme="7"/>
+      </right>
+      <top style="medium">
+        <color theme="7"/>
+      </top>
+      <bottom style="medium">
+        <color theme="7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="7"/>
+      </left>
+      <right style="medium">
+        <color theme="7"/>
+      </right>
+      <top style="medium">
+        <color theme="7"/>
+      </top>
+      <bottom style="medium">
+        <color theme="7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="8"/>
+      </left>
+      <right style="medium">
+        <color theme="8"/>
+      </right>
+      <top style="medium">
+        <color theme="8"/>
+      </top>
+      <bottom style="medium">
+        <color theme="8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5"/>
+      </left>
+      <right style="medium">
+        <color theme="5"/>
+      </right>
+      <top style="medium">
+        <color theme="5"/>
+      </top>
+      <bottom style="medium">
+        <color theme="5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="6"/>
+      </left>
+      <right style="medium">
+        <color theme="6"/>
+      </right>
+      <top style="medium">
+        <color theme="6"/>
+      </top>
+      <bottom style="medium">
+        <color theme="6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -564,22 +664,6 @@
     <xf numFmtId="170" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -597,11 +681,30 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB84"/>
+          <bgColor rgb="FFFFEB84"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -623,6 +726,62 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFEB84"/>
           <bgColor rgb="FFFFEB84"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF63BE7B"/>
+          <bgColor rgb="FF63BE7B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8696B"/>
+          <bgColor rgb="FFF8696B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF63BE7B"/>
+          <bgColor rgb="FF63BE7B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8696B"/>
+          <bgColor rgb="FFF8696B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF63BE7B"/>
+          <bgColor rgb="FF63BE7B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8696B"/>
+          <bgColor rgb="FFF8696B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF63BE7B"/>
+          <bgColor rgb="FF63BE7B"/>
         </patternFill>
       </fill>
     </dxf>
@@ -882,55 +1041,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="59" min="1" max="1"/>
-    <col width="46" customWidth="1" style="59" min="5" max="5"/>
+    <col width="24" customWidth="1" style="70" min="1" max="1"/>
+    <col width="46" customWidth="1" style="70" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="77" t="inlineStr">
+      <c r="A1" s="63" t="inlineStr">
         <is>
           <t>SUMMARY / CONTROL  (proof slice)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="78" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>Imports from other tabs (the only cross-tab references):</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="79" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="70" thickBot="1">
+      <c r="A4" s="65" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B4" s="79" t="inlineStr">
+      <c r="B4" s="65" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="79" t="inlineStr">
+      <c r="C4" s="65" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="79" t="inlineStr">
+      <c r="D4" s="65" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E4" s="79" t="inlineStr">
+      <c r="E4" s="65" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="16" customHeight="1" s="70" thickBot="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>(import) cross-section</t>
@@ -946,11 +1105,11 @@
           <t>mm²</t>
         </is>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="72">
         <f>Geometry!$D$6</f>
         <v/>
       </c>
-      <c r="E5" s="80" t="inlineStr">
+      <c r="E5" s="66" t="inlineStr">
         <is>
           <t>IMPORT cell — the one cross-tab link. Local formulas below use this, so their precedents stay on this tab.</t>
         </is>
@@ -976,9 +1135,75 @@
         <f>A_x_in/1000</f>
         <v/>
       </c>
-      <c r="E6" s="81" t="inlineStr">
+      <c r="E6" s="67" t="inlineStr">
         <is>
           <t>Uses the local import (A_x_in), not Geometry directly → Excel highlights it on this tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>(import) electrolysis current</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>I_app_in</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" s="73">
+        <f>'Electrochemistry'!$D$6</f>
+        <v/>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>From Electrochemistry (theme 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>(import) O₂:H₂ uptake</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>O2_per_H2_in</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="74">
+        <f>Biology!$D$5</f>
+        <v/>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>From Biology (theme 5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>(import) tip speed</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tip_speed_in</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" s="75">
+        <f>'Mass Transfer'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>From Mass Transfer (theme 6).</t>
         </is>
       </c>
     </row>
@@ -990,45 +1215,46 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor theme="7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="59" min="1" max="1"/>
-    <col width="40" customWidth="1" style="59" min="5" max="5"/>
+    <col width="22" customWidth="1" style="70" min="1" max="1"/>
+    <col width="40" customWidth="1" style="70" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="77" t="inlineStr">
+      <c r="A1" s="63" t="inlineStr">
         <is>
           <t>GEOMETRY  (proof slice — formula precedents are all on this tab)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="79" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B2" s="79" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" s="79" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D2" s="79" t="inlineStr">
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E2" s="79" t="inlineStr">
+      <c r="E2" s="65" t="inlineStr">
         <is>
           <t>Source / assumption</t>
         </is>
@@ -1053,7 +1279,7 @@
       <c r="D3" s="33" t="n">
         <v>27.48</v>
       </c>
-      <c r="E3" s="82" t="inlineStr">
+      <c r="E3" s="68" t="inlineStr">
         <is>
           <t>Pioreactor 20 mL vial, measured.</t>
         </is>
@@ -1078,7 +1304,7 @@
       <c r="D4" s="33" t="n">
         <v>1.1</v>
       </c>
-      <c r="E4" s="80" t="inlineStr">
+      <c r="E4" s="66" t="inlineStr">
         <is>
           <t>Borosilicate, estimated.</t>
         </is>
@@ -1104,7 +1330,7 @@
         <f>vial_OD-2*vial_wall</f>
         <v/>
       </c>
-      <c r="E5" s="81" t="inlineStr">
+      <c r="E5" s="67" t="inlineStr">
         <is>
           <t>OD − 2 walls.</t>
         </is>
@@ -1130,7 +1356,7 @@
         <f>PI()/4*vial_ID^2</f>
         <v/>
       </c>
-      <c r="E6" s="81" t="inlineStr">
+      <c r="E6" s="67" t="inlineStr">
         <is>
           <t>Uniform-cylinder body.</t>
         </is>
@@ -1142,6 +1368,418 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor theme="8"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="70" min="1" max="1"/>
+    <col width="40" customWidth="1" style="70" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="76" t="inlineStr">
+        <is>
+          <t>ELECTROCHEMISTRY  (proof slice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="77" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B2" s="77" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" s="77" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D2" s="77" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E2" s="77" t="inlineStr">
+        <is>
+          <t>Source / assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LED intensity</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>intensity</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="66" t="inlineStr">
+        <is>
+          <t>Electrode drive setpoint. Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gerrit slope</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>gerrit_slope</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mA/%</t>
+        </is>
+      </c>
+      <c r="D4" s="34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E4" s="68" t="inlineStr">
+        <is>
+          <t>Empirical fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gerrit intercept</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>gerrit_int</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mA</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E5" s="68" t="inlineStr">
+        <is>
+          <t>Empirical fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Electrolysis current</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>I_app</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" s="35">
+        <f>(gerrit_slope*intensity+gerrit_int)/1000</f>
+        <v/>
+      </c>
+      <c r="E6" s="67" t="inlineStr">
+        <is>
+          <t>Gerrit's Law.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor theme="5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="70" min="1" max="1"/>
+    <col width="40" customWidth="1" style="70" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="76" t="inlineStr">
+        <is>
+          <t>BIOLOGY  (proof slice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="77" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B2" s="77" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" s="77" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D2" s="77" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E2" s="77" t="inlineStr">
+        <is>
+          <t>Source / assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gas ratio H₂</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>bio_H2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="66" t="inlineStr">
+        <is>
+          <t>Uptake ratio basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gas ratio O₂</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>bio_O2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="66" t="inlineStr">
+        <is>
+          <t>Uptake ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>O₂ per H₂</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>O2_per_H2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="35">
+        <f>bio_O2/bio_H2</f>
+        <v/>
+      </c>
+      <c r="E5" s="67" t="inlineStr">
+        <is>
+          <t>Derived ratio.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor theme="6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="70" min="1" max="1"/>
+    <col width="40" customWidth="1" style="70" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="76" t="inlineStr">
+        <is>
+          <t>MASS TRANSFER  (proof slice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="77" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B2" s="77" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" s="77" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D2" s="77" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E2" s="77" t="inlineStr">
+        <is>
+          <t>Source / assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Stir speed</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>stir_rpm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1/min</t>
+        </is>
+      </c>
+      <c r="D3" s="33" t="n">
+        <v>500</v>
+      </c>
+      <c r="E3" s="66" t="inlineStr">
+        <is>
+          <t>Stir setpoint. Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Stir-bar length</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>stir_len</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="66" t="inlineStr">
+        <is>
+          <t>Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tip speed</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tip_speed</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D5" s="35">
+        <f>PI()*(stir_len/1000)*stir_rpm/60</f>
+        <v/>
+      </c>
+      <c r="E5" s="67" t="inlineStr">
+        <is>
+          <t>π·d·rpm/60.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1150,14 +1788,14 @@
   <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" style="59" min="1" max="1"/>
-    <col width="15" customWidth="1" style="59" min="2" max="2"/>
-    <col width="11" customWidth="1" style="59" min="3" max="3"/>
-    <col width="12" customWidth="1" style="59" min="4" max="4"/>
-    <col width="70" customWidth="1" style="59" min="5" max="5"/>
+    <col width="44" customWidth="1" style="70" min="1" max="1"/>
+    <col width="15" customWidth="1" style="70" min="2" max="2"/>
+    <col width="11" customWidth="1" style="70" min="3" max="3"/>
+    <col width="12" customWidth="1" style="70" min="4" max="4"/>
+    <col width="70" customWidth="1" style="70" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" s="59">
+    <row r="1" ht="17.25" customHeight="1" s="70">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>electroPioreactor gas model</t>
@@ -1165,55 +1803,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>AMYBO aseptic electro-bioreactor - hydrogen-oxidising bacteria (C. necator) grown on electrolytic H₂/O₂ + dosed CO₂. UK English, SI.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="59">
+    <row r="4" ht="15" customHeight="1" s="70">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="59">
+    <row r="5" ht="15" customHeight="1" s="70">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Verified / handbook / defined / standard</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="59">
+    <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Literature-supported (~90%)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="59">
+      <c r="D6">
+        <f t="array" ref="D6">A_x_in/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="70">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Design assumption (~70%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="59">
+    <row r="8" ht="15" customHeight="1" s="70">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Weak / coarse estimate (~50%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="59">
+    <row r="9" ht="15" customHeight="1" s="70">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Guess - replace when known</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="59">
+    <row r="10" ht="15" customHeight="1" s="70">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - need to measure</t>
@@ -1247,7 +1889,7 @@
       <c r="C13" s="34" t="n"/>
       <c r="D13" s="35" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="59">
+    <row r="14" ht="15" customHeight="1" s="70">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>0.  SELECTORS</t>
@@ -1258,7 +1900,7 @@
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="10" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="59">
+    <row r="15" ht="15" customHeight="1" s="70">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
@@ -1285,7 +1927,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="59">
+    <row r="16" ht="15" customHeight="1" s="70">
       <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Reactor version</t>
@@ -1312,7 +1954,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="59">
+    <row r="17" ht="15" customHeight="1" s="70">
       <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Sparger type</t>
@@ -1339,7 +1981,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="59">
+    <row r="18" ht="15" customHeight="1" s="70">
       <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Sinter porosity grade (if Sintered)</t>
@@ -1364,7 +2006,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="59">
+    <row r="19" ht="15" customHeight="1" s="70">
       <c r="A19" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  valid version 1</t>
@@ -1391,7 +2033,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="59">
+    <row r="20" ht="15" customHeight="1" s="70">
       <c r="A20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  valid version 2</t>
@@ -1418,7 +2060,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="59">
+    <row r="21" ht="15" customHeight="1" s="70">
       <c r="A21" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  valid sparger 1</t>
@@ -1445,7 +2087,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="59">
+    <row r="22" ht="15" customHeight="1" s="70">
       <c r="A22" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  valid sparger 2</t>
@@ -1472,7 +2114,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="59">
+    <row r="24" ht="15" customHeight="1" s="70">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>1A.  REACTOR VERSION DATA</t>
@@ -1483,7 +2125,7 @@
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1" s="59">
+    <row r="25" ht="15" customHeight="1" s="70">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
@@ -1510,7 +2152,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="59">
+    <row r="26" ht="15" customHeight="1" s="70">
       <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Vial outer diameter - AEP0.1.1</t>
@@ -1535,7 +2177,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="59">
+    <row r="27" ht="15" customHeight="1" s="70">
       <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Vial outer diameter - AEP0.2</t>
@@ -1560,7 +2202,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="59">
+    <row r="28" ht="15" customHeight="1" s="70">
       <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Internal usable depth - AEP0.1.1</t>
@@ -1576,7 +2218,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D28" s="60" t="n">
+      <c r="D28" s="37" t="n">
         <v>55</v>
       </c>
       <c r="E28" s="18" t="inlineStr">
@@ -1585,7 +2227,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="59">
+    <row r="29" ht="15" customHeight="1" s="70">
       <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Internal usable depth - AEP0.2</t>
@@ -1601,7 +2243,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D29" s="60" t="n">
+      <c r="D29" s="37" t="n">
         <v>95</v>
       </c>
       <c r="E29" s="18" t="inlineStr">
@@ -1610,7 +2252,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="59">
+    <row r="30" ht="15" customHeight="1" s="70">
       <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Recommended max working volume - AEP0.1.1</t>
@@ -1626,7 +2268,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D30" s="60" t="n">
+      <c r="D30" s="37" t="n">
         <v>16</v>
       </c>
       <c r="E30" s="16" t="inlineStr">
@@ -1635,7 +2277,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="59">
+    <row r="31" ht="15" customHeight="1" s="70">
       <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Recommended max working volume - AEP0.2</t>
@@ -1651,7 +2293,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D31" s="60" t="n">
+      <c r="D31" s="37" t="n">
         <v>30</v>
       </c>
       <c r="E31" s="16" t="inlineStr">
@@ -1660,7 +2302,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="59">
+    <row r="32" ht="15" customHeight="1" s="70">
       <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Total internal vial volume - AEP0.1.1</t>
@@ -1676,7 +2318,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D32" s="60" t="n">
+      <c r="D32" s="37" t="n">
         <v>20</v>
       </c>
       <c r="E32" s="19" t="inlineStr">
@@ -1685,7 +2327,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="59">
+    <row r="33" ht="15" customHeight="1" s="70">
       <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Total internal vial volume - AEP0.2</t>
@@ -1701,7 +2343,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D33" s="60" t="n">
+      <c r="D33" s="37" t="n">
         <v>40</v>
       </c>
       <c r="E33" s="19" t="inlineStr">
@@ -1710,7 +2352,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="59">
+    <row r="35" ht="15" customHeight="1" s="70">
       <c r="A35" s="9" t="inlineStr">
         <is>
           <t>1B.  ACTIVE REACTOR GEOMETRY</t>
@@ -1721,7 +2363,7 @@
       <c r="D35" s="10" t="n"/>
       <c r="E35" s="10" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1" s="59">
+    <row r="36" ht="15" customHeight="1" s="70">
       <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
@@ -1748,7 +2390,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="59">
+    <row r="37" ht="15" customHeight="1" s="70">
       <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Vial outer diameter</t>
@@ -1774,7 +2416,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="19.5" customHeight="1" s="59">
+    <row r="38" ht="19.5" customHeight="1" s="70">
       <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Vial wall thickness</t>
@@ -1799,7 +2441,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="59">
+    <row r="39" ht="15" customHeight="1" s="70">
       <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Vial internal diameter</t>
@@ -1825,7 +2467,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="59">
+    <row r="40" ht="15" customHeight="1" s="70">
       <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Internal cross-sectional area</t>
@@ -1841,7 +2483,7 @@
           <t>mm²</t>
         </is>
       </c>
-      <c r="D40" s="61">
+      <c r="D40" s="39">
         <f>PI()/4*vial_ID^2</f>
         <v/>
       </c>
@@ -1851,7 +2493,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="59">
+    <row r="41" ht="15" customHeight="1" s="70">
       <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Internal usable depth</t>
@@ -1867,7 +2509,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D41" s="61">
+      <c r="D41" s="39">
         <f>IF(rx_ver=ver_name_1,D_int_1,IF(rx_ver=ver_name_2,D_int_2,NA()))</f>
         <v/>
       </c>
@@ -1877,7 +2519,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="59">
+    <row r="42" ht="15" customHeight="1" s="70">
       <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Recommended max working volume (datum)</t>
@@ -1893,7 +2535,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D42" s="61">
+      <c r="D42" s="39">
         <f>IF(rx_ver=ver_name_1,Vmax_1,IF(rx_ver=ver_name_2,Vmax_2,NA()))</f>
         <v/>
       </c>
@@ -1903,7 +2545,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="59">
+    <row r="43" ht="15" customHeight="1" s="70">
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Total internal vial volume</t>
@@ -1919,7 +2561,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D43" s="61">
+      <c r="D43" s="39">
         <f>IF(rx_ver=ver_name_1,Vtot_1,IF(rx_ver=ver_name_2,Vtot_2,NA()))</f>
         <v/>
       </c>
@@ -1929,7 +2571,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="59">
+    <row r="44" ht="15" customHeight="1" s="70">
       <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Bare liquid level (datum height)</t>
@@ -1955,7 +2597,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="59">
+    <row r="45" ht="15" customHeight="1" s="70">
       <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Electrode rod diameter</t>
@@ -1971,7 +2613,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D45" s="60" t="n">
+      <c r="D45" s="37" t="n">
         <v>6</v>
       </c>
       <c r="E45" s="15" t="inlineStr">
@@ -1980,7 +2622,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="59">
+    <row r="46" ht="15" customHeight="1" s="70">
       <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Number of electrodes</t>
@@ -2005,7 +2647,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="19.5" customHeight="1" s="59">
+    <row r="47" ht="19.5" customHeight="1" s="70">
       <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Electrode tip clearance above base</t>
@@ -2021,7 +2663,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D47" s="60" t="n">
+      <c r="D47" s="37" t="n">
         <v>22</v>
       </c>
       <c r="E47" s="15" t="inlineStr">
@@ -2030,7 +2672,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="59">
+    <row r="48" ht="15" customHeight="1" s="70">
       <c r="A48" s="22" t="inlineStr">
         <is>
           <t>Electrode insertion depth (derived)</t>
@@ -2046,7 +2688,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D48" s="61">
+      <c r="D48" s="39">
         <f>D_int-elec_clear</f>
         <v/>
       </c>
@@ -2056,7 +2698,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="59">
+    <row r="49" ht="15" customHeight="1" s="70">
       <c r="A49" s="12" t="inlineStr">
         <is>
           <t>Sparge tube OD</t>
@@ -2072,7 +2714,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D49" s="62" t="n">
+      <c r="D49" s="40" t="n">
         <v>3.175</v>
       </c>
       <c r="E49" s="20" t="inlineStr">
@@ -2081,7 +2723,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="59">
+    <row r="50" ht="15" customHeight="1" s="70">
       <c r="A50" s="12" t="inlineStr">
         <is>
           <t>Sparge tube ID</t>
@@ -2097,7 +2739,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D50" s="63" t="n">
+      <c r="D50" s="41" t="n">
         <v>1.5875</v>
       </c>
       <c r="E50" s="20" t="inlineStr">
@@ -2106,7 +2748,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="59">
+    <row r="51" ht="15" customHeight="1" s="70">
       <c r="A51" s="12" t="inlineStr">
         <is>
           <t>Sparge release height (= anode tip)</t>
@@ -2122,7 +2764,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D51" s="61">
+      <c r="D51" s="39">
         <f>elec_clear</f>
         <v/>
       </c>
@@ -2132,7 +2774,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="59">
+    <row r="52" ht="15" customHeight="1" s="70">
       <c r="A52" s="12" t="inlineStr">
         <is>
           <t>Efflux tube OD</t>
@@ -2148,7 +2790,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D52" s="62" t="n">
+      <c r="D52" s="40" t="n">
         <v>3.175</v>
       </c>
       <c r="E52" s="20" t="inlineStr">
@@ -2157,7 +2799,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="59">
+    <row r="53" ht="15" customHeight="1" s="70">
       <c r="A53" s="12" t="inlineStr">
         <is>
           <t>Efflux tube ID</t>
@@ -2173,7 +2815,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D53" s="63" t="n">
+      <c r="D53" s="41" t="n">
         <v>1.5875</v>
       </c>
       <c r="E53" s="20" t="inlineStr">
@@ -2182,7 +2824,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="59">
+    <row r="54" ht="15" customHeight="1" s="70">
       <c r="A54" s="12" t="inlineStr">
         <is>
           <t>Electrode submerged length (@datum)</t>
@@ -2208,7 +2850,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="59">
+    <row r="55" ht="15" customHeight="1" s="70">
       <c r="A55" s="12" t="inlineStr">
         <is>
           <t>Electrode displaced volume</t>
@@ -2224,7 +2866,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D55" s="64">
+      <c r="D55" s="42">
         <f>rod_n*(PI()/4*rod_d^2)*elec_sub_L/1000</f>
         <v/>
       </c>
@@ -2234,7 +2876,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="59">
+    <row r="56" ht="15" customHeight="1" s="70">
       <c r="A56" s="12" t="inlineStr">
         <is>
           <t>Sparge tube displaced volume</t>
@@ -2250,7 +2892,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D56" s="64">
+      <c r="D56" s="42">
         <f>(PI()/4*spg_OD^2)*MAX(0,h_datum-spg_tip_h)/1000</f>
         <v/>
       </c>
@@ -2260,7 +2902,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="59">
+    <row r="57" ht="15" customHeight="1" s="70">
       <c r="A57" s="12" t="inlineStr">
         <is>
           <t>Efflux tube submerged length</t>
@@ -2276,7 +2918,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D57" s="64">
+      <c r="D57" s="42">
         <f>(eff_OD+eff_ID)/2</f>
         <v/>
       </c>
@@ -2286,7 +2928,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="59">
+    <row r="58" ht="15" customHeight="1" s="70">
       <c r="A58" s="12" t="inlineStr">
         <is>
           <t>Efflux tube displaced volume</t>
@@ -2302,7 +2944,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D58" s="65">
+      <c r="D58" s="43">
         <f>(PI()/4*(eff_OD^2-eff_ID^2))*eff_sub_L/1000</f>
         <v/>
       </c>
@@ -2312,7 +2954,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="59">
+    <row r="59" ht="15" customHeight="1" s="70">
       <c r="A59" s="12" t="inlineStr">
         <is>
           <t>Total displaced volume</t>
@@ -2328,7 +2970,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D59" s="64">
+      <c r="D59" s="42">
         <f>elec_disp+spg_disp+eff_disp</f>
         <v/>
       </c>
@@ -2338,7 +2980,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="59">
+    <row r="60" ht="15" customHeight="1" s="70">
       <c r="A60" s="22" t="inlineStr">
         <is>
           <t>LIQUID VOLUME TO CHARGE</t>
@@ -2364,7 +3006,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="59">
+    <row r="61" ht="15" customHeight="1" s="70">
       <c r="A61" s="22" t="inlineStr">
         <is>
           <t>Resulting liquid level</t>
@@ -2390,7 +3032,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="59">
+    <row r="62" ht="15" customHeight="1" s="70">
       <c r="A62" s="22" t="inlineStr">
         <is>
           <t>Sparge depth / bubble path length</t>
@@ -2416,7 +3058,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="59">
+    <row r="63" ht="15" customHeight="1" s="70">
       <c r="A63" s="22" t="inlineStr">
         <is>
           <t>Gas-liquid interfacial area</t>
@@ -2432,7 +3074,7 @@
           <t>mm²</t>
         </is>
       </c>
-      <c r="D63" s="61">
+      <c r="D63" s="39">
         <f>A_x-(rod_n*(PI()/4*rod_d^2)+(PI()/4*spg_OD^2)+(PI()/4*eff_OD^2))</f>
         <v/>
       </c>
@@ -2442,7 +3084,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="59">
+    <row r="64" ht="15" customHeight="1" s="70">
       <c r="A64" s="12" t="inlineStr">
         <is>
           <t>Extra headspace tube OD</t>
@@ -2458,7 +3100,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D64" s="64">
+      <c r="D64" s="42">
         <f>eff_OD</f>
         <v/>
       </c>
@@ -2468,7 +3110,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="59">
+    <row r="65" ht="15" customHeight="1" s="70">
       <c r="A65" s="12" t="inlineStr">
         <is>
           <t>Number of extra headspace tubes</t>
@@ -2493,7 +3135,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="59">
+    <row r="66" ht="15" customHeight="1" s="70">
       <c r="A66" s="12" t="inlineStr">
         <is>
           <t>Extra tube protrusion</t>
@@ -2509,7 +3151,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D66" s="60" t="n">
+      <c r="D66" s="37" t="n">
         <v>5</v>
       </c>
       <c r="E66" s="21" t="inlineStr">
@@ -2518,7 +3160,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="19.5" customHeight="1" s="59">
+    <row r="67" ht="19.5" customHeight="1" s="70">
       <c r="A67" s="12" t="inlineStr">
         <is>
           <t>Total in-vial insert volume</t>
@@ -2534,7 +3176,7 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="D67" s="64">
+      <c r="D67" s="42">
         <f>(rod_n*(PI()/4*rod_d^2)*elec_ins+(PI()/4*spg_OD^2)*spg_len+(PI()/4*(eff_OD^2-eff_ID^2))*(D_int-h_actual)+xtube_n*(PI()/4*xtube_OD^2)*xtube_pro)/1000</f>
         <v/>
       </c>
@@ -2544,7 +3186,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" s="59">
+    <row r="68" ht="15" customHeight="1" s="70">
       <c r="A68" s="22" t="inlineStr">
         <is>
           <t>Headspace gas volume</t>
@@ -2570,7 +3212,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="59">
+    <row r="70" ht="15" customHeight="1" s="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
           <t>2.  ELECTROLYSIS  (constant current from LED intensity - Gerrit)</t>
@@ -2581,7 +3223,7 @@
       <c r="D70" s="10" t="n"/>
       <c r="E70" s="10" t="n"/>
     </row>
-    <row r="71" ht="15" customHeight="1" s="59">
+    <row r="71" ht="15" customHeight="1" s="70">
       <c r="A71" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
@@ -2608,7 +3250,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="59">
+    <row r="72" ht="15" customHeight="1" s="70">
       <c r="A72" s="12" t="inlineStr">
         <is>
           <t>LED intensity setpoint (Pioreactor LED_D)</t>
@@ -2633,7 +3275,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="59">
+    <row r="73" ht="15" customHeight="1" s="70">
       <c r="A73" s="12" t="inlineStr">
         <is>
           <t>Gerrit's Law - slope</t>
@@ -2658,7 +3300,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" s="59">
+    <row r="74" ht="15" customHeight="1" s="70">
       <c r="A74" s="12" t="inlineStr">
         <is>
           <t>Gerrit's Law - intercept</t>
@@ -2674,7 +3316,7 @@
           <t>mA</t>
         </is>
       </c>
-      <c r="D74" s="66" t="n">
+      <c r="D74" s="47" t="n">
         <v>2.6</v>
       </c>
       <c r="E74" s="16" t="inlineStr">
@@ -2683,7 +3325,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="59">
+    <row r="75" ht="15" customHeight="1" s="70">
       <c r="A75" s="12" t="inlineStr">
         <is>
           <t>Gerrit's Law - min valid intensity</t>
@@ -2708,7 +3350,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" s="59">
+    <row r="76" ht="15" customHeight="1" s="70">
       <c r="A76" s="12" t="inlineStr">
         <is>
           <t>Gerrit's Law - max valid intensity</t>
@@ -2733,7 +3375,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="59">
+    <row r="77" ht="15" customHeight="1" s="70">
       <c r="A77" s="12" t="inlineStr">
         <is>
           <t>Faraday constant</t>
@@ -2749,7 +3391,7 @@
           <t>C/mol</t>
         </is>
       </c>
-      <c r="D77" s="67" t="n">
+      <c r="D77" s="49" t="n">
         <v>96485.33212000001</v>
       </c>
       <c r="E77" s="23" t="inlineStr">
@@ -2758,7 +3400,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="59">
+    <row r="78" ht="15" customHeight="1" s="70">
       <c r="A78" s="12" t="inlineStr">
         <is>
           <t>Electrons per H₂</t>
@@ -2783,7 +3425,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="59">
+    <row r="79" ht="15" customHeight="1" s="70">
       <c r="A79" s="12" t="inlineStr">
         <is>
           <t>Electrons per O₂</t>
@@ -2808,7 +3450,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="59">
+    <row r="80" ht="15" customHeight="1" s="70">
       <c r="A80" s="12" t="inlineStr">
         <is>
           <t>Faradaic efficiency – H₂ at cathode (HER share)</t>
@@ -2833,7 +3475,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="59">
+    <row r="81" ht="15" customHeight="1" s="70">
       <c r="A81" s="12" t="inlineStr">
         <is>
           <t>Electrolysis current (Gerrit's Law)</t>
@@ -2849,7 +3491,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D81" s="65">
+      <c r="D81" s="43">
         <f>(gerrit_slope*intensity+gerrit_int)/1000</f>
         <v/>
       </c>
@@ -2859,7 +3501,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="59">
+    <row r="82" ht="15" customHeight="1" s="70">
       <c r="A82" s="12" t="inlineStr">
         <is>
           <t>Gerrit's Law validity flag</t>
@@ -2885,7 +3527,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="59">
+    <row r="83" ht="15" customHeight="1" s="70">
       <c r="A83" s="12" t="inlineStr">
         <is>
           <t>H₂ generation rate</t>
@@ -2901,7 +3543,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D83" s="68">
+      <c r="D83" s="28">
         <f>I_app*etaF/(z_e_H2*F_const)*3600</f>
         <v/>
       </c>
@@ -2911,7 +3553,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="59">
+    <row r="84" ht="15" customHeight="1" s="70">
       <c r="A84" s="12" t="inlineStr">
         <is>
           <t>O₂ generation rate (anodic, gross)</t>
@@ -2927,7 +3569,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D84" s="68">
+      <c r="D84" s="28">
         <f>I_app*etaF_OER/(z_e_O2*F_const)*3600</f>
         <v/>
       </c>
@@ -2953,7 +3595,7 @@
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D85" s="68">
+      <c r="D85" s="28">
         <f>rH2_gen/60*R_gas*T_K/P_atm*1000000</f>
         <v/>
       </c>
@@ -2963,7 +3605,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="59">
+    <row r="86" ht="15" customHeight="1" s="70">
       <c r="A86" s="12" t="inlineStr">
         <is>
           <t>O₂ generation rate (volumetric)</t>
@@ -2979,7 +3621,7 @@
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D86" s="68">
+      <c r="D86" s="28">
         <f>rO2_gen/60*R_gas*T_K/P_atm*1000000</f>
         <v/>
       </c>
@@ -2989,7 +3631,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="59">
+    <row r="87" ht="15" customHeight="1" s="70">
       <c r="A87" s="12" t="inlineStr">
         <is>
           <t>Total gas generation rate</t>
@@ -3005,7 +3647,7 @@
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D87" s="68">
+      <c r="D87" s="28">
         <f>V_H2_gen+V_O2_gen</f>
         <v/>
       </c>
@@ -3015,8 +3657,8 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="59"/>
-    <row r="89" ht="15" customHeight="1" s="59">
+    <row r="88" ht="15" customHeight="1" s="70"/>
+    <row r="89" ht="15" customHeight="1" s="70">
       <c r="A89" s="9" t="inlineStr">
         <is>
           <t>3.  BIOLOGY  (cells consume 100% of evolved H₂; O₂ &amp; CO₂ pro-rata)</t>
@@ -3031,7 +3673,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" s="59">
+    <row r="90" ht="15" customHeight="1" s="70">
       <c r="A90" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
@@ -3058,7 +3700,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1" s="59">
+    <row r="91" ht="15" customHeight="1" s="70">
       <c r="A91" s="12" t="inlineStr">
         <is>
           <t>Gas requirement ratio - H₂</t>
@@ -3083,7 +3725,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="15" customHeight="1" s="59">
+    <row r="92" ht="15" customHeight="1" s="70">
       <c r="A92" s="12" t="inlineStr">
         <is>
           <t>Gas requirement ratio - O₂</t>
@@ -3108,7 +3750,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1" s="59">
+    <row r="93" ht="15" customHeight="1" s="70">
       <c r="A93" s="12" t="inlineStr">
         <is>
           <t>Gas requirement ratio - CO₂</t>
@@ -3133,7 +3775,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="15" customHeight="1" s="59">
+    <row r="94" ht="15" customHeight="1" s="70">
       <c r="A94" s="12" t="inlineStr">
         <is>
           <t>H₂ consumed</t>
@@ -3149,7 +3791,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D94" s="68">
+      <c r="D94" s="28">
         <f>rH2_gen</f>
         <v/>
       </c>
@@ -3175,7 +3817,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D95" s="68">
+      <c r="D95" s="28">
         <f>H2_cons*bio_O2/bio_H2</f>
         <v/>
       </c>
@@ -3185,7 +3827,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1" s="59">
+    <row r="96" ht="15" customHeight="1" s="70">
       <c r="A96" s="12" t="inlineStr">
         <is>
           <t>CO₂ consumed (carbon fixation)</t>
@@ -3201,7 +3843,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D96" s="68">
+      <c r="D96" s="28">
         <f>H2_cons*bio_CO2/bio_H2</f>
         <v/>
       </c>
@@ -3211,7 +3853,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="15" customHeight="1" s="59">
+    <row r="97" ht="15" customHeight="1" s="70">
       <c r="A97" s="22" t="inlineStr">
         <is>
           <t>EXCESS O₂ to remove</t>
@@ -3227,7 +3869,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D97" s="68">
+      <c r="D97" s="28">
         <f>O2_net_gen-O2_cons</f>
         <v/>
       </c>
@@ -3237,8 +3879,8 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="15" customHeight="1" s="59"/>
-    <row r="99" ht="15" customHeight="1" s="59">
+    <row r="98" ht="15" customHeight="1" s="70"/>
+    <row r="99" ht="15" customHeight="1" s="70">
       <c r="A99" s="9" t="inlineStr">
         <is>
           <t>4.  O₂ CONSTRAINT  (growth ceiling; cathodic competition is the real driver)</t>
@@ -3249,7 +3891,7 @@
       <c r="D99" s="10" t="n"/>
       <c r="E99" s="10" t="n"/>
     </row>
-    <row r="100" ht="15" customHeight="1" s="59">
+    <row r="100" ht="15" customHeight="1" s="70">
       <c r="A100" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
@@ -3276,7 +3918,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="59">
+    <row r="101" ht="15" customHeight="1" s="70">
       <c r="A101" s="12" t="inlineStr">
         <is>
           <t>Temperature</t>
@@ -3292,7 +3934,7 @@
           <t>°C</t>
         </is>
       </c>
-      <c r="D101" s="60" t="n">
+      <c r="D101" s="37" t="n">
         <v>30</v>
       </c>
       <c r="E101" s="15" t="inlineStr">
@@ -3301,7 +3943,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="15" customHeight="1" s="59">
+    <row r="102" ht="15" customHeight="1" s="70">
       <c r="A102" s="12" t="inlineStr">
         <is>
           <t>Temperature (absolute)</t>
@@ -3327,7 +3969,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="15" customHeight="1" s="59">
+    <row r="103" ht="15" customHeight="1" s="70">
       <c r="A103" s="12" t="inlineStr">
         <is>
           <t>Surface pressure</t>
@@ -3352,7 +3994,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="15" customHeight="1" s="59">
+    <row r="104" ht="15" customHeight="1" s="70">
       <c r="A104" s="12" t="inlineStr">
         <is>
           <t>Standard atmosphere (atm-&gt;Pa)</t>
@@ -3377,7 +4019,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="15" customHeight="1" s="59">
+    <row r="105" ht="15" customHeight="1" s="70">
       <c r="A105" s="12" t="inlineStr">
         <is>
           <t>Henry solubility O₂ (ref, 298.15 K)</t>
@@ -3402,7 +4044,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="15" customHeight="1" s="59">
+    <row r="106" ht="15" customHeight="1" s="70">
       <c r="A106" s="12" t="inlineStr">
         <is>
           <t>Henry T-dependence O₂</t>
@@ -3427,7 +4069,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="15" customHeight="1" s="59">
+    <row r="107" ht="15" customHeight="1" s="70">
       <c r="A107" s="12" t="inlineStr">
         <is>
           <t>Reference temperature</t>
@@ -3452,7 +4094,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="15" customHeight="1" s="59">
+    <row r="108" ht="15" customHeight="1" s="70">
       <c r="A108" s="12" t="inlineStr">
         <is>
           <t>Henry solubility O₂ at T</t>
@@ -3478,7 +4120,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="15" customHeight="1" s="59">
+    <row r="109" ht="15" customHeight="1" s="70">
       <c r="A109" s="12" t="inlineStr">
         <is>
           <t>O₂ growth-inhibition ceiling (gas)</t>
@@ -3503,7 +4145,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="19.5" customHeight="1" s="59">
+    <row r="110" ht="19.5" customHeight="1" s="70">
       <c r="A110" s="12" t="n"/>
       <c r="C110" s="14" t="inlineStr">
         <is>
@@ -3529,7 +4171,7 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D111" s="61">
+      <c r="D111" s="39">
         <f>O2_ceil_atm*Pa_per_atm</f>
         <v/>
       </c>
@@ -3539,7 +4181,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="15" customHeight="1" s="59">
+    <row r="112" ht="15" customHeight="1" s="70">
       <c r="A112" s="12" t="inlineStr">
         <is>
           <t>Dissolved-O₂ ceiling</t>
@@ -3555,7 +4197,7 @@
           <t>mol/m³</t>
         </is>
       </c>
-      <c r="D112" s="65">
+      <c r="D112" s="43">
         <f>H_O2_T*O2_ceil_Pa</f>
         <v/>
       </c>
@@ -3565,7 +4207,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="15" customHeight="1" s="59">
+    <row r="113" ht="15" customHeight="1" s="70">
       <c r="A113" s="22" t="inlineStr">
         <is>
           <t>Dissolved-O₂ ceiling</t>
@@ -3581,7 +4223,7 @@
           <t>µM</t>
         </is>
       </c>
-      <c r="D113" s="61">
+      <c r="D113" s="39">
         <f>O2_ceil_C*1000</f>
         <v/>
       </c>
@@ -3591,8 +4233,8 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="15" customHeight="1" s="59"/>
-    <row r="115" ht="15" customHeight="1" s="59">
+    <row r="114" ht="15" customHeight="1" s="70"/>
+    <row r="115" ht="15" customHeight="1" s="70">
       <c r="A115" s="9" t="inlineStr">
         <is>
           <t>5.  CO₂ DOSING  (SodaStream + regulator + solenoid + needle valve)</t>
@@ -3603,7 +4245,7 @@
       <c r="D115" s="10" t="n"/>
       <c r="E115" s="10" t="n"/>
     </row>
-    <row r="116" ht="15" customHeight="1" s="59">
+    <row r="116" ht="15" customHeight="1" s="70">
       <c r="A116" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
@@ -3630,7 +4272,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="15" customHeight="1" s="59">
+    <row r="117" ht="15" customHeight="1" s="70">
       <c r="A117" s="12" t="inlineStr">
         <is>
           <t>CO₂ volumetric flow rate</t>
@@ -3646,7 +4288,7 @@
           <t>mL/min</t>
         </is>
       </c>
-      <c r="D117" s="60" t="n">
+      <c r="D117" s="37" t="n">
         <v>10</v>
       </c>
       <c r="E117" s="15" t="inlineStr">
@@ -3655,7 +4297,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="15" customHeight="1" s="59">
+    <row r="118" ht="15" customHeight="1" s="70">
       <c r="A118" s="12" t="inlineStr">
         <is>
           <t>Sparge duration per pulse</t>
@@ -3681,7 +4323,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1" s="59">
+    <row r="119" ht="15" customHeight="1" s="70">
       <c r="A119" s="12" t="inlineStr">
         <is>
           <t>Sparge interval</t>
@@ -3707,7 +4349,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1" s="59">
+    <row r="120" ht="15" customHeight="1" s="70">
       <c r="A120" s="12" t="inlineStr">
         <is>
           <t>Min reliable pulse (solenoid floor)</t>
@@ -3732,7 +4374,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="15" customHeight="1" s="59">
+    <row r="121" ht="15" customHeight="1" s="70">
       <c r="A121" s="12" t="inlineStr">
         <is>
           <t>Ideal gas constant</t>
@@ -3748,7 +4390,7 @@
           <t>J/mol/K</t>
         </is>
       </c>
-      <c r="D121" s="69" t="n">
+      <c r="D121" s="53" t="n">
         <v>8.314462618</v>
       </c>
       <c r="E121" s="23" t="inlineStr">
@@ -3757,7 +4399,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="15" customHeight="1" s="59">
+    <row r="122" ht="15" customHeight="1" s="70">
       <c r="A122" s="12" t="inlineStr">
         <is>
           <t>Molar mass CO₂</t>
@@ -3773,7 +4415,7 @@
           <t>g/mol</t>
         </is>
       </c>
-      <c r="D122" s="70" t="n">
+      <c r="D122" s="54" t="n">
         <v>44.0095</v>
       </c>
       <c r="E122" s="23" t="inlineStr">
@@ -3782,7 +4424,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="15" customHeight="1" s="59">
+    <row r="123" ht="15" customHeight="1" s="70">
       <c r="A123" s="12" t="inlineStr">
         <is>
           <t>CO₂ molar flow during sparge</t>
@@ -3808,7 +4450,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="15" customHeight="1" s="59">
+    <row r="124" ht="15" customHeight="1" s="70">
       <c r="A124" s="12" t="inlineStr">
         <is>
           <t>CO₂ per pulse</t>
@@ -3834,7 +4476,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="15" customHeight="1" s="59">
+    <row r="125" ht="15" customHeight="1" s="70">
       <c r="A125" s="12" t="inlineStr">
         <is>
           <t>Pulses per hour</t>
@@ -3860,7 +4502,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="15" customHeight="1" s="59">
+    <row r="126" ht="15" customHeight="1" s="70">
       <c r="A126" s="12" t="inlineStr">
         <is>
           <t>Pulses per day</t>
@@ -3876,7 +4518,7 @@
           <t>1/d</t>
         </is>
       </c>
-      <c r="D126" s="61">
+      <c r="D126" s="39">
         <f>pulses_h*24</f>
         <v/>
       </c>
@@ -3898,7 +4540,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D127" s="68">
+      <c r="D127" s="28">
         <f>CO2_pulse*pulses_h</f>
         <v/>
       </c>
@@ -3908,7 +4550,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="15" customHeight="1" s="59">
+    <row r="128" ht="15" customHeight="1" s="70">
       <c r="A128" s="22" t="inlineStr">
         <is>
           <t>CO₂ supply : carbon demand</t>
@@ -3934,7 +4576,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="15" customHeight="1" s="59">
+    <row r="129" ht="15" customHeight="1" s="70">
       <c r="A129" s="22" t="inlineStr">
         <is>
           <t>Sparge duty cycle</t>
@@ -3950,7 +4592,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D129" s="65">
+      <c r="D129" s="43">
         <f>spg_dur/(spg_int*60)</f>
         <v/>
       </c>
@@ -3960,14 +4602,14 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="15" customHeight="1" s="59">
+    <row r="130" ht="15" customHeight="1" s="70">
       <c r="E130" t="inlineStr">
         <is>
           <t>https://iapws.org/documents/release/Surf-H2O</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="15" customHeight="1" s="59">
+    <row r="131" ht="15" customHeight="1" s="70">
       <c r="A131" s="9" t="inlineStr">
         <is>
           <t>6.  CO₂ BUBBLE SIZE  (orifice or sinter)</t>
@@ -3982,7 +4624,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="15" customHeight="1" s="59">
+    <row r="132" ht="15" customHeight="1" s="70">
       <c r="A132" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
@@ -4009,7 +4651,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="15" customHeight="1" s="59">
+    <row r="133" ht="15" customHeight="1" s="70">
       <c r="A133" s="12" t="inlineStr">
         <is>
           <t>Surface tension (water, T)</t>
@@ -4025,7 +4667,7 @@
           <t>N/m</t>
         </is>
       </c>
-      <c r="D133" s="70" t="n">
+      <c r="D133" s="54" t="n">
         <v>0.0712</v>
       </c>
       <c r="E133" s="16" t="inlineStr">
@@ -4034,7 +4676,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="15" customHeight="1" s="59">
+    <row r="134" ht="15" customHeight="1" s="70">
       <c r="A134" s="12" t="inlineStr">
         <is>
           <t>Liquid density (water, T)</t>
@@ -4059,7 +4701,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="15" customHeight="1" s="59">
+    <row r="135" ht="15" customHeight="1" s="70">
       <c r="A135" s="12" t="inlineStr">
         <is>
           <t>Gravitational acceleration</t>
@@ -4075,7 +4717,7 @@
           <t>m/s²</t>
         </is>
       </c>
-      <c r="D135" s="67" t="n">
+      <c r="D135" s="49" t="n">
         <v>9.806649999999999</v>
       </c>
       <c r="E135" s="23" t="inlineStr">
@@ -4084,7 +4726,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="15" customHeight="1" s="59">
+    <row r="136" ht="15" customHeight="1" s="70">
       <c r="A136" s="12" t="inlineStr">
         <is>
           <t>O₂ diffusivity in water (T)</t>
@@ -4109,7 +4751,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="15" customHeight="1" s="59">
+    <row r="137" ht="15" customHeight="1" s="70">
       <c r="A137" s="12" t="inlineStr">
         <is>
           <t>Pore size - grade 0</t>
@@ -4134,7 +4776,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="15" customHeight="1" s="59">
+    <row r="138" ht="15" customHeight="1" s="70">
       <c r="A138" s="12" t="inlineStr">
         <is>
           <t>Pore size - grade 1</t>
@@ -4159,7 +4801,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="15" customHeight="1" s="59">
+    <row r="139" ht="15" customHeight="1" s="70">
       <c r="A139" s="12" t="inlineStr">
         <is>
           <t>Pore size - grade 2</t>
@@ -4184,7 +4826,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="15" customHeight="1" s="59">
+    <row r="140" ht="15" customHeight="1" s="70">
       <c r="A140" s="12" t="inlineStr">
         <is>
           <t>Pore size - grade 3</t>
@@ -4209,7 +4851,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="15" customHeight="1" s="59">
+    <row r="141" ht="15" customHeight="1" s="70">
       <c r="A141" s="12" t="inlineStr">
         <is>
           <t>Pore size - grade 4</t>
@@ -4234,7 +4876,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="15" customHeight="1" s="59">
+    <row r="142" ht="15" customHeight="1" s="70">
       <c r="A142" s="12" t="inlineStr">
         <is>
           <t>Pore size - grade 5</t>
@@ -4250,7 +4892,7 @@
           <t>µm</t>
         </is>
       </c>
-      <c r="D142" s="66" t="n">
+      <c r="D142" s="47" t="n">
         <v>1.3</v>
       </c>
       <c r="E142" s="16" t="inlineStr">
@@ -4259,7 +4901,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="15" customHeight="1" s="59">
+    <row r="143" ht="15" customHeight="1" s="70">
       <c r="A143" s="12" t="inlineStr">
         <is>
           <t>Selected sinter pore diameter</t>
@@ -4285,7 +4927,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="15" customHeight="1" s="59">
+    <row r="144" ht="15" customHeight="1" s="70">
       <c r="A144" s="12" t="inlineStr">
         <is>
           <t>Tube orifice diameter</t>
@@ -4311,7 +4953,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="15" customHeight="1" s="59">
+    <row r="145" ht="15" customHeight="1" s="70">
       <c r="A145" s="12" t="inlineStr">
         <is>
           <t>Effective orifice/pore diameter</t>
@@ -4337,7 +4979,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="15" customHeight="1" s="59">
+    <row r="146" ht="15" customHeight="1" s="70">
       <c r="A146" s="22" t="inlineStr">
         <is>
           <t>Bubble detachment diameter</t>
@@ -4353,7 +4995,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D146" s="68">
+      <c r="D146" s="28">
         <f>(6*d_orifice*sigma/(rho_L*g_const))^(1/3)</f>
         <v/>
       </c>
@@ -4363,7 +5005,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="15" customHeight="1" s="59">
+    <row r="147" ht="15" customHeight="1" s="70">
       <c r="A147" s="22" t="inlineStr">
         <is>
           <t>Bubble diameter (display)</t>
@@ -4379,7 +5021,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D147" s="64">
+      <c r="D147" s="42">
         <f>d_bubble*1000</f>
         <v/>
       </c>
@@ -4410,7 +5052,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="15" customHeight="1" s="59">
+    <row r="149" ht="15" customHeight="1" s="70">
       <c r="A149" s="12" t="inlineStr">
         <is>
           <t>Mendelson coefficient b</t>
@@ -4426,7 +5068,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D149" s="71" t="n">
+      <c r="D149" s="57" t="n">
         <v>0.505</v>
       </c>
       <c r="E149" s="26" t="inlineStr">
@@ -4435,7 +5077,7 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="15" customHeight="1" s="59">
+    <row r="150" ht="15" customHeight="1" s="70">
       <c r="A150" s="12" t="inlineStr">
         <is>
           <t>Bubble rise velocity</t>
@@ -4451,7 +5093,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D150" s="65">
+      <c r="D150" s="43">
         <f>SQRT(mend_a*sigma/(rho_L*d_bubble)+mend_b*g_const*d_bubble)</f>
         <v/>
       </c>
@@ -4461,8 +5103,8 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="15" customHeight="1" s="59"/>
-    <row r="152" ht="15" customHeight="1" s="59">
+    <row r="151" ht="15" customHeight="1" s="70"/>
+    <row r="152" ht="15" customHeight="1" s="70">
       <c r="A152" s="9" t="inlineStr">
         <is>
           <t>7.  O₂ STRIPPING CAPACITY  (kLa estimate - low confidence)</t>
@@ -4473,7 +5115,7 @@
       <c r="D152" s="10" t="n"/>
       <c r="E152" s="10" t="n"/>
     </row>
-    <row r="153" ht="15" customHeight="1" s="59">
+    <row r="153" ht="15" customHeight="1" s="70">
       <c r="A153" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
@@ -4500,7 +5142,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="15" customHeight="1" s="59">
+    <row r="154" ht="15" customHeight="1" s="70">
       <c r="A154" s="12" t="inlineStr">
         <is>
           <t>Superficial gas velocity (sparge on)</t>
@@ -4516,7 +5158,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D154" s="68">
+      <c r="D154" s="28">
         <f>(Q_CO2/1000000/60)/(A_x/1000000)</f>
         <v/>
       </c>
@@ -4526,7 +5168,7 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="15" customHeight="1" s="59">
+    <row r="155" ht="15" customHeight="1" s="70">
       <c r="A155" s="12" t="inlineStr">
         <is>
           <t>Gas holdup (sparge on)</t>
@@ -4542,7 +5184,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D155" s="68">
+      <c r="D155" s="28">
         <f>u_sg/u_rise</f>
         <v/>
       </c>
@@ -4552,7 +5194,7 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="15" customHeight="1" s="59">
+    <row r="156" ht="15" customHeight="1" s="70">
       <c r="A156" s="12" t="inlineStr">
         <is>
           <t>Interfacial area for transfer</t>
@@ -4578,7 +5220,7 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="15" customHeight="1" s="59">
+    <row r="157" ht="15" customHeight="1" s="70">
       <c r="A157" s="12" t="inlineStr">
         <is>
           <t>Bubble-liquid contact time</t>
@@ -4594,7 +5236,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D157" s="65">
+      <c r="D157" s="43">
         <f>d_bubble/u_rise</f>
         <v/>
       </c>
@@ -4604,7 +5246,7 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="15" customHeight="1" s="59">
+    <row r="158" ht="15" customHeight="1" s="70">
       <c r="A158" s="12" t="inlineStr">
         <is>
           <t>Liquid-film coefficient kL</t>
@@ -4620,7 +5262,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D158" s="68">
+      <c r="D158" s="28">
         <f>2*SQRT(D_O2/(PI()*t_contact))</f>
         <v/>
       </c>
@@ -4630,7 +5272,7 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="15" customHeight="1" s="59">
+    <row r="159" ht="15" customHeight="1" s="70">
       <c r="A159" s="22" t="inlineStr">
         <is>
           <t>kLa during sparge</t>
@@ -4646,7 +5288,7 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D159" s="68">
+      <c r="D159" s="28">
         <f>kL*a_int</f>
         <v/>
       </c>
@@ -4656,7 +5298,7 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="15" customHeight="1" s="59">
+    <row r="160" ht="15" customHeight="1" s="70">
       <c r="A160" s="12" t="inlineStr">
         <is>
           <t>kLa time-averaged</t>
@@ -4682,7 +5324,7 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="15" customHeight="1" s="59">
+    <row r="161" ht="15" customHeight="1" s="70">
       <c r="A161" s="12" t="inlineStr">
         <is>
           <t>O₂ strip rate at ceiling (sparge on)</t>
@@ -4698,7 +5340,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D161" s="68">
+      <c r="D161" s="28">
         <f>IF(d_bubble&lt;0.001,0,kLa_sparge*(V_charge/1000000)*O2_ceil_C*3600)</f>
         <v/>
       </c>
@@ -4724,7 +5366,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D162" s="68">
+      <c r="D162" s="28">
         <f>strip_sparge*duty</f>
         <v/>
       </c>
@@ -4734,7 +5376,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="15" customHeight="1" s="59">
+    <row r="163" ht="15" customHeight="1" s="70">
       <c r="A163" s="22" t="inlineStr">
         <is>
           <t>Strip capacity : excess-O₂</t>
@@ -4750,7 +5392,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D163" s="64">
+      <c r="D163" s="42">
         <f>IF(O2_excess&gt;0,strip_avg/O2_excess,NA())</f>
         <v/>
       </c>
@@ -4760,7 +5402,7 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="15" customHeight="1" s="59">
+    <row r="164" ht="15" customHeight="1" s="70">
       <c r="A164" s="12" t="inlineStr">
         <is>
           <t>Required time-avg kLa</t>
@@ -4776,7 +5418,7 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D164" s="68">
+      <c r="D164" s="28">
         <f>IF(O2_excess&gt;0,O2_excess/3600/((V_charge/1000000)*O2_ceil_C),NA())</f>
         <v/>
       </c>
@@ -4786,8 +5428,8 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="19.5" customHeight="1" s="59"/>
-    <row r="166" ht="15" customHeight="1" s="59">
+    <row r="165" ht="19.5" customHeight="1" s="70"/>
+    <row r="166" ht="15" customHeight="1" s="70">
       <c r="A166" s="9" t="inlineStr">
         <is>
           <t>8.  MEDIA CARRYOVER CEILING  (vent-filter clog risk)</t>
@@ -4825,7 +5467,7 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="15" customHeight="1" s="59">
+    <row r="168" ht="15" customHeight="1" s="70">
       <c r="A168" s="12" t="inlineStr">
         <is>
           <t>Entrainment velocity ceiling (rule of thumb)</t>
@@ -4841,7 +5483,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D168" s="62" t="n">
+      <c r="D168" s="40" t="n">
         <v>0.05</v>
       </c>
       <c r="E168" s="26" t="inlineStr">
@@ -4850,7 +5492,7 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="15" customHeight="1" s="59">
+    <row r="169" ht="15" customHeight="1" s="70">
       <c r="A169" s="22" t="inlineStr">
         <is>
           <t>Carryover flag</t>
@@ -4876,8 +5518,8 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="15" customHeight="1" s="59"/>
-    <row r="171" ht="15" customHeight="1" s="59">
+    <row r="170" ht="15" customHeight="1" s="70"/>
+    <row r="171" ht="15" customHeight="1" s="70">
       <c r="A171" s="9" t="inlineStr">
         <is>
           <t>9.  DOSING-SCHEDULE FEASIBILITY</t>
@@ -4888,7 +5530,7 @@
       <c r="D171" s="10" t="n"/>
       <c r="E171" s="10" t="n"/>
     </row>
-    <row r="172" ht="15" customHeight="1" s="59">
+    <row r="172" ht="15" customHeight="1" s="70">
       <c r="A172" s="11" t="inlineStr">
         <is>
           <t>Parameter</t>
@@ -4915,7 +5557,7 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="15" customHeight="1" s="59">
+    <row r="173" ht="15" customHeight="1" s="70">
       <c r="A173" s="12" t="inlineStr">
         <is>
           <t>O₂ accumulated per interval</t>
@@ -4941,7 +5583,7 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="15" customHeight="1" s="59">
+    <row r="174" ht="15" customHeight="1" s="70">
       <c r="A174" s="12" t="inlineStr">
         <is>
           <t>O₂ removable per pulse</t>
@@ -4967,7 +5609,7 @@
         </is>
       </c>
     </row>
-    <row r="175">
+    <row r="175" ht="24" customHeight="1" s="70">
       <c r="A175" s="22" t="inlineStr">
         <is>
           <t>Per-pulse balance</t>
@@ -4983,7 +5625,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D175" s="64">
+      <c r="D175" s="42">
         <f>IF(O2_accum&gt;0,O2_strip_pulse/O2_accum,NA())</f>
         <v/>
       </c>
@@ -5026,7 +5668,7 @@
       <c r="D177" s="51" t="n"/>
       <c r="E177" s="26" t="n"/>
     </row>
-    <row r="179" ht="24" customHeight="1" s="59">
+    <row r="179" ht="24" customHeight="1" s="70">
       <c r="A179" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">10.  FARADAIC O₂ BALANCE &amp; BUBBLE-REGIME CHECK </t>
@@ -5064,7 +5706,7 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="24" customHeight="1" s="59">
+    <row r="181" ht="24" customHeight="1" s="70">
       <c r="A181" s="12" t="inlineStr">
         <is>
           <t>Sparge tube in-vial length</t>
@@ -5080,7 +5722,7 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D181" s="68">
+      <c r="D181" s="28">
         <f>D_int-spg_tip_h</f>
         <v/>
       </c>
@@ -5090,7 +5732,7 @@
         </is>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="24" customHeight="1" s="70">
       <c r="A182" s="12" t="inlineStr">
         <is>
           <t>Anodic O₂ faradaic efficiency</t>
@@ -5115,7 +5757,7 @@
         </is>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="24" customHeight="1" s="70">
       <c r="A183" s="12" t="inlineStr">
         <is>
           <t>Electrons per O₂ reduced (cathode)</t>
@@ -5156,7 +5798,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D184" s="68">
+      <c r="D184" s="28">
         <f>I_app*(1-etaF)/(z_e_ORR*F_const)*3600</f>
         <v/>
       </c>
@@ -5182,7 +5824,7 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D185" s="68">
+      <c r="D185" s="28">
         <f>rO2_gen-O2_cathode_ORR</f>
         <v/>
       </c>
@@ -5208,7 +5850,7 @@
           <t>kg/m³</t>
         </is>
       </c>
-      <c r="D186" s="68">
+      <c r="D186" s="28">
         <f>P_atm*(M_CO2/1000)/(R_gas*T_K)</f>
         <v/>
       </c>
@@ -5259,7 +5901,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D188" s="68">
+      <c r="D188" s="28">
         <f>(Q_CO2/1000000/60)/(n_pores_active*(PI()/4*d_orifice^2))</f>
         <v/>
       </c>
@@ -5269,7 +5911,7 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="36" customHeight="1" s="59">
+    <row r="189" ht="36" customHeight="1" s="70">
       <c r="A189" s="12" t="inlineStr">
         <is>
           <t>Orifice Weber number</t>
@@ -5285,7 +5927,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D189" s="68">
+      <c r="D189" s="28">
         <f>rho_CO2*v_orifice^2*d_orifice/sigma</f>
         <v/>
       </c>
@@ -5295,7 +5937,7 @@
         </is>
       </c>
     </row>
-    <row r="190">
+    <row r="190" ht="24" customHeight="1" s="70">
       <c r="A190" s="12" t="inlineStr">
         <is>
           <t>Bubble-formation regime</t>
@@ -5311,7 +5953,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D190" s="68">
+      <c r="D190" s="28">
         <f>IF(d_bubble&lt;0.001,"Sinter OOR – add fine-bubble model",IF(We_orifice&lt;2,"Static","Dynamic"))</f>
         <v/>
       </c>
@@ -5337,7 +5979,7 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D191" s="68">
+      <c r="D191" s="28">
         <f>O2_ceil_C*(V_charge/1000000)/O2_excess*60</f>
         <v/>
       </c>
@@ -5363,7 +6005,7 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D192" s="68">
+      <c r="D192" s="28">
         <f>IF(O2_excess-strip_avg&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_excess-strip_avg)*60,9999)</f>
         <v/>
       </c>
@@ -5423,7 +6065,7 @@
           <t>1/min</t>
         </is>
       </c>
-      <c r="D196" s="72" t="n">
+      <c r="D196" s="58" t="n">
         <v>500</v>
       </c>
       <c r="E196" s="31" t="inlineStr">
@@ -5448,10 +6090,10 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D197" s="72" t="n">
+      <c r="D197" s="58" t="n">
         <v>12</v>
       </c>
-      <c r="E197" s="73" t="inlineStr">
+      <c r="E197" s="59" t="inlineStr">
         <is>
           <t>Magnetic stir bar. Pioreactor max 20 mm; confirm the supplied bar's length. Input.</t>
         </is>
@@ -5473,7 +6115,7 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D198" s="68">
+      <c r="D198" s="28">
         <f>PI()*(stir_len/1000)*stir_rpm/60</f>
         <v/>
       </c>
@@ -5499,11 +6141,11 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D199" s="68">
+      <c r="D199" s="28">
         <f>tip_speed/(vial_ID/1000)</f>
         <v/>
       </c>
-      <c r="E199" s="73" t="inlineStr">
+      <c r="E199" s="59" t="inlineStr">
         <is>
           <t>Surface renewal ≈ tip speed / vial ID. Coarse proxy.</t>
         </is>
@@ -5525,11 +6167,11 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D200" s="68">
+      <c r="D200" s="28">
         <f>2*SQRT(D_O2*s_renew/PI())</f>
         <v/>
       </c>
-      <c r="E200" s="73" t="inlineStr">
+      <c r="E200" s="59" t="inlineStr">
         <is>
           <t>Danckwerts surface-renewal estimate — coarse; measure by gassing-out (§15).</t>
         </is>
@@ -5551,7 +6193,7 @@
           <t>1/m</t>
         </is>
       </c>
-      <c r="D201" s="68">
+      <c r="D201" s="28">
         <f>interface_A/V_charge</f>
         <v/>
       </c>
@@ -5577,11 +6219,11 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D202" s="68">
+      <c r="D202" s="28">
         <f>kL_surf*a_surf</f>
         <v/>
       </c>
-      <c r="E202" s="73" t="inlineStr">
+      <c r="E202" s="59" t="inlineStr">
         <is>
           <t>kL_surf × a_surf.</t>
         </is>
@@ -5603,11 +6245,11 @@
           <t>mol/h</t>
         </is>
       </c>
-      <c r="D203" s="68">
+      <c r="D203" s="28">
         <f>kLa_surf_used*(V_charge/1000000)*O2_ceil_C*3600</f>
         <v/>
       </c>
-      <c r="E203" s="73" t="inlineStr">
+      <c r="E203" s="59" t="inlineStr">
         <is>
           <t>O₂ removed across the stirred surface at ceiling driving force, headspace ~O₂-free. Best case.</t>
         </is>
@@ -5629,11 +6271,11 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D204" s="68">
+      <c r="D204" s="28">
         <f>IF(O2_excess&gt;0,surf_strip/O2_excess,NA())</f>
         <v/>
       </c>
-      <c r="E204" s="73" t="inlineStr">
+      <c r="E204" s="59" t="inlineStr">
         <is>
           <t>Surface strip : surplus. Coarse (kL_surf). ≫ bubble path — the dominant O₂ route.</t>
         </is>
@@ -5655,7 +6297,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D205" s="68">
+      <c r="D205" s="28">
         <f>IF(CO2_supply&gt;0,O2_excess/CO2_supply,NA())</f>
         <v/>
       </c>
@@ -5681,7 +6323,7 @@
           <t>µM</t>
         </is>
       </c>
-      <c r="D206" s="68">
+      <c r="D206" s="28">
         <f>H_O2_T*y_O2_vent*P_atm*1000</f>
         <v/>
       </c>
@@ -5707,7 +6349,7 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D207" s="68">
+      <c r="D207" s="28">
         <f>headspace_V/(Q_CO2*duty)</f>
         <v/>
       </c>
@@ -5717,7 +6359,7 @@
         </is>
       </c>
     </row>
-    <row r="208">
+    <row r="208" ht="24" customHeight="1" s="70">
       <c r="A208" s="12" t="inlineStr">
         <is>
           <t>Combined O₂ removal : excess</t>
@@ -5733,11 +6375,11 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D208" s="68">
+      <c r="D208" s="28">
         <f>IF(O2_excess&gt;0,(strip_avg+surf_strip)/O2_excess,NA())</f>
         <v/>
       </c>
-      <c r="E208" s="73" t="inlineStr">
+      <c r="E208" s="59" t="inlineStr">
         <is>
           <t>Gas removal (bubble + surface) vs the steady-growth surplus O2_excess (which already nets the cathodic sink and biological uptake). &gt;=1 = ceiling held at steady growth.</t>
         </is>
@@ -5759,7 +6401,7 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D209" s="68">
+      <c r="D209" s="28">
         <f>O2_ceil_C*(V_charge/1000000)/O2_net_gen*60</f>
         <v/>
       </c>
@@ -5769,7 +6411,7 @@
         </is>
       </c>
     </row>
-    <row r="210">
+    <row r="210" ht="36" customHeight="1" s="70">
       <c r="A210" s="12" t="inlineStr">
         <is>
           <t>O₂ time-to-ceiling (with all removal)</t>
@@ -5785,11 +6427,11 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D210" s="68">
+      <c r="D210" s="28">
         <f>IF(O2_net_gen-strip_avg-surf_strip&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_net_gen-strip_avg-surf_strip)*60,9999)</f>
         <v/>
       </c>
-      <c r="E210" s="73" t="inlineStr">
+      <c r="E210" s="59" t="inlineStr">
         <is>
           <t>LAG-with-removal partner to t_O2_ceiling_lag: cells not yet consuming, so removal (bubble + surface) must offset the full net electrolytic O₂ (O2_net_gen, which already nets the cathodic sink), not the steady surplus. 9999 = removal holds the ceiling (no finite time).</t>
         </is>
@@ -5845,10 +6487,10 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D214" s="69" t="n">
+      <c r="D214" s="53" t="n">
         <v>0.00033</v>
       </c>
-      <c r="E214" s="74" t="inlineStr">
+      <c r="E214" s="60" t="inlineStr">
         <is>
           <t>Sander (2023) compilation; CO₂ ~25× more soluble than O₂.</t>
         </is>
@@ -5870,10 +6512,10 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D215" s="69" t="n">
+      <c r="D215" s="53" t="n">
         <v>2400</v>
       </c>
-      <c r="E215" s="74" t="inlineStr">
+      <c r="E215" s="60" t="inlineStr">
         <is>
           <t>Sander (2023): d ln(Hcp)/d(1/T) for CO₂.</t>
         </is>
@@ -5895,7 +6537,7 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D216" s="68">
+      <c r="D216" s="28">
         <f>H_CO2ref*EXP(H_CO2T*(1/T_K-1/T_ref))</f>
         <v/>
       </c>
@@ -5921,7 +6563,7 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D217" s="68">
+      <c r="D217" s="28">
         <f>P_atm</f>
         <v/>
       </c>
@@ -5947,7 +6589,7 @@
           <t>mol/m³</t>
         </is>
       </c>
-      <c r="D218" s="68">
+      <c r="D218" s="28">
         <f>H_CO2_T*p_CO2_sparge</f>
         <v/>
       </c>
@@ -5973,10 +6615,10 @@
           <t>µM</t>
         </is>
       </c>
-      <c r="D219" s="72" t="n">
+      <c r="D219" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="E219" s="73" t="inlineStr">
+      <c r="E219" s="59" t="inlineStr">
         <is>
           <t>RuBisCO Km(CO₂) ~ order 50 µM. Coarse — confirm.</t>
         </is>
@@ -5998,7 +6640,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="D220" s="68">
+      <c r="D220" s="28">
         <f>CO2_diss*1000/Km_CO2</f>
         <v/>
       </c>
@@ -6024,10 +6666,10 @@
           <t>mol/L</t>
         </is>
       </c>
-      <c r="D221" s="69" t="n">
+      <c r="D221" s="53" t="n">
         <v>4.45e-07</v>
       </c>
-      <c r="E221" s="74" t="inlineStr">
+      <c r="E221" s="60" t="inlineStr">
         <is>
           <t>CO₂(aq)+H₂O ⇌ H⁺+HCO₃⁻, pKa1 6.35 (25 °C).</t>
         </is>
@@ -6049,11 +6691,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D222" s="68">
+      <c r="D222" s="28">
         <f>-LOG10(SQRT(Ka1_carb*(CO2_diss/1000)))</f>
         <v/>
       </c>
-      <c r="E222" s="73" t="inlineStr">
+      <c r="E222" s="59" t="inlineStr">
         <is>
           <t>Unbuffered worst case (pure water + CO₂) — lower bound only; the Sydow phosphate medium holds pH near setpoint.</t>
         </is>
@@ -6109,10 +6751,10 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D226" s="69" t="n">
+      <c r="D226" s="53" t="n">
         <v>7.8e-06</v>
       </c>
-      <c r="E226" s="74" t="inlineStr">
+      <c r="E226" s="60" t="inlineStr">
         <is>
           <t>Sander (2023). H₂ ~1.7× less soluble than O₂.</t>
         </is>
@@ -6134,10 +6776,10 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D227" s="69" t="n">
+      <c r="D227" s="53" t="n">
         <v>500</v>
       </c>
-      <c r="E227" s="74" t="inlineStr">
+      <c r="E227" s="60" t="inlineStr">
         <is>
           <t>Sander (2023): d ln(Hcp)/d(1/T) for H₂ (weak T-dependence).</t>
         </is>
@@ -6159,7 +6801,7 @@
           <t>mol/m³/Pa</t>
         </is>
       </c>
-      <c r="D228" s="68">
+      <c r="D228" s="28">
         <f>H_H2ref*EXP(H_H2T*(1/T_K-1/T_ref))</f>
         <v/>
       </c>
@@ -6185,7 +6827,7 @@
           <t>mol/m³</t>
         </is>
       </c>
-      <c r="D229" s="68">
+      <c r="D229" s="28">
         <f>H_H2_T*P_atm</f>
         <v/>
       </c>
@@ -6195,7 +6837,7 @@
         </is>
       </c>
     </row>
-    <row r="230">
+    <row r="230" ht="24" customHeight="1" s="70">
       <c r="A230" s="12" t="inlineStr">
         <is>
           <t>Time to saturate dissolved H₂ (LAG)</t>
@@ -6211,7 +6853,7 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D230" s="68">
+      <c r="D230" s="28">
         <f>C_H2_sat*(V_charge/1000000)/rH2_gen*60</f>
         <v/>
       </c>
@@ -6237,17 +6879,17 @@
           <t>1/h</t>
         </is>
       </c>
-      <c r="D231" s="68">
+      <c r="D231" s="28">
         <f>rH2_gen/(V_charge/1000000)/C_H2_sat</f>
         <v/>
       </c>
-      <c r="E231" s="73" t="inlineStr">
+      <c r="E231" s="59" t="inlineStr">
         <is>
           <t>H₂ evolved ÷ saturable pool. ≫1 → cells must consume in near-real-time or it escapes.</t>
         </is>
       </c>
     </row>
-    <row r="232">
+    <row r="232" ht="24" customHeight="1" s="70">
       <c r="A232" s="12" t="inlineStr">
         <is>
           <t>H₂ headspace safety flag</t>
@@ -6263,7 +6905,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D232" s="68">
+      <c r="D232" s="28">
         <f>IF(H2_turnover&gt;1,"EXPLOSIVE","watch")</f>
         <v/>
       </c>
@@ -6323,7 +6965,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D236" s="72" t="inlineStr">
+      <c r="D236" s="58" t="inlineStr">
         <is>
           <t>Optimal</t>
         </is>
@@ -6350,7 +6992,7 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D237" s="72" t="n">
+      <c r="D237" s="58" t="n">
         <v>1</v>
       </c>
       <c r="E237" s="31" t="inlineStr">
@@ -6375,7 +7017,7 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D238" s="72" t="n">
+      <c r="D238" s="58" t="n">
         <v>1</v>
       </c>
       <c r="E238" s="31" t="inlineStr">
@@ -6400,7 +7042,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D239" s="72" t="n">
+      <c r="D239" s="58" t="n">
         <v>0.5</v>
       </c>
       <c r="E239" s="31" t="inlineStr">
@@ -6425,7 +7067,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D240" s="72" t="n">
+      <c r="D240" s="58" t="n">
         <v>2</v>
       </c>
       <c r="E240" s="31" t="inlineStr">
@@ -6450,7 +7092,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D241" s="68">
+      <c r="D241" s="28">
         <f>carbon_margin_min*CO2_cons/(nCO2_rate*3600)</f>
         <v/>
       </c>
@@ -6460,7 +7102,7 @@
         </is>
       </c>
     </row>
-    <row r="242">
+    <row r="242" ht="24" customHeight="1" s="70">
       <c r="A242" s="12" t="inlineStr">
         <is>
           <t>Duty floor — O₂ venting (lag)</t>
@@ -6476,7 +7118,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D242" s="68">
+      <c r="D242" s="28">
         <f>O2_net_gen/(target_DO_frac*(O2_ceil_Pa/P_atm))/(nCO2_rate*3600)</f>
         <v/>
       </c>
@@ -6502,7 +7144,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D243" s="68">
+      <c r="D243" s="28">
         <f>MAX(duty_carbon,duty_O2vent)</f>
         <v/>
       </c>
@@ -6528,7 +7170,7 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D244" s="68">
+      <c r="D244" s="28">
         <f>target_DO_frac*t_O2_ceiling_lag</f>
         <v/>
       </c>
@@ -6554,17 +7196,17 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D245" s="75">
+      <c r="D245" s="61">
         <f>pulse_floor</f>
         <v/>
       </c>
-      <c r="E245" s="76" t="inlineStr">
+      <c r="E245" s="62" t="inlineStr">
         <is>
           <t>ANSWER. Shortest reliable pulse → most frequent, smoothest DO, best OD-read windows.</t>
         </is>
       </c>
     </row>
-    <row r="246">
+    <row r="246" ht="24" customHeight="1" s="70">
       <c r="A246" s="12" t="inlineStr">
         <is>
           <t>► OPTIMAL sparge interval</t>
@@ -6580,11 +7222,11 @@
           <t>min</t>
         </is>
       </c>
-      <c r="D246" s="75">
+      <c r="D246" s="61">
         <f>MIN(spg_dur_opt/(60*duty_opt),spg_int_max)</f>
         <v/>
       </c>
-      <c r="E246" s="76" t="inlineStr">
+      <c r="E246" s="62" t="inlineStr">
         <is>
           <t>ANSWER. From optimal duty at the floor pulse, capped by the O₂-flush frequency limit. Set sched_mode=Optimal to apply.</t>
         </is>
@@ -6606,11 +7248,11 @@
           <t>s</t>
         </is>
       </c>
-      <c r="D247" s="68">
+      <c r="D247" s="28">
         <f>spg_int_opt*60</f>
         <v/>
       </c>
-      <c r="E247" s="76" t="inlineStr">
+      <c r="E247" s="62" t="inlineStr">
         <is>
           <t>Convenience: interval in seconds.</t>
         </is>
@@ -6632,7 +7274,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D248" s="68">
+      <c r="D248" s="28">
         <f>spg_dur_opt/(spg_int_opt*60)</f>
         <v/>
       </c>
@@ -6658,7 +7300,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D249" s="68">
+      <c r="D249" s="28">
         <f>IF(spg_int_opt&lt;spg_dur_opt/(60*duty_opt)-0.0001,"O2-FREQ",IF(duty_O2vent&gt;=duty_carbon,"O2-VENT","CARBON"))</f>
         <v/>
       </c>
@@ -6684,7 +7326,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D250" s="68">
+      <c r="D250" s="28">
         <f>IF(spg_int_opt*60-spg_dur_opt&gt;=5,"OK","TIGHT")</f>
         <v/>
       </c>
@@ -6694,7 +7336,7 @@
         </is>
       </c>
     </row>
-    <row r="251">
+    <row r="251" ht="36" customHeight="1" s="70">
       <c r="A251" s="12" t="inlineStr">
         <is>
           <t>ACCURACY LIMIT — no validated kinetics</t>
@@ -6710,11 +7352,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D251" s="68">
+      <c r="D251" s="28">
         <f>"see note →"</f>
         <v/>
       </c>
-      <c r="E251" s="73" t="inlineStr">
+      <c r="E251" s="59" t="inlineStr">
         <is>
           <t>Constraint-proxy optimiser, not a fitted growth model — no validated μ(O₂,pH,CO₂) or lag kinetics exist for this system. Gives the lag-minimising direction, not an exact optimum; bounded by etaF, surface kL and the unbuffered-pH simplification. Validate empirically.</t>
         </is>
@@ -6770,16 +7412,16 @@
           <t>1/h</t>
         </is>
       </c>
-      <c r="D255" s="72" t="n">
+      <c r="D255" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="E255" s="73" t="inlineStr">
+      <c r="E255" s="59" t="inlineStr">
         <is>
           <t>Measured surface kLa (gassing-out). 0 = use the §11 estimate. kLa = slope of −LN(1−DO/DO_sat) vs time.</t>
         </is>
       </c>
     </row>
-    <row r="256">
+    <row r="256" ht="24" customHeight="1" s="70">
       <c r="A256" s="12" t="inlineStr">
         <is>
           <t>Surface kLa used downstream</t>
@@ -6795,7 +7437,7 @@
           <t>1/s</t>
         </is>
       </c>
-      <c r="D256" s="68">
+      <c r="D256" s="28">
         <f>IF(kLa_meas&gt;0,kLa_meas/3600,kLa_surf)</f>
         <v/>
       </c>
@@ -6810,48 +7452,91 @@
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D82">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
       <formula>"OUT"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D97">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1.5e-05"/>
+        <cfvo type="num" val="4e-05"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D128">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="20"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D163">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D169">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2">
       <formula>"RISK"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D176">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="2">
+      <formula>"LOW"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D189">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D190">
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
       <formula>"Static"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"Dynamic"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D176">
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="1">
-      <formula>"LOW"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D232">
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
-      <formula>"EXPLOSIVE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D208">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="D191">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="1"/>
-        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="15"/>
+        <cfvo type="num" val="60"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -6870,24 +7555,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D163">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="D208">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
-        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
-        <cfvo type="num" val="2"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D191">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="num" val="5"/>
-        <cfvo type="num" val="15"/>
-        <cfvo type="num" val="60"/>
+        <cfvo type="num" val="3"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -6906,64 +7579,33 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D128">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="num" val="1"/>
-        <cfvo type="num" val="5"/>
-        <cfvo type="num" val="20"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D189">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <cfvo type="num" val="4"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D97">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1.5e-05"/>
-        <cfvo type="num" val="4e-05"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
+  <conditionalFormatting sqref="D232">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="2">
+      <formula>"EXPLOSIVE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D250">
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="1">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"TIGHT"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list" errorStyle="stop">
+    <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list">
       <formula1>$D$19:$D$20</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list" errorStyle="stop">
+    <dataValidation sqref="D17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list">
       <formula1>$D$21:$D$22</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list" errorStyle="stop">
+    <dataValidation sqref="D18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list">
       <formula1>"0,1,2,3,4,5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list" errorStyle="stop">
+    <dataValidation sqref="D236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose a value from the dropdown list." type="list">
       <formula1>"Manual,Optimal"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Electrochemistry" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Biology" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Mass Transfer" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Dosing" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Model" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="a_int">Model!$D$156</definedName>
@@ -205,24 +206,237 @@
     <definedName name="z_e_H2">Model!$D$78</definedName>
     <definedName name="z_e_O2">Model!$D$79</definedName>
     <definedName name="z_e_ORR">Model!$D$183</definedName>
-    <definedName name="A_x_in" localSheetId="0">Summary!$D$5</definedName>
-    <definedName name="I_app_in" localSheetId="0">Summary!$D$7</definedName>
-    <definedName name="O2_per_H2_in" localSheetId="0">Summary!$D$8</definedName>
-    <definedName name="tip_speed_in" localSheetId="0">Summary!$D$9</definedName>
-    <definedName name="A_x" localSheetId="1">Geometry!$D$6</definedName>
-    <definedName name="vial_ID" localSheetId="1">Geometry!$D$5</definedName>
-    <definedName name="vial_OD" localSheetId="1">Geometry!$D$3</definedName>
-    <definedName name="vial_wall" localSheetId="1">Geometry!$D$4</definedName>
+    <definedName name="rx_ver" localSheetId="0">Summary!$D$3</definedName>
+    <definedName name="sparger" localSheetId="0">Summary!$D$4</definedName>
+    <definedName name="por_grade" localSheetId="0">Summary!$D$5</definedName>
+    <definedName name="ver_name_1" localSheetId="1">Geometry!$D$3</definedName>
+    <definedName name="ver_name_2" localSheetId="1">Geometry!$D$4</definedName>
+    <definedName name="vial_OD_1" localSheetId="1">Geometry!$D$5</definedName>
+    <definedName name="vial_OD_2" localSheetId="1">Geometry!$D$6</definedName>
+    <definedName name="D_int_1" localSheetId="1">Geometry!$D$7</definedName>
+    <definedName name="D_int_2" localSheetId="1">Geometry!$D$8</definedName>
+    <definedName name="Vmax_1" localSheetId="1">Geometry!$D$9</definedName>
+    <definedName name="Vmax_2" localSheetId="1">Geometry!$D$10</definedName>
+    <definedName name="Vtot_1" localSheetId="1">Geometry!$D$11</definedName>
+    <definedName name="Vtot_2" localSheetId="1">Geometry!$D$12</definedName>
+    <definedName name="vial_OD" localSheetId="1">Geometry!$D$13</definedName>
+    <definedName name="vial_wall" localSheetId="1">Geometry!$D$14</definedName>
+    <definedName name="vial_ID" localSheetId="1">Geometry!$D$15</definedName>
+    <definedName name="A_x" localSheetId="1">Geometry!$D$16</definedName>
+    <definedName name="D_int" localSheetId="1">Geometry!$D$17</definedName>
+    <definedName name="V_max" localSheetId="1">Geometry!$D$18</definedName>
+    <definedName name="V_vial_total" localSheetId="1">Geometry!$D$19</definedName>
+    <definedName name="h_datum" localSheetId="1">Geometry!$D$20</definedName>
+    <definedName name="rod_d" localSheetId="1">Geometry!$D$21</definedName>
+    <definedName name="rod_n" localSheetId="1">Geometry!$D$22</definedName>
+    <definedName name="elec_clear" localSheetId="1">Geometry!$D$23</definedName>
+    <definedName name="elec_ins" localSheetId="1">Geometry!$D$24</definedName>
+    <definedName name="spg_OD" localSheetId="1">Geometry!$D$25</definedName>
+    <definedName name="spg_ID" localSheetId="1">Geometry!$D$26</definedName>
+    <definedName name="spg_tip_h" localSheetId="1">Geometry!$D$27</definedName>
+    <definedName name="eff_OD" localSheetId="1">Geometry!$D$28</definedName>
+    <definedName name="eff_ID" localSheetId="1">Geometry!$D$29</definedName>
+    <definedName name="elec_sub_L" localSheetId="1">Geometry!$D$30</definedName>
+    <definedName name="elec_disp" localSheetId="1">Geometry!$D$31</definedName>
+    <definedName name="spg_disp" localSheetId="1">Geometry!$D$32</definedName>
+    <definedName name="eff_sub_L" localSheetId="1">Geometry!$D$33</definedName>
+    <definedName name="eff_disp" localSheetId="1">Geometry!$D$34</definedName>
+    <definedName name="disp_tot" localSheetId="1">Geometry!$D$35</definedName>
+    <definedName name="V_charge" localSheetId="1">Geometry!$D$36</definedName>
+    <definedName name="h_actual" localSheetId="1">Geometry!$D$37</definedName>
+    <definedName name="sparge_depth" localSheetId="1">Geometry!$D$38</definedName>
+    <definedName name="interface_A" localSheetId="1">Geometry!$D$39</definedName>
+    <definedName name="xtube_OD" localSheetId="1">Geometry!$D$40</definedName>
+    <definedName name="xtube_n" localSheetId="1">Geometry!$D$41</definedName>
+    <definedName name="xtube_pro" localSheetId="1">Geometry!$D$42</definedName>
+    <definedName name="V_inserts" localSheetId="1">Geometry!$D$43</definedName>
+    <definedName name="headspace_V" localSheetId="1">Geometry!$D$44</definedName>
+    <definedName name="spg_len" localSheetId="1">Geometry!$D$45</definedName>
+    <definedName name="rx_ver" localSheetId="1">Geometry!$D$48</definedName>
     <definedName name="intensity" localSheetId="2">Electrochemistry!$D$3</definedName>
     <definedName name="gerrit_slope" localSheetId="2">Electrochemistry!$D$4</definedName>
     <definedName name="gerrit_int" localSheetId="2">Electrochemistry!$D$5</definedName>
-    <definedName name="I_app" localSheetId="2">Electrochemistry!$D$6</definedName>
+    <definedName name="gerrit_min" localSheetId="2">Electrochemistry!$D$6</definedName>
+    <definedName name="gerrit_max" localSheetId="2">Electrochemistry!$D$7</definedName>
+    <definedName name="F_const" localSheetId="2">Electrochemistry!$D$8</definedName>
+    <definedName name="z_e_H2" localSheetId="2">Electrochemistry!$D$9</definedName>
+    <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$10</definedName>
+    <definedName name="etaF" localSheetId="2">Electrochemistry!$D$11</definedName>
+    <definedName name="I_app" localSheetId="2">Electrochemistry!$D$12</definedName>
+    <definedName name="I_valid" localSheetId="2">Electrochemistry!$D$13</definedName>
+    <definedName name="rH2_gen" localSheetId="2">Electrochemistry!$D$14</definedName>
+    <definedName name="rO2_gen" localSheetId="2">Electrochemistry!$D$15</definedName>
+    <definedName name="V_H2_gen" localSheetId="2">Electrochemistry!$D$16</definedName>
+    <definedName name="V_O2_gen" localSheetId="2">Electrochemistry!$D$17</definedName>
+    <definedName name="V_gas_total" localSheetId="2">Electrochemistry!$D$18</definedName>
+    <definedName name="etaF_OER" localSheetId="2">Electrochemistry!$D$19</definedName>
+    <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$20</definedName>
+    <definedName name="O2_cathode_ORR" localSheetId="2">Electrochemistry!$D$21</definedName>
+    <definedName name="O2_net_gen" localSheetId="2">Electrochemistry!$D$22</definedName>
+    <definedName name="P_atm" localSheetId="2">Electrochemistry!$D$25</definedName>
+    <definedName name="T_K" localSheetId="2">Electrochemistry!$D$26</definedName>
+    <definedName name="R_gas" localSheetId="2">Electrochemistry!$D$27</definedName>
     <definedName name="bio_H2" localSheetId="3">Biology!$D$3</definedName>
     <definedName name="bio_O2" localSheetId="3">Biology!$D$4</definedName>
-    <definedName name="O2_per_H2" localSheetId="3">Biology!$D$5</definedName>
-    <definedName name="stir_rpm" localSheetId="4">'Mass Transfer'!$D$3</definedName>
-    <definedName name="stir_len" localSheetId="4">'Mass Transfer'!$D$4</definedName>
-    <definedName name="tip_speed" localSheetId="4">'Mass Transfer'!$D$5</definedName>
+    <definedName name="bio_CO2" localSheetId="3">Biology!$D$5</definedName>
+    <definedName name="H2_cons" localSheetId="3">Biology!$D$6</definedName>
+    <definedName name="O2_cons" localSheetId="3">Biology!$D$7</definedName>
+    <definedName name="CO2_cons" localSheetId="3">Biology!$D$8</definedName>
+    <definedName name="O2_excess" localSheetId="3">Biology!$D$9</definedName>
+    <definedName name="T_C" localSheetId="3">Biology!$D$10</definedName>
+    <definedName name="T_K" localSheetId="3">Biology!$D$11</definedName>
+    <definedName name="P_atm" localSheetId="3">Biology!$D$12</definedName>
+    <definedName name="Pa_per_atm" localSheetId="3">Biology!$D$13</definedName>
+    <definedName name="H_O2ref" localSheetId="3">Biology!$D$14</definedName>
+    <definedName name="H_O2T" localSheetId="3">Biology!$D$15</definedName>
+    <definedName name="T_ref" localSheetId="3">Biology!$D$16</definedName>
+    <definedName name="H_O2_T" localSheetId="3">Biology!$D$17</definedName>
+    <definedName name="O2_ceil_atm" localSheetId="3">Biology!$D$18</definedName>
+    <definedName name="O2_ceil_Pa" localSheetId="3">Biology!$D$19</definedName>
+    <definedName name="O2_ceil_C" localSheetId="3">Biology!$D$20</definedName>
+    <definedName name="O2_ceil_uM" localSheetId="3">Biology!$D$21</definedName>
+    <definedName name="H_CO2ref" localSheetId="3">Biology!$D$22</definedName>
+    <definedName name="H_CO2T" localSheetId="3">Biology!$D$23</definedName>
+    <definedName name="H_CO2_T" localSheetId="3">Biology!$D$24</definedName>
+    <definedName name="p_CO2_sparge" localSheetId="3">Biology!$D$25</definedName>
+    <definedName name="CO2_diss" localSheetId="3">Biology!$D$26</definedName>
+    <definedName name="Km_CO2" localSheetId="3">Biology!$D$27</definedName>
+    <definedName name="CO2_carbon_margin" localSheetId="3">Biology!$D$28</definedName>
+    <definedName name="Ka1_carb" localSheetId="3">Biology!$D$29</definedName>
+    <definedName name="pH_CO2_unbuf" localSheetId="3">Biology!$D$30</definedName>
+    <definedName name="H_H2ref" localSheetId="3">Biology!$D$31</definedName>
+    <definedName name="H_H2T" localSheetId="3">Biology!$D$32</definedName>
+    <definedName name="H_H2_T" localSheetId="3">Biology!$D$33</definedName>
+    <definedName name="C_H2_sat" localSheetId="3">Biology!$D$34</definedName>
+    <definedName name="t_H2_sat" localSheetId="3">Biology!$D$35</definedName>
+    <definedName name="H2_turnover" localSheetId="3">Biology!$D$36</definedName>
+    <definedName name="H2_safety" localSheetId="3">Biology!$D$37</definedName>
+    <definedName name="rH2_gen" localSheetId="3">Biology!$D$40</definedName>
+    <definedName name="O2_net_gen" localSheetId="3">Biology!$D$41</definedName>
+    <definedName name="V_charge" localSheetId="3">Biology!$D$42</definedName>
+    <definedName name="spg_name_1" localSheetId="4">'Mass Transfer'!$D$3</definedName>
+    <definedName name="spg_name_2" localSheetId="4">'Mass Transfer'!$D$4</definedName>
+    <definedName name="sigma" localSheetId="4">'Mass Transfer'!$D$5</definedName>
+    <definedName name="rho_L" localSheetId="4">'Mass Transfer'!$D$6</definedName>
+    <definedName name="g_const" localSheetId="4">'Mass Transfer'!$D$7</definedName>
+    <definedName name="D_O2" localSheetId="4">'Mass Transfer'!$D$8</definedName>
+    <definedName name="por0_um" localSheetId="4">'Mass Transfer'!$D$9</definedName>
+    <definedName name="por1_um" localSheetId="4">'Mass Transfer'!$D$10</definedName>
+    <definedName name="por2_um" localSheetId="4">'Mass Transfer'!$D$11</definedName>
+    <definedName name="por3_um" localSheetId="4">'Mass Transfer'!$D$12</definedName>
+    <definedName name="por4_um" localSheetId="4">'Mass Transfer'!$D$13</definedName>
+    <definedName name="por5_um" localSheetId="4">'Mass Transfer'!$D$14</definedName>
+    <definedName name="por_pore" localSheetId="4">'Mass Transfer'!$D$15</definedName>
+    <definedName name="tube_d_m" localSheetId="4">'Mass Transfer'!$D$16</definedName>
+    <definedName name="d_orifice" localSheetId="4">'Mass Transfer'!$D$17</definedName>
+    <definedName name="d_bubble" localSheetId="4">'Mass Transfer'!$D$18</definedName>
+    <definedName name="d_bubble_mm" localSheetId="4">'Mass Transfer'!$D$19</definedName>
+    <definedName name="mend_a" localSheetId="4">'Mass Transfer'!$D$20</definedName>
+    <definedName name="mend_b" localSheetId="4">'Mass Transfer'!$D$21</definedName>
+    <definedName name="u_rise" localSheetId="4">'Mass Transfer'!$D$22</definedName>
+    <definedName name="u_sg" localSheetId="4">'Mass Transfer'!$D$23</definedName>
+    <definedName name="holdup" localSheetId="4">'Mass Transfer'!$D$24</definedName>
+    <definedName name="a_int" localSheetId="4">'Mass Transfer'!$D$25</definedName>
+    <definedName name="t_contact" localSheetId="4">'Mass Transfer'!$D$26</definedName>
+    <definedName name="kL" localSheetId="4">'Mass Transfer'!$D$27</definedName>
+    <definedName name="kLa_sparge" localSheetId="4">'Mass Transfer'!$D$28</definedName>
+    <definedName name="kLa_avg" localSheetId="4">'Mass Transfer'!$D$29</definedName>
+    <definedName name="strip_sparge" localSheetId="4">'Mass Transfer'!$D$30</definedName>
+    <definedName name="strip_avg" localSheetId="4">'Mass Transfer'!$D$31</definedName>
+    <definedName name="strip_ratio" localSheetId="4">'Mass Transfer'!$D$32</definedName>
+    <definedName name="kLa_req" localSheetId="4">'Mass Transfer'!$D$33</definedName>
+    <definedName name="u_g_max" localSheetId="4">'Mass Transfer'!$D$34</definedName>
+    <definedName name="carry_flag" localSheetId="4">'Mass Transfer'!$D$35</definedName>
+    <definedName name="rho_CO2" localSheetId="4">'Mass Transfer'!$D$36</definedName>
+    <definedName name="n_pores_active" localSheetId="4">'Mass Transfer'!$D$37</definedName>
+    <definedName name="v_orifice" localSheetId="4">'Mass Transfer'!$D$38</definedName>
+    <definedName name="We_orifice" localSheetId="4">'Mass Transfer'!$D$39</definedName>
+    <definedName name="bubble_regime" localSheetId="4">'Mass Transfer'!$D$40</definedName>
+    <definedName name="t_O2_ceiling" localSheetId="4">'Mass Transfer'!$D$41</definedName>
+    <definedName name="t_O2_ceiling_strip" localSheetId="4">'Mass Transfer'!$D$42</definedName>
+    <definedName name="stir_rpm" localSheetId="4">'Mass Transfer'!$D$43</definedName>
+    <definedName name="stir_len" localSheetId="4">'Mass Transfer'!$D$44</definedName>
+    <definedName name="tip_speed" localSheetId="4">'Mass Transfer'!$D$45</definedName>
+    <definedName name="s_renew" localSheetId="4">'Mass Transfer'!$D$46</definedName>
+    <definedName name="kL_surf" localSheetId="4">'Mass Transfer'!$D$47</definedName>
+    <definedName name="a_surf" localSheetId="4">'Mass Transfer'!$D$48</definedName>
+    <definedName name="kLa_surf" localSheetId="4">'Mass Transfer'!$D$49</definedName>
+    <definedName name="surf_strip" localSheetId="4">'Mass Transfer'!$D$50</definedName>
+    <definedName name="surf_ratio" localSheetId="4">'Mass Transfer'!$D$51</definedName>
+    <definedName name="y_O2_vent" localSheetId="4">'Mass Transfer'!$D$52</definedName>
+    <definedName name="DO_vent_eq" localSheetId="4">'Mass Transfer'!$D$53</definedName>
+    <definedName name="hs_flush_time" localSheetId="4">'Mass Transfer'!$D$54</definedName>
+    <definedName name="O2_removal_ratio" localSheetId="4">'Mass Transfer'!$D$55</definedName>
+    <definedName name="t_O2_ceiling_lag" localSheetId="4">'Mass Transfer'!$D$56</definedName>
+    <definedName name="t_O2_ceiling_rem" localSheetId="4">'Mass Transfer'!$D$57</definedName>
+    <definedName name="sched_mode" localSheetId="4">'Mass Transfer'!$D$58</definedName>
+    <definedName name="spg_dur_man" localSheetId="4">'Mass Transfer'!$D$59</definedName>
+    <definedName name="spg_int_man" localSheetId="4">'Mass Transfer'!$D$60</definedName>
+    <definedName name="target_DO_frac" localSheetId="4">'Mass Transfer'!$D$61</definedName>
+    <definedName name="carbon_margin_min" localSheetId="4">'Mass Transfer'!$D$62</definedName>
+    <definedName name="duty_carbon" localSheetId="4">'Mass Transfer'!$D$63</definedName>
+    <definedName name="duty_O2vent" localSheetId="4">'Mass Transfer'!$D$64</definedName>
+    <definedName name="duty_opt" localSheetId="4">'Mass Transfer'!$D$65</definedName>
+    <definedName name="spg_int_max" localSheetId="4">'Mass Transfer'!$D$66</definedName>
+    <definedName name="spg_dur_opt" localSheetId="4">'Mass Transfer'!$D$67</definedName>
+    <definedName name="spg_int_opt" localSheetId="4">'Mass Transfer'!$D$68</definedName>
+    <definedName name="spg_int_opt_s" localSheetId="4">'Mass Transfer'!$D$69</definedName>
+    <definedName name="duty_actual" localSheetId="4">'Mass Transfer'!$D$70</definedName>
+    <definedName name="opt_binding" localSheetId="4">'Mass Transfer'!$D$71</definedName>
+    <definedName name="od_ok" localSheetId="4">'Mass Transfer'!$D$72</definedName>
+    <definedName name="kinetic_caveat" localSheetId="4">'Mass Transfer'!$D$73</definedName>
+    <definedName name="kLa_meas" localSheetId="4">'Mass Transfer'!$D$74</definedName>
+    <definedName name="kLa_surf_used" localSheetId="4">'Mass Transfer'!$D$75</definedName>
+    <definedName name="O2_excess" localSheetId="4">'Mass Transfer'!$D$78</definedName>
+    <definedName name="CO2_cons" localSheetId="4">'Mass Transfer'!$D$79</definedName>
+    <definedName name="O2_ceil_Pa" localSheetId="4">'Mass Transfer'!$D$80</definedName>
+    <definedName name="O2_ceil_C" localSheetId="4">'Mass Transfer'!$D$81</definedName>
+    <definedName name="T_K" localSheetId="4">'Mass Transfer'!$D$82</definedName>
+    <definedName name="P_atm" localSheetId="4">'Mass Transfer'!$D$83</definedName>
+    <definedName name="H_O2_T" localSheetId="4">'Mass Transfer'!$D$84</definedName>
+    <definedName name="nCO2_rate" localSheetId="4">'Mass Transfer'!$D$85</definedName>
+    <definedName name="duty" localSheetId="4">'Mass Transfer'!$D$86</definedName>
+    <definedName name="R_gas" localSheetId="4">'Mass Transfer'!$D$87</definedName>
+    <definedName name="Q_CO2" localSheetId="4">'Mass Transfer'!$D$88</definedName>
+    <definedName name="M_CO2" localSheetId="4">'Mass Transfer'!$D$89</definedName>
+    <definedName name="pulse_floor" localSheetId="4">'Mass Transfer'!$D$90</definedName>
+    <definedName name="CO2_supply" localSheetId="4">'Mass Transfer'!$D$91</definedName>
+    <definedName name="O2_net_gen" localSheetId="4">'Mass Transfer'!$D$92</definedName>
+    <definedName name="A_x" localSheetId="4">'Mass Transfer'!$D$93</definedName>
+    <definedName name="interface_A" localSheetId="4">'Mass Transfer'!$D$94</definedName>
+    <definedName name="vial_ID" localSheetId="4">'Mass Transfer'!$D$95</definedName>
+    <definedName name="headspace_V" localSheetId="4">'Mass Transfer'!$D$96</definedName>
+    <definedName name="spg_ID" localSheetId="4">'Mass Transfer'!$D$97</definedName>
+    <definedName name="V_charge" localSheetId="4">'Mass Transfer'!$D$98</definedName>
+    <definedName name="por_grade" localSheetId="4">'Mass Transfer'!$D$99</definedName>
+    <definedName name="sparger" localSheetId="4">'Mass Transfer'!$D$100</definedName>
+    <definedName name="Q_CO2" localSheetId="5">Dosing!$D$3</definedName>
+    <definedName name="spg_dur" localSheetId="5">Dosing!$D$4</definedName>
+    <definedName name="spg_int" localSheetId="5">Dosing!$D$5</definedName>
+    <definedName name="pulse_floor" localSheetId="5">Dosing!$D$6</definedName>
+    <definedName name="R_gas" localSheetId="5">Dosing!$D$7</definedName>
+    <definedName name="M_CO2" localSheetId="5">Dosing!$D$8</definedName>
+    <definedName name="nCO2_rate" localSheetId="5">Dosing!$D$9</definedName>
+    <definedName name="CO2_pulse" localSheetId="5">Dosing!$D$10</definedName>
+    <definedName name="pulses_h" localSheetId="5">Dosing!$D$11</definedName>
+    <definedName name="pulses_d" localSheetId="5">Dosing!$D$12</definedName>
+    <definedName name="CO2_supply" localSheetId="5">Dosing!$D$13</definedName>
+    <definedName name="CO2_sd_ratio" localSheetId="5">Dosing!$D$14</definedName>
+    <definedName name="duty" localSheetId="5">Dosing!$D$15</definedName>
+    <definedName name="O2_accum" localSheetId="5">Dosing!$D$16</definedName>
+    <definedName name="O2_strip_pulse" localSheetId="5">Dosing!$D$17</definedName>
+    <definedName name="sched_bal" localSheetId="5">Dosing!$D$18</definedName>
+    <definedName name="dur_ok" localSheetId="5">Dosing!$D$19</definedName>
+    <definedName name="O2_excess" localSheetId="5">Dosing!$D$22</definedName>
+    <definedName name="CO2_cons" localSheetId="5">Dosing!$D$23</definedName>
+    <definedName name="P_atm" localSheetId="5">Dosing!$D$24</definedName>
+    <definedName name="T_K" localSheetId="5">Dosing!$D$25</definedName>
+    <definedName name="spg_int_opt" localSheetId="5">Dosing!$D$26</definedName>
+    <definedName name="spg_int_man" localSheetId="5">Dosing!$D$27</definedName>
+    <definedName name="spg_dur_opt" localSheetId="5">Dosing!$D$28</definedName>
+    <definedName name="strip_sparge" localSheetId="5">Dosing!$D$29</definedName>
+    <definedName name="spg_dur_man" localSheetId="5">Dosing!$D$30</definedName>
+    <definedName name="sched_mode" localSheetId="5">Dosing!$D$31</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -240,7 +454,7 @@
     <numFmt numFmtId="170" formatCode="0.000000000"/>
     <numFmt numFmtId="171" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -385,6 +599,14 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -477,7 +699,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -571,11 +793,25 @@
         <color theme="6"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="9"/>
+      </left>
+      <right style="medium">
+        <color theme="9"/>
+      </right>
+      <top style="medium">
+        <color theme="9"/>
+      </top>
+      <bottom style="medium">
+        <color theme="9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -692,6 +928,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1041,173 +1284,399 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="70" min="1" max="1"/>
-    <col width="46" customWidth="1" style="70" min="5" max="5"/>
+    <col width="30" customWidth="1" style="70" min="1" max="1"/>
+    <col width="15" customWidth="1" style="70" min="2" max="2"/>
+    <col width="60" customWidth="1" style="70" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="63" t="inlineStr">
-        <is>
-          <t>SUMMARY / CONTROL  (proof slice)</t>
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>SUMMARY / CONTROL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="77" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B2" s="77" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" s="77" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D2" s="77" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E2" s="77" t="inlineStr">
+        <is>
+          <t>Source / assumption</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="64" t="inlineStr">
-        <is>
-          <t>Imports from other tabs (the only cross-tab references):</t>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Reactor version</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>rx_ver</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="36" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Active build. Choose from the values below. Dropdown.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1" s="70" thickBot="1">
-      <c r="A4" s="65" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B4" s="65" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="65" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D4" s="65" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="E4" s="65" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Sparger type</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>sparger</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="inlineStr">
+        <is>
+          <t>Tube</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>CO₂ delivery route. Choose from the values below. Dropdown.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1" s="70" thickBot="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>(import) cross-section</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>A_x_in</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>mm²</t>
-        </is>
-      </c>
-      <c r="D5" s="72">
-        <f>Geometry!$D$6</f>
-        <v/>
-      </c>
-      <c r="E5" s="66" t="inlineStr">
-        <is>
-          <t>IMPORT cell — the one cross-tab link. Local formulas below use this, so their precedents stay on this tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Liquid per mm depth (demo)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>mL_per_mm</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>mL/mm</t>
-        </is>
-      </c>
-      <c r="D6" s="35">
-        <f>A_x_in/1000</f>
-        <v/>
-      </c>
-      <c r="E6" s="67" t="inlineStr">
-        <is>
-          <t>Uses the local import (A_x_in), not Geometry directly → Excel highlights it on this tab.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Sinter porosity grade (if Sintered)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>por_grade</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>ISO 4793 / DURAN class; 0 = coarsest. Dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>(import) electrolysis current</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>I_app_in</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" s="73">
-        <f>'Electrochemistry'!$D$6</f>
-        <v/>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>From Electrochemistry (theme 8).</t>
+      <c r="A7" s="76" t="inlineStr">
+        <is>
+          <t>RESULTS  (imported — borders show source tab)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(import) O₂:H₂ uptake</t>
+          <t>► Optimal pulse (s)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>O2_per_H2_in</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" s="74">
-        <f>Biology!$D$5</f>
+          <t>spg_dur_opt_sum</t>
+        </is>
+      </c>
+      <c r="D8" s="79">
+        <f>'Mass Transfer'!$D$67</f>
         <v/>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>From Biology (theme 5).</t>
+          <t>From Mass Transfer.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(import) tip speed</t>
+          <t>► Optimal interval (min)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tip_speed_in</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" s="75">
-        <f>'Mass Transfer'!$D$5</f>
+          <t>spg_int_opt_sum</t>
+        </is>
+      </c>
+      <c r="D9" s="79">
+        <f>'Mass Transfer'!$D$68</f>
         <v/>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>From Mass Transfer (theme 6).</t>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>O₂ removal : surplus</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>O2_removal_ratio_sum</t>
+        </is>
+      </c>
+      <c r="D10" s="79">
+        <f>'Mass Transfer'!$D$55</f>
+        <v/>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>O₂ time-to-ceiling, lag (min)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t_O2_ceiling_lag_sum</t>
+        </is>
+      </c>
+      <c r="D11" s="79">
+        <f>'Mass Transfer'!$D$56</f>
+        <v/>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Carbon margin (×Km)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CO2_carbon_margin_sum</t>
+        </is>
+      </c>
+      <c r="D12" s="80">
+        <f>Biology!$D$28</f>
+        <v/>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CO₂ supply : demand</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CO2_sd_ratio_sum</t>
+        </is>
+      </c>
+      <c r="D13" s="81">
+        <f>Dosing!$D$14</f>
+        <v/>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>From Dosing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Current-law valid?</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>I_valid_sum</t>
+        </is>
+      </c>
+      <c r="D14" s="82">
+        <f>Electrochemistry!$D$13</f>
+        <v/>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>From Electrochemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Carryover</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>carry_flag_sum</t>
+        </is>
+      </c>
+      <c r="D15" s="79">
+        <f>'Mass Transfer'!$D$35</f>
+        <v/>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bubble regime</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>bubble_regime_sum</t>
+        </is>
+      </c>
+      <c r="D16" s="79">
+        <f>'Mass Transfer'!$D$40</f>
+        <v/>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pulse ≥ floor?</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>dur_ok_sum</t>
+        </is>
+      </c>
+      <c r="D17" s="81">
+        <f>Dosing!$D$19</f>
+        <v/>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>From Dosing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OD-read window?</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>od_ok_sum</t>
+        </is>
+      </c>
+      <c r="D18" s="79">
+        <f>'Mass Transfer'!$D$72</f>
+        <v/>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>H₂ headspace</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2_safety_sum</t>
+        </is>
+      </c>
+      <c r="D19" s="80">
+        <f>Biology!$D$37</f>
+        <v/>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="D3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose from the list." type="list" errorStyle="stop">
+      <formula1>"AEP0.1.1,AEP0.2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose from the list." type="list" errorStyle="stop">
+      <formula1>"Tube,Sintered"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose from the list." type="list" errorStyle="stop">
+      <formula1>"0,1,2,3,4,5"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1219,146 +1688,1181 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="70" min="1" max="1"/>
-    <col width="40" customWidth="1" style="70" min="5" max="5"/>
+    <col width="30" customWidth="1" style="70" min="1" max="1"/>
+    <col width="15" customWidth="1" style="70" min="2" max="2"/>
+    <col width="60" customWidth="1" style="70" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="63" t="inlineStr">
-        <is>
-          <t>GEOMETRY  (proof slice — formula precedents are all on this tab)</t>
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>GEOMETRY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B2" s="65" t="inlineStr">
+      <c r="B2" s="77" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" s="65" t="inlineStr">
+      <c r="C2" s="77" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D2" s="65" t="inlineStr">
+      <c r="D2" s="77" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E2" s="65" t="inlineStr">
+      <c r="E2" s="77" t="inlineStr">
         <is>
           <t>Source / assumption</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  valid version 1</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>ver_name_1</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="36" t="inlineStr">
+        <is>
+          <t>AEP0.1.1</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Current build (20 mL Pioreactor vial, assumed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  valid version 2</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>ver_name_2</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="inlineStr">
+        <is>
+          <t>AEP0.2</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Planned build (40 mL Pioreactor vial).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Vial outer diameter - AEP0.1.1</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>vial_OD_1</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Pioreactor 20 mL vial, measured OD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Vial outer diameter - AEP0.2</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>vial_OD_2</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>40 mL vial — same diameter as 20 mL (Pioreactor source). Using 27.48 mm until measured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Internal usable depth - AEP0.1.1</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>D_int_1</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="n">
+        <v>55</v>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>20 mL vial total height 57.4 mm; usable depth est. Measure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Internal usable depth - AEP0.2</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>D_int_2</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>95</v>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>40 mL internal depth — measure. ~double the 20 mL (same diameter, double volume).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Recommended max working volume - AEP0.1.1</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Vmax_1</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Pioreactor docs: 8-16 mL for 20 mL vial; using max as level datum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Recommended max working volume - AEP0.2</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Vmax_2</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Pioreactor docs recommend 10–30 mL working volume for the 40 mL vial; using the top of that range as level datum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Total internal vial volume - AEP0.1.1</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Vtot_1</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>To cap underside (&gt; nominal). Placeholder - measure (water to fill).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Total internal vial volume - AEP0.2</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Vtot_2</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Placeholder - measure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Vial outer diameter</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>vial_OD</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D3" s="33" t="n">
-        <v>27.48</v>
-      </c>
-      <c r="E3" s="68" t="inlineStr">
-        <is>
-          <t>Pioreactor 20 mL vial, measured.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="D13" s="38">
+        <f>IF(rx_ver=ver_name_1,vial_OD_1,IF(rx_ver=ver_name_2,vial_OD_2,NA()))</f>
+        <v/>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>Selected by rx_ver; invalid version returns an error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Vial wall thickness</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>vial_wall</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D14" s="30" t="n">
         <v>1.1</v>
       </c>
-      <c r="E4" s="66" t="inlineStr">
-        <is>
-          <t>Borosilicate, estimated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>Borosilicate vial; Pioreactor publish neither wall nor internal diameter, so wall estimated ~1.1 mm (typical for this glass-vial class).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Vial internal diameter</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>vial_ID</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D5" s="35">
+      <c r="D15" s="38">
         <f>vial_OD-2*vial_wall</f>
         <v/>
       </c>
-      <c r="E5" s="67" t="inlineStr">
-        <is>
-          <t>OD − 2 walls.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Internal cross-section</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>OD minus two wall thicknesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Internal cross-sectional area</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>A_x</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>mm²</t>
         </is>
       </c>
-      <c r="D6" s="35">
+      <c r="D16" s="39">
         <f>PI()/4*vial_ID^2</f>
         <v/>
       </c>
-      <c r="E6" s="67" t="inlineStr">
-        <is>
-          <t>Uniform-cylinder body.</t>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>Uniform-cylinder body approximation (neck excluded - see headspace).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Internal usable depth</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>D_int</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D17" s="39">
+        <f>IF(rx_ver=ver_name_1,D_int_1,IF(rx_ver=ver_name_2,D_int_2,NA()))</f>
+        <v/>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>Selected by rx_ver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Recommended max working volume (datum)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>V_max</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D18" s="39">
+        <f>IF(rx_ver=ver_name_1,Vmax_1,IF(rx_ver=ver_name_2,Vmax_2,NA()))</f>
+        <v/>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>Selected by rx_ver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Total internal vial volume</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>V_vial_total</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D19" s="39">
+        <f>IF(rx_ver=ver_name_1,Vtot_1,IF(rx_ver=ver_name_2,Vtot_2,NA()))</f>
+        <v/>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>Selected by rx_ver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Bare liquid level (datum height)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>h_datum</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D20" s="38">
+        <f>V_max*1000/A_x</f>
+        <v/>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>Height the bare max volume reaches with no inserts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Electrode rod diameter</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>rod_d</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D21" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>6 mm rod electrodes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Number of electrodes</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>rod_n</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>Anode + cathode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Electrode tip clearance above base</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>elec_clear</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D23" s="37" t="n">
+        <v>22</v>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Held constant across builds (OD clear zone). 22 mm ↔ 33 mm insertion in AEP0.1.1. Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Electrode insertion depth (derived)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>elec_ins</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D24" s="39">
+        <f>D_int-elec_clear</f>
+        <v/>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>Cap underside -&gt; tip. Increases for the taller AEP0.2 to keep clearance constant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Sparge tube OD</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>spg_OD</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D25" s="40" t="n">
+        <v>3.175</v>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>1/8" OD Flexelene 135C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Sparge tube ID</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>spg_ID</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D26" s="41" t="n">
+        <v>1.5875</v>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>1/16" ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Sparge release height (= anode tip)</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>spg_tip_h</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D27" s="39">
+        <f>elec_clear</f>
+        <v/>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>CO₂ released near anode tip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Efflux tube OD</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>eff_OD</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="n">
+        <v>3.175</v>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>1/8" OD Flexelene 135C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Efflux tube ID</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>eff_ID</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D29" s="41" t="n">
+        <v>1.5875</v>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>1/16" ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Electrode submerged length (@datum)</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>elec_sub_L</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D30" s="38">
+        <f>MAX(0,h_datum-elec_clear)</f>
+        <v/>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>For displacement bookkeeping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Electrode displaced volume</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>elec_disp</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D31" s="42">
+        <f>rod_n*(PI()/4*rod_d^2)*elec_sub_L/1000</f>
+        <v/>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>Submerged rod volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Sparge tube displaced volume</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>spg_disp</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D32" s="42">
+        <f>(PI()/4*spg_OD^2)*MAX(0,h_datum-spg_tip_h)/1000</f>
+        <v/>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>Submerged sparge-tube volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Efflux tube submerged length</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>eff_sub_L</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D33" s="42">
+        <f>(eff_OD+eff_ID)/2</f>
+        <v/>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>45 deg cut; level held at top of the ID opening, so wall is wetted from tip up to (OD+ID)/2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Efflux tube displaced volume</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>eff_disp</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D34" s="43">
+        <f>(PI()/4*(eff_OD^2-eff_ID^2))*eff_sub_L/1000</f>
+        <v/>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Annular wall only (bore is open to withdrawal). 45 deg approximation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Total displaced volume</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>disp_tot</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D35" s="42">
+        <f>elec_disp+spg_disp+eff_disp</f>
+        <v/>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>Sum of submerged inserts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>LIQUID VOLUME TO CHARGE</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>V_charge</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D36" s="44">
+        <f>ROUND(V_max-disp_tot,0)</f>
+        <v/>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>Integer mL to charge so the level matches the bare datum despite inserts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Resulting liquid level</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>h_actual</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D37" s="38">
+        <f>(V_charge+disp_tot)*1000/A_x</f>
+        <v/>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>Level achieved by the integer charge (displacement taken at datum; sub-mm error).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Sparge depth / bubble path length</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>sparge_depth</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D38" s="38">
+        <f>MAX(0,h_actual-spg_tip_h)</f>
+        <v/>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>Release point to surface.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>Gas-liquid interfacial area</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>interface_A</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>mm²</t>
+        </is>
+      </c>
+      <c r="D39" s="39">
+        <f>A_x-(rod_n*(PI()/4*rod_d^2)+(PI()/4*spg_OD^2)+(PI()/4*eff_OD^2))</f>
+        <v/>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>Free surface = cross-section minus inserts piercing it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Extra headspace tube OD</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>xtube_OD</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D40" s="42">
+        <f>eff_OD</f>
+        <v/>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>3 further 1/8" tubes (gas-out, etc.) through the cap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Number of extra headspace tubes</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>xtube_n</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D41" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>Protrude through the cap into headspace. 1x media in, 2x gas out</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Extra tube protrusion</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>xtube_pro</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D42" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>Each protrudes ~5 mm below cap (45 deg cut). Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Total in-vial insert volume</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>V_inserts</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D43" s="42">
+        <f>(rod_n*(PI()/4*rod_d^2)*elec_ins+(PI()/4*spg_OD^2)*spg_len+(PI()/4*(eff_OD^2-eff_ID^2))*(D_int-h_actual)+xtube_n*(PI()/4*xtube_OD^2)*xtube_pro)/1000</f>
+        <v/>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>In-vial inserts: electrodes &amp; sparge solid; efflux annular (open bore); extra tubes solid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Headspace gas volume</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>headspace_V</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D44" s="38">
+        <f>V_vial_total-V_charge-V_inserts</f>
+        <v/>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>Total vial volume - liquid charged - inserts (captures neck narrowing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Sparge tube in-vial length</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>spg_len</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D45" s="28">
+        <f>D_int-spg_tip_h</f>
+        <v/>
+      </c>
+      <c r="E45" s="29" t="inlineStr">
+        <is>
+          <t>Cap underside to release point; tracks spg_tip_h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="83" t="inlineStr">
+        <is>
+          <t>IMPORTS (from other tabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>(import) Reactor version</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>rx_ver</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48">
+        <f>Summary!$D$3</f>
+        <v/>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>From Summary.</t>
         </is>
       </c>
     </row>
@@ -1374,17 +2878,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="70" min="1" max="1"/>
-    <col width="40" customWidth="1" style="70" min="5" max="5"/>
+    <col width="30" customWidth="1" style="70" min="1" max="1"/>
+    <col width="15" customWidth="1" style="70" min="2" max="2"/>
+    <col width="60" customWidth="1" style="70" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
-        <is>
-          <t>ELECTROCHEMISTRY  (proof slice)</t>
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>ELECTROCHEMISTRY</t>
         </is>
       </c>
     </row>
@@ -1416,107 +2921,609 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LED intensity</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>LED intensity setpoint (Pioreactor LED_D)</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>intensity</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D3" s="33" t="n">
+      <c r="D3" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="66" t="inlineStr">
-        <is>
-          <t>Electrode drive setpoint. Input.</t>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Electrode drive via LED_D channel. Input.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Gerrit slope</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Gerrit's Law - slope</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>gerrit_slope</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>mA/%</t>
         </is>
       </c>
-      <c r="D4" s="34" t="n">
+      <c r="D4" s="46" t="n">
         <v>1.03</v>
       </c>
-      <c r="E4" s="68" t="inlineStr">
-        <is>
-          <t>Empirical fit.</t>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Empirical current-vs-intensity fit (constant-current; electrolyte/volume-independent).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Gerrit intercept</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Gerrit's Law - intercept</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>gerrit_int</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>mA</t>
         </is>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D5" s="47" t="n">
         <v>2.6</v>
       </c>
-      <c r="E5" s="68" t="inlineStr">
-        <is>
-          <t>Empirical fit.</t>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Intercept of the same fit.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Electrolysis current</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Gerrit's Law - min valid intensity</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>gerrit_min</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D6" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Fit validated from 3%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Gerrit's Law - max valid intensity</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>gerrit_max</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Fit validated to 25%; above this constant-current may fail as cell V nears the 5 V rail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Faraday constant</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>F_const</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>C/mol</t>
+        </is>
+      </c>
+      <c r="D8" s="49" t="n">
+        <v>96485.33212000001</v>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>NIST CODATA (exact, SI 2019).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Electrons per H₂</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>z_e_H2</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>2H⁺ + 2e⁻ -&gt; H₂.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Electrons per O₂</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>z_e_O2</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>2H₂O -&gt; O₂ + 4H⁺ + 4e⁻.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Faradaic efficiency – H₂ at cathode (HER share)</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>etaF</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Cathodic H₂ faradaic efficiency. Neutral-pH HER peaks ~97% and competes with O₂ reduction, so true FE is likely &lt;1 and unmeasured (Clary 2020, PNAS 117:32947). 1.0 = optimistic; measure by gas collection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Electrolysis current (Gerrit's Law)</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>I_app</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D6" s="35">
+      <c r="D12" s="43">
         <f>(gerrit_slope*intensity+gerrit_int)/1000</f>
         <v/>
       </c>
-      <c r="E6" s="67" t="inlineStr">
-        <is>
-          <t>Gerrit's Law.</t>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>I(mA) = slope x intensity + intercept; /1000 -&gt; A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Gerrit's Law validity flag</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>I_valid</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="51">
+        <f>IF(AND(intensity&gt;=gerrit_min,intensity&lt;=gerrit_max),"OK","OUT")</f>
+        <v/>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>Linear fit only validated over the stated range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>H₂ generation rate</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>rH2_gen</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D14" s="28">
+        <f>I_app*etaF/(z_e_H2*F_const)*3600</f>
+        <v/>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>Faraday: I x etaF /(z F).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>O₂ generation rate (anodic, gross)</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>rO2_gen</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D15" s="28">
+        <f>I_app*etaF_OER/(z_e_O2*F_const)*3600</f>
+        <v/>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>Anodic OER, gross. Uses etaF_OER (anodic), not the cathodic etaF. H₂:O₂(anodic) = 2:1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>H₂ generation rate (volumetric)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>V_H2_gen</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D16" s="28">
+        <f>rH2_gen/60*R_gas*T_K/P_atm*1000000</f>
+        <v/>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>Ideal gas at surface T,P. Collect gas over water to check against this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>O₂ generation rate (volumetric)</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>V_O2_gen</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D17" s="28">
+        <f>rO2_gen/60*R_gas*T_K/P_atm*1000000</f>
+        <v/>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>Anodic gross O₂.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Total gas generation rate</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>V_gas_total</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D18" s="28">
+        <f>V_H2_gen+V_O2_gen</f>
+        <v/>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>Total electrolytic gas (H₂+O₂) — abiotic check: collect over water, no cells, to verify Gerrit/etaF. Less if etaF&lt;1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Anodic O₂ faradaic efficiency</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>etaF_OER</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>OER at the anode assumed ~100% faradaic; the cell's inefficiency is cathodic (O₂ reduction competing with H₂), not anodic. Design assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Electrons per O₂ reduced (cathode)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>z_e_ORR</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>Electrons per cathodic O₂. 4 = to water; 2 = peroxide (favoured on non-Pt, neutral pH) — consumes 2× the O₂/amp, and H₂O₂ is biocidal. Inert while etaF=1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>O₂ consumed at cathode (ORR)</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>O2_cathode_ORR</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D21" s="28">
+        <f>I_app*(1-etaF)/(z_e_ORR*F_const)*3600</f>
+        <v/>
+      </c>
+      <c r="E21" s="29" t="inlineStr">
+        <is>
+          <t>Cathodic current not making H₂ (1−etaF) reduces dissolved O₂. 0 at etaF=1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Net O₂ to dissolved pool</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>O2_net_gen</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D22" s="28">
+        <f>rO2_gen-O2_cathode_ORR</f>
+        <v/>
+      </c>
+      <c r="E22" s="29" t="inlineStr">
+        <is>
+          <t>Anodic O₂ minus cathodic consumption — the O₂ the dissolved pool receives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="83" t="inlineStr">
+        <is>
+          <t>IMPORTS (from other tabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>(import) Surface pressure</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P_atm</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D25" s="80">
+        <f>Biology!$D$12</f>
+        <v/>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>(import) Temperature (absolute)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>T_K</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D26" s="80">
+        <f>Biology!$D$11</f>
+        <v/>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>(import) Ideal gas constant</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>R_gas</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>J/mol/K</t>
+        </is>
+      </c>
+      <c r="D27" s="81">
+        <f>Dosing!$D$7</f>
+        <v/>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>From Dosing.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
+      <formula>"OUT"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1528,17 +3535,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="70" min="1" max="1"/>
-    <col width="40" customWidth="1" style="70" min="5" max="5"/>
+    <col width="30" customWidth="1" style="70" min="1" max="1"/>
+    <col width="15" customWidth="1" style="70" min="2" max="2"/>
+    <col width="60" customWidth="1" style="70" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
-        <is>
-          <t>BIOLOGY  (proof slice)</t>
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>BIOLOGY  (uptake, O₂ ceiling, dissolved CO₂, H₂)</t>
         </is>
       </c>
     </row>
@@ -1570,82 +3578,1003 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Gas ratio H₂</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Gas requirement ratio - H₂</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>bio_H2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D3" s="33" t="n">
+      <c r="D3" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="E3" s="66" t="inlineStr">
-        <is>
-          <t>Uptake ratio basis.</t>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>H₂:O₂:CO₂ UPTAKE ratio (not feed; phase-dependent, Lu &amp; Yu 2019). Knallgas caps O₂:H₂≤0.5; growth gives O₂:H₂≈0.29–0.35, CO₂:H₂≈0.15–0.19. 6:2:1 = mid-range central. Feed optimum 7:2:1 (Ishizaki 2001). Can't measure pre-growth.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Gas ratio O₂</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Gas requirement ratio - O₂</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>bio_O2</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D4" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="66" t="inlineStr">
-        <is>
-          <t>Uptake ratio.</t>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>O₂:H₂ uptake, range 0.29–0.35 (×6 → 1.75–2.1). 2 = central; 1.8 (lean) is growth-protective.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>O₂ per H₂</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>O2_per_H2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Gas requirement ratio - CO₂</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>bio_CO2</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D5" s="35">
-        <f>bio_O2/bio_H2</f>
-        <v/>
-      </c>
-      <c r="E5" s="67" t="inlineStr">
-        <is>
-          <t>Derived ratio.</t>
+      <c r="D5" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>CO₂:H₂ uptake, range 0.15–0.19 (×6 → 0.9–1.15). 1 = central. Supply ≫ demand → non-limiting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>H₂ consumed</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>H2_cons</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D6" s="28">
+        <f>rH2_gen</f>
+        <v/>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Assumes 100% of evolved H₂ consumed — steady growth only; ~0 during lag (see §13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>O₂ consumed</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>O2_cons</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D7" s="28">
+        <f>H2_cons*bio_O2/bio_H2</f>
+        <v/>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>H₂ consumed × O₂:H₂. Steady growth only; ~0 during lag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>CO₂ consumed (carbon fixation)</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>CO2_cons</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D8" s="28">
+        <f>H2_cons*bio_CO2/bio_H2</f>
+        <v/>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>H₂ consumed x (CO₂/H₂ ratio).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>EXCESS O₂ to remove</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>O2_excess</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D9" s="28">
+        <f>O2_net_gen-O2_cons</f>
+        <v/>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>Net O₂ (after cathode) minus biological uptake — the surplus to strip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>T_C</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>C. necator optimum ~30 °C. Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Temperature (absolute)</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>T_K</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D11" s="38">
+        <f>T_C+273.15</f>
+        <v/>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>°C + 273.15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Surface pressure</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>P_atm</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>101325</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Atmospheric at the liquid surface (assumed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Standard atmosphere (atm-&gt;Pa)</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Pa_per_atm</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Pa/atm</t>
+        </is>
+      </c>
+      <c r="D13" s="50" t="n">
+        <v>101325</v>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>Defined: 1 atm = 101 325 Pa exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Henry solubility O₂ (ref, 298.15 K)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>H_O2ref</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³/Pa</t>
+        </is>
+      </c>
+      <c r="D14" s="50" t="n">
+        <v>1.3e-05</v>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>Sander (2023) compilation (supersedes 2015), value from Burkholder et al. 2019.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Henry T-dependence O₂</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>H_O2T</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D15" s="50" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>Sander (2023): d ln(Hcp)/d(1/T).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Reference temperature</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>T_ref</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D16" s="50" t="n">
+        <v>298.15</v>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>Standard reference for Henry constants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Henry solubility O₂ at T</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>H_O2_T</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³/Pa</t>
+        </is>
+      </c>
+      <c r="D17" s="52">
+        <f>H_O2ref*EXP(H_O2T*(1/T_K-1/T_ref))</f>
+        <v/>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>van 't Hoff correction to reactor T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>O₂ growth-inhibition ceiling (gas)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>O2_ceil_atm</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>atm</t>
+        </is>
+      </c>
+      <c r="D18" s="50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Whole-cell growth inhibited above ~0.30 atm O₂ (Amer &amp; Kim 2023); the [NiFe] hydrogenase itself is O₂-tolerant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>O₂ ceiling (partial pressure)</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>O2_ceil_Pa</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D19" s="39">
+        <f>O2_ceil_atm*Pa_per_atm</f>
+        <v/>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>Ceiling in Pa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Dissolved-O₂ ceiling</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>O2_ceil_C</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³</t>
+        </is>
+      </c>
+      <c r="D20" s="43">
+        <f>H_O2_T*O2_ceil_Pa</f>
+        <v/>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>Henry's law at the gas ceiling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Dissolved-O₂ ceiling</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>O2_ceil_uM</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="D21" s="39">
+        <f>O2_ceil_C*1000</f>
+        <v/>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>mol/m³ = mM; ×1000 = µM. Aim: minimise dissolved O₂; floor set by O₂-removal capacity (§11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Henry solubility CO₂ (ref, 298.15 K)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>H_CO2ref</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³/Pa</t>
+        </is>
+      </c>
+      <c r="D22" s="53" t="n">
+        <v>0.00033</v>
+      </c>
+      <c r="E22" s="60" t="inlineStr">
+        <is>
+          <t>Sander (2023) compilation; CO₂ ~25× more soluble than O₂.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Henry T-dependence CO₂</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>H_CO2T</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D23" s="53" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E23" s="60" t="inlineStr">
+        <is>
+          <t>Sander (2023): d ln(Hcp)/d(1/T) for CO₂.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Henry solubility CO₂ at T</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>H_CO2_T</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³/Pa</t>
+        </is>
+      </c>
+      <c r="D24" s="28">
+        <f>H_CO2ref*EXP(H_CO2T*(1/T_K-1/T_ref))</f>
+        <v/>
+      </c>
+      <c r="E24" s="29" t="inlineStr">
+        <is>
+          <t>van 't Hoff to reactor T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>CO₂ partial pressure at sparge</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>p_CO2_sparge</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D25" s="28">
+        <f>P_atm</f>
+        <v/>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>Pure-CO₂ sparge: p_CO₂ ≈ surface pressure during a pulse. Assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Dissolved CO₂ (during sparge)</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>CO2_diss</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³</t>
+        </is>
+      </c>
+      <c r="D26" s="28">
+        <f>H_CO2_T*p_CO2_sparge</f>
+        <v/>
+      </c>
+      <c r="E26" s="29" t="inlineStr">
+        <is>
+          <t>Equilibrium dissolved CO₂ while sparging (mol/m³ = mM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>RuBisCO Km for CO₂</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Km_CO2</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="D27" s="58" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" s="59" t="inlineStr">
+        <is>
+          <t>RuBisCO Km(CO₂) ~ order 50 µM. Coarse — confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Carbon margin (dissolved CO₂ : Km)</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>CO2_carbon_margin</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D28" s="28">
+        <f>CO2_diss*1000/Km_CO2</f>
+        <v/>
+      </c>
+      <c r="E28" s="29" t="inlineStr">
+        <is>
+          <t>Dissolved CO₂ : RuBisCO Km. ≫1 = saturating (duty-averaged lower).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Carbonic-acid Ka1 (apparent)</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Ka1_carb</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>mol/L</t>
+        </is>
+      </c>
+      <c r="D29" s="53" t="n">
+        <v>4.45e-07</v>
+      </c>
+      <c r="E29" s="60" t="inlineStr">
+        <is>
+          <t>CO₂(aq)+H₂O ⇌ H⁺+HCO₃⁻, pKa1 6.35 (25 °C).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>pH — UNBUFFERED worst case</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>pH_CO2_unbuf</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="28">
+        <f>-LOG10(SQRT(Ka1_carb*(CO2_diss/1000)))</f>
+        <v/>
+      </c>
+      <c r="E30" s="59" t="inlineStr">
+        <is>
+          <t>Unbuffered worst case (pure water + CO₂) — lower bound only; the Sydow phosphate medium holds pH near setpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Henry solubility H₂ (ref, 298.15 K)</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>H_H2ref</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³/Pa</t>
+        </is>
+      </c>
+      <c r="D31" s="53" t="n">
+        <v>7.8e-06</v>
+      </c>
+      <c r="E31" s="60" t="inlineStr">
+        <is>
+          <t>Sander (2023). H₂ ~1.7× less soluble than O₂.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Henry T-dependence H₂</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>H_H2T</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D32" s="53" t="n">
+        <v>500</v>
+      </c>
+      <c r="E32" s="60" t="inlineStr">
+        <is>
+          <t>Sander (2023): d ln(Hcp)/d(1/T) for H₂ (weak T-dependence).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Henry solubility H₂ at T</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>H_H2_T</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³/Pa</t>
+        </is>
+      </c>
+      <c r="D33" s="28">
+        <f>H_H2ref*EXP(H_H2T*(1/T_K-1/T_ref))</f>
+        <v/>
+      </c>
+      <c r="E33" s="29" t="inlineStr">
+        <is>
+          <t>van 't Hoff to reactor T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Dissolved-H₂ saturation (1 atm)</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>C_H2_sat</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>mol/m³</t>
+        </is>
+      </c>
+      <c r="D34" s="28">
+        <f>H_H2_T*P_atm</f>
+        <v/>
+      </c>
+      <c r="E34" s="29" t="inlineStr">
+        <is>
+          <t>Max dissolved H₂ at 1 atm — the cells' H₂ ceiling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Time to saturate dissolved H₂ (LAG)</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>t_H2_sat</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D35" s="28">
+        <f>C_H2_sat*(V_charge/1000000)/rH2_gen*60</f>
+        <v/>
+      </c>
+      <c r="E35" s="29" t="inlineStr">
+        <is>
+          <t>Lag: dissolved H₂ saturates this fast unconsumed, then bubbles off (lost + explosive headspace). Mirrors the O₂ lag timescale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>H₂ pool turnovers per hour</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>H2_turnover</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>1/h</t>
+        </is>
+      </c>
+      <c r="D36" s="28">
+        <f>rH2_gen/(V_charge/1000000)/C_H2_sat</f>
+        <v/>
+      </c>
+      <c r="E36" s="59" t="inlineStr">
+        <is>
+          <t>H₂ evolved ÷ saturable pool. ≫1 → cells must consume in near-real-time or it escapes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>H₂ headspace safety flag</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>H2_safety</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="28">
+        <f>IF(H2_turnover&gt;1,"EXPLOSIVE","watch")</f>
+        <v/>
+      </c>
+      <c r="E37" s="32" t="inlineStr">
+        <is>
+          <t>On when H₂ escapes faster than it dissolves (H2_turnover&gt;1) → explosive H₂+O₂ headspace (4–94% in O₂). On at any useful current — headspace venting is mandatory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="83" t="inlineStr">
+        <is>
+          <t>IMPORTS (from other tabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>(import) H₂ generation rate</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>rH2_gen</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D40" s="82">
+        <f>Electrochemistry!$D$14</f>
+        <v/>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>From Electrochemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>(import) Net O₂ to dissolved pool</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>O2_net_gen</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D41" s="82">
+        <f>Electrochemistry!$D$22</f>
+        <v/>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>From Electrochemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>(import) LIQUID VOLUME TO CHARGE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>V_charge</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D42" s="84">
+        <f>Geometry!$D$36</f>
+        <v/>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>From Geometry.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D9">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1.5e-05"/>
+        <cfvo type="num" val="4e-05"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D37">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="2">
+      <formula>"EXPLOSIVE"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1657,17 +4586,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="70" min="1" max="1"/>
-    <col width="40" customWidth="1" style="70" min="5" max="5"/>
+    <col width="30" customWidth="1" style="70" min="1" max="1"/>
+    <col width="15" customWidth="1" style="70" min="2" max="2"/>
+    <col width="60" customWidth="1" style="70" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
-        <is>
-          <t>MASS TRANSFER  (proof slice)</t>
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>MASS TRANSFER  (bubbles, surface kLa, O₂ removal, carryover)</t>
         </is>
       </c>
     </row>
@@ -1699,87 +4629,3370 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Stir speed</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  valid sparger 1</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>spg_name_1</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="36" t="inlineStr">
+        <is>
+          <t>Tube</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Bare 1/8" OD x 1/16" ID Flexelene 135C tube orifice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  valid sparger 2</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>spg_name_2</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="inlineStr">
+        <is>
+          <t>Sintered</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>10 mm sintered-glass disc annulus on a tubular anode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Surface tension (water, T)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>N/m</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>IAPWS R1-76(2014) formulation, evaluated at 30 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Liquid density (water, T)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>rho_L</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>kg/m³</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="n">
+        <v>995.65</v>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>IAPWS-95, evaluated at 30 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Gravitational acceleration</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>g_const</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>m/s²</t>
+        </is>
+      </c>
+      <c r="D7" s="49" t="n">
+        <v>9.806649999999999</v>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Standard gravity (defined).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>O₂ diffusivity in water (T)</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>D_O2</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>m²/s</t>
+        </is>
+      </c>
+      <c r="D8" s="50" t="n">
+        <v>2.249e-09</v>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>O₂ diffusivity in water at 30 °C. Han &amp; Bartels (1996) fit log₁₀(D[cm²/s]) = −4.410 + 773.8/T − (506.4/T)² → 2.25e-9 m²/s at 303.15 K.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Pore size - grade 0</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>por0_um</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>µm</t>
+        </is>
+      </c>
+      <c r="D9" s="50" t="n">
+        <v>205</v>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>DURAN P0 160-250 µm, midpoint. ISO 4793 (paywalled) underlies; DURAN table is free.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Pore size - grade 1</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>por1_um</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>µm</t>
+        </is>
+      </c>
+      <c r="D10" s="50" t="n">
+        <v>130</v>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>DURAN P1 100-160 µm, midpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Pore size - grade 2</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>por2_um</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>µm</t>
+        </is>
+      </c>
+      <c r="D11" s="50" t="n">
+        <v>70</v>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>DURAN P2 40-100 µm, midpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Pore size - grade 3</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>por3_um</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>µm</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="n">
+        <v>28</v>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>DURAN P3 16-40 µm, midpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Pore size - grade 4</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>por4_um</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>µm</t>
+        </is>
+      </c>
+      <c r="D13" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>DURAN P4 10-16 µm, midpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Pore size - grade 5</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>por5_um</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>µm</t>
+        </is>
+      </c>
+      <c r="D14" s="47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>DURAN P5 1.0-1.6 µm, midpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Selected sinter pore diameter</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>por_pore</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D15" s="56">
+        <f>CHOOSE(por_grade+1,por0_um,por1_um,por2_um,por3_um,por4_um,por5_um)/1000000</f>
+        <v/>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>Picked by por_grade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Tube orifice diameter</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>tube_d_m</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D16" s="56">
+        <f>spg_ID/1000</f>
+        <v/>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>Tube ID in metres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Effective orifice/pore diameter</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>d_orifice</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D17" s="56">
+        <f>IF(sparger=spg_name_1,tube_d_m,IF(sparger=spg_name_2,por_pore,NA()))</f>
+        <v/>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>Tube ID or sinter pore; invalid sparger returns an error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Bubble detachment diameter</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>d_bubble</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D18" s="28">
+        <f>(6*d_orifice*sigma/(rho_L*g_const))^(1/3)</f>
+        <v/>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>Static low-flow force balance (buoyancy vs surface tension); valid in the quasi-static regime — see bubble_regime (§10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Bubble diameter (display)</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>d_bubble_mm</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D19" s="42">
+        <f>d_bubble*1000</f>
+        <v/>
+      </c>
+      <c r="E19" s="26" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Mendelson coefficient a</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>mend_a</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>Mendelson (1967) wave-theory bubble rise correlation (AIChE J, paywalled).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Mendelson coefficient b</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>mend_b</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="57" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>Mendelson (1967), as above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Bubble rise velocity</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>u_rise</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D22" s="43">
+        <f>SQRT(mend_a*sigma/(rho_L*d_bubble)+mend_b*g_const*d_bubble)</f>
+        <v/>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>Mendelson rise velocity, valid ~1–10 mm. Sub-mm bubbles (fine sinters) are out of range → bubble strip excluded and flagged (bubble_regime); §11 surface path and §14 optimiser unaffected. Tube = 4.1 mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Superficial gas velocity (sparge on)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>u_sg</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D23" s="28">
+        <f>(Q_CO2/1000000/60)/(A_x/1000000)</f>
+        <v/>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>Gas flow / liquid cross-section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Gas holdup (sparge on)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>holdup</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="28">
+        <f>u_sg/u_rise</f>
+        <v/>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>ε ≈ superficial gas velocity / rise velocity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Interfacial area for transfer</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>a_int</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>1/m</t>
+        </is>
+      </c>
+      <c r="D25" s="38">
+        <f>6*holdup/d_bubble</f>
+        <v/>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>a = 6ε/d_b (spheres).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Bubble-liquid contact time</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>t_contact</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D26" s="43">
+        <f>d_bubble/u_rise</f>
+        <v/>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>d_b / rise velocity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Liquid-film coefficient kL</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>kL</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D27" s="28">
+        <f>2*SQRT(D_O2/(PI()*t_contact))</f>
+        <v/>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Higbie penetration theory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>kLa during sparge</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>kLa_sparge</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>1/s</t>
+        </is>
+      </c>
+      <c r="D28" s="28">
+        <f>kL*a_int</f>
+        <v/>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>kL x a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kLa time-averaged</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>kLa_avg</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>1/s</t>
+        </is>
+      </c>
+      <c r="D29" s="52">
+        <f>kLa_sparge*duty</f>
+        <v/>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>x duty cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>O₂ strip rate at ceiling (sparge on)</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>strip_sparge</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D30" s="28">
+        <f>IF(d_bubble&lt;0.001,0,kLa_sparge*(V_charge/1000000)*O2_ceil_C*3600)</f>
+        <v/>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
+        <is>
+          <t>Bubble O₂ strip at the ceiling driving force (best case). 0 for sub-mm bubbles (fine sinter, bubble model out of range — see bubble_regime).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>O₂ strip rate time-averaged</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>strip_avg</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D31" s="28">
+        <f>strip_sparge*duty</f>
+        <v/>
+      </c>
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>x duty cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Strip capacity : excess-O₂</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>strip_ratio</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D32" s="42">
+        <f>IF(O2_excess&gt;0,strip_avg/O2_excess,NA())</f>
+        <v/>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
+        <is>
+          <t>Bubble strip : surplus. ≪1 — the §11 surface path is the real route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Required time-avg kLa</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>kLa_req</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>1/s</t>
+        </is>
+      </c>
+      <c r="D33" s="28">
+        <f>IF(O2_excess&gt;0,O2_excess/3600/((V_charge/1000000)*O2_ceil_C),NA())</f>
+        <v/>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>kLa that would exactly strip the excess at the ceiling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Entrainment velocity ceiling (rule of thumb)</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>u_g_max</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D34" s="40" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
+        <is>
+          <t>Provisional superficial-velocity ceiling above which droplet carryover to the hydrophilic vent filters becomes likely. Replace with measured value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Carryover flag</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>carry_flag</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="51">
+        <f>IF(u_sg&gt;u_g_max,"RISK","OK")</f>
+        <v/>
+      </c>
+      <c r="E35" s="26" t="inlineStr">
+        <is>
+          <t>Operating gas velocity vs ceiling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>CO₂ gas density (T,P)</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>rho_CO2</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>kg/m³</t>
+        </is>
+      </c>
+      <c r="D36" s="28">
+        <f>P_atm*(M_CO2/1000)/(R_gas*T_K)</f>
+        <v/>
+      </c>
+      <c r="E36" s="29" t="inlineStr">
+        <is>
+          <t>Ideal gas at surface conditions; for the orifice Weber number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Active sparge orifices</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>n_pores_active</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="32" t="inlineStr">
+        <is>
+          <t>Tube = 1. Sinter pore count unknown; 1 = worst case. DATA GAP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Gas velocity at orifice</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>v_orifice</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D38" s="28">
+        <f>(Q_CO2/1000000/60)/(n_pores_active*(PI()/4*d_orifice^2))</f>
+        <v/>
+      </c>
+      <c r="E38" s="29" t="inlineStr">
+        <is>
+          <t>Per-orifice superficial gas velocity during a sparge pulse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Orifice Weber number</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>We_orifice</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D39" s="28">
+        <f>rho_CO2*v_orifice^2*d_orifice/sigma</f>
+        <v/>
+      </c>
+      <c r="E39" s="29" t="inlineStr">
+        <is>
+          <t>Gas inertia vs surface tension at the orifice. Sets whether bubble detachment is quasi-static.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Bubble-formation regime</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>bubble_regime</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D40" s="28">
+        <f>IF(d_bubble&lt;0.001,"Sinter OOR – add fine-bubble model",IF(We_orifice&lt;2,"Static","Dynamic"))</f>
+        <v/>
+      </c>
+      <c r="E40" s="29" t="inlineStr">
+        <is>
+          <t>Tate's law assumes quasi-static detachment (We&lt;~2). 'Sinter OOR' = sub-mm bubble; the fine-sinter model isn't built yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>O₂ time-to-ceiling (no removal)</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>t_O2_ceiling</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D41" s="28">
+        <f>O2_ceil_C*(V_charge/1000000)/O2_excess*60</f>
+        <v/>
+      </c>
+      <c r="E41" s="29" t="inlineStr">
+        <is>
+          <t>Minutes to reach the O₂ ceiling from ~0 with no removal (steady, etaF=1) — the O₂ timescale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>O₂ time-to-ceiling (with time-avg strip)</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>t_O2_ceiling_strip</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D42" s="28">
+        <f>IF(O2_excess-strip_avg&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_excess-strip_avg)*60,9999)</f>
+        <v/>
+      </c>
+      <c r="E42" s="29" t="inlineStr">
+        <is>
+          <t>As above, crediting time-averaged bubble strip (≈unchanged → bubbles aren't the mechanism). 9999 = cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Stir-bar speed</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>stir_rpm</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>1/min</t>
         </is>
       </c>
-      <c r="D3" s="33" t="n">
+      <c r="D43" s="58" t="n">
         <v>500</v>
       </c>
-      <c r="E3" s="66" t="inlineStr">
-        <is>
-          <t>Stir setpoint. Input.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>Pioreactor stir setpoint. RPM floor ~125 (stalls below). Input/confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Stir-bar length</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>stir_len</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D44" s="58" t="n">
         <v>12</v>
       </c>
-      <c r="E4" s="66" t="inlineStr">
-        <is>
-          <t>Input.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tip speed</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="E44" s="59" t="inlineStr">
+        <is>
+          <t>Magnetic stir bar. Pioreactor max 20 mm; confirm the supplied bar's length. Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Stir-bar tip speed</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>tip_speed</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
       </c>
-      <c r="D5" s="35">
+      <c r="D45" s="28">
         <f>PI()*(stir_len/1000)*stir_rpm/60</f>
         <v/>
       </c>
-      <c r="E5" s="67" t="inlineStr">
+      <c r="E45" s="29" t="inlineStr">
         <is>
           <t>π·d·rpm/60.</t>
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Surface renewal frequency</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>s_renew</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>1/s</t>
+        </is>
+      </c>
+      <c r="D46" s="28">
+        <f>tip_speed/(vial_ID/1000)</f>
+        <v/>
+      </c>
+      <c r="E46" s="59" t="inlineStr">
+        <is>
+          <t>Surface renewal ≈ tip speed / vial ID. Coarse proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Surface liquid-film coeff kL</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>kL_surf</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D47" s="28">
+        <f>2*SQRT(D_O2*s_renew/PI())</f>
+        <v/>
+      </c>
+      <c r="E47" s="59" t="inlineStr">
+        <is>
+          <t>Danckwerts surface-renewal estimate — coarse; measure by gassing-out (§15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Surface area per volume</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>a_surf</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>1/m</t>
+        </is>
+      </c>
+      <c r="D48" s="28">
+        <f>interface_A/V_charge</f>
+        <v/>
+      </c>
+      <c r="E48" s="29" t="inlineStr">
+        <is>
+          <t>Free-surface area / liquid volume (mm²/mL = 1/m); uses interface_A (§1B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Surface O₂ transfer kLa</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>kLa_surf</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>1/s</t>
+        </is>
+      </c>
+      <c r="D49" s="28">
+        <f>kL_surf*a_surf</f>
+        <v/>
+      </c>
+      <c r="E49" s="59" t="inlineStr">
+        <is>
+          <t>kL_surf × a_surf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>O₂ strip via surface (ceiling)</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>surf_strip</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D50" s="28">
+        <f>kLa_surf_used*(V_charge/1000000)*O2_ceil_C*3600</f>
+        <v/>
+      </c>
+      <c r="E50" s="59" t="inlineStr">
+        <is>
+          <t>O₂ removed across the stirred surface at ceiling driving force, headspace ~O₂-free. Best case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>Surface strip : excess-O₂</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>surf_ratio</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D51" s="28">
+        <f>IF(O2_excess&gt;0,surf_strip/O2_excess,NA())</f>
+        <v/>
+      </c>
+      <c r="E51" s="59" t="inlineStr">
+        <is>
+          <t>Surface strip : surplus. Coarse (kL_surf). ≫ bubble path — the dominant O₂ route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Headspace O₂ frac. to vent excess</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>y_O2_vent</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="28">
+        <f>IF(CO2_supply&gt;0,O2_excess/CO2_supply,NA())</f>
+        <v/>
+      </c>
+      <c r="E52" s="29" t="inlineStr">
+        <is>
+          <t>Headspace O₂ fraction at which the vented CO₂ carries the surplus out. kL-independent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>DO in equilib. with that headspace</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>DO_vent_eq</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="D53" s="28">
+        <f>H_O2_T*y_O2_vent*P_atm*1000</f>
+        <v/>
+      </c>
+      <c r="E53" s="29" t="inlineStr">
+        <is>
+          <t>Dissolved O₂ matching that headspace fraction. ≪ ceiling → vent-feasible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Headspace flush time</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>hs_flush_time</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D54" s="28">
+        <f>headspace_V/(Q_CO2*duty)</f>
+        <v/>
+      </c>
+      <c r="E54" s="29" t="inlineStr">
+        <is>
+          <t>Avg CO₂ flow to displace one headspace volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Combined O₂ removal : excess</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>O2_removal_ratio</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D55" s="28">
+        <f>IF(O2_excess&gt;0,(strip_avg+surf_strip)/O2_excess,NA())</f>
+        <v/>
+      </c>
+      <c r="E55" s="59" t="inlineStr">
+        <is>
+          <t>Gas removal (bubble + surface) vs the steady-growth surplus O2_excess (which already nets the cathodic sink and biological uptake). &gt;=1 = ceiling held at steady growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>O₂ time-to-ceiling (LAG, no uptake)</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>t_O2_ceiling_lag</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D56" s="28">
+        <f>O2_ceil_C*(V_charge/1000000)/O2_net_gen*60</f>
+        <v/>
+      </c>
+      <c r="E56" s="29" t="inlineStr">
+        <is>
+          <t>Lag/establishment: no biological O₂ uptake yet, so the full net O₂ accumulates. Worst case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>O₂ time-to-ceiling (with all removal)</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>t_O2_ceiling_rem</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D57" s="28">
+        <f>IF(O2_net_gen-strip_avg-surf_strip&gt;0,O2_ceil_C*(V_charge/1000000)/(O2_net_gen-strip_avg-surf_strip)*60,9999)</f>
+        <v/>
+      </c>
+      <c r="E57" s="59" t="inlineStr">
+        <is>
+          <t>LAG-with-removal partner to t_O2_ceiling_lag: cells not yet consuming, so removal (bubble + surface) must offset the full net electrolytic O₂ (O2_net_gen, which already nets the cathodic sink), not the steady surplus. 9999 = removal holds the ceiling (no finite time).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Schedule mode</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>sched_mode</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="58" t="inlineStr">
+        <is>
+          <t>Optimal</t>
+        </is>
+      </c>
+      <c r="E58" s="31" t="inlineStr">
+        <is>
+          <t>Manual = use the values you type below; Optimal = the model computes &amp; applies the optimum. Dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>Manual pulse duration</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>spg_dur_man</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D59" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="31" t="inlineStr">
+        <is>
+          <t>Your pulse length, used when sched_mode=Manual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>Manual sparge interval</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>spg_int_man</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D60" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="31" t="inlineStr">
+        <is>
+          <t>Your interval, used when sched_mode=Manual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>Target dissolved-O₂ ceiling fraction</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>target_DO_frac</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E61" s="31" t="inlineStr">
+        <is>
+          <t>Hold DO at ≤ this × the inhibition ceiling. Lower = safer O₂ margin → needs more flushing. Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Min carbon supply margin</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>carbon_margin_min</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="31" t="inlineStr">
+        <is>
+          <t>Required CO₂ supply : fixation demand. Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Duty floor — carbon</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>duty_carbon</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D63" s="28">
+        <f>carbon_margin_min*CO2_cons/(nCO2_rate*3600)</f>
+        <v/>
+      </c>
+      <c r="E63" s="29" t="inlineStr">
+        <is>
+          <t>Duty needed so CO₂ supply ≥ margin × fixation demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Duty floor — O₂ venting (lag)</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>duty_O2vent</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" s="28">
+        <f>O2_net_gen/(target_DO_frac*(O2_ceil_Pa/P_atm))/(nCO2_rate*3600)</f>
+        <v/>
+      </c>
+      <c r="E64" s="29" t="inlineStr">
+        <is>
+          <t>Duty so the vented CO₂ throughput carries the worst-case (lag, no uptake) net O₂ out at ≤ target DO. Usually the binding floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>Optimal duty cycle</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>duty_opt</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D65" s="28">
+        <f>MAX(duty_carbon,duty_O2vent)</f>
+        <v/>
+      </c>
+      <c r="E65" s="29" t="inlineStr">
+        <is>
+          <t>Least feasible CO₂ (binding of the two floors). O₂-venting binds, not pH (buffer holds pH; over-dose limited by pCO₂ lag).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>Max interval — O₂ flush frequency</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>spg_int_max</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D66" s="28">
+        <f>target_DO_frac*t_O2_ceiling_lag</f>
+        <v/>
+      </c>
+      <c r="E66" s="29" t="inlineStr">
+        <is>
+          <t>Pulses must be frequent enough that DO doesn't spike past target between flushes (lag worst-case).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>► OPTIMAL pulse duration</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>spg_dur_opt</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D67" s="61">
+        <f>pulse_floor</f>
+        <v/>
+      </c>
+      <c r="E67" s="62" t="inlineStr">
+        <is>
+          <t>ANSWER. Shortest reliable pulse → most frequent, smoothest DO, best OD-read windows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>► OPTIMAL sparge interval</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>spg_int_opt</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D68" s="61">
+        <f>MIN(spg_dur_opt/(60*duty_opt),spg_int_max)</f>
+        <v/>
+      </c>
+      <c r="E68" s="62" t="inlineStr">
+        <is>
+          <t>ANSWER. From optimal duty at the floor pulse, capped by the O₂-flush frequency limit. Set sched_mode=Optimal to apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  optimal interval (seconds)</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>spg_int_opt_s</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D69" s="28">
+        <f>spg_int_opt*60</f>
+        <v/>
+      </c>
+      <c r="E69" s="62" t="inlineStr">
+        <is>
+          <t>Convenience: interval in seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  resulting duty / binding constraint</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>duty_actual</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="28">
+        <f>spg_dur_opt/(spg_int_opt*60)</f>
+        <v/>
+      </c>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>Achieved duty at the optimum (= duty_opt unless the flush-frequency cap binds, raising it).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  binding constraint</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>opt_binding</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" s="28">
+        <f>IF(spg_int_opt&lt;spg_dur_opt/(60*duty_opt)-0.0001,"O2-FREQ",IF(duty_O2vent&gt;=duty_carbon,"O2-VENT","CARBON"))</f>
+        <v/>
+      </c>
+      <c r="E71" s="29" t="inlineStr">
+        <is>
+          <t>Which limit sets the schedule: O2-VENT (O₂ removal), O2-FREQ (flush frequency), or CARBON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OD-window check</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>od_ok</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D72" s="28">
+        <f>IF(spg_int_opt*60-spg_dur_opt&gt;=5,"OK","TIGHT")</f>
+        <v/>
+      </c>
+      <c r="E72" s="29" t="inlineStr">
+        <is>
+          <t>≥5 s gap between pulses for an OD read. Can't measure OD while sparging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>ACCURACY LIMIT — no validated kinetics</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>kinetic_caveat</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" s="28">
+        <f>"see note →"</f>
+        <v/>
+      </c>
+      <c r="E73" s="59" t="inlineStr">
+        <is>
+          <t>Constraint-proxy optimiser, not a fitted growth model — no validated μ(O₂,pH,CO₂) or lag kinetics exist for this system. Gives the lag-minimising direction, not an exact optimum; bounded by etaF, surface kL and the unbuffered-pH simplification. Validate empirically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>Measured surface kLa</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>kLa_meas</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>1/h</t>
+        </is>
+      </c>
+      <c r="D74" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="59" t="inlineStr">
+        <is>
+          <t>Measured surface kLa (gassing-out). 0 = use the §11 estimate. kLa = slope of −LN(1−DO/DO_sat) vs time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>Surface kLa used downstream</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>kLa_surf_used</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>1/s</t>
+        </is>
+      </c>
+      <c r="D75" s="28">
+        <f>IF(kLa_meas&gt;0,kLa_meas/3600,kLa_surf)</f>
+        <v/>
+      </c>
+      <c r="E75" s="29" t="inlineStr">
+        <is>
+          <t>What §11 actually uses: the measured value if entered, otherwise the theoretical estimate. Swap estimate→truth here once measured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="83" t="inlineStr">
+        <is>
+          <t>IMPORTS (from other tabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>(import) EXCESS O₂ to remove</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>O2_excess</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D78" s="80">
+        <f>Biology!$D$9</f>
+        <v/>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>(import) CO₂ consumed (carbon fixation)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CO2_cons</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D79" s="80">
+        <f>Biology!$D$8</f>
+        <v/>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>(import) O₂ ceiling (partial pressure)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>O2_ceil_Pa</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D80" s="80">
+        <f>Biology!$D$19</f>
+        <v/>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>(import) Dissolved-O₂ ceiling</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>O2_ceil_C</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>mol/m³</t>
+        </is>
+      </c>
+      <c r="D81" s="80">
+        <f>Biology!$D$20</f>
+        <v/>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>(import) Temperature (absolute)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>T_K</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D82" s="80">
+        <f>Biology!$D$11</f>
+        <v/>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>(import) Surface pressure</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P_atm</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D83" s="80">
+        <f>Biology!$D$12</f>
+        <v/>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>(import) Henry solubility O₂ at T</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>H_O2_T</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>mol/m³/Pa</t>
+        </is>
+      </c>
+      <c r="D84" s="80">
+        <f>Biology!$D$17</f>
+        <v/>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>(import) CO₂ molar flow during sparge</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>nCO2_rate</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>mol/s</t>
+        </is>
+      </c>
+      <c r="D85" s="81">
+        <f>Dosing!$D$9</f>
+        <v/>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>From Dosing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>(import) Sparge duty cycle</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>duty</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" s="81">
+        <f>Dosing!$D$15</f>
+        <v/>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>From Dosing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>(import) Ideal gas constant</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>R_gas</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>J/mol/K</t>
+        </is>
+      </c>
+      <c r="D87" s="81">
+        <f>Dosing!$D$7</f>
+        <v/>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>From Dosing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>(import) CO₂ volumetric flow rate</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Q_CO2</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D88" s="81">
+        <f>Dosing!$D$3</f>
+        <v/>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>From Dosing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>(import) Molar mass CO₂</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>M_CO2</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>g/mol</t>
+        </is>
+      </c>
+      <c r="D89" s="81">
+        <f>Dosing!$D$8</f>
+        <v/>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>From Dosing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>(import) Min reliable pulse (solenoid floor)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>pulse_floor</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D90" s="81">
+        <f>Dosing!$D$6</f>
+        <v/>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>From Dosing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>(import) Average CO₂ supply rate</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CO2_supply</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D91" s="81">
+        <f>Dosing!$D$13</f>
+        <v/>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>From Dosing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>(import) Net O₂ to dissolved pool</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>O2_net_gen</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D92" s="82">
+        <f>Electrochemistry!$D$22</f>
+        <v/>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>From Electrochemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>(import) Internal cross-sectional area</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>A_x</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>mm²</t>
+        </is>
+      </c>
+      <c r="D93" s="84">
+        <f>Geometry!$D$16</f>
+        <v/>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>From Geometry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>(import) Gas-liquid interfacial area</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>interface_A</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>mm²</t>
+        </is>
+      </c>
+      <c r="D94" s="84">
+        <f>Geometry!$D$39</f>
+        <v/>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>From Geometry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>(import) Vial internal diameter</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>vial_ID</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D95" s="84">
+        <f>Geometry!$D$15</f>
+        <v/>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>From Geometry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>(import) Headspace gas volume</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>headspace_V</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D96" s="84">
+        <f>Geometry!$D$44</f>
+        <v/>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>From Geometry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>(import) Sparge tube ID</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>spg_ID</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D97" s="84">
+        <f>Geometry!$D$26</f>
+        <v/>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>From Geometry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>(import) LIQUID VOLUME TO CHARGE</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>V_charge</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="D98" s="84">
+        <f>Geometry!$D$36</f>
+        <v/>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>From Geometry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>(import) Sinter porosity grade (if Sintered)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>por_grade</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="D99">
+        <f>Summary!$D$5</f>
+        <v/>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>From Summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>(import) Sparger type</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>sparger</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D100">
+        <f>Summary!$D$4</f>
+        <v/>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>From Summary.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="D32">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="2"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D35">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="2">
+      <formula>"RISK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D39">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="2"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D40">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"Static"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+      <formula>"Dynamic"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D41">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="15"/>
+        <cfvo type="num" val="60"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D51">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="3"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D55">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="3"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D56">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="15"/>
+        <cfvo type="num" val="60"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D72">
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="1">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
+      <formula>"TIGHT"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor theme="9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="70" min="1" max="1"/>
+    <col width="15" customWidth="1" style="70" min="2" max="2"/>
+    <col width="60" customWidth="1" style="70" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="78" t="inlineStr">
+        <is>
+          <t>CO₂ DOSING &amp; SCHEDULE  (dosing, feasibility, optimiser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="77" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B2" s="77" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" s="77" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D2" s="77" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E2" s="77" t="inlineStr">
+        <is>
+          <t>Source / assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>CO₂ volumetric flow rate</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Q_CO2</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D3" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Needle-valve setting at ~atmospheric surface. Input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Sparge duration per pulse</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>spg_dur</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D4" s="38">
+        <f>IF(sched_mode="Optimal",spg_dur_opt,IF(sched_mode="Manual",spg_dur_man,NA()))</f>
+        <v/>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Pulse duration ACTUALLY USED. Driven by §14: Manual→spg_dur_man, Optimal→computed optimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Sparge interval</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>spg_int</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D5" s="38">
+        <f>IF(sched_mode="Optimal",spg_int_opt,IF(sched_mode="Manual",spg_int_man,NA()))</f>
+        <v/>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Sparge interval ACTUALLY USED. Driven by §14: Manual→spg_int_man, Optimal→computed optimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Min reliable pulse (solenoid floor)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>pulse_floor</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Smallest dependable actuation. Provisional - characterise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Ideal gas constant</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>R_gas</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>J/mol/K</t>
+        </is>
+      </c>
+      <c r="D7" s="53" t="n">
+        <v>8.314462618</v>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>NIST CODATA (exact, SI 2019).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Molar mass CO₂</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>M_CO2</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>g/mol</t>
+        </is>
+      </c>
+      <c r="D8" s="54" t="n">
+        <v>44.0095</v>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>NIST WebBook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>CO₂ molar flow during sparge</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>nCO2_rate</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>mol/s</t>
+        </is>
+      </c>
+      <c r="D9" s="55">
+        <f>P_atm*(Q_CO2/1000000/60)/(R_gas*T_K)</f>
+        <v/>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>Ideal gas n=PV/RT at surface conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>CO₂ per pulse</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>CO2_pulse</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>mol</t>
+        </is>
+      </c>
+      <c r="D10" s="52">
+        <f>nCO2_rate*spg_dur</f>
+        <v/>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>Molar flow x duration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Pulses per hour</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>pulses_h</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>1/h</t>
+        </is>
+      </c>
+      <c r="D11" s="38">
+        <f>60/spg_int</f>
+        <v/>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>60 / interval(min).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Pulses per day</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>pulses_d</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>1/d</t>
+        </is>
+      </c>
+      <c r="D12" s="39">
+        <f>pulses_h*24</f>
+        <v/>
+      </c>
+      <c r="E12" s="20" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Average CO₂ supply rate</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>CO2_supply</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D13" s="28">
+        <f>CO2_pulse*pulses_h</f>
+        <v/>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>Time-averaged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>CO₂ supply : carbon demand</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>CO2_sd_ratio</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D14" s="38">
+        <f>IF(CO2_cons&gt;0,CO2_supply/CO2_cons,NA())</f>
+        <v/>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>Carbon supply : demand (~20× = over-dosed, non-limiting). CO₂ mostly bursts at the surface → §11 headspace sweep active from pulse 1. High pCO₂ extends lag (Amer &amp; Kim 2023).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Sparge duty cycle</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>duty</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="43">
+        <f>spg_dur/(spg_int*60)</f>
+        <v/>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>Fraction of time sparging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>O₂ accumulated per interval</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>O2_accum</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>mol</t>
+        </is>
+      </c>
+      <c r="D16" s="52">
+        <f>O2_excess/60*spg_int</f>
+        <v/>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>Excess O₂ generated between pulses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>O₂ removable per pulse</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>O2_strip_pulse</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>mol</t>
+        </is>
+      </c>
+      <c r="D17" s="52">
+        <f>strip_sparge/3600*spg_dur</f>
+        <v/>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>O₂ a pulse strips (at ceiling).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Per-pulse balance</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>sched_bal</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D18" s="42">
+        <f>IF(O2_accum&gt;0,O2_strip_pulse/O2_accum,NA())</f>
+        <v/>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>&gt;=1 = each pulse clears the interval's O₂ by stripping alone. Bubble path only — the dominant O₂ route is the §11 surface/headspace path; see §14 optimiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Duration floor check</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>dur_ok</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="51">
+        <f>IF(spg_dur&gt;=pulse_floor,"OK","LOW")</f>
+        <v/>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>Pulse must exceed reliable actuation time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="83" t="inlineStr">
+        <is>
+          <t>IMPORTS (from other tabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>(import) EXCESS O₂ to remove</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>O2_excess</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D22" s="80">
+        <f>Biology!$D$9</f>
+        <v/>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>(import) CO₂ consumed (carbon fixation)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CO2_cons</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D23" s="80">
+        <f>Biology!$D$8</f>
+        <v/>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>(import) Surface pressure</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>P_atm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D24" s="80">
+        <f>Biology!$D$12</f>
+        <v/>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>(import) Temperature (absolute)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>T_K</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D25" s="80">
+        <f>Biology!$D$11</f>
+        <v/>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>From Biology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>(import) ► OPTIMAL sparge interval</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>spg_int_opt</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D26" s="79">
+        <f>'Mass Transfer'!$D$68</f>
+        <v/>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>(import) Manual sparge interval</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>spg_int_man</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D27" s="79">
+        <f>'Mass Transfer'!$D$60</f>
+        <v/>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>(import) ► OPTIMAL pulse duration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>spg_dur_opt</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D28" s="79">
+        <f>'Mass Transfer'!$D$67</f>
+        <v/>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>(import) O₂ strip rate at ceiling (sparge on)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>strip_sparge</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mol/h</t>
+        </is>
+      </c>
+      <c r="D29" s="79">
+        <f>'Mass Transfer'!$D$30</f>
+        <v/>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>(import) Manual pulse duration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>spg_dur_man</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D30" s="79">
+        <f>'Mass Transfer'!$D$59</f>
+        <v/>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>(import) Schedule mode</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sched_mode</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="79">
+        <f>'Mass Transfer'!$D$58</f>
+        <v/>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>From Mass Transfer.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="5"/>
+        <cfvo type="num" val="20"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="2">
+      <formula>"LOW"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D58" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid entry" error="Choose from the list." type="list" errorStyle="stop">
+      <formula1>"Manual,Optimal"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1809,6 +8022,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="70">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -2114,6 +8328,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="70">
       <c r="A24" s="9" t="inlineStr">
         <is>
@@ -2352,6 +8567,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="15" customHeight="1" s="70">
       <c r="A35" s="9" t="inlineStr">
         <is>
@@ -3212,6 +9428,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70" ht="15" customHeight="1" s="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
@@ -5668,6 +11885,7 @@
       <c r="D177" s="51" t="n"/>
       <c r="E177" s="26" t="n"/>
     </row>
+    <row r="178"/>
     <row r="179" ht="24" customHeight="1" s="70">
       <c r="A179" s="9" t="inlineStr">
         <is>
@@ -6015,6 +12233,7 @@
         </is>
       </c>
     </row>
+    <row r="193"/>
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
@@ -6437,6 +12656,7 @@
         </is>
       </c>
     </row>
+    <row r="211"/>
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
@@ -6701,6 +12921,7 @@
         </is>
       </c>
     </row>
+    <row r="223"/>
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
@@ -6915,6 +13136,7 @@
         </is>
       </c>
     </row>
+    <row r="233"/>
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
@@ -7362,6 +13584,7 @@
         </is>
       </c>
     </row>
+    <row r="252"/>
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -1284,7 +1284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="70" min="1" max="1"/>
@@ -1405,7 +1405,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="76" t="inlineStr">
         <is>
@@ -1664,6 +1663,93 @@
           <t>From Biology.</t>
         </is>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="76" t="inlineStr">
+        <is>
+          <t>KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Verified / handbook / defined / standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Literature-supported (~90%)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <f t="array" ref="D6">A_x_in/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Design assumption (~70%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Weak / coarse estimate (~50%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Guess - replace when known</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - need to measure</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>variable (set/measure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>fixed data / constant</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="n"/>
+      <c r="C30" s="34" t="n"/>
+      <c r="D30" s="35" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="n"/>
+      <c r="C31" s="34" t="n"/>
+      <c r="D31" s="35" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -2832,7 +2918,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="83" t="inlineStr">
         <is>
@@ -3429,7 +3514,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="83" t="inlineStr">
         <is>
@@ -4471,7 +4555,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="83" t="inlineStr">
         <is>
@@ -6504,7 +6587,6 @@
         </is>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="83" t="inlineStr">
         <is>
@@ -7694,7 +7776,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="83" t="inlineStr">
         <is>
@@ -8022,7 +8103,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="70">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -8328,7 +8408,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="70">
       <c r="A24" s="9" t="inlineStr">
         <is>
@@ -8567,7 +8646,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="15" customHeight="1" s="70">
       <c r="A35" s="9" t="inlineStr">
         <is>
@@ -9428,7 +9506,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70" ht="15" customHeight="1" s="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
@@ -11885,7 +11962,6 @@
       <c r="D177" s="51" t="n"/>
       <c r="E177" s="26" t="n"/>
     </row>
-    <row r="178"/>
     <row r="179" ht="24" customHeight="1" s="70">
       <c r="A179" s="9" t="inlineStr">
         <is>
@@ -12233,7 +12309,6 @@
         </is>
       </c>
     </row>
-    <row r="193"/>
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
@@ -12656,7 +12731,6 @@
         </is>
       </c>
     </row>
-    <row r="211"/>
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
@@ -12921,7 +12995,6 @@
         </is>
       </c>
     </row>
-    <row r="223"/>
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
@@ -13136,7 +13209,6 @@
         </is>
       </c>
     </row>
-    <row r="233"/>
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
@@ -13584,7 +13656,6 @@
         </is>
       </c>
     </row>
-    <row r="252"/>
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -328,8 +328,9 @@
     <definedName name="z_e_H2" localSheetId="2">Electrochemistry!$D$16</definedName>
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$17</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
+    <definedName name="HOCl_max" localSheetId="3">Chemistry!$D$125</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -347,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="1044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="1057">
   <si>
     <t>CO₂ DOSING FLOWRATES</t>
   </si>
@@ -3479,6 +3480,45 @@
   </si>
   <si>
     <t>Pous 2022 &amp; 2023; Rovira-Alsina 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max achievable HOCl (medium chloride × HOCl fraction)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOCl_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mg/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conservative ceiling: all chloride oxidised to free chlorine, ×HOCl fraction at operating pH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organism DO data present?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red = the selected organism has no measured DO thresholds, so every DO/sparge verdict above is running on missing data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHEMISTRY OUTCOMES (Chemistry tab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endpoint pH (worst-case, full sparge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating pH at the CO2 trough. Green 6.5-7.5; red outside 6-8.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max HOCl (bleaching)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mg/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst-case hypochlorite from the medium's chloride. Green &lt;0.1, red &gt;1 mg/L. Zero for chloride-free media.</t>
   </si>
 </sst>
 </file>
@@ -3866,7 +3906,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -4052,6 +4092,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFC00"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFC00"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFFFC00"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFC00"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11"/>
@@ -4059,7 +4114,7 @@
     <xf numFmtId="0" fontId="29" fillId="10" borderId="11"/>
     <xf numFmtId="0" fontId="30" fillId="18" borderId="11"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4241,6 +4296,7 @@
     <xf numFmtId="168" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="170" fontId="27" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf applyNumberFormat="1" numFmtId="165" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -5284,13 +5340,17 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="91"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="99"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="21"/>
+    <row r="34" spans="1:6">
+      <c r="A34" s="91" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D34" s="96" t="str">
+        <f>IF(AND(ISNUMBER(Biology!$D$45),ISNUMBER(Biology!$D$46),ISNUMBER(Biology!$D$47),ISNUMBER(Biology!$D$48)),"inputs present","DATA GAP - organism DO thresholds unmeasured; DO &amp; sparge results unreliable")</f>
+        <v>DATA GAP - organism DO thresholds unmeasured; DO &amp; sparge results unreliable</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>1049</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="110" t="s">
@@ -5677,29 +5737,40 @@
       <c r="E63" s="20"/>
       <c r="F63" s="20"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="20"/>
-      <c r="B64" s="20"/>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="110"/>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="20"/>
-      <c r="B66" s="20"/>
-      <c r="C66" s="20"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
+    <row r="64" spans="1:6">
+      <c r="A64" s="110" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="91" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C65" s="96" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D65" s="131">
+        <f>Chemistry!$D$103</f>
+        <v>6.31</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="91" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C66" s="96" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D66" s="131">
+        <f>Chemistry!$D$125</f>
+        <v>8.87</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="20"/>
@@ -5718,6 +5789,28 @@
       <c r="F68" s="20"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D65">
+    <cfRule type="expression" dxfId="15" priority="21" stopIfTrue="1">
+      <formula>OR(D65&lt;6,D65&gt;8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="22" stopIfTrue="1">
+      <formula>OR(D65&lt;6.5,D65&gt;7.5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="23" stopIfTrue="1">
+      <formula>ISNUMBER(D65)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D66">
+    <cfRule type="expression" dxfId="15" priority="24" stopIfTrue="1">
+      <formula>D66&gt;1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="25" stopIfTrue="1">
+      <formula>D66&gt;0.1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="26" stopIfTrue="1">
+      <formula>ISNUMBER(D66)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B54:B62">
     <cfRule type="expression" dxfId="22" priority="15" stopIfTrue="1">
       <formula>EXACT(B54,"HIGH")</formula>
@@ -5745,15 +5838,15 @@
       <formula>ISNUMBER(SEARCH("calibrate this",D13))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D19:D33">
+  <conditionalFormatting sqref="D19:D34">
     <cfRule type="expression" dxfId="15" priority="11" stopIfTrue="1">
-      <formula>OR(ISNUMBER(SEARCH("INCONSISTENT",D19)),ISNUMBER(SEARCH("OVER",D19)),ISNUMBER(SEARCH("BELOW",D19)),ISNUMBER(SEARCH("EXCEED",D19)),ISNUMBER(SEARCH("NO CALIB",D19)),ISNUMBER(SEARCH("calibrate this",D19)),ISNUMBER(SEARCH("RISK",D19)),ISNUMBER(SEARCH("EXPLOSIVE",D19)),ISNUMBER(SEARCH("OOR",D19)),ISNUMBER(SEARCH("insufficient",D19)),ISNUMBER(SEARCH("TIP SPEED",D19)),ISNUMBER(SEARCH("SHORTFALL",D19)),EXACT(D19,"OUT"),EXACT(D19,"LOW"))</formula>
+      <formula>OR(ISNUMBER(SEARCH("INCONSISTENT",D19)),ISNUMBER(SEARCH("OVER",D19)),ISNUMBER(SEARCH("BELOW",D19)),ISNUMBER(SEARCH("EXCEED",D19)),ISNUMBER(SEARCH("NO CALIB",D19)),ISNUMBER(SEARCH("calibrate this",D19)),ISNUMBER(SEARCH("RISK",D19)),ISNUMBER(SEARCH("EXPLOSIVE",D19)),ISNUMBER(SEARCH("OOR",D19)),ISNUMBER(SEARCH("insufficient",D19)),ISNUMBER(SEARCH("TIP SPEED",D19)),ISNUMBER(SEARCH("SHORTFALL",D19)),EXACT(D19,"OUT"),EXACT(D19,"LOW"),ISNUMBER(SEARCH("GAP",D19)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="12" stopIfTrue="1">
       <formula>OR(ISNUMBER(SEARCH("above optimum",D19)),ISNUMBER(SEARCH("watch",D19)),ISNUMBER(SEARCH("NEAREST",D19)),ISNUMBER(SEARCH("unknown",D19)),ISNUMBER(SEARCH("TIGHT",D19)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="13" stopIfTrue="1">
-      <formula>OR(EXACT(D19,"OK"),ISNUMBER(SEARCH("calibrated:",D19)),ISNUMBER(SEARCH("optimum",D19)),ISNUMBER(SEARCH("above min",D19)),ISNUMBER(SEARCH("CARBON-limited",D19)),ISNUMBER(SEARCH("Static",D19)),ISNUMBER(SEARCH("Dynamic",D19)))</formula>
+      <formula>OR(EXACT(D19,"OK"),ISNUMBER(SEARCH("calibrated:",D19)),ISNUMBER(SEARCH("optimum",D19)),ISNUMBER(SEARCH("above min",D19)),ISNUMBER(SEARCH("CARBON-limited",D19)),ISNUMBER(SEARCH("Static",D19)),ISNUMBER(SEARCH("Dynamic",D19)),ISNUMBER(SEARCH("present",D19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8349,7 +8442,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFC00"/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -9945,6 +10038,24 @@
     </row>
     <row r="123" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="111"/>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="17" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B125" s="18" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D125" s="63">
+        <f>pH_Cl*pH_fHOCl*52460</f>
+        <v>8.87</v>
+      </c>
+      <c r="E125" s="52" t="s">
+        <v>1047</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13099,7 +13210,7 @@
       </c>
       <c r="C113" s="20"/>
       <c r="D113" s="24" t="e">
-        <f>IF(ISNUMBER(DO_ss),IF(DO_ss&lt;DO_impair,"Surface stripping holds DO under impairment - sparge is CARBON-limited (long interval); the O2-limited interval is the conservative fallback until kL_surf is measured","Surface stripping insufficient - sparge must vent O2 - use the O2-limited interval"),"organism DO unknown")</f>
+        <f>IF(AND(ISNUMBER(DO_ss),ISNUMBER(DO_impair)),IF(DO_ss&lt;DO_impair,"Surface stripping holds DO under impairment - sparge is CARBON-limited (long interval); the O2-limited interval is the conservative fallback until kL_surf is measured","Surface stripping insufficient - sparge must vent O2 - use the O2-limited interval"),"organism DO unknown")</f>
         <v>#N/A</v>
       </c>
       <c r="E113" s="84" t="s">
@@ -13392,7 +13503,7 @@
         <v>112</v>
       </c>
       <c r="D131" s="24" t="e">
-        <f>O2_excess*32/(DO_impair*3600*(V_charge/1000000)*a_surf)</f>
+        <f>IF(ISNUMBER(DO_impair),O2_excess*32/(DO_impair*3600*(V_charge/1000000)*a_surf),NA())</f>
         <v>#N/A</v>
       </c>
       <c r="E131" s="108" t="s">

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martincurrie/andeye Dropbox/andeye/Projects/electroPioreactor/Media/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D464189B-8A15-2342-B5DA-D9385230985D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C80E64-664B-9C44-BF75-F5FF75F96D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="16300" windowHeight="18060" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="14280" windowHeight="18060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -114,6 +114,7 @@
     <definedName name="has_cal" localSheetId="5">'Mass Transfer'!$D$119</definedName>
     <definedName name="headspace_V" localSheetId="1">Geometry!$D$49</definedName>
     <definedName name="headspace_V" localSheetId="5">'Mass Transfer'!$D$19</definedName>
+    <definedName name="HOCl_max" localSheetId="3">Chemistry!$D$125</definedName>
     <definedName name="holdup" localSheetId="5">'Mass Transfer'!$D$48</definedName>
     <definedName name="hs_flush_time" localSheetId="5">'Mass Transfer'!$D$77</definedName>
     <definedName name="I_app" localSheetId="2">Electrochemistry!$D$19</definedName>
@@ -328,9 +329,8 @@
     <definedName name="z_e_H2" localSheetId="2">Electrochemistry!$D$16</definedName>
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$17</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
-    <definedName name="HOCl_max" localSheetId="3">Chemistry!$D$125</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -348,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="1057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="1054">
   <si>
     <t>CO₂ DOSING FLOWRATES</t>
   </si>
@@ -3482,43 +3482,34 @@
     <t>Pous 2022 &amp; 2023; Rovira-Alsina 2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Max achievable HOCl (medium chloride × HOCl fraction)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOCl_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mg/L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conservative ceiling: all chloride oxidised to free chlorine, ×HOCl fraction at operating pH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organism DO data present?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red = the selected organism has no measured DO thresholds, so every DO/sparge verdict above is running on missing data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHEMISTRY OUTCOMES (Chemistry tab)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endpoint pH (worst-case, full sparge)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating pH at the CO2 trough. Green 6.5-7.5; red outside 6-8.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max HOCl (bleaching)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mg/L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worst-case hypochlorite from the medium's chloride. Green &lt;0.1, red &gt;1 mg/L. Zero for chloride-free media.</t>
+    <t>Max achievable HOCl (medium chloride × HOCl fraction)</t>
+  </si>
+  <si>
+    <t>HOCl_max</t>
+  </si>
+  <si>
+    <t>mg/L</t>
+  </si>
+  <si>
+    <t>conservative ceiling: all chloride oxidised to free chlorine, ×HOCl fraction at operating pH</t>
+  </si>
+  <si>
+    <t>Organism DO data present?</t>
+  </si>
+  <si>
+    <t>Red = the selected organism has no measured DO thresholds, so every DO/sparge verdict above is running on missing data.</t>
+  </si>
+  <si>
+    <t>Endpoint pH (worst-case, full sparge)</t>
+  </si>
+  <si>
+    <t>Operating pH at the CO2 trough. Green 6.5-7.5; red outside 6-8.</t>
+  </si>
+  <si>
+    <t>Max HOCl (bleaching)</t>
+  </si>
+  <si>
+    <t>Worst-case hypochlorite from the medium's chloride. Green &lt;0.1, red &gt;1 mg/L. Zero for chloride-free media.</t>
   </si>
 </sst>
 </file>
@@ -4114,7 +4105,7 @@
     <xf numFmtId="0" fontId="29" fillId="10" borderId="11"/>
     <xf numFmtId="0" fontId="30" fillId="18" borderId="11"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4294,9 +4285,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf applyNumberFormat="1" numFmtId="165" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -4304,7 +4294,7 @@
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="29">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4400,6 +4390,54 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4749,7 +4787,7 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -5148,9 +5186,9 @@
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
-      <c r="D23" s="92" t="e">
+      <c r="D23" s="92" t="str">
         <f>'Mass Transfer'!$D$113</f>
-        <v>#N/A</v>
+        <v>organism DO unknown</v>
       </c>
       <c r="E23" s="23" t="str">
         <f>HYPERLINK("#'Mass Transfer'!D113","→ Mass")</f>
@@ -5322,7 +5360,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="91" t="s">
         <v>103</v>
       </c>
@@ -5340,10 +5378,11 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="91" t="s">
         <v>1048</v>
       </c>
+      <c r="C34" s="20"/>
       <c r="D34" s="96" t="str">
         <f>IF(AND(ISNUMBER(Biology!$D$45),ISNUMBER(Biology!$D$46),ISNUMBER(Biology!$D$47),ISNUMBER(Biology!$D$48)),"inputs present","DATA GAP - organism DO thresholds unmeasured; DO &amp; sparge results unreliable")</f>
         <v>DATA GAP - organism DO thresholds unmeasured; DO &amp; sparge results unreliable</v>
@@ -5352,137 +5391,145 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="110" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="20"/>
+    <row r="35" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="91" t="s">
+        <v>1050</v>
+      </c>
       <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="21"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D35" s="130">
+        <f>Chemistry!$D$103</f>
+        <v>6.3125785894509363</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="91" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="109"/>
+        <v>1052</v>
+      </c>
       <c r="C36" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="D36" s="92">
+      <c r="D36" s="130">
+        <f>Chemistry!$D$125</f>
+        <v>8.877523507988645</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="110" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="21"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="91" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" s="109"/>
+      <c r="C38" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="92">
         <f>'Mass Transfer'!$D$108</f>
         <v>1.9407611529861681</v>
       </c>
-      <c r="E36" s="23" t="str">
+      <c r="E38" s="23" t="str">
         <f>HYPERLINK("#'Mass Transfer'!D108","→ Mass")</f>
         <v>→ Mass</v>
       </c>
-      <c r="F36" s="21" t="s">
+      <c r="F38" s="21" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="91" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="91" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="109"/>
-      <c r="C37" s="28" t="s">
+      <c r="B39" s="109"/>
+      <c r="C39" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="D37" s="92">
+      <c r="D39" s="92">
         <f>'Mass Transfer'!$D$112</f>
         <v>178.08128884816398</v>
       </c>
-      <c r="E37" s="23" t="str">
+      <c r="E39" s="23" t="str">
         <f>HYPERLINK("#'Mass Transfer'!D112","→ Mass")</f>
         <v>→ Mass</v>
       </c>
-      <c r="F37" s="21" t="s">
+      <c r="F39" s="21" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="91" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="91" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20" t="s">
+      <c r="B40" s="20"/>
+      <c r="C40" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="92">
+      <c r="D40" s="92">
         <f>'Mass Transfer'!$D$68</f>
         <v>0.31415926535897931</v>
       </c>
-      <c r="E38" s="23" t="str">
+      <c r="E40" s="23" t="str">
         <f>HYPERLINK("#'Mass Transfer'!D68","→ Mass")</f>
         <v>→ Mass</v>
       </c>
-      <c r="F38" s="21" t="s">
+      <c r="F40" s="21" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="91" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="91" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20" t="s">
+      <c r="B41" s="20"/>
+      <c r="C41" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="D39" s="97">
+      <c r="D41" s="97">
         <f>Biology!$D$35</f>
         <v>585.59956132513264</v>
       </c>
-      <c r="E39" s="23" t="str">
+      <c r="E41" s="23" t="str">
         <f>HYPERLINK("#Biology!D35","→ Biology")</f>
         <v>→ Biology</v>
       </c>
-      <c r="F39" s="21" t="s">
+      <c r="F41" s="21" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="20"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-    </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="89" t="s">
-        <v>118</v>
-      </c>
+      <c r="A42" s="20"/>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
-      <c r="D42" s="29"/>
+      <c r="D42" s="20"/>
       <c r="E42" s="20"/>
       <c r="F42" s="20"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
+      <c r="A43" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="100" t="s">
-        <v>120</v>
+      <c r="A44" s="89" t="s">
+        <v>118</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
@@ -5491,8 +5538,8 @@
       <c r="F44" s="20"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="31" t="s">
-        <v>121</v>
+      <c r="A45" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
@@ -5501,28 +5548,28 @@
       <c r="F45" s="20"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="32" t="s">
-        <v>122</v>
+      <c r="A46" s="100" t="s">
+        <v>120</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="29"/>
-      <c r="E46" s="94"/>
+      <c r="E46" s="20"/>
       <c r="F46" s="20"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="33" t="s">
-        <v>123</v>
+      <c r="A47" s="31" t="s">
+        <v>121</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
       <c r="D47" s="29"/>
-      <c r="E47" s="94"/>
+      <c r="E47" s="20"/>
       <c r="F47" s="20"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="90" t="s">
-        <v>124</v>
+      <c r="A48" s="32" t="s">
+        <v>122</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
@@ -5531,246 +5578,239 @@
       <c r="F48" s="20"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="34" t="s">
-        <v>125</v>
+      <c r="A49" s="33" t="s">
+        <v>123</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="94"/>
       <c r="F49" s="20"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="35" t="s">
-        <v>126</v>
+      <c r="A50" s="90" t="s">
+        <v>124</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="94"/>
       <c r="F50" s="20"/>
     </row>
-    <row r="51" spans="1:6" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="86" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+    </row>
+    <row r="53" spans="1:6" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="86" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="52" spans="1:6" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="87" t="s">
+    <row r="54" spans="1:6" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="87" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="88" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="88" t="s">
         <v>129</v>
       </c>
-      <c r="B53" s="20"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="94"/>
-      <c r="F54" s="20"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="36" t="s">
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="20"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="94"/>
+      <c r="F56" s="20"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="B55" s="36" t="s">
+      <c r="B57" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="C55" s="36" t="s">
+      <c r="C57" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="D55" s="36" t="s">
+      <c r="D57" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36" t="s">
+      <c r="E57" s="36"/>
+      <c r="F57" s="36" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="20" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B58" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="C58" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="D56" s="37" t="str">
+      <c r="D58" s="37" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/surface-kla.md","surface-kla.md →")</f>
         <v>surface-kla.md →</v>
       </c>
-      <c r="E56" s="110"/>
-      <c r="F56" s="21" t="s">
+      <c r="E58" s="110"/>
+      <c r="F58" s="21" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="20" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B59" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="C59" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="D57" s="37" t="str">
+      <c r="D59" s="37" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/faradaic-efficiency.md","faradaic-efficiency.md →")</f>
         <v>faradaic-efficiency.md →</v>
       </c>
-      <c r="E57" s="20"/>
-      <c r="F57" s="21" t="s">
+      <c r="E59" s="20"/>
+      <c r="F59" s="21" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="20" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="20" t="s">
+      <c r="B60" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C60" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="37" t="str">
+      <c r="D60" s="37" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/dissolved-oxygen.md","dissolved-oxygen.md →")</f>
         <v>dissolved-oxygen.md →</v>
       </c>
-      <c r="E58" s="20"/>
-      <c r="F58" s="21" t="s">
+      <c r="E60" s="20"/>
+      <c r="F60" s="21" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="20" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B59" s="20" t="s">
+      <c r="B61" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="C61" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="D59" s="37" t="str">
+      <c r="D61" s="37" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/flow-calibration.md","flow-calibration.md →")</f>
         <v>flow-calibration.md →</v>
       </c>
-      <c r="E59" s="20"/>
-      <c r="F59" s="21" t="s">
+      <c r="E61" s="20"/>
+      <c r="F61" s="21" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="20" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c r="B62" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="C60" s="20" t="s">
+      <c r="C62" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="D60" s="37" t="str">
+      <c r="D62" s="37" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/knallgas-stoichiometry.md","knallgas-stoichiometry.md →")</f>
         <v>knallgas-stoichiometry.md →</v>
       </c>
-      <c r="E60" s="20"/>
-      <c r="F60" s="21" t="s">
+      <c r="E62" s="20"/>
+      <c r="F62" s="21" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="20" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="B63" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="C61" s="20" t="s">
+      <c r="C63" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="D61" s="37" t="str">
+      <c r="D63" s="37" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/sinter-porosity.md","sinter-porosity.md →")</f>
         <v>sinter-porosity.md →</v>
       </c>
-      <c r="E61" s="20"/>
-      <c r="F61" s="21" t="s">
+      <c r="E63" s="20"/>
+      <c r="F63" s="21" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="20" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="B62" s="20" t="s">
+      <c r="B64" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="C62" s="20" t="s">
+      <c r="C64" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="D62" s="37" t="str">
+      <c r="D64" s="37" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/README.md","README.md →")</f>
         <v>README.md →</v>
       </c>
-      <c r="E62" s="20"/>
-      <c r="F62" s="21" t="s">
+      <c r="E64" s="20"/>
+      <c r="F64" s="21" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="20"/>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="101"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="110" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="91" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C65" s="96" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D65" s="131">
-        <f>Chemistry!$D$103</f>
-        <v>6.31</v>
-      </c>
-      <c r="F65" s="21" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="91" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C66" s="96" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D66" s="131">
-        <f>Chemistry!$D$125</f>
-        <v>8.87</v>
-      </c>
-      <c r="F66" s="21" t="s">
-        <v>1056</v>
-      </c>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="20"/>
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="101"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="20"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="20"/>
@@ -5780,73 +5820,65 @@
       <c r="E67" s="20"/>
       <c r="F67" s="20"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="20"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="D65">
-    <cfRule type="expression" dxfId="15" priority="21" stopIfTrue="1">
-      <formula>OR(D65&lt;6,D65&gt;8)</formula>
+  <conditionalFormatting sqref="B56:B64">
+    <cfRule type="expression" dxfId="28" priority="15" stopIfTrue="1">
+      <formula>EXACT(B56,"HIGH")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="22" stopIfTrue="1">
-      <formula>OR(D65&lt;6.5,D65&gt;7.5)</formula>
+    <cfRule type="expression" dxfId="27" priority="16" stopIfTrue="1">
+      <formula>EXACT(B56,"MED")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="23" stopIfTrue="1">
-      <formula>ISNUMBER(D65)</formula>
+    <cfRule type="expression" dxfId="26" priority="17" stopIfTrue="1">
+      <formula>EXACT(B56,"LOW")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D66">
-    <cfRule type="expression" dxfId="15" priority="24" stopIfTrue="1">
-      <formula>D66&gt;1</formula>
+  <conditionalFormatting sqref="C56:C64">
+    <cfRule type="expression" dxfId="25" priority="18" stopIfTrue="1">
+      <formula>EXACT(C56,"low")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="25" stopIfTrue="1">
-      <formula>D66&gt;0.1</formula>
+    <cfRule type="expression" dxfId="24" priority="19" stopIfTrue="1">
+      <formula>EXACT(C56,"med")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="26" stopIfTrue="1">
-      <formula>ISNUMBER(D66)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B54:B62">
-    <cfRule type="expression" dxfId="22" priority="15" stopIfTrue="1">
-      <formula>EXACT(B54,"HIGH")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="16" stopIfTrue="1">
-      <formula>EXACT(B54,"MED")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="17" stopIfTrue="1">
-      <formula>EXACT(B54,"LOW")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C54:C62">
-    <cfRule type="expression" dxfId="19" priority="18" stopIfTrue="1">
-      <formula>EXACT(C54,"low")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="19" stopIfTrue="1">
-      <formula>EXACT(C54,"med")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="20" stopIfTrue="1">
-      <formula>EXACT(C54,"high")</formula>
+    <cfRule type="expression" dxfId="23" priority="20" stopIfTrue="1">
+      <formula>EXACT(C56,"high")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:D16">
-    <cfRule type="expression" dxfId="16" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="14" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("calibrate this",D13))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D19:D34">
-    <cfRule type="expression" dxfId="15" priority="11" stopIfTrue="1">
+  <conditionalFormatting sqref="D19:D36">
+    <cfRule type="expression" dxfId="21" priority="11" stopIfTrue="1">
       <formula>OR(ISNUMBER(SEARCH("INCONSISTENT",D19)),ISNUMBER(SEARCH("OVER",D19)),ISNUMBER(SEARCH("BELOW",D19)),ISNUMBER(SEARCH("EXCEED",D19)),ISNUMBER(SEARCH("NO CALIB",D19)),ISNUMBER(SEARCH("calibrate this",D19)),ISNUMBER(SEARCH("RISK",D19)),ISNUMBER(SEARCH("EXPLOSIVE",D19)),ISNUMBER(SEARCH("OOR",D19)),ISNUMBER(SEARCH("insufficient",D19)),ISNUMBER(SEARCH("TIP SPEED",D19)),ISNUMBER(SEARCH("SHORTFALL",D19)),EXACT(D19,"OUT"),EXACT(D19,"LOW"),ISNUMBER(SEARCH("GAP",D19)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="12" stopIfTrue="1">
       <formula>OR(ISNUMBER(SEARCH("above optimum",D19)),ISNUMBER(SEARCH("watch",D19)),ISNUMBER(SEARCH("NEAREST",D19)),ISNUMBER(SEARCH("unknown",D19)),ISNUMBER(SEARCH("TIGHT",D19)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="13" stopIfTrue="1">
       <formula>OR(EXACT(D19,"OK"),ISNUMBER(SEARCH("calibrated:",D19)),ISNUMBER(SEARCH("optimum",D19)),ISNUMBER(SEARCH("above min",D19)),ISNUMBER(SEARCH("CARBON-limited",D19)),ISNUMBER(SEARCH("Static",D19)),ISNUMBER(SEARCH("Dynamic",D19)),ISNUMBER(SEARCH("present",D19)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D35">
+    <cfRule type="expression" dxfId="18" priority="21" stopIfTrue="1">
+      <formula>OR(D35&lt;6,D35&gt;8)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="22" stopIfTrue="1">
+      <formula>OR(D35&lt;6.5,D35&gt;7.5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="23" stopIfTrue="1">
+      <formula>ISNUMBER(D35)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D36">
+    <cfRule type="expression" dxfId="15" priority="24" stopIfTrue="1">
+      <formula>D36&gt;1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="25" stopIfTrue="1">
+      <formula>D36&gt;0.1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="26" stopIfTrue="1">
+      <formula>ISNUMBER(D36)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8442,7 +8474,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFC00"/>
   </sheetPr>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -8497,7 +8529,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>895</v>
       </c>
@@ -8515,7 +8547,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
         <v>899</v>
       </c>
@@ -8533,7 +8565,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
         <v>903</v>
       </c>
@@ -8551,7 +8583,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>907</v>
       </c>
@@ -8755,7 +8787,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
         <v>931</v>
       </c>
@@ -8798,7 +8830,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="84" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
         <v>944</v>
       </c>
@@ -8815,7 +8847,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="17" t="s">
         <v>945</v>
       </c>
@@ -8832,7 +8864,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="17" t="s">
         <v>946</v>
       </c>
@@ -8849,7 +8881,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="84" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="17" t="s">
         <v>947</v>
       </c>
@@ -8866,7 +8898,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="17" t="s">
         <v>948</v>
       </c>
@@ -8883,7 +8915,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
         <v>949</v>
       </c>
@@ -8900,7 +8932,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="17" t="s">
         <v>950</v>
       </c>
@@ -8917,7 +8949,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="17" t="s">
         <v>951</v>
       </c>
@@ -8934,7 +8966,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="84" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="17" t="s">
         <v>952</v>
       </c>
@@ -8951,7 +8983,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
         <v>953</v>
       </c>
@@ -8969,7 +9001,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="36" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="17" t="s">
         <v>957</v>
       </c>
@@ -9005,7 +9037,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="17" t="s">
         <v>965</v>
       </c>
@@ -9023,7 +9055,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="17" t="s">
         <v>969</v>
       </c>
@@ -9041,7 +9073,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="36" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="17" t="s">
         <v>973</v>
       </c>
@@ -9077,7 +9109,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="36" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="17" t="s">
         <v>981</v>
       </c>
@@ -9841,9 +9873,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:6" s="129" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B101" s="130"/>
-      <c r="C101" s="130"/>
+    <row r="101" spans="1:6" s="99" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B101" s="129"/>
+      <c r="C101" s="129"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="16" t="s">
@@ -9862,7 +9894,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="17" t="s">
         <v>1004</v>
       </c>
@@ -9883,7 +9915,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="72" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="17" t="s">
         <v>1009</v>
       </c>
@@ -9906,7 +9938,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="108" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A107" s="17" t="s">
         <v>1014</v>
       </c>
@@ -9924,7 +9956,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="17" t="s">
         <v>1018</v>
       </c>
@@ -9942,7 +9974,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="17" t="s">
         <v>1022</v>
       </c>
@@ -9960,7 +9992,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="17" t="s">
         <v>1026</v>
       </c>
@@ -10039,7 +10071,7 @@
     <row r="123" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="111"/>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:5" ht="24" x14ac:dyDescent="0.2">
       <c r="A125" s="17" t="s">
         <v>1044</v>
       </c>
@@ -10051,7 +10083,7 @@
       </c>
       <c r="D125" s="63">
         <f>pH_Cl*pH_fHOCl*52460</f>
-        <v>8.87</v>
+        <v>8.877523507988645</v>
       </c>
       <c r="E125" s="52" t="s">
         <v>1047</v>
@@ -13209,9 +13241,9 @@
         <v>842</v>
       </c>
       <c r="C113" s="20"/>
-      <c r="D113" s="24" t="e">
+      <c r="D113" s="24" t="str">
         <f>IF(AND(ISNUMBER(DO_ss),ISNUMBER(DO_impair)),IF(DO_ss&lt;DO_impair,"Surface stripping holds DO under impairment - sparge is CARBON-limited (long interval); the O2-limited interval is the conservative fallback until kL_surf is measured","Surface stripping insufficient - sparge must vent O2 - use the O2-limited interval"),"organism DO unknown")</f>
-        <v>#N/A</v>
+        <v>organism DO unknown</v>
       </c>
       <c r="E113" s="84" t="s">
         <v>843</v>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -330,7 +330,7 @@
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$17</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -9012,8 +9012,8 @@
         <v>959</v>
       </c>
       <c r="D36" s="63">
-        <f>(2*mc_Na2HPO4/MW_Na2HPO4+mc_NaH2PO4_2H2O/MW_NaH2PO4_2H2O+2*mc_K2SO4/MW_K2SO4)-2*(mc_NH42SO4/MW_NH42SO4+mc_MgSO4_7H2O/MW_MgSO4_7H2O+mc_K2SO4/MW_K2SO4+mc_CaSO4_2H2O/MW_CaSO4_2H2O)</f>
-        <v>3.8509331025108465E-2</v>
+        <f>(2*mc_Na2HPO4/MW_Na2HPO4+mc_NaH2PO4_2H2O/MW_NaH2PO4_2H2O+2*mc_K2SO4/MW_K2SO4+2*mc_MgSO4_7H2O/MW_MgSO4_7H2O+2*mc_CaSO4_2H2O/MW_CaSO4_2H2O)-2*(mc_NH42SO4/MW_NH42SO4+mc_MgSO4_7H2O/MW_MgSO4_7H2O+mc_K2SO4/MW_K2SO4+mc_CaSO4_2H2O/MW_CaSO4_2H2O)</f>
+        <v>0.046128</v>
       </c>
       <c r="E36" s="52" t="s">
         <v>960</v>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -5384,8 +5384,8 @@
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="96" t="str">
-        <f>IF(AND(ISNUMBER(Biology!$D$45),ISNUMBER(Biology!$D$46),ISNUMBER(Biology!$D$47),ISNUMBER(Biology!$D$48)),"inputs present","DATA GAP - organism DO thresholds unmeasured; DO &amp; sparge results unreliable")</f>
-        <v>DATA GAP - organism DO thresholds unmeasured; DO &amp; sparge results unreliable</v>
+        <f>IF(AND(ISNUMBER(Biology!$D$45),ISNUMBER(Biology!$D$46),ISNUMBER(Biology!$D$47),ISNUMBER(Biology!$D$48)),"inputs present","DATA GAP - organism DO thresholds unmeasured; results unreliable")</f>
+        <v>DATA GAP - organism DO thresholds unmeasured; results unreliable</v>
       </c>
       <c r="F34" s="21" t="s">
         <v>1049</v>
@@ -9985,8 +9985,8 @@
         <v>1024</v>
       </c>
       <c r="D109" s="65" t="str">
-        <f>IF(pH_Cl&gt;0.0005,"BLEACHING RISK: chloride medium + electrolysis makes up to "&amp;TEXT(bleach_rate,"0")&amp;" mg/L/h free chlorine (FE=1 ceiling); "&amp;TEXT(pH_fHOCl*100,"0")&amp;"% is biocidal HOCl at pH "&amp;TEXT(pH_op,"0.0")&amp;"; ~1 ppm in minutes","chloride-free: no chlorine evolution, no bleaching")</f>
-        <v>chloride-free: no chlorine evolution, no bleaching</v>
+        <f>IF(HOCl_max&gt;1,"BLEACH RISK: HOCl "&amp;TEXT(HOCl_max,"0.0")&amp;" mg/L (&gt;biocidal)",IF(HOCl_max&gt;0.1,"HOCl "&amp;TEXT(HOCl_max,"0.0")&amp;" mg/L - watch","no bleaching (negligible chloride)"))</f>
+        <v>BLEACH RISK: HOCl 8.9 mg/L (&gt;biocidal)</v>
       </c>
       <c r="E109" s="52" t="s">
         <v>1025</v>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -329,6 +329,11 @@
     <definedName name="z_e_H2" localSheetId="2">Electrochemistry!$D$16</definedName>
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$17</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
+    <definedName name="O2_src_guard" localSheetId="5">'Mass Transfer'!$D$132</definedName>
+    <definedName name="DO_ss_sawtooth" localSheetId="5">'Mass Transfer'!$D$133</definedName>
+    <definedName name="spg_int_regime" localSheetId="5">'Mass Transfer'!$D$134</definedName>
+    <definedName name="DO_ss_sawtooth_lag" localSheetId="5">'Mass Transfer'!$D$135</definedName>
+    <definedName name="n_cross" localSheetId="3">Chemistry!$D$105</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
@@ -348,7 +353,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="1127">
   <si>
     <t>CO₂ DOSING FLOWRATES</t>
   </si>
@@ -3510,6 +3515,225 @@
   </si>
   <si>
     <t>Worst-case hypochlorite from the medium's chloride. Green &lt;0.1, red &gt;1 mg/L. Zero for chloride-free media.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O₂ guard source (surface-uncredited)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O2_src_guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst-case O₂ source the safety guards size on: net O₂ generation with the surface-strip credit withheld (kL_surf is a ~375%-uncertain best-case proxy and must not gate a safety guard). = O2_net_gen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sawtooth steady DO (surface-credited, STEADY src)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO_ss_sawtooth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/m³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steady-state DO if surface stripping is credited and the source is the STEADY surplus (O2_excess). Diagnostic only — the SHIPPED guard sizes on the LAG cap (see D135). = D108/32.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sparge regime (surface-held vs sparge-needed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spg_int_regime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SURFACE-HELD if the steady surface path alone keeps DO below the target fraction of the ceiling; else SPARGE-NEEDED. Steady-state verdict only — the shipped 2.85-min cap is the LAG worst case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sawtooth steady DO (LAG src — what the guard banks on)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO_ss_sawtooth_lag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/m³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lag-source companion to D133: surface-credited steady DO using the LARGER lag source (O2_net_gen). Reads ~54% of ceiling — this is the worst case the shipped guard sizes on, NOT the 18% steady figure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O₂ removable across the stirred surface at ceiling driving force — a FEASIBILITY CEILING for surf_ratio / O2_removal_ratio only. NEVER subtracted inside a safety guard (kL_surf is a ~375%-uncertain best-case proxy); the guards size on O2_src_guard (D132) with this credit withheld.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dissolved O2 matching that vent headspace fraction. With the corrected mole fraction y_O2_vent = O2_excess/(O2_excess+CO2_supply), this evaluates to ~8.9 uM at the ed04 operating point - well below the ~336 uM inhibition ceiling, so at this CO2 dose the vent leg is a comfortable kL-independent backstop. (The old O2_excess/CO2_supply form was a ratio, not a mole fraction.) The margin shrinks as CO2 supply falls relative to the O2 surplus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Least feasible CO₂ (binding of the two floors). O₂-venting now binds (duty_O2vent ≈ 10× duty_carbon), not the carbon/pH floor — true post-fix.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pH-grid crossings (must be exactly 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_cross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count of +→− sign crossings of the charge residual on the pH grid. Exactly 1 = a single bracketed root inside [4,9]. 0 (root outside the grid) or &gt;1 (non-monotone) must NOT be read as pH 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phosphate Ka3 (pKa 12.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOCl-tolerance evidence (Comments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threshold seed 0.2 mg/L free chlorine = conservative FIRST-IMPAIRMENT floor for suspended gram-negative environmental bacteria; deliberately below water-industry disinfection doses. Tiers: 0.02-0.1 no inhibition; 0.2 first-impairment (pick); 0.3-0.6 measurable die-off; 0.75-1.75 complete regrowth inhibition.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. necator: no direct HOCl MIC; genus-mate C. metallidurans is documented chlorine/chloramine-TOLERANT (Gomez-Alvarez/Wang 2018, STOTEN). 0.2 mg/L is a safety UNDERestimate, not its breaking point — do not assume necator is chlorine-fragile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrogenophaga: dominant chlorine/chloramine-RESISTANT genus in chloraminated distribution systems; survives &gt;0.5 mg/L. Treat as resistant; 0.2 mg/L is a floor, not an observed inhibition point.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xanthobacter: no species value found in literature (genuine gap — not invented); use the 0.2 mg/L gram-negative fallback. CONSERVATIVE-FLOOR CAVEAT: the 0.2 seed is a safety floor; real impairment for these resistant genera is likely higher (mid-tenths to &gt;1 mg/L). necator/Xanthobacter rows are inferred, not measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure surface kLa (kL_surf)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">med</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375% sensitivity — the single biggest lever; decides the safe sparge interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure / confirm vial total volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~106% on the schedule — sets the liquid charge, headspace and flush sizing; water-fill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure cathodic Faradaic efficiency (etaF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">med</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~100% — sets the H2/O2 split; the O2 figures are an upper bound at etaF=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm knallgas uptake ratio (H2:O2:CO2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~95% on the O2 surplus + carbon demand; needs a growing culture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure anodic Faradaic efficiency (etaF_OER)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">med</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~43% on the O2-removal duty; assumed 1, but un-measured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure vial wall thickness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high-leverage caliper measurement — drives the headspace/displacement budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bench-characterise the solenoid pulse floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~27% — the recommended pulse IS pulse_floor; trivial to characterise on the bench</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Determine organism minimum DO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lower DO guardrail; a gap for every organism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calibrate flow for each reactor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">each experiment; only ed04 done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure / confirm sinter porosity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bubble size; currently grade 0 from Gerrit's disc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record lab ambient pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~33% via the O2 ceiling; also Henry solubilities + gas volumes</t>
   </si>
 </sst>
 </file>
@@ -4787,7 +5011,7 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -5665,163 +5889,228 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="20" t="s">
-        <v>135</v>
+        <v>1083</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>136</v>
+        <v>1084</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>137</v>
+        <v>1085</v>
       </c>
       <c r="D58" s="37" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/surface-kla.md","surface-kla.md →")</f>
-        <v>surface-kla.md →</v>
       </c>
       <c r="E58" s="110"/>
       <c r="F58" s="21" t="s">
-        <v>138</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="20" t="s">
-        <v>139</v>
+        <v>1087</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>136</v>
+        <v>1088</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>137</v>
+        <v>1089</v>
       </c>
       <c r="D59" s="37" t="str">
-        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/faradaic-efficiency.md","faradaic-efficiency.md →")</f>
-        <v>faradaic-efficiency.md →</v>
-      </c>
-      <c r="E59" s="20"/>
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/vial-geometry.md","vial-geometry.md →")</f>
+      </c>
+      <c r="E59" s="110"/>
       <c r="F59" s="21" t="s">
-        <v>140</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="20" t="s">
-        <v>141</v>
+        <v>1091</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>142</v>
+        <v>1092</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>143</v>
+        <v>1093</v>
       </c>
       <c r="D60" s="37" t="str">
-        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/dissolved-oxygen.md","dissolved-oxygen.md →")</f>
-        <v>dissolved-oxygen.md →</v>
-      </c>
-      <c r="E60" s="20"/>
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/faradaic-efficiency.md","faradaic-efficiency.md →")</f>
+      </c>
+      <c r="E60" s="110"/>
       <c r="F60" s="21" t="s">
-        <v>144</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="20" t="s">
-        <v>145</v>
+        <v>1095</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>142</v>
+        <v>1096</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>143</v>
+        <v>1097</v>
       </c>
       <c r="D61" s="37" t="str">
-        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/flow-calibration.md","flow-calibration.md →")</f>
-        <v>flow-calibration.md →</v>
-      </c>
-      <c r="E61" s="20"/>
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/knallgas-stoichiometry.md","knallgas-stoichiometry.md →")</f>
+      </c>
+      <c r="E61" s="110"/>
       <c r="F61" s="21" t="s">
-        <v>146</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="20" t="s">
-        <v>147</v>
+        <v>1099</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>142</v>
+        <v>1100</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>148</v>
+        <v>1101</v>
       </c>
       <c r="D62" s="37" t="str">
-        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/knallgas-stoichiometry.md","knallgas-stoichiometry.md →")</f>
-        <v>knallgas-stoichiometry.md →</v>
-      </c>
-      <c r="E62" s="20"/>
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/faradaic-efficiency.md","faradaic-efficiency.md →")</f>
+      </c>
+      <c r="E62" s="110"/>
       <c r="F62" s="21" t="s">
-        <v>149</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="20" t="s">
-        <v>150</v>
+        <v>1103</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>151</v>
+        <v>1104</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>143</v>
+        <v>1105</v>
       </c>
       <c r="D63" s="37" t="str">
-        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/sinter-porosity.md","sinter-porosity.md →")</f>
-        <v>sinter-porosity.md →</v>
-      </c>
-      <c r="E63" s="20"/>
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/vial-geometry.md","vial-geometry.md →")</f>
+      </c>
+      <c r="E63" s="110"/>
       <c r="F63" s="21" t="s">
-        <v>152</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="20" t="s">
-        <v>153</v>
+        <v>1107</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>151</v>
+        <v>1108</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>143</v>
+        <v>1109</v>
       </c>
       <c r="D64" s="37" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/flow-calibration.md","flow-calibration.md →")</f>
+      </c>
+      <c r="E64" s="110"/>
+      <c r="F64" s="21" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="20" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D65" s="37" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/dissolved-oxygen.md","dissolved-oxygen.md →")</f>
+      </c>
+      <c r="E65" s="110"/>
+      <c r="F65" s="21" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="20" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D66" s="37" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/flow-calibration.md","flow-calibration.md →")</f>
+      </c>
+      <c r="E66" s="110"/>
+      <c r="F66" s="21" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="20" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D67" s="37" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/sinter-porosity.md","sinter-porosity.md →")</f>
+      </c>
+      <c r="E67" s="110"/>
+      <c r="F67" s="21" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="20" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D68" s="37" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/README.md","README.md →")</f>
-        <v>README.md →</v>
-      </c>
-      <c r="E64" s="20"/>
-      <c r="F64" s="21" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="20"/>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="101"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="20"/>
-      <c r="B66" s="20"/>
-      <c r="C66" s="20"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="20"/>
-      <c r="B67" s="20"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
+      </c>
+      <c r="E68" s="110"/>
+      <c r="F68" s="21" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="20"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="101"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="20"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="29"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="20"/>
+      <c r="B71" s="20"/>
+      <c r="C71" s="20"/>
+      <c r="D71" s="29"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B56:B64">
+  <conditionalFormatting sqref="B56:B68">
     <cfRule type="expression" dxfId="28" priority="15" stopIfTrue="1">
       <formula>EXACT(B56,"HIGH")</formula>
     </cfRule>
@@ -5832,7 +6121,7 @@
       <formula>EXACT(B56,"LOW")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C56:C64">
+  <conditionalFormatting sqref="C56:C68">
     <cfRule type="expression" dxfId="25" priority="18" stopIfTrue="1">
       <formula>EXACT(C56,"low")</formula>
     </cfRule>
@@ -8474,7 +8763,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFC00"/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -8717,7 +9006,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
-        <v>927</v>
+        <v>1077</v>
       </c>
       <c r="B17" s="53">
         <v>4.1999999999999998E-13</v>
@@ -9905,8 +10194,7 @@
         <v>1006</v>
       </c>
       <c r="D103" s="63">
-        <f>SUM(C50:C100)</f>
-        <v>6.3125785894509363</v>
+        <f>IF(n_cross=1,SUM(C50:C100),NA())</f>
       </c>
       <c r="E103" s="52" t="s">
         <v>1007</v>
@@ -9933,10 +10221,31 @@
         <v>1012</v>
       </c>
     </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="17" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B105" s="18" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D105" s="63">
+        <f>SUMPRODUCT((B50:B99&gt;=0)*(B51:B100&lt;0))</f>
+      </c>
+      <c r="E105" s="52" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F105" s="20"/>
+    </row>
     <row r="106" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="111" t="s">
         <v>1013</v>
       </c>
+      <c r="G106" s="70" t="s">
+        <v>1078</v>
+      </c>
     </row>
     <row r="107" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A107" s="17" t="s">
@@ -9955,6 +10264,9 @@
       <c r="E107" s="52" t="s">
         <v>1017</v>
       </c>
+      <c r="G107" s="70" t="s">
+        <v>1079</v>
+      </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="17" t="s">
@@ -9973,6 +10285,9 @@
       <c r="E108" s="52" t="s">
         <v>1021</v>
       </c>
+      <c r="G108" s="70" t="s">
+        <v>1080</v>
+      </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="17" t="s">
@@ -9984,12 +10299,14 @@
       <c r="C109" s="19" t="s">
         <v>1024</v>
       </c>
-      <c r="D109" s="65" t="str">
-        <f>IF(HOCl_max&gt;1,"BLEACH RISK: HOCl "&amp;TEXT(HOCl_max,"0.0")&amp;" mg/L (&gt;biocidal)",IF(HOCl_max&gt;0.1,"HOCl "&amp;TEXT(HOCl_max,"0.0")&amp;" mg/L - watch","no bleaching (negligible chloride)"))</f>
-        <v>BLEACH RISK: HOCl 8.9 mg/L (&gt;biocidal)</v>
+      <c r="D109" s="65">
+        <f>IF(HOCl_max&gt;0.2,"BLEACH RISK: HOCl "&amp;TEXT(HOCl_max,"0.0")&amp;" mg/L (&gt;0.2 first-impairment)",IF(HOCl_max&gt;0.02,"HOCl "&amp;TEXT(HOCl_max,"0.0")&amp;" mg/L - watch","no bleaching (negligible chloride)"))</f>
       </c>
       <c r="E109" s="52" t="s">
         <v>1025</v>
+      </c>
+      <c r="G109" s="70" t="s">
+        <v>1081</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
@@ -10008,6 +10325,9 @@
       </c>
       <c r="E110" s="52" t="s">
         <v>1029</v>
+      </c>
+      <c r="G110" s="70" t="s">
+        <v>1082</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -11171,7 +11491,7 @@
   <sheetPr>
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -12519,7 +12839,7 @@
         <v>9.793362894083752E-5</v>
       </c>
       <c r="E73" s="70" t="s">
-        <v>734</v>
+        <v>1070</v>
       </c>
       <c r="F73" s="20"/>
     </row>
@@ -12553,8 +12873,7 @@
         <v>160</v>
       </c>
       <c r="D75" s="49">
-        <f>IF(CO2_supply&gt;0,O2_excess/CO2_supply,NA())</f>
-        <v>0.5</v>
+        <f>IF(CO2_supply&gt;0,O2_excess/(O2_excess+CO2_supply),NA())</f>
       </c>
       <c r="E75" s="102" t="s">
         <v>740</v>
@@ -12575,8 +12894,8 @@
         <f>H_O2_T*y_O2_vent*P_atm*1000</f>
         <v>559.53915741172045</v>
       </c>
-      <c r="E76" s="102" t="s">
-        <v>743</v>
+      <c r="E76" s="70" t="s">
+        <v>1071</v>
       </c>
       <c r="F76" s="20"/>
     </row>
@@ -12777,8 +13096,7 @@
         <v>160</v>
       </c>
       <c r="D87" s="49">
-        <f>MAX(0,O2_net_gen-surf_strip)/(target_DO_frac*(O2_ceil_Pa/P_atm))/(nCO2_rate*3600)</f>
-        <v>0</v>
+        <f>O2_src_guard/(target_DO_frac*(O2_ceil_Pa/P_atm))/(nCO2_rate*3600)</f>
       </c>
       <c r="E87" s="102" t="s">
         <v>777</v>
@@ -12799,8 +13117,8 @@
         <f>MAX(duty_carbon,duty_O2vent)</f>
         <v>7.3422747452322058E-5</v>
       </c>
-      <c r="E88" s="102" t="s">
-        <v>780</v>
+      <c r="E88" s="70" t="s">
+        <v>1072</v>
       </c>
       <c r="F88" s="20"/>
     </row>
@@ -12815,8 +13133,7 @@
         <v>71</v>
       </c>
       <c r="D89" s="49">
-        <f>target_DO_frac*O2_ceil_C*(V_charge/1000000)/MAX(0.000000000001,O2_net_gen-surf_strip)*60</f>
-        <v>151075572.50116453</v>
+        <f>target_DO_frac*O2_ceil_C*(V_charge/1000000)/O2_src_guard*60</f>
       </c>
       <c r="E89" s="102" t="s">
         <v>783</v>
@@ -12909,9 +13226,8 @@
       <c r="C94" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D94" s="49" t="str">
-        <f>IF(spg_int_opt&lt;spg_dur_opt/(60*duty_opt)-0.0001,"O2-FREQ",IF(duty_O2vent&gt;=duty_carbon,"O2-VENT","CARBON"))</f>
-        <v>CARBON</v>
+      <c r="D94" s="49">
+        <f>IF(spg_int_opt&gt;=spg_int_max-0.0001,"O2-CEILING",IF(spg_int_opt&lt;spg_dur_opt/(60*duty_opt)-0.0001,"O2-FREQ",IF(duty_O2vent&gt;=duty_carbon,"O2-VENT","CARBON")))</f>
       </c>
       <c r="E94" s="102" t="s">
         <v>798</v>
@@ -13544,12 +13860,76 @@
       <c r="F131" s="20"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A132" s="20"/>
-      <c r="B132" s="20"/>
-      <c r="C132" s="20"/>
-      <c r="D132" s="29"/>
-      <c r="E132" s="20"/>
+      <c r="A132" s="17" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B132" s="18" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C132" s="19" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D132" s="29">
+        <f>O2_net_gen</f>
+      </c>
+      <c r="E132" s="70" t="s">
+        <v>1057</v>
+      </c>
       <c r="F132" s="20"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133" s="17" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B133" s="18" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C133" s="19" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D133" s="29">
+        <f>O2_excess/(kLa_surf_used*3600*(V_charge/1000000))</f>
+      </c>
+      <c r="E133" s="70" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F133" s="20"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A134" s="20" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B134" s="20" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C134" s="20" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D134" s="29">
+        <f>IF(DO_ss_sawtooth&lt;target_DO_frac*O2_ceil_C,"SURFACE-HELD","SPARGE-NEEDED")</f>
+      </c>
+      <c r="E134" s="70" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F134" s="20"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135" s="20" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B135" s="20" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C135" s="20" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D135" s="29">
+        <f>O2_net_gen/(kLa_surf_used*3600*(V_charge/1000000))</f>
+      </c>
+      <c r="E135" s="70" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F135" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D32">

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -353,7 +353,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="1132">
   <si>
     <t>CO₂ DOSING FLOWRATES</t>
   </si>
@@ -3734,6 +3734,21 @@
   </si>
   <si>
     <t xml:space="preserve">~33% via the O2 ceiling; also Henry solubilities + gas volumes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pous 2022 (BiTE 101010) / Pous 2023 (JECE 111550), UdG recipe = 0.01 g/L. A 10× as-built value (0.1 g/L) is hypothesised but UNCONFIRMED — no batch sheet or lab-book in repo; Cl⁻ and HOCl scale linearly, so confirm the bench-weighed mass before any 0.1 entry. Do not overwrite this literature value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLEACH RISK fires when HOCl_max&gt;0.2 mg/L (watch &gt;0.02); pH-aware via the trough HOCl fraction (D104→D125). 0.2 mg/L = WHO minimum free-chlorine residual / lower bound of the free-Cl MSC range 0.021–0.39 mg/L — a precautionary floor, not an organism MIC (no published MIC for C. necator; the genus is chlorine-tolerant, so true impairment is higher). Verdict insensitive: HOCl_max exceeds even a 1 mg/L bactericidal level ~9×.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sander (2023) compilation; CO₂ ~28× more soluble than O₂ (vs the 1.2e-5 O₂ Hcp).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sander (2023). H₂ ~1.5× less soluble than O₂ (vs the 1.2e-5 O₂ Hcp).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penetration-theory / surface-renewal proxy (Higbie form, t=1/s_renew) — coarse; measure by gassing-out (§15).</t>
   </si>
 </sst>
 </file>
@@ -9269,7 +9284,7 @@
         <v>0.01</v>
       </c>
       <c r="E33" s="52" t="s">
-        <v>937</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -10303,7 +10318,7 @@
         <f>IF(HOCl_max&gt;0.2,"BLEACH RISK: HOCl "&amp;TEXT(HOCl_max,"0.0")&amp;" mg/L (&gt;0.2 first-impairment)",IF(HOCl_max&gt;0.02,"HOCl "&amp;TEXT(HOCl_max,"0.0")&amp;" mg/L - watch","no bleaching (negligible chloride)"))</f>
       </c>
       <c r="E109" s="52" t="s">
-        <v>1025</v>
+        <v>1128</v>
       </c>
       <c r="G109" s="70" t="s">
         <v>1081</v>
@@ -10938,7 +10953,7 @@
         <v>3.3E-4</v>
       </c>
       <c r="E29" s="68" t="s">
-        <v>495</v>
+        <v>1129</v>
       </c>
       <c r="F29" s="20"/>
     </row>
@@ -11105,7 +11120,7 @@
         <v>7.7999999999999999E-6</v>
       </c>
       <c r="E38" s="68" t="s">
-        <v>523</v>
+        <v>1130</v>
       </c>
       <c r="F38" s="20"/>
     </row>
@@ -12782,7 +12797,7 @@
         <v>1.8864104282465861E-4</v>
       </c>
       <c r="E70" s="70" t="s">
-        <v>725</v>
+        <v>1131</v>
       </c>
       <c r="F70" s="20"/>
     </row>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -366,7 +366,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="1161">
   <si>
     <t>CO₂ DOSING FLOWRATES</t>
   </si>
@@ -3840,6 +3840,15 @@
   </si>
   <si>
     <t xml:space="preserve">Free HOCl (operative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANSWER. Recommended on the best kL_surf estimate: when surface stripping holds DO (SURFACE-HELD, D134) the binding limit is carbon supply → the carbon-limited interval (D112); otherwise the O₂-limited fallback (D89). An estimated kL_surf&gt;0 beats assuming zero — measure it to confirm (improvement #1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O₂-limited FALLBACK interval: zero-surface worst case (sparge vents all O₂; no surface credit). Applies only if measured kL_surf &lt; kL_surf_crit (D131). The recommended interval (D91) credits the surface estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conservative O₂-vent duty: net O₂ with the surface-strip credit withheld (O2_src_guard). Sizes the O₂-limited fallback; the recommended schedule credits the surface estimate when DO is held.</t>
   </si>
 </sst>
 </file>
@@ -13455,7 +13464,7 @@
         <v>7.3422747452322069E-4</v>
       </c>
       <c r="E87" s="102" t="s">
-        <v>749</v>
+        <v>1160</v>
       </c>
       <c r="F87" s="20"/>
     </row>
@@ -13493,7 +13502,7 @@
         <v>2.8464317102116774</v>
       </c>
       <c r="E89" s="102" t="s">
-        <v>754</v>
+        <v>1159</v>
       </c>
       <c r="F89" s="20"/>
     </row>
@@ -13527,11 +13536,11 @@
         <v>69</v>
       </c>
       <c r="D91" s="128">
-        <f>MIN(spg_dur_opt/(60*duty_opt),spg_int_max)</f>
-        <v>2.8464317102116774</v>
+        <f>IF(spg_int_regime="SURFACE-HELD",spg_int_carbon,MIN(spg_dur_opt/(60*duty_opt),spg_int_max))</f>
+        <v>178.08128884816398</v>
       </c>
       <c r="E91" s="82" t="s">
-        <v>760</v>
+        <v>1158</v>
       </c>
       <c r="F91" s="20"/>
     </row>
@@ -13584,8 +13593,8 @@
         <v>137</v>
       </c>
       <c r="D94" s="49" t="str">
-        <f>IF(spg_int_opt&gt;=spg_int_max-0.0001,"O2-CEILING",IF(spg_int_opt&lt;spg_dur_opt/(60*duty_opt)-0.0001,"O2-FREQ",IF(duty_O2vent&gt;=duty_carbon,"O2-VENT","CARBON")))</f>
-        <v>O2-CEILING</v>
+        <f>IF(spg_int_regime="SURFACE-HELD","CARBON (surface holds DO)",IF(spg_int_opt&gt;=spg_int_max-0.0001,"O2-CEILING",IF(spg_int_opt&lt;spg_dur_opt/(60*duty_opt)-0.0001,"O2-FREQ",IF(duty_O2vent&gt;=duty_carbon,"O2-VENT","CARBON"))))</f>
+        <v>CARBON (surface holds DO)</v>
       </c>
       <c r="E94" s="102" t="s">
         <v>769</v>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -5729,6 +5729,10 @@
       <c r="F34" s="21" t="s">
         <v>1018</v>
       </c>
+      <c r="E34" s="23" t="str">
+        <f>HYPERLINK("#Biology!D45","→ Biology")</f>
+        <v>→ Biology</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="91" t="s">
@@ -5742,12 +5746,16 @@
       <c r="F35" s="21" t="s">
         <v>1020</v>
       </c>
+      <c r="E35" s="23" t="str">
+        <f>HYPERLINK("#Chemistry!D103","→ Chemistry")</f>
+        <v>→ Chemistry</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="91" t="s">
         <v>1157</v>
       </c>
-      <c r="C36" s="28" t="s">
+      <c r="C36" s="20" t="s">
         <v>104</v>
       </c>
       <c r="D36" s="130">
@@ -5756,6 +5764,10 @@
       </c>
       <c r="F36" s="21" t="s">
         <v>1022</v>
+      </c>
+      <c r="E36" s="23" t="str">
+        <f>HYPERLINK("#Chemistry!D139","→ Chemistry")</f>
+        <v>→ Chemistry</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -5773,7 +5785,7 @@
         <v>103</v>
       </c>
       <c r="B38" s="109"/>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="20" t="s">
         <v>104</v>
       </c>
       <c r="D38" s="92">
@@ -5793,7 +5805,7 @@
         <v>106</v>
       </c>
       <c r="B39" s="109"/>
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="20" t="s">
         <v>69</v>
       </c>
       <c r="D39" s="92">

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -340,13 +340,20 @@
     <definedName name="I_Cl_FE" localSheetId="3">Chemistry!$D$131</definedName>
     <definedName name="I_Cl_mt" localSheetId="3">Chemistry!$D$132</definedName>
     <definedName name="I_Cl" localSheetId="3">Chemistry!$D$133</definedName>
-    <definedName name="Cl2_prod" localSheetId="3">Chemistry!$D$134</definedName>
+    <definedName name="P_HOCl" localSheetId="3">Chemistry!$D$134</definedName>
     <definedName name="NH3_N" localSheetId="3">Chemistry!$D$135</definedName>
-    <definedName name="Cl_demand" localSheetId="3">Chemistry!$D$136</definedName>
-    <definedName name="t_run" localSheetId="3">Chemistry!$D$137</definedName>
-    <definedName name="Cl2_cum" localSheetId="3">Chemistry!$D$138</definedName>
-    <definedName name="free_HOCl" localSheetId="3">Chemistry!$D$139</definedName>
-    <definedName name="bleach_thresh" localSheetId="3">Chemistry!$D$140</definedName>
+    <definedName name="k1_NH2Cl" localSheetId="3">Chemistry!$D$136</definedName>
+    <definedName name="pKa_NH4" localSheetId="3">Chemistry!$D$137</definedName>
+    <definedName name="NH3_free" localSheetId="3">Chemistry!$D$138</definedName>
+    <definedName name="HOCl_ss" localSheetId="3">Chemistry!$D$139</definedName>
+    <definedName name="HOCl_ss_mgL" localSheetId="3">Chemistry!$D$140</definedName>
+    <definedName name="f_local" localSheetId="3">Chemistry!$D$141</definedName>
+    <definedName name="tau_NH2Cl" localSheetId="3">Chemistry!$D$142</definedName>
+    <definedName name="NH2Cl_mgL" localSheetId="3">Chemistry!$D$143</definedName>
+    <definedName name="R_chloramine" localSheetId="3">Chemistry!$D$144</definedName>
+    <definedName name="C_eff" localSheetId="3">Chemistry!$D$145</definedName>
+    <definedName name="Cl_onset" localSheetId="3">Chemistry!$D$146</definedName>
+    <definedName name="Cl_kill" localSheetId="3">Chemistry!$D$147</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -366,7 +373,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="1161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="1233">
   <si>
     <t>CO₂ DOSING FLOWRATES</t>
   </si>
@@ -3849,6 +3856,222 @@
   </si>
   <si>
     <t xml:space="preserve">Conservative O₂-vent duty: net O₂ with the surface-strip credit withheld (O2_src_guard). Sizes the O₂-limited fallback; the recommended schedule credits the surface estimate when DO is held.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREE-CHLORINE PENALTY MODEL (graded, kinetic — operative; supersedes the naïve FE=1 ceiling above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max active-Cl evolution efficiency (high-Cl plateau)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FE_CER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active-chlorine current efficiency on the high-chloride plateau (~100% &gt;50 mM; Vos &amp; Koper, JACS 140:10270 / JEAC 819:260). At trace Cl⁻ the chloride mass-transport limit (D132) binds instead, so production scales with chloride, not this value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cl⁻ mass-transfer coefficient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">km_Cl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cm/s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stirred small cell, k_m = D/δ; 1e-3–1e-2 cm/s (Bard &amp; Faulkner Ch.1; measured stirred cells 2–8e-3). Central 3e-3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anode wetted area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A_anode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cm²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt/Ti rod 6 mm dia × ~3.5 cm submerged ≈ 6 cm²; ~5 used. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cl₂ current — efficiency-limited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I_Cl_FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied anode current × plateau efficiency.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cl₂ current — chloride mass-transport limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I_Cl_mt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i_lim = n·F·k_m·[Cl⁻]·A; n=1; [Cl⁻] mol/cm³ = pH_Cl/1000. Caps chlorine at the chloride flux — binds at trace Cl⁻ (~0.26 mA for UdG), so production scales with chloride.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realistic chlorine current (binding limit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I_Cl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smaller of efficiency- and mass-transport-limited.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volumetric free-chlorine production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_HOCl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/L/s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_HOCl = I_Cl/(2·F·V). 2 e⁻ per Cl₂→HOCl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium ammonium (as N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NH3_N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mg/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active-medium total ammonium × 14.007 g/mol N.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monochloramine formation rate constant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k1_NH2Cl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M⁻¹s⁻¹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOCl + NH₃ → NH₂Cl, k₁ = 4.2e6 M⁻¹s⁻¹ (Morris &amp; Isaac 1983; Jafvert &amp; Valentine 1992, ES&amp;T 26:577, DOI 10.1021/es00027a022). Fast but NOT instantaneous.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ammonium pKa (NH₄⁺/NH₃)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pKa_NH4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only free NH₃ reacts with HOCl; at pH 7 just ~0.6% of the ammonium pool is free NH₃ — so the sink is finite and a steady residual coexists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free ammonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NH3_free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NH₃ = NH₄_tot/(1+10^(pKa_NH4−pH)). The reactive fraction that scavenges HOCl.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steady bulk free HOCl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOCl_ss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[HOCl]_ss = production/(k₁·NH₃_free). Non-zero by construction; rises with current, falls with ammonium/pH.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steady bulk free HOCl (mass)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOCl_ss_mgL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulk free chlorine, mg/L. Small for UdG — below the impairment onset, so no bulk sterilisation (UdG runs for days).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anode boundary-layer enrichment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f_local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local HOCl at the anode is higher than bulk before it diffuses out and meets ammonia (boundary-layer time ~0.1–10 s ≫ ms bulk scavenging). f_local ≥ 1; sub-mM value unmeasured — SENSITIVITY parameter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monochloramine effective residence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tau_NH2Cl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time combined chlorine persists before consumption (growth N-uptake, cathodic reduction, dilution). Lit: minutes–hours; system-specific value unknown — SENSITIVITY parameter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steady combined chlorine (monochloramine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NH2Cl_mgL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production held as monochloramine over its residence, capped at the ammonium capacity (5.06 mg Cl₂/mg N). Longer-lived and still biocidal — not harmless.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monochloramine potency divisor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R_chloramine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monochloramine is ~18–70× less biocidal than free chlorine (EPA SWTR ~18×, Giardia; IWA 2008 ~70×, E. coli). 25 = conservative (kinder-to-chloramine).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EFFECTIVE biocidal chlorine load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_eff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERATIVE bleaching value: local-weighted free HOCl + combined chlorine ÷ potency. Graded, non-zero; scales with chloride and current. Supersedes the FE=1 ceiling (D125).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free-chlorine impairment onset (sub-lethal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cl_onset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth measurably slowed above ~0.1 mg/L free-Cl-equiv (graded, gram-negative proxy; Murray 2017 Ecotox 26:1115; HOCl oxidative-stress onset). Distinct from kill.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free-chlorine kill threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cl_kill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1–5 mg/L for tolerant gram-negatives; 2 used. Above C_eff this → biofilm/electrode damage (Baek 2021, CEJ 405:126742).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operative flag: effective biocidal chlorine (C_eff, D145) vs the sub-lethal onset (D146) and kill (D147). Graded — MILD for trace-chloride UdG, SEVERE only at high chloride/current.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective biocidal chlorine</t>
   </si>
 </sst>
 </file>
@@ -5753,14 +5976,14 @@
     </row>
     <row r="36" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="91" t="s">
-        <v>1157</v>
+        <v>1232</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>104</v>
       </c>
       <c r="D36" s="130">
-        <f>Chemistry!$D$139</f>
-        <v>0</v>
+        <f>Chemistry!$D$145</f>
+        <v>0.6821</v>
       </c>
       <c r="F36" s="21" t="s">
         <v>1022</v>
@@ -10440,11 +10663,11 @@
         <v>994</v>
       </c>
       <c r="D109" s="65" t="str">
-        <f>IF(free_HOCl&gt;bleach_thresh,"FREE-CHLORINE RISK: "&amp;TEXT(free_HOCl,"0.00")&amp;" mg/L (&gt; "&amp;TEXT(bleach_thresh,"0.00")&amp;" onset)","no free chlorine (CER&lt;1% at trace Cl⁻; ammonium breakpoint demand scavenges it)")</f>
-        <v>no free chlorine (CER&lt;1% at trace Cl⁻; ammonium breakpoint demand scavenges it)</v>
+        <f>IF(C_eff&lt;Cl_onset,"negligible free chlorine ("&amp;TEXT(C_eff,"0.00")&amp;" mg/L &lt; onset)",IF(C_eff&lt;Cl_kill,"MILD sub-lethal penalty: "&amp;TEXT(C_eff,"0.00")&amp;" mg/L (chloride costs lag/growth — Sydow 2017; chloride-free avoids it)","SEVERE free chlorine: "&amp;TEXT(C_eff,"0.0")&amp;" mg/L → biofilm/electrode damage (Baek 2021)"))</f>
+        <v>MILD sub-lethal penalty: 0.68 mg/L (chloride costs lag/growth — Sydow 2017; chloride-free avoids it)</v>
       </c>
       <c r="E109" s="52" t="s">
-        <v>1156</v>
+        <v>1231</v>
       </c>
       <c r="G109" s="70" t="s">
         <v>1050</v>
@@ -10552,236 +10775,357 @@
     </row>
     <row r="127">
       <c r="A127" s="111" t="s">
-        <v>1104</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="17" t="s">
-        <v>1105</v>
+        <v>1162</v>
       </c>
       <c r="B128" s="18" t="s">
-        <v>1106</v>
+        <v>1163</v>
       </c>
       <c r="C128" s="19" t="s">
-        <v>1107</v>
+        <v>1164</v>
       </c>
       <c r="D128" s="53">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="E128" s="52" t="s">
-        <v>1108</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="17" t="s">
-        <v>1109</v>
+        <v>1166</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>1110</v>
+        <v>1167</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>1111</v>
+        <v>1168</v>
       </c>
       <c r="D129" s="53">
         <v>0.003</v>
       </c>
       <c r="E129" s="52" t="s">
-        <v>1112</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="17" t="s">
-        <v>1113</v>
+        <v>1170</v>
       </c>
       <c r="B130" s="18" t="s">
-        <v>1114</v>
+        <v>1171</v>
       </c>
       <c r="C130" s="19" t="s">
-        <v>1115</v>
+        <v>1172</v>
       </c>
       <c r="D130" s="53">
         <v>5</v>
       </c>
       <c r="E130" s="52" t="s">
-        <v>1116</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="17" t="s">
-        <v>1117</v>
+        <v>1174</v>
       </c>
       <c r="B131" s="18" t="s">
-        <v>1118</v>
+        <v>1175</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>1119</v>
+        <v>1176</v>
       </c>
       <c r="D131" s="63">
         <f>Iappc*FE_CER</f>
-        <v>5.692e-05</v>
+        <v>0.002846</v>
       </c>
       <c r="E131" s="52" t="s">
-        <v>1120</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="17" t="s">
-        <v>1121</v>
+        <v>1178</v>
       </c>
       <c r="B132" s="18" t="s">
-        <v>1122</v>
+        <v>1179</v>
       </c>
       <c r="C132" s="19" t="s">
-        <v>1119</v>
+        <v>1176</v>
       </c>
       <c r="D132" s="63">
         <f>Fcc*km_Cl*(pH_Cl/1000)*A_anode</f>
         <v>0.0002608</v>
       </c>
       <c r="E132" s="52" t="s">
-        <v>1123</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="17" t="s">
-        <v>1124</v>
+        <v>1181</v>
       </c>
       <c r="B133" s="18" t="s">
-        <v>1125</v>
+        <v>1182</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>1119</v>
+        <v>1176</v>
       </c>
       <c r="D133" s="63">
         <f>MIN(I_Cl_FE,I_Cl_mt)</f>
-        <v>5.692e-05</v>
+        <v>0.0002608</v>
       </c>
       <c r="E133" s="52" t="s">
-        <v>1126</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="17" t="s">
-        <v>1127</v>
+        <v>1184</v>
       </c>
       <c r="B134" s="18" t="s">
-        <v>1128</v>
+        <v>1185</v>
       </c>
       <c r="C134" s="19" t="s">
-        <v>1129</v>
+        <v>1186</v>
       </c>
       <c r="D134" s="63">
-        <f>I_Cl/(2*Fcc)*52460*3600/VLc</f>
-        <v>3.713</v>
+        <f>I_Cl/(2*Fcc*VLc)</f>
+        <v>9.011e-08</v>
       </c>
       <c r="E134" s="52" t="s">
-        <v>1130</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="17" t="s">
-        <v>1131</v>
+        <v>1188</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>1132</v>
+        <v>1189</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>1133</v>
+        <v>1190</v>
       </c>
       <c r="D135" s="63">
         <f>pH_NT*14007</f>
         <v>99.64</v>
       </c>
       <c r="E135" s="52" t="s">
-        <v>1134</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="17" t="s">
-        <v>1135</v>
+        <v>1192</v>
       </c>
       <c r="B136" s="18" t="s">
-        <v>1136</v>
+        <v>1193</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D136" s="63">
-        <f>10*NH3_N</f>
-        <v>996.4</v>
+        <v>1194</v>
+      </c>
+      <c r="D136" s="53">
+        <v>4200000</v>
       </c>
       <c r="E136" s="52" t="s">
-        <v>1137</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="17" t="s">
-        <v>1138</v>
+        <v>1196</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>1139</v>
+        <v>1197</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>1140</v>
+        <v>1164</v>
       </c>
       <c r="D137" s="53">
-        <v>168</v>
+        <v>9.25</v>
       </c>
       <c r="E137" s="52" t="s">
-        <v>1141</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="17" t="s">
-        <v>1142</v>
+        <v>1199</v>
       </c>
       <c r="B138" s="18" t="s">
-        <v>1143</v>
+        <v>1200</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>1133</v>
+        <v>1201</v>
       </c>
       <c r="D138" s="63">
-        <f>Cl2_prod*t_run</f>
-        <v>623.8</v>
+        <f>pH_NT/(1+10^(pKa_NH4-pH_op))</f>
+        <v>8.205e-06</v>
       </c>
       <c r="E138" s="52" t="s">
-        <v>1144</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="17" t="s">
-        <v>1145</v>
+        <v>1203</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>1146</v>
+        <v>1204</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>1133</v>
+        <v>1201</v>
       </c>
       <c r="D139" s="63">
-        <f>MAX(0,Cl2_cum-Cl_demand)*pH_fHOCl</f>
-        <v>0.0</v>
+        <f>P_HOCl/(k1_NH2Cl*NH3_free)</f>
+        <v>2.615e-09</v>
       </c>
       <c r="E139" s="52" t="s">
-        <v>1147</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="17" t="s">
-        <v>1148</v>
+        <v>1206</v>
       </c>
       <c r="B140" s="18" t="s">
-        <v>1149</v>
+        <v>1207</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D140" s="53">
-        <v>0.05</v>
+        <v>1190</v>
+      </c>
+      <c r="D140" s="63">
+        <f>HOCl_ss*52460</f>
+        <v>0.0001372</v>
       </c>
       <c r="E140" s="52" t="s">
-        <v>1150</v>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="17" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B141" s="18" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D141" s="53">
+        <v>10</v>
+      </c>
+      <c r="E141" s="52" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="17" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B142" s="18" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C142" s="19" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D142" s="53">
+        <v>1</v>
+      </c>
+      <c r="E142" s="52" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="17" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B143" s="18" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D143" s="63">
+        <f>MIN(P_HOCl*tau_NH2Cl*3600*52460,5.06*NH3_N)</f>
+        <v>17.02</v>
+      </c>
+      <c r="E143" s="52" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="17" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B144" s="18" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C144" s="19" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D144" s="53">
+        <v>25</v>
+      </c>
+      <c r="E144" s="52" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="17" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B145" s="18" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D145" s="63">
+        <f>f_local*pH_fHOCl*HOCl_ss_mgL+NH2Cl_mgL/R_chloramine</f>
+        <v>0.6821</v>
+      </c>
+      <c r="E145" s="52" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="17" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B146" s="18" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D146" s="53">
+        <v>0.1</v>
+      </c>
+      <c r="E146" s="52" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="17" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B147" s="18" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D147" s="53">
+        <v>2</v>
+      </c>
+      <c r="E147" s="52" t="s">
+        <v>1230</v>
       </c>
     </row>
   </sheetData>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -373,7 +373,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="1233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="1238">
   <si>
     <t>CO₂ DOSING FLOWRATES</t>
   </si>
@@ -4072,6 +4072,21 @@
   </si>
   <si>
     <t xml:space="preserve">Effective biocidal chlorine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your setting (blank → recommended)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set by the Summary 'Your setting' override (G13/G15) when filled; otherwise this Manual/Optimal selector + the manual cells below apply. Optimal = recommended schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your pulse length when sched_mode=Manual. Easiest: type into the Summary 'Your setting' column (G13) instead — it overrides everything.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your interval when sched_mode=Manual. Easiest: type into the Summary 'Your setting' column (G15) instead — it overrides everything.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≥5 s gap between pulses for an OD read (uses the schedule IN USE, so it responds to your override). Can't measure OD while sparging.</t>
   </si>
 </sst>
 </file>
@@ -5575,6 +5590,9 @@
       <c r="F12" s="16" t="s">
         <v>29</v>
       </c>
+      <c r="G12" s="16" t="s">
+        <v>1233</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
@@ -5595,6 +5613,7 @@
       <c r="F13" s="21" t="s">
         <v>67</v>
       </c>
+      <c r="G13" s="107"/>
     </row>
     <row r="14" spans="1:6" s="3" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
@@ -5630,6 +5649,7 @@
       <c r="F15" s="21" t="s">
         <v>70</v>
       </c>
+      <c r="G15" s="107"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="29" t="s">
@@ -13709,7 +13729,7 @@
         <v>730</v>
       </c>
       <c r="E81" s="69" t="s">
-        <v>731</v>
+        <v>1234</v>
       </c>
       <c r="F81" s="20"/>
     </row>
@@ -13727,7 +13747,7 @@
         <v>1</v>
       </c>
       <c r="E82" s="69" t="s">
-        <v>734</v>
+        <v>1235</v>
       </c>
       <c r="F82" s="20"/>
     </row>
@@ -13745,7 +13765,7 @@
         <v>1</v>
       </c>
       <c r="E83" s="69" t="s">
-        <v>737</v>
+        <v>1236</v>
       </c>
       <c r="F83" s="20"/>
     </row>
@@ -13968,11 +13988,11 @@
         <v>137</v>
       </c>
       <c r="D95" s="49" t="str">
-        <f>IF(spg_int_opt*60-spg_dur_opt&gt;=5,"OK","TIGHT")</f>
+        <f>IF(spg_int*60-spg_dur&gt;=5,"OK","TIGHT")</f>
         <v>OK</v>
       </c>
       <c r="E95" s="102" t="s">
-        <v>772</v>
+        <v>1237</v>
       </c>
       <c r="F95" s="20"/>
     </row>
@@ -14406,7 +14426,7 @@
         <v>13</v>
       </c>
       <c r="D121" s="24">
-        <f>IF(sched_mode="Optimal",spg_dur_opt,IF(sched_mode="Manual",spg_dur_man,NA()))</f>
+        <f>IF(AND(ISNUMBER(Summary!$G$13),Summary!$G$13&gt;0),Summary!$G$13,IF(sched_mode="Manual",spg_dur_man,spg_dur_opt))</f>
         <v>0.78451304982496561</v>
       </c>
       <c r="E121" s="20"/>
@@ -14423,8 +14443,8 @@
         <v>69</v>
       </c>
       <c r="D122" s="24">
-        <f>IF(sched_mode="Optimal",spg_int_opt,IF(sched_mode="Manual",spg_int_man,NA()))</f>
-        <v>2.8464317102116774</v>
+        <f>IF(AND(ISNUMBER(Summary!$G$15),Summary!$G$15&gt;0),Summary!$G$15,IF(sched_mode="Manual",spg_int_man,spg_int_opt))</f>
+        <v>178.08128884816398</v>
       </c>
       <c r="E122" s="20"/>
       <c r="F122" s="20"/>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -355,7 +355,7 @@
     <definedName name="Cl_onset" localSheetId="3">Chemistry!$D$146</definedName>
     <definedName name="Cl_kill" localSheetId="3">Chemistry!$D$147</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -5571,7 +5571,7 @@
       <c r="E11" s="20"/>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>66</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
         <v>1102</v>
       </c>
@@ -5630,7 +5630,7 @@
       <c r="E14" s="20"/>
       <c r="F14" s="21"/>
     </row>
-    <row r="15" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="91" t="s">
         <v>68</v>
       </c>
@@ -6211,12 +6211,12 @@
       <c r="E52" s="20"/>
       <c r="F52" s="20"/>
     </row>
-    <row r="53" spans="1:6" s="20" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="86" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="54" spans="1:6" s="20" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="87" t="s">
         <v>125</v>
       </c>
@@ -9154,12 +9154,12 @@
     <col min="5" max="5" width="39.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="111" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
         <v>856</v>
       </c>
@@ -9176,12 +9176,12 @@
         <v>860</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="110" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
         <v>862</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>866</v>
       </c>
@@ -9217,7 +9217,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
         <v>870</v>
       </c>
@@ -9235,7 +9235,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
         <v>874</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>878</v>
       </c>
@@ -9271,7 +9271,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>882</v>
       </c>
@@ -9296,7 +9296,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
         <v>888</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
         <v>894</v>
       </c>
@@ -9331,7 +9331,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>895</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
         <v>896</v>
       </c>
@@ -9367,7 +9367,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>897</v>
       </c>
@@ -9385,7 +9385,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
         <v>1046</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>898</v>
       </c>
@@ -9421,7 +9421,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
         <v>899</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
         <v>900</v>
       </c>
@@ -9457,7 +9457,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
         <v>901</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
         <v>909</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
         <v>914</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="17" t="s">
         <v>915</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="17" t="s">
         <v>916</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="17" t="s">
         <v>917</v>
       </c>
@@ -9568,7 +9568,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="17" t="s">
         <v>918</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
         <v>919</v>
       </c>
@@ -9602,7 +9602,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="17" t="s">
         <v>920</v>
       </c>
@@ -9619,7 +9619,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="17" t="s">
         <v>921</v>
       </c>
@@ -10491,7 +10491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="20">
         <v>8.6999999999999993</v>
       </c>
@@ -10504,7 +10504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="20">
         <v>8.8000000000000007</v>
       </c>
@@ -10517,7 +10517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="20">
         <v>8.9</v>
       </c>
@@ -10530,7 +10530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="20">
         <v>9</v>
       </c>
@@ -10543,11 +10543,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" s="99" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:3" s="99" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B101" s="129"/>
       <c r="C101" s="129"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="16" t="s">
         <v>24</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="17" t="s">
         <v>974</v>
       </c>
@@ -10585,7 +10585,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="17" t="s">
         <v>979</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="36" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ht="36" x14ac:dyDescent="0.2">
       <c r="A105" s="17" t="s">
         <v>1042</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="111" t="s">
         <v>999</v>
       </c>
@@ -10772,7 +10772,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="111"/>
     </row>
     <row r="125" spans="1:5" ht="24" x14ac:dyDescent="0.2">
@@ -10793,12 +10793,12 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:1">
       <c r="A127" s="111" t="s">
         <v>1161</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:5">
       <c r="A128" s="17" t="s">
         <v>1162</v>
       </c>
@@ -10815,7 +10815,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:5">
       <c r="A129" s="17" t="s">
         <v>1166</v>
       </c>
@@ -10832,7 +10832,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:5">
       <c r="A130" s="17" t="s">
         <v>1170</v>
       </c>
@@ -10849,7 +10849,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:5">
       <c r="A131" s="17" t="s">
         <v>1174</v>
       </c>
@@ -10867,7 +10867,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:5">
       <c r="A132" s="17" t="s">
         <v>1178</v>
       </c>
@@ -10885,7 +10885,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:5">
       <c r="A133" s="17" t="s">
         <v>1181</v>
       </c>
@@ -10903,7 +10903,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:5">
       <c r="A134" s="17" t="s">
         <v>1184</v>
       </c>
@@ -10915,13 +10915,13 @@
       </c>
       <c r="D134" s="63">
         <f>I_Cl/(2*Fcc*VLc)</f>
-        <v>9.011e-08</v>
+        <v>9.011E-08</v>
       </c>
       <c r="E134" s="52" t="s">
         <v>1187</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:5">
       <c r="A135" s="17" t="s">
         <v>1188</v>
       </c>
@@ -10939,7 +10939,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:5">
       <c r="A136" s="17" t="s">
         <v>1192</v>
       </c>
@@ -10956,7 +10956,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:5">
       <c r="A137" s="17" t="s">
         <v>1196</v>
       </c>
@@ -10973,7 +10973,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:5">
       <c r="A138" s="17" t="s">
         <v>1199</v>
       </c>
@@ -10985,13 +10985,13 @@
       </c>
       <c r="D138" s="63">
         <f>pH_NT/(1+10^(pKa_NH4-pH_op))</f>
-        <v>8.205e-06</v>
+        <v>8.205E-06</v>
       </c>
       <c r="E138" s="52" t="s">
         <v>1202</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:5">
       <c r="A139" s="17" t="s">
         <v>1203</v>
       </c>
@@ -11003,13 +11003,13 @@
       </c>
       <c r="D139" s="63">
         <f>P_HOCl/(k1_NH2Cl*NH3_free)</f>
-        <v>2.615e-09</v>
+        <v>2.615E-09</v>
       </c>
       <c r="E139" s="52" t="s">
         <v>1205</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:5">
       <c r="A140" s="17" t="s">
         <v>1206</v>
       </c>
@@ -11027,7 +11027,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:5">
       <c r="A141" s="17" t="s">
         <v>1209</v>
       </c>
@@ -11044,7 +11044,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:5">
       <c r="A142" s="17" t="s">
         <v>1212</v>
       </c>
@@ -11061,7 +11061,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:5">
       <c r="A143" s="17" t="s">
         <v>1216</v>
       </c>
@@ -11079,7 +11079,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:5">
       <c r="A144" s="17" t="s">
         <v>1219</v>
       </c>
@@ -11096,7 +11096,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:5">
       <c r="A145" s="17" t="s">
         <v>1222</v>
       </c>
@@ -11114,7 +11114,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:5">
       <c r="A146" s="17" t="s">
         <v>1225</v>
       </c>
@@ -11131,7 +11131,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:5">
       <c r="A147" s="17" t="s">
         <v>1228</v>
       </c>
@@ -16945,7 +16945,7 @@
       <c r="P75" s="3"/>
       <c r="Q75" s="3"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
     </row>
   </sheetData>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -5969,12 +5969,12 @@
         <f>IF(AND(ISNUMBER(Biology!$D$45),ISNUMBER(Biology!$D$46),ISNUMBER(Biology!$D$47),ISNUMBER(Biology!$D$48)),"inputs present","DATA GAP - organism DO thresholds unmeasured; results unreliable")</f>
         <v>DATA GAP - organism DO thresholds unmeasured; results unreliable</v>
       </c>
-      <c r="F34" s="21" t="s">
-        <v>1018</v>
-      </c>
       <c r="E34" s="23" t="str">
         <f>HYPERLINK("#Biology!D45","→ Biology")</f>
         <v>→ Biology</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>1018</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -5986,13 +5986,13 @@
         <f>Chemistry!$D$103</f>
         <v>6.3125785894509363</v>
       </c>
-      <c r="F35" s="21" t="s">
-        <v>1020</v>
-      </c>
       <c r="E35" s="23" t="str">
         <f>HYPERLINK("#Chemistry!D103","→ Chemistry")</f>
         <v>→ Chemistry</v>
       </c>
+      <c r="F35" s="21" t="s">
+        <v>1020</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="91" t="s">
@@ -6005,12 +6005,12 @@
         <f>Chemistry!$D$145</f>
         <v>0.6821</v>
       </c>
-      <c r="F36" s="21" t="s">
-        <v>1022</v>
-      </c>
       <c r="E36" s="23" t="str">
         <f>HYPERLINK("#Chemistry!D139","→ Chemistry")</f>
         <v>→ Chemistry</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>1022</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -355,7 +355,7 @@
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$17</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -5425,7 +5425,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="92">
-        <f>IF(D13&gt;0.5,ROUND(D13,0),ROUND(D13,1-(1+INT(LOG10(ABS(D13))))))</f>
+        <f>IF(AND(ISNUMBER($G$13),$G$13&gt;0),$G$13,IF(D13&gt;0.5,ROUND(D13,0),ROUND(D13,1-(1+INT(LOG10(ABS(D13)))))))</f>
         <v>1</v>
       </c>
       <c r="E14" s="20"/>
@@ -5461,7 +5461,7 @@
         <v>69</v>
       </c>
       <c r="D16" s="92">
-        <f>IF(D15&gt;0.5,ROUND(D15,0),ROUND(D15,1-(1+INT(LOG10(ABS(D15))))))</f>
+        <f>IF(AND(ISNUMBER($G$15),$G$15&gt;0),$G$15,IF(D15&gt;0.5,ROUND(D15,0),ROUND(D15,1-(1+INT(LOG10(ABS(D15)))))))</f>
         <v>181</v>
       </c>
       <c r="E16" s="93"/>
@@ -5624,8 +5624,8 @@
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
       <c r="D26" s="91" t="str">
-        <f>IFERROR(IF('Mass Transfer'!$D$126&gt;=1,"OK","SHORTFALL (CO2 &lt; demand)"),"calibrate this reactor first")</f>
-        <v>OK</v>
+        <f>IFERROR("×"&amp;TEXT('Mass Transfer'!$D$126,"0.0")&amp;IF('Mass Transfer'!$D$126&gt;=1," OK"," SHORTFALL (CO2 &lt; demand)"),"calibrate this reactor first")</f>
+        <v>×2.0 OK</v>
       </c>
       <c r="E26" s="23" t="str">
         <f>HYPERLINK("#'Mass Transfer'!D126","→ Mass")</f>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -355,7 +355,7 @@
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$17</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
+  <calcPr calcMode="auto" calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martincurrie/andeye Dropbox/andeye/Projects/electroPioreactor/Media/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE8A6AA-1BC9-A14E-9E7B-6C6F3FEBE8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3C7980-1D95-3947-AA29-6DC022E03979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="600" windowWidth="25640" windowHeight="18060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2780" yWindow="580" windowWidth="25640" windowHeight="18060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -354,8 +354,26 @@
     <definedName name="z_e_H2" localSheetId="2">Electrochemistry!$D$16</definedName>
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$17</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
+    <definedName name="D_CO2" localSheetId="5">'Mass Transfer'!$D$138</definedName>
+    <definedName name="pCO2_air" localSheetId="5">'Mass Transfer'!$D$139</definedName>
+    <definedName name="C_sat_CO2" localSheetId="5">'Mass Transfer'!$D$140</definedName>
+    <definedName name="C_air_CO2" localSheetId="5">'Mass Transfer'!$D$141</definedName>
+    <definedName name="sqrtD_CO2" localSheetId="5">'Mass Transfer'!$D$142</definedName>
+    <definedName name="kLa_CO2_on" localSheetId="5">'Mass Transfer'!$D$143</definedName>
+    <definedName name="kLa_CO2_off" localSheetId="5">'Mass Transfer'!$D$144</definedName>
+    <definedName name="t_on_CO2" localSheetId="5">'Mass Transfer'!$D$145</definedName>
+    <definedName name="t_off_CO2" localSheetId="5">'Mass Transfer'!$D$146</definedName>
+    <definedName name="saw_a" localSheetId="5">'Mass Transfer'!$D$147</definedName>
+    <definedName name="saw_b" localSheetId="5">'Mass Transfer'!$D$148</definedName>
+    <definedName name="CO2_cyc_start" localSheetId="5">'Mass Transfer'!$D$149</definedName>
+    <definedName name="CO2_cyc_end" localSheetId="5">'Mass Transfer'!$D$150</definedName>
+    <definedName name="CO2_int_on" localSheetId="5">'Mass Transfer'!$D$151</definedName>
+    <definedName name="CO2_int_off" localSheetId="5">'Mass Transfer'!$D$152</definedName>
+    <definedName name="CO2_cyc_avg" localSheetId="5">'Mass Transfer'!$D$153</definedName>
+    <definedName name="CO2aqc_ss" localSheetId="5">'Mass Transfer'!$D$154</definedName>
+    <definedName name="sched_valid" localSheetId="5">'Mass Transfer'!$D$155</definedName>
   </definedNames>
-  <calcPr calcMode="auto" calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -373,7 +391,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="1249">
   <si>
     <t>CO₂ DOSING FLOWRATES</t>
   </si>
@@ -3882,9 +3900,6 @@
     <t>Effective biocidal chlorine</t>
   </si>
   <si>
-    <t>Your setting (blank → recommended)</t>
-  </si>
-  <si>
     <t>Set by the Summary 'Your setting' override (G13/G15) when filled; otherwise this Manual/Optimal selector + the manual cells below apply. Optimal = recommended schedule.</t>
   </si>
   <si>
@@ -3895,6 +3910,234 @@
   </si>
   <si>
     <t>≥5 s gap between pulses for an OD read (uses the schedule IN USE, so it responds to your override). Can't measure OD while sparging.</t>
+  </si>
+  <si>
+    <t>Override</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule → dissolved-CO₂ sawtooth model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limit-cycle dissolved CO₂ from the sparge pulse/gap schedule; feeds Chemistry CO2aqc (D5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO₂ molecular diffusivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D_CO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m²/s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO₂ molecular diffusivity in water ~25°C, Cussler/Tamimi 1994. FLAG: scaled against the 30°C D_O2, ~3% bias on kLa, conservative.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atmospheric pCO₂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pCO2_air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atmospheric pCO₂ ~400 ppm; between-pulse decay target; assumes ventilated headspace.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO₂ saturation (pure sparge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_sat_CO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/m³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure-CO₂ sparge saturation = pulse asymptote &amp; upper clamp ~29.28.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO₂ air-equilibrium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_air_CO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/m³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air-equilibrium = gap asymptote &amp; lower clamp ~0.0116.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diffusivity scaling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sqrtD_CO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penetration-theory diffusivity scaling kL~D^0.5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kLa CO₂ during pulse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kLa_CO2_on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bubble-path CO₂ transfer during a pulse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kLa CO₂ between pulses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kLa_CO2_off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface-path CO₂ stripping between pulses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulse duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_on_CO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulse duration = in-use schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_off_CO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARD floored at 0; without it interval&lt;pulse drives the average negative and a more-than-full-sparge schedule wrongly reports the no-sparge pH.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulse decay factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saw_a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exp(-kLa_CO2_on*t_on_CO2); fraction of the saturation gap left at pulse end.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap decay factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saw_b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exp(-kLa_CO2_off*t_off_CO2); fraction of the air-eq gap left at gap end.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycle-start CO₂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO2_cyc_start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/m³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodic limit-cycle concentration at the start of each pulse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycle-end CO₂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO2_cyc_end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/m³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentration at the end of each pulse (start of the gap).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulse time-integral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO2_int_on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol.s/m³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">∫C dt over the pulse (analytic, first-order relaxation toward C_sat_CO2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap time-integral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO2_int_off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol.s/m³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">∫C dt over the gap (analytic, first-order relaxation toward C_air_CO2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycle-average CO₂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO2_cyc_avg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/m³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycle time-average dissolved CO₂, schedule-dependent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steady dissolved CO₂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO2aqc_ss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mol/L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bounded steady dissolved CO₂; the value Chemistry D5 is repointed to.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule validity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sched_valid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surfaces the duty&gt;1 misuse the guard absorbs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule-dependent steady-state dissolved CO₂ (sawtooth limit cycle, bounded air-eq..saturation) - was the fixed full-sparge worst case</t>
   </si>
 </sst>
 </file>
@@ -4276,7 +4519,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -4477,6 +4720,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11"/>
@@ -4484,7 +4742,7 @@
     <xf numFmtId="0" fontId="28" fillId="10" borderId="11"/>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="11"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4665,6 +4923,7 @@
     <xf numFmtId="168" fontId="41" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="32" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -4672,7 +4931,7 @@
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="30">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4896,6 +5155,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
+          <bgColor rgb="FFBDD7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5392,7 +5659,7 @@
         <v>29</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5414,7 +5681,7 @@
       <c r="F13" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="106"/>
+      <c r="G13" s="130"/>
     </row>
     <row r="14" spans="1:7" s="3" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
@@ -5450,7 +5717,7 @@
       <c r="F15" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="106"/>
+      <c r="G15" s="130"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="28" t="s">
@@ -6292,6 +6559,16 @@
       <c r="F71" s="20"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="expression" dxfId="29" priority="1" stopIfTrue="1">
+      <formula>AND(ISNUMBER($G$13),$G$13&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="expression" dxfId="29" priority="2" stopIfTrue="1">
+      <formula>AND(ISNUMBER($G$15),$G$15&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B56:B68">
     <cfRule type="expression" dxfId="28" priority="15" stopIfTrue="1">
       <formula>EXACT(B56,"HIGH")</formula>
@@ -9011,11 +9288,11 @@
         <v>860</v>
       </c>
       <c r="D5" s="64">
-        <f>Biology!$D$33/1000</f>
-        <v>3.3437250000000002E-2</v>
+        <f>'Mass Transfer'!$D$154</f>
+        <v>1.8102E-5</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>861</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -12031,7 +12308,7 @@
   <sheetPr>
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -13530,7 +13807,7 @@
         <v>730</v>
       </c>
       <c r="E81" s="68" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="F81" s="20"/>
     </row>
@@ -13548,7 +13825,7 @@
         <v>1</v>
       </c>
       <c r="E82" s="68" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="F82" s="20"/>
     </row>
@@ -13566,7 +13843,7 @@
         <v>1</v>
       </c>
       <c r="E83" s="68" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="F83" s="20"/>
     </row>
@@ -13793,7 +14070,7 @@
         <v>OK</v>
       </c>
       <c r="E95" s="101" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="F95" s="20"/>
     </row>
@@ -14478,6 +14755,358 @@
         <v>1025</v>
       </c>
       <c r="F135" s="20"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137" s="20" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B137" s="20"/>
+      <c r="C137" s="20"/>
+      <c r="D137" s="20"/>
+      <c r="E137" s="20" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F137" s="20"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" s="17" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B138" s="18" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C138" s="19" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D138" s="124">
+        <v>1.92E-9</v>
+      </c>
+      <c r="E138" s="67" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F138" s="20"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139" s="17" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B139" s="18" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D139" s="124">
+        <v>40</v>
+      </c>
+      <c r="E139" s="67" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F139" s="20"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" s="17" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B140" s="18" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C140" s="19" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D140" s="48">
+        <f>Biology!$D$31*P_atm</f>
+        <v>29.280</v>
+      </c>
+      <c r="E140" s="67" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F140" s="20"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" s="17" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B141" s="18" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D141" s="48">
+        <f>Biology!$D$31*pCO2_air</f>
+        <v>0.011559</v>
+      </c>
+      <c r="E141" s="67" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F141" s="20"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="17" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B142" s="18" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C142" s="19" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D142" s="48">
+        <f>SQRT(D_CO2/D_O2)</f>
+        <v>0.92396</v>
+      </c>
+      <c r="E142" s="67" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F142" s="20"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" s="17" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B143" s="18" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D143" s="48">
+        <f>kLa_sparge*sqrtD_CO2</f>
+        <v>0.015245</v>
+      </c>
+      <c r="E143" s="67" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F143" s="20"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="17" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B144" s="18" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C144" s="19" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D144" s="48">
+        <f>kLa_surf*sqrtD_CO2</f>
+        <v>0.0049913</v>
+      </c>
+      <c r="E144" s="67" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F144" s="20"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="17" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B145" s="18" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D145" s="48">
+        <f>spg_dur</f>
+        <v>0.7845</v>
+      </c>
+      <c r="E145" s="67" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F145" s="20"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="17" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B146" s="18" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D146" s="48">
+        <f>MAX(0,spg_int*60-spg_dur)</f>
+        <v>10684.1</v>
+      </c>
+      <c r="E146" s="68" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F146" s="20"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" s="17" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B147" s="18" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D147" s="48">
+        <f>EXP(-kLa_CO2_on*t_on_CO2)</f>
+        <v>0.98811</v>
+      </c>
+      <c r="E147" s="68" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F147" s="20"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148" s="17" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B148" s="18" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C148" s="19" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D148" s="48">
+        <f>EXP(-kLa_CO2_off*t_off_CO2)</f>
+        <v>0</v>
+      </c>
+      <c r="E148" s="68" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F148" s="20"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149" s="17" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B149" s="18" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D149" s="48">
+        <f>(C_air_CO2*(1-saw_b)+saw_b*C_sat_CO2*(1-saw_a))/(1-saw_a*saw_b)</f>
+        <v>0.011559</v>
+      </c>
+      <c r="E149" s="67" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F149" s="20"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" s="17" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B150" s="18" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C150" s="19" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D150" s="48">
+        <f>C_sat_CO2+(CO2_cyc_start-C_sat_CO2)*saw_a</f>
+        <v>0.360</v>
+      </c>
+      <c r="E150" s="67" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F150" s="20"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" s="17" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B151" s="18" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D151" s="48">
+        <f>C_sat_CO2*t_on_CO2+(CO2_cyc_start-C_sat_CO2)/kLa_CO2_on*(1-saw_a)</f>
+        <v>0.140</v>
+      </c>
+      <c r="E151" s="68" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F151" s="20"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" s="17" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B152" s="18" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C152" s="19" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D152" s="48">
+        <f>C_air_CO2*t_off_CO2+(CO2_cyc_end-C_air_CO2)/kLa_CO2_off*(1-saw_b)</f>
+        <v>193.3</v>
+      </c>
+      <c r="E152" s="68" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F152" s="20"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" s="17" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B153" s="18" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C153" s="19" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D153" s="48">
+        <f>(CO2_int_on+CO2_int_off)/(t_on_CO2+t_off_CO2)</f>
+        <v>0.018102</v>
+      </c>
+      <c r="E153" s="67" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F153" s="20"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" s="17" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B154" s="18" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C154" s="19" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D154" s="48">
+        <f>MIN(C_sat_CO2,MAX(C_air_CO2,CO2_cyc_avg))/1000</f>
+        <v>1.8102E-5</v>
+      </c>
+      <c r="E154" s="67" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F154" s="20"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" s="17" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B155" s="18" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C155" s="19" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D155" s="48" t="str">
+        <f>IF(spg_int*60&gt;=spg_dur,"OK","INVALID: interval &lt; pulse")</f>
+        <v>OK</v>
+      </c>
+      <c r="E155" s="68" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F155" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D32">

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -356,24 +356,33 @@
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
     <definedName name="D_CO2" localSheetId="5">'Mass Transfer'!$D$138</definedName>
     <definedName name="pCO2_air" localSheetId="5">'Mass Transfer'!$D$139</definedName>
-    <definedName name="C_sat_CO2" localSheetId="5">'Mass Transfer'!$D$140</definedName>
-    <definedName name="C_air_CO2" localSheetId="5">'Mass Transfer'!$D$141</definedName>
-    <definedName name="sqrtD_CO2" localSheetId="5">'Mass Transfer'!$D$142</definedName>
-    <definedName name="kLa_CO2_on" localSheetId="5">'Mass Transfer'!$D$143</definedName>
-    <definedName name="kLa_CO2_off" localSheetId="5">'Mass Transfer'!$D$144</definedName>
-    <definedName name="t_on_CO2" localSheetId="5">'Mass Transfer'!$D$145</definedName>
-    <definedName name="t_off_CO2" localSheetId="5">'Mass Transfer'!$D$146</definedName>
-    <definedName name="saw_a" localSheetId="5">'Mass Transfer'!$D$147</definedName>
-    <definedName name="saw_b" localSheetId="5">'Mass Transfer'!$D$148</definedName>
-    <definedName name="CO2_cyc_start" localSheetId="5">'Mass Transfer'!$D$149</definedName>
-    <definedName name="CO2_cyc_end" localSheetId="5">'Mass Transfer'!$D$150</definedName>
-    <definedName name="CO2_int_on" localSheetId="5">'Mass Transfer'!$D$151</definedName>
-    <definedName name="CO2_int_off" localSheetId="5">'Mass Transfer'!$D$152</definedName>
-    <definedName name="CO2_cyc_avg" localSheetId="5">'Mass Transfer'!$D$153</definedName>
-    <definedName name="CO2aqc_ss" localSheetId="5">'Mass Transfer'!$D$154</definedName>
-    <definedName name="sched_valid" localSheetId="5">'Mass Transfer'!$D$155</definedName>
+    <definedName name="headspace_V_m3" localSheetId="5">'Mass Transfer'!$D$140</definedName>
+    <definedName name="V_L_m3" localSheetId="5">'Mass Transfer'!$D$141</definedName>
+    <definedName name="Q_vent" localSheetId="5">'Mass Transfer'!$D$142</definedName>
+    <definedName name="k_vent" localSheetId="5">'Mass Transfer'!$D$143</definedName>
+    <definedName name="tau_hs" localSheetId="5">'Mass Transfer'!$D$144</definedName>
+    <definedName name="C_sat_CO2" localSheetId="5">'Mass Transfer'!$D$145</definedName>
+    <definedName name="C_air_CO2" localSheetId="5">'Mass Transfer'!$D$146</definedName>
+    <definedName name="sqrtD_CO2" localSheetId="5">'Mass Transfer'!$D$147</definedName>
+    <definedName name="kLa_CO2_off" localSheetId="5">'Mass Transfer'!$D$148</definedName>
+    <definedName name="tau_surf_floor" localSheetId="5">'Mass Transfer'!$D$149</definedName>
+    <definedName name="n_hs_gas" localSheetId="5">'Mass Transfer'!$D$150</definedName>
+    <definedName name="t_on_CO2" localSheetId="5">'Mass Transfer'!$D$151</definedName>
+    <definedName name="t_off_CO2" localSheetId="5">'Mass Transfer'!$D$152</definedName>
+    <definedName name="eon_CO2" localSheetId="5">'Mass Transfer'!$D$153</definedName>
+    <definedName name="e1_CO2" localSheetId="5">'Mass Transfer'!$D$154</definedName>
+    <definedName name="e2_CO2" localSheetId="5">'Mass Transfer'!$D$155</definedName>
+    <definedName name="coef_CO2" localSheetId="5">'Mass Transfer'!$D$156</definedName>
+    <definedName name="Ca_CO2" localSheetId="5">'Mass Transfer'!$D$157</definedName>
+    <definedName name="Cb_CO2" localSheetId="5">'Mass Transfer'!$D$158</definedName>
+    <definedName name="CO2_int_on" localSheetId="5">'Mass Transfer'!$D$159</definedName>
+    <definedName name="CO2_int_off" localSheetId="5">'Mass Transfer'!$D$160</definedName>
+    <definedName name="CO2_cyc_avg" localSheetId="5">'Mass Transfer'!$D$161</definedName>
+    <definedName name="CO2aqc_ss" localSheetId="5">'Mass Transfer'!$D$162</definedName>
+    <definedName name="vent_floor_chk" localSheetId="5">'Mass Transfer'!$D$163</definedName>
+    <definedName name="sched_valid" localSheetId="5">'Mass Transfer'!$D$164</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" iterateDelta="1E-4"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -9288,8 +9297,8 @@
         <v>860</v>
       </c>
       <c r="D5" s="64">
-        <f>'Mass Transfer'!$D$154</f>
-        <v>1.8102E-5</v>
+        <f>'Mass Transfer'!$D$162</f>
+        <v>8.724353186629647E-4</v>
       </c>
       <c r="E5" s="51" t="s">
         <v>1248</v>
@@ -12308,7 +12317,7 @@
   <sheetPr>
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F164"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -14769,344 +14778,730 @@
       <c r="F137" s="20"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A138" s="17" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B138" s="18" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C138" s="19" t="s">
-        <v>1178</v>
+      <c r="A138" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO₂ molecular diffusivity</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D_CO2</t>
+        </is>
+      </c>
+      <c r="C138" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m²/s</t>
+        </is>
       </c>
       <c r="D138" s="124">
         <v>1.92E-9</v>
       </c>
-      <c r="E138" s="67" t="s">
-        <v>1179</v>
+      <c r="E138" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO₂ diffusivity in water ~25°C, Cussler/Tamimi 1994.</t>
+        </is>
       </c>
       <c r="F138" s="20"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A139" s="17" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B139" s="18" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C139" s="19" t="s">
-        <v>1182</v>
+      <c r="A139" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atmospheric CO₂ partial pressure</t>
+        </is>
+      </c>
+      <c r="B139" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pCO2_air</t>
+        </is>
+      </c>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pa</t>
+        </is>
       </c>
       <c r="D139" s="124">
         <v>40</v>
       </c>
-      <c r="E139" s="67" t="s">
-        <v>1183</v>
+      <c r="E139" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atmospheric pCO₂ (~400 ppm).</t>
+        </is>
       </c>
       <c r="F139" s="20"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A140" s="17" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B140" s="18" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C140" s="19" t="s">
-        <v>1186</v>
+      <c r="A140" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Headspace volume (SI)</t>
+        </is>
+      </c>
+      <c r="B140" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">headspace_V_m3</t>
+        </is>
+      </c>
+      <c r="C140" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m³</t>
+        </is>
       </c>
       <c r="D140" s="48">
+        <f>headspace_V/1000000</f>
+        <v>2.6124284559171357E-6</v>
+      </c>
+      <c r="E140" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Geometry headspace volume converted mL→m³.</t>
+        </is>
+      </c>
+      <c r="F140" s="20"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquid volume (SI)</t>
+        </is>
+      </c>
+      <c r="B141" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V_L_m3</t>
+        </is>
+      </c>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m³</t>
+        </is>
+      </c>
+      <c r="D141" s="48">
+        <f>V_charge/1000000</f>
+        <v>1.5E-5</v>
+      </c>
+      <c r="E141" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Charged liquid volume converted mL→m³.</t>
+        </is>
+      </c>
+      <c r="F141" s="20"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Headspace vent bleed</t>
+        </is>
+      </c>
+      <c r="B142" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q_vent</t>
+        </is>
+      </c>
+      <c r="C142" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mL/min</t>
+        </is>
+      </c>
+      <c r="D142" s="124">
+        <v>0.5</v>
+      </c>
+      <c r="E142" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slow restricted vent bleed - dead-volume + tube + near-closed solenoid leak. KEY NEW UNCERTAIN PARAMETER - measure. NOT free membrane diffusion, which would clear in seconds and could not reproduce the run-2 acidification.</t>
+        </is>
+      </c>
+      <c r="F142" s="20"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Headspace vent rate</t>
+        </is>
+      </c>
+      <c r="B143" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">k_vent</t>
+        </is>
+      </c>
+      <c r="C143" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/s</t>
+        </is>
+      </c>
+      <c r="D143" s="48">
+        <f>(Q_vent/1000000/60)/headspace_V_m3</f>
+        <v>3.189880019281822E-3</v>
+      </c>
+      <c r="E143" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First-order headspace clearance from the vent volumetric bleed.</t>
+        </is>
+      </c>
+      <c r="F143" s="20"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Headspace residence time</t>
+        </is>
+      </c>
+      <c r="B144" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tau_hs</t>
+        </is>
+      </c>
+      <c r="C144" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">min</t>
+        </is>
+      </c>
+      <c r="D144" s="48">
+        <f>headspace_V_m3/(Q_vent/1000000/60)/60</f>
+        <v>5.224856911834271</v>
+      </c>
+      <c r="E144" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time constant for the headspace to clear through the vent.</t>
+        </is>
+      </c>
+      <c r="F144" s="20"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO₂ saturation (pure sparge)</t>
+        </is>
+      </c>
+      <c r="B145" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C_sat_CO2</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mol/m³</t>
+        </is>
+      </c>
+      <c r="D145" s="48">
         <f>Biology!$D$31*P_atm</f>
-        <v>29.280</v>
-      </c>
-      <c r="E140" s="67" t="s">
-        <v>1187</v>
-      </c>
-      <c r="F140" s="20"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A141" s="17" t="s">
-        <v>1188</v>
-      </c>
-      <c r="B141" s="18" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C141" s="19" t="s">
-        <v>1190</v>
-      </c>
-      <c r="D141" s="48">
+        <v>29.279978066256632</v>
+      </c>
+      <c r="E145" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Henry-law dissolved CO₂ at pure-CO₂ saturation.</t>
+        </is>
+      </c>
+      <c r="F145" s="20"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO₂ air-equilibrium</t>
+        </is>
+      </c>
+      <c r="B146" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C_air_CO2</t>
+        </is>
+      </c>
+      <c r="C146" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mol/m³</t>
+        </is>
+      </c>
+      <c r="D146" s="48">
         <f>Biology!$D$31*pCO2_air</f>
-        <v>0.011559</v>
-      </c>
-      <c r="E141" s="67" t="s">
-        <v>1191</v>
-      </c>
-      <c r="F141" s="20"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A142" s="17" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B142" s="18" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C142" s="19" t="s">
-        <v>1194</v>
-      </c>
-      <c r="D142" s="48">
+        <v>1.155883664100928E-2</v>
+      </c>
+      <c r="E146" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Henry-law dissolved CO₂ in equilibrium with room air.</t>
+        </is>
+      </c>
+      <c r="F146" s="20"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diffusivity scaling (CO₂/O₂)</t>
+        </is>
+      </c>
+      <c r="B147" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sqrtD_CO2</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D147" s="48">
         <f>SQRT(D_CO2/D_O2)</f>
-        <v>0.92396</v>
-      </c>
-      <c r="E142" s="67" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F142" s="20"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A143" s="17" t="s">
-        <v>1196</v>
-      </c>
-      <c r="B143" s="18" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C143" s="19" t="s">
-        <v>1198</v>
-      </c>
-      <c r="D143" s="48">
-        <f>kLa_sparge*sqrtD_CO2</f>
-        <v>0.015245</v>
-      </c>
-      <c r="E143" s="67" t="s">
-        <v>1199</v>
-      </c>
-      <c r="F143" s="20"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A144" s="17" t="s">
-        <v>1200</v>
-      </c>
-      <c r="B144" s="18" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C144" s="19" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D144" s="48">
+        <v>0.9239657792511647</v>
+      </c>
+      <c r="E147" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penetration-theory √(D_CO₂/D_O₂) scaling of the O₂ transfer coefficient.</t>
+        </is>
+      </c>
+      <c r="F147" s="20"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO₂ surface transfer coefficient</t>
+        </is>
+      </c>
+      <c r="B148" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kLa_CO2_off</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/s</t>
+        </is>
+      </c>
+      <c r="D148" s="48">
         <f>kLa_surf*sqrtD_CO2</f>
-        <v>0.0049913</v>
-      </c>
-      <c r="E144" s="67" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F144" s="20"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" s="17" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B145" s="18" t="s">
-        <v>1205</v>
-      </c>
-      <c r="C145" s="19" t="s">
-        <v>1206</v>
-      </c>
-      <c r="D145" s="48">
+        <v>4.991283516870223E-3</v>
+      </c>
+      <c r="E148" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surface kLa for CO₂ between pulses (surface path).</t>
+        </is>
+      </c>
+      <c r="F148" s="20"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surface-relaxation time</t>
+        </is>
+      </c>
+      <c r="B149" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tau_surf_floor</t>
+        </is>
+      </c>
+      <c r="C149" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">min</t>
+        </is>
+      </c>
+      <c r="D149" s="48">
+        <f>1/kLa_CO2_off/60</f>
+        <v>3.3391544700545235</v>
+      </c>
+      <c r="E149" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time constant for the liquid to relax to the headspace via the surface.</t>
+        </is>
+      </c>
+      <c r="F149" s="20"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Headspace gas inventory</t>
+        </is>
+      </c>
+      <c r="B150" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n_hs_gas</t>
+        </is>
+      </c>
+      <c r="C150" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mol</t>
+        </is>
+      </c>
+      <c r="D150" s="48">
+        <f>P_atm*headspace_V_m3/(R_gas*T_K)</f>
+        <v>1.0501933416012095E-4</v>
+      </c>
+      <c r="E150" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moles of gas in the headspace at P_atm, T_K (ideal-gas).</t>
+        </is>
+      </c>
+      <c r="F150" s="20"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pulse duration</t>
+        </is>
+      </c>
+      <c r="B151" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t_on_CO2</t>
+        </is>
+      </c>
+      <c r="C151" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="D151" s="48">
         <f>spg_dur</f>
-        <v>0.7845</v>
-      </c>
-      <c r="E145" s="67" t="s">
-        <v>1207</v>
-      </c>
-      <c r="F145" s="20"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A146" s="17" t="s">
-        <v>1208</v>
-      </c>
-      <c r="B146" s="18" t="s">
-        <v>1209</v>
-      </c>
-      <c r="C146" s="19" t="s">
-        <v>1210</v>
-      </c>
-      <c r="D146" s="48">
+        <v>0.7845130498249656</v>
+      </c>
+      <c r="E151" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sparge pulse on-time from the schedule.</t>
+        </is>
+      </c>
+      <c r="F151" s="20"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gap duration</t>
+        </is>
+      </c>
+      <c r="B152" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t_off_CO2</t>
+        </is>
+      </c>
+      <c r="C152" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="D152" s="48">
         <f>MAX(0,spg_int*60-spg_dur)</f>
-        <v>10684.1</v>
-      </c>
-      <c r="E146" s="68" t="s">
-        <v>1211</v>
-      </c>
-      <c r="F146" s="20"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" s="17" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B147" s="18" t="s">
-        <v>1213</v>
-      </c>
-      <c r="C147" s="19" t="s">
-        <v>1214</v>
-      </c>
-      <c r="D147" s="48">
-        <f>EXP(-kLa_CO2_on*t_on_CO2)</f>
-        <v>0.98811</v>
-      </c>
-      <c r="E147" s="68" t="s">
-        <v>1215</v>
-      </c>
-      <c r="F147" s="20"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A148" s="17" t="s">
-        <v>1216</v>
-      </c>
-      <c r="B148" s="18" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C148" s="19" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D148" s="48">
+        <v>10684.092817840014</v>
+      </c>
+      <c r="E152" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time between pulses, guard-floored at 0.</t>
+        </is>
+      </c>
+      <c r="F152" s="20"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On-phase surface decay</t>
+        </is>
+      </c>
+      <c r="B153" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eon_CO2</t>
+        </is>
+      </c>
+      <c r="C153" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D153" s="48">
+        <f>EXP(-kLa_CO2_off*t_on_CO2)</f>
+        <v>0.996091929408022</v>
+      </c>
+      <c r="E153" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surface-path liquid decay factor over the pulse.</t>
+        </is>
+      </c>
+      <c r="F153" s="20"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Off-phase surface decay</t>
+        </is>
+      </c>
+      <c r="B154" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e1_CO2</t>
+        </is>
+      </c>
+      <c r="C154" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D154" s="48">
         <f>EXP(-kLa_CO2_off*t_off_CO2)</f>
-        <v>0</v>
-      </c>
-      <c r="E148" s="68" t="s">
-        <v>1219</v>
-      </c>
-      <c r="F148" s="20"/>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A149" s="17" t="s">
-        <v>1220</v>
-      </c>
-      <c r="B149" s="18" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C149" s="19" t="s">
-        <v>1222</v>
-      </c>
-      <c r="D149" s="48">
-        <f>(C_air_CO2*(1-saw_b)+saw_b*C_sat_CO2*(1-saw_a))/(1-saw_a*saw_b)</f>
-        <v>0.011559</v>
-      </c>
-      <c r="E149" s="67" t="s">
-        <v>1223</v>
-      </c>
-      <c r="F149" s="20"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A150" s="17" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B150" s="18" t="s">
-        <v>1225</v>
-      </c>
-      <c r="C150" s="19" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D150" s="48">
-        <f>C_sat_CO2+(CO2_cyc_start-C_sat_CO2)*saw_a</f>
-        <v>0.360</v>
-      </c>
-      <c r="E150" s="67" t="s">
-        <v>1227</v>
-      </c>
-      <c r="F150" s="20"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A151" s="17" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B151" s="18" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C151" s="19" t="s">
-        <v>1230</v>
-      </c>
-      <c r="D151" s="48">
-        <f>C_sat_CO2*t_on_CO2+(CO2_cyc_start-C_sat_CO2)/kLa_CO2_on*(1-saw_a)</f>
-        <v>0.140</v>
-      </c>
-      <c r="E151" s="68" t="s">
-        <v>1231</v>
-      </c>
-      <c r="F151" s="20"/>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A152" s="17" t="s">
-        <v>1232</v>
-      </c>
-      <c r="B152" s="18" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C152" s="19" t="s">
-        <v>1234</v>
-      </c>
-      <c r="D152" s="48">
-        <f>C_air_CO2*t_off_CO2+(CO2_cyc_end-C_air_CO2)/kLa_CO2_off*(1-saw_b)</f>
-        <v>193.3</v>
-      </c>
-      <c r="E152" s="68" t="s">
-        <v>1235</v>
-      </c>
-      <c r="F152" s="20"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A153" s="17" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B153" s="18" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C153" s="19" t="s">
-        <v>1238</v>
-      </c>
-      <c r="D153" s="48">
+        <v>6.922007698981812E-24</v>
+      </c>
+      <c r="E154" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surface-path liquid decay factor over the gap.</t>
+        </is>
+      </c>
+      <c r="F154" s="20"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Off-phase vent decay</t>
+        </is>
+      </c>
+      <c r="B155" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e2_CO2</t>
+        </is>
+      </c>
+      <c r="C155" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D155" s="48">
+        <f>EXP(-k_vent*t_off_CO2)</f>
+        <v>1.5805963161657336E-15</v>
+      </c>
+      <c r="E155" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Headspace vent decay factor over the gap.</t>
+        </is>
+      </c>
+      <c r="F155" s="20"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two-compartment coupling coef</t>
+        </is>
+      </c>
+      <c r="B156" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coef_CO2</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mol/m³</t>
+        </is>
+      </c>
+      <c r="D156" s="48">
+        <f>(C_sat_CO2-C_air_CO2)*kLa_CO2_off/(kLa_CO2_off-k_vent)</f>
+        <v>81.09620008021494</v>
+      </c>
+      <c r="E156" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coupling coefficient linking the venting headspace to the liquid relaxation.</t>
+        </is>
+      </c>
+      <c r="F156" s="20"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cycle-start liquid CO₂</t>
+        </is>
+      </c>
+      <c r="B157" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ca_CO2</t>
+        </is>
+      </c>
+      <c r="C157" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mol/m³</t>
+        </is>
+      </c>
+      <c r="D157" s="48">
+        <f>(e1_CO2*C_sat_CO2*(1-eon_CO2)+C_air_CO2*(1-e1_CO2)+coef_CO2*(e2_CO2-e1_CO2))/(1-e1_CO2*eon_CO2)</f>
+        <v>1.155883664113746E-2</v>
+      </c>
+      <c r="E157" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closed-form limit-cycle dissolved CO₂ at the start of each pulse.</t>
+        </is>
+      </c>
+      <c r="F157" s="20"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End-of-pulse liquid CO₂</t>
+        </is>
+      </c>
+      <c r="B158" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cb_CO2</t>
+        </is>
+      </c>
+      <c r="C158" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mol/m³</t>
+        </is>
+      </c>
+      <c r="D158" s="48">
+        <f>C_sat_CO2+(Ca_CO2-C_sat_CO2)*eon_CO2</f>
+        <v>0.1259418851060765</v>
+      </c>
+      <c r="E158" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dissolved CO₂ at the end of the pulse (start of the gap).</t>
+        </is>
+      </c>
+      <c r="F158" s="20"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On-phase CO₂ integral</t>
+        </is>
+      </c>
+      <c r="B159" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO2_int_on</t>
+        </is>
+      </c>
+      <c r="C159" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mol.s/m³</t>
+        </is>
+      </c>
+      <c r="D159" s="48">
+        <f>C_sat_CO2*t_on_CO2+(Ca_CO2-C_sat_CO2)/kLa_CO2_off*(1-eon_CO2)</f>
+        <v>5.3964836756566825E-2</v>
+      </c>
+      <c r="E159" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time-integral of dissolved CO₂ over the pulse.</t>
+        </is>
+      </c>
+      <c r="F159" s="20"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Off-phase CO₂ integral</t>
+        </is>
+      </c>
+      <c r="B160" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO2_int_off</t>
+        </is>
+      </c>
+      <c r="C160" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mol.s/m³</t>
+        </is>
+      </c>
+      <c r="D160" s="48">
+        <f>C_air_CO2*t_off_CO2+(Cb_CO2-C_air_CO2)/kLa_CO2_off*(1-e1_CO2)+coef_CO2*((1-e2_CO2)/k_vent-(1-e1_CO2)/kLa_CO2_off)</f>
+        <v>9321.810394212807</v>
+      </c>
+      <c r="E160" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time-integral of dissolved CO₂ over the gap, including the venting-headspace term.</t>
+        </is>
+      </c>
+      <c r="F160" s="20"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cycle-average CO₂</t>
+        </is>
+      </c>
+      <c r="B161" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO2_cyc_avg</t>
+        </is>
+      </c>
+      <c r="C161" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mol/m³</t>
+        </is>
+      </c>
+      <c r="D161" s="48">
         <f>(CO2_int_on+CO2_int_off)/(t_on_CO2+t_off_CO2)</f>
-        <v>0.018102</v>
-      </c>
-      <c r="E153" s="67" t="s">
-        <v>1239</v>
-      </c>
-      <c r="F153" s="20"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A154" s="17" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B154" s="18" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C154" s="19" t="s">
-        <v>1242</v>
-      </c>
-      <c r="D154" s="48">
+        <v>0.8724353186629646</v>
+      </c>
+      <c r="E161" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Limit-cycle time-average dissolved CO₂ over one pulse+gap.</t>
+        </is>
+      </c>
+      <c r="F161" s="20"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Steady dissolved CO₂</t>
+        </is>
+      </c>
+      <c r="B162" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO2aqc_ss</t>
+        </is>
+      </c>
+      <c r="C162" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mol/L</t>
+        </is>
+      </c>
+      <c r="D162" s="48">
         <f>MIN(C_sat_CO2,MAX(C_air_CO2,CO2_cyc_avg))/1000</f>
-        <v>1.8102E-5</v>
-      </c>
-      <c r="E154" s="67" t="s">
-        <v>1243</v>
-      </c>
-      <c r="F154" s="20"/>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A155" s="17" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B155" s="18" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C155" s="19" t="s">
-        <v>1246</v>
-      </c>
-      <c r="D155" s="48" t="str">
+        <v>8.724353186629647E-4</v>
+      </c>
+      <c r="E162" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bounded steady dissolved CO₂; the value Chemistry D5 is repointed to (two-compartment headspace model).</t>
+        </is>
+      </c>
+      <c r="F162" s="20"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent-path sanity check</t>
+        </is>
+      </c>
+      <c r="B163" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vent_floor_chk</t>
+        </is>
+      </c>
+      <c r="C163" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D163" s="48" t="str">
+        <f>IF(tau_hs&gt;=tau_surf_floor,"vent is slow path - OK","WARNING: surface clears faster than vent - run2 cannot stay acidic")</f>
+        <v>vent is slow path - OK</v>
+      </c>
+      <c r="E163" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirms the vent is the rate-limiting path; if the surface cleared faster, run 2 could not stay acidic.</t>
+        </is>
+      </c>
+      <c r="F163" s="20"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schedule validity</t>
+        </is>
+      </c>
+      <c r="B164" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sched_valid</t>
+        </is>
+      </c>
+      <c r="C164" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D164" s="48" t="str">
         <f>IF(spg_int*60&gt;=spg_dur,"OK","INVALID: interval &lt; pulse")</f>
         <v>OK</v>
       </c>
-      <c r="E155" s="68" t="s">
-        <v>1247</v>
-      </c>
-      <c r="F155" s="20"/>
+      <c r="E164" s="67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surfaces an interval&lt;pulse misconfiguration.</t>
+        </is>
+      </c>
+      <c r="F164" s="20"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D32">

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -6061,7 +6061,7 @@
       <c r="C35" s="20"/>
       <c r="D35" s="129">
         <f>Chemistry!$D$103</f>
-        <v>6.0708472792648696</v>
+        <v>7.3834297974</v>
       </c>
       <c r="E35" s="23" t="str">
         <f>HYPERLINK("#Chemistry!D103","→ Chemistry")</f>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D36" s="129">
         <f>Chemistry!$D$145</f>
-        <v>0</v>
+        <v>0.6807516555</v>
       </c>
       <c r="E36" s="23" t="str">
         <f>HYPERLINK("#Chemistry!D139","→ Chemistry")</f>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="D103" s="62">
         <f>IF(n_cross=1,SUM(C50:C100),NA())</f>
-        <v>6.0708472792648696</v>
+        <v>7.3834297974</v>
       </c>
       <c r="E103" s="51" t="s">
         <v>969</v>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="D104" s="62">
         <f>1/(1+10^(pH_op-pKa_HOCl))</f>
-        <v>0.96716420803891789</v>
+        <v>0.5667723118</v>
       </c>
       <c r="E104" s="51" t="s">
         <v>974</v>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D109" s="64" t="str">
         <f>IF(C_eff&lt;Cl_onset,"negligible free chlorine ("&amp;TEXT(C_eff,"0.00")&amp;" mg/L &lt; onset)",IF(C_eff&lt;Cl_kill,"MILD sub-lethal penalty: "&amp;TEXT(C_eff,"0.00")&amp;" mg/L (chloride costs lag/growth — Sydow 2017; chloride-free avoids it)","SEVERE free chlorine: "&amp;TEXT(C_eff,"0.0")&amp;" mg/L → biofilm/electrode damage (Baek 2021)"))</f>
-        <v>negligible free chlorine (0.00 mg/L &lt; onset)</v>
+        <v>MILD sub-lethal penalty: 0.68 mg/L (chloride costs lag/growth — Sydow 2017; chloride-free avoids it)</v>
       </c>
       <c r="E109" s="51" t="s">
         <v>1167</v>
@@ -10792,7 +10792,7 @@
       </c>
       <c r="D110" s="64" t="str">
         <f>IF(pH_op&lt;6.5,"pH BELOW HOB optimum (&lt;6.5) — reduce CO₂ dose",IF(pH_op&gt;7.5,"pH above optimum (&gt;7.5)","pH in HOB band 6.5–7.5"))</f>
-        <v>pH BELOW HOB optimum (&lt;6.5) — reduce CO₂ dose</v>
+        <v>pH in HOB band 6.5-7.5</v>
       </c>
       <c r="E110" s="51" t="s">
         <v>988</v>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="D125" s="62">
         <f>pH_Cl*pH_fHOCl*52460</f>
-        <v>0</v>
+        <v>5.3582403096</v>
       </c>
       <c r="E125" s="51" t="s">
         <v>1092</v>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="D138" s="62">
         <f>pH_NT/(1+10^(pKa_NH4-pH_op))</f>
-        <v>9.4420710576766854E-6</v>
+        <v>9.542413029E-5</v>
       </c>
       <c r="E138" s="51" t="s">
         <v>1138</v>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="D139" s="62">
         <f>P_HOCl/(k1_NH2Cl*NH3_free)</f>
-        <v>0</v>
+        <v>2.2482664447E-10</v>
       </c>
       <c r="E139" s="51" t="s">
         <v>1141</v>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="D145" s="62">
         <f>f_local*pH_fHOCl*HOCl_ss_mgL+NH2Cl_mgL/R_chloramine</f>
-        <v>0</v>
+        <v>0.6807516555</v>
       </c>
       <c r="E145" s="51" t="s">
         <v>1160</v>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martincurrie/andeye Dropbox/andeye/Projects/electroPioreactor/Media/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3C7980-1D95-3947-AA29-6DC022E03979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8775397F-2CA4-D643-B203-BF9035C146C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="580" windowWidth="25640" windowHeight="18060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1480" yWindow="580" windowWidth="25640" windowHeight="18060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -34,11 +34,15 @@
     <definedName name="bleach_rate" localSheetId="3">Chemistry!$D$107</definedName>
     <definedName name="bleach_t1ppm" localSheetId="3">Chemistry!$D$108</definedName>
     <definedName name="bubble_regime" localSheetId="5">'Mass Transfer'!$D$64</definedName>
+    <definedName name="C_air_CO2" localSheetId="5">'Mass Transfer'!$D$146</definedName>
     <definedName name="C_eff" localSheetId="3">Chemistry!$D$145</definedName>
     <definedName name="C_H2_sat" localSheetId="4">Biology!$D$41</definedName>
+    <definedName name="C_sat_CO2" localSheetId="5">'Mass Transfer'!$D$145</definedName>
+    <definedName name="Ca_CO2" localSheetId="5">'Mass Transfer'!$D$157</definedName>
     <definedName name="cal_warning" localSheetId="5">'Mass Transfer'!$D$120</definedName>
     <definedName name="carbon_margin_min" localSheetId="5">'Mass Transfer'!$D$85</definedName>
     <definedName name="carry_flag" localSheetId="5">'Mass Transfer'!$D$59</definedName>
+    <definedName name="Cb_CO2" localSheetId="5">'Mass Transfer'!$D$158</definedName>
     <definedName name="Cl_kill" localSheetId="3">Chemistry!$D$147</definedName>
     <definedName name="Cl_mc02" localSheetId="3">Chemistry!$D$38</definedName>
     <definedName name="Cl_onset" localSheetId="3">Chemistry!$D$146</definedName>
@@ -46,13 +50,19 @@
     <definedName name="CO2_carbon_margin" localSheetId="4">Biology!$D$35</definedName>
     <definedName name="CO2_cons" localSheetId="4">Biology!$D$15</definedName>
     <definedName name="CO2_cons" localSheetId="5">'Mass Transfer'!$D$10</definedName>
+    <definedName name="CO2_cyc_avg" localSheetId="5">'Mass Transfer'!$D$161</definedName>
     <definedName name="CO2_diss" localSheetId="4">Biology!$D$33</definedName>
+    <definedName name="CO2_int_off" localSheetId="5">'Mass Transfer'!$D$160</definedName>
+    <definedName name="CO2_int_on" localSheetId="5">'Mass Transfer'!$D$159</definedName>
     <definedName name="CO2_pulse" localSheetId="5">'Mass Transfer'!$D$123</definedName>
     <definedName name="CO2_sd_ratio" localSheetId="5">'Mass Transfer'!$D$126</definedName>
     <definedName name="CO2_supply" localSheetId="5">'Mass Transfer'!$D$100</definedName>
     <definedName name="CO2aqc" localSheetId="3">Chemistry!$D$5</definedName>
+    <definedName name="CO2aqc_ss" localSheetId="5">'Mass Transfer'!$D$162</definedName>
+    <definedName name="coef_CO2" localSheetId="5">'Mass Transfer'!$D$156</definedName>
     <definedName name="d_bubble" localSheetId="5">'Mass Transfer'!$D$42</definedName>
     <definedName name="d_bubble_mm" localSheetId="5">'Mass Transfer'!$D$43</definedName>
+    <definedName name="D_CO2" localSheetId="5">'Mass Transfer'!$D$138</definedName>
     <definedName name="D_int" localSheetId="1">Geometry!$D$22</definedName>
     <definedName name="D_int_1" localSheetId="1">Geometry!$D$12</definedName>
     <definedName name="D_int_2" localSheetId="1">Geometry!$D$13</definedName>
@@ -80,6 +90,8 @@
     <definedName name="duty_carbon" localSheetId="5">'Mass Transfer'!$D$86</definedName>
     <definedName name="duty_O2vent" localSheetId="5">'Mass Transfer'!$D$87</definedName>
     <definedName name="duty_opt" localSheetId="5">'Mass Transfer'!$D$88</definedName>
+    <definedName name="e1_CO2" localSheetId="5">'Mass Transfer'!$D$154</definedName>
+    <definedName name="e2_CO2" localSheetId="5">'Mass Transfer'!$D$155</definedName>
     <definedName name="eff_disp" localSheetId="1">Geometry!$D$39</definedName>
     <definedName name="eff_ID" localSheetId="1">Geometry!$D$34</definedName>
     <definedName name="eff_OD" localSheetId="1">Geometry!$D$33</definedName>
@@ -90,6 +102,7 @@
     <definedName name="elec_sub_L" localSheetId="1">Geometry!$D$35</definedName>
     <definedName name="electrode_sel" localSheetId="2">Electrochemistry!$D$8</definedName>
     <definedName name="electrode_sel" localSheetId="0">Summary!$D$3</definedName>
+    <definedName name="eon_CO2" localSheetId="5">'Mass Transfer'!$D$153</definedName>
     <definedName name="etaF" localSheetId="2">Electrochemistry!$D$18</definedName>
     <definedName name="etaF_OER" localSheetId="2">Electrochemistry!$D$26</definedName>
     <definedName name="F_const" localSheetId="2">Electrochemistry!$D$15</definedName>
@@ -122,6 +135,7 @@
     <definedName name="has_cal" localSheetId="5">'Mass Transfer'!$D$119</definedName>
     <definedName name="headspace_V" localSheetId="1">Geometry!$D$49</definedName>
     <definedName name="headspace_V" localSheetId="5">'Mass Transfer'!$D$19</definedName>
+    <definedName name="headspace_V_m3" localSheetId="5">'Mass Transfer'!$D$140</definedName>
     <definedName name="HOCl_max" localSheetId="3">Chemistry!$D$125</definedName>
     <definedName name="HOCl_ss" localSheetId="3">Chemistry!$D$139</definedName>
     <definedName name="HOCl_ss_mgL" localSheetId="3">Chemistry!$D$140</definedName>
@@ -136,6 +150,7 @@
     <definedName name="intensity" localSheetId="2">Electrochemistry!$D$10</definedName>
     <definedName name="interface_A" localSheetId="1">Geometry!$D$44</definedName>
     <definedName name="interface_A" localSheetId="5">'Mass Transfer'!$D$14</definedName>
+    <definedName name="k_vent" localSheetId="5">'Mass Transfer'!$D$143</definedName>
     <definedName name="k1_NH2Cl" localSheetId="3">Chemistry!$D$136</definedName>
     <definedName name="Ka_HOCl" localSheetId="3">Chemistry!$D$20</definedName>
     <definedName name="Ka_NH4" localSheetId="3">Chemistry!$D$18</definedName>
@@ -150,6 +165,7 @@
     <definedName name="kL_surf" localSheetId="5">'Mass Transfer'!$D$70</definedName>
     <definedName name="kL_surf_crit" localSheetId="5">'Mass Transfer'!$D$131</definedName>
     <definedName name="kLa_avg" localSheetId="5">'Mass Transfer'!$D$53</definedName>
+    <definedName name="kLa_CO2_off" localSheetId="5">'Mass Transfer'!$D$148</definedName>
     <definedName name="kLa_meas" localSheetId="5">'Mass Transfer'!$D$97</definedName>
     <definedName name="kLa_req" localSheetId="5">'Mass Transfer'!$D$57</definedName>
     <definedName name="kLa_sparge" localSheetId="5">'Mass Transfer'!$D$52</definedName>
@@ -184,6 +200,7 @@
     <definedName name="MW_NaHCO3" localSheetId="3">Chemistry!$B$28</definedName>
     <definedName name="MW_NH42SO4" localSheetId="3">Chemistry!$B$32</definedName>
     <definedName name="n_cross" localSheetId="3">Chemistry!$D$105</definedName>
+    <definedName name="n_hs_gas" localSheetId="5">'Mass Transfer'!$D$150</definedName>
     <definedName name="n_pores_active" localSheetId="5">'Mass Transfer'!$D$61</definedName>
     <definedName name="nCO2_rate" localSheetId="5">'Mass Transfer'!$D$104</definedName>
     <definedName name="NH2Cl_mgL" localSheetId="3">Chemistry!$D$143</definedName>
@@ -219,6 +236,7 @@
     <definedName name="p_CO2_sparge" localSheetId="4">Biology!$D$32</definedName>
     <definedName name="P_HOCl" localSheetId="3">Chemistry!$D$134</definedName>
     <definedName name="Pa_per_atm" localSheetId="4">Biology!$D$20</definedName>
+    <definedName name="pCO2_air" localSheetId="5">'Mass Transfer'!$D$139</definedName>
     <definedName name="pH_band_flag" localSheetId="3">Chemistry!$D$110</definedName>
     <definedName name="pH_Cl" localSheetId="3">Chemistry!$D$47</definedName>
     <definedName name="pH_CO2_unbuf" localSheetId="4">Biology!$D$37</definedName>
@@ -244,6 +262,7 @@
     <definedName name="pulses_d" localSheetId="5">'Mass Transfer'!$D$125</definedName>
     <definedName name="pulses_h" localSheetId="5">'Mass Transfer'!$D$124</definedName>
     <definedName name="Q_CO2" localSheetId="5">'Mass Transfer'!$D$102</definedName>
+    <definedName name="Q_vent" localSheetId="5">'Mass Transfer'!$D$142</definedName>
     <definedName name="R_chloramine" localSheetId="3">Chemistry!$D$144</definedName>
     <definedName name="R_gas" localSheetId="3">Chemistry!$D$9</definedName>
     <definedName name="R_gas" localSheetId="2">Electrochemistry!$D$7</definedName>
@@ -263,6 +282,7 @@
     <definedName name="sched_bal" localSheetId="5">'Mass Transfer'!$D$129</definedName>
     <definedName name="sched_mode" localSheetId="5">'Mass Transfer'!$D$81</definedName>
     <definedName name="sched_regime" localSheetId="5">'Mass Transfer'!$D$113</definedName>
+    <definedName name="sched_valid" localSheetId="5">'Mass Transfer'!$D$164</definedName>
     <definedName name="SID_mc02" localSheetId="3">Chemistry!$D$36</definedName>
     <definedName name="SID_udg" localSheetId="3">Chemistry!$D$40</definedName>
     <definedName name="sigma" localSheetId="5">'Mass Transfer'!$D$29</definedName>
@@ -287,6 +307,7 @@
     <definedName name="spg_name_2" localSheetId="5">'Mass Transfer'!$D$28</definedName>
     <definedName name="spg_OD" localSheetId="1">Geometry!$D$30</definedName>
     <definedName name="spg_tip_h" localSheetId="1">Geometry!$D$32</definedName>
+    <definedName name="sqrtD_CO2" localSheetId="5">'Mass Transfer'!$D$147</definedName>
     <definedName name="stir_bar_L" localSheetId="1">Geometry!$D$52</definedName>
     <definedName name="stir_len" localSheetId="5">'Mass Transfer'!$D$5</definedName>
     <definedName name="stir_rpm" localSheetId="5">'Mass Transfer'!$D$67</definedName>
@@ -306,9 +327,13 @@
     <definedName name="t_O2_ceiling_lag" localSheetId="5">'Mass Transfer'!$D$79</definedName>
     <definedName name="t_O2_ceiling_rem" localSheetId="5">'Mass Transfer'!$D$80</definedName>
     <definedName name="t_O2_ceiling_strip" localSheetId="5">'Mass Transfer'!$D$66</definedName>
+    <definedName name="t_off_CO2" localSheetId="5">'Mass Transfer'!$D$152</definedName>
+    <definedName name="t_on_CO2" localSheetId="5">'Mass Transfer'!$D$151</definedName>
     <definedName name="T_ref" localSheetId="4">Biology!$D$23</definedName>
     <definedName name="target_DO_frac" localSheetId="5">'Mass Transfer'!$D$84</definedName>
+    <definedName name="tau_hs" localSheetId="5">'Mass Transfer'!$D$144</definedName>
     <definedName name="tau_NH2Cl" localSheetId="3">Chemistry!$D$142</definedName>
+    <definedName name="tau_surf_floor" localSheetId="5">'Mass Transfer'!$D$149</definedName>
     <definedName name="temp_C" localSheetId="0">Summary!$D$8</definedName>
     <definedName name="tip_speed" localSheetId="5">'Mass Transfer'!$D$68</definedName>
     <definedName name="tip_warn" localSheetId="5">'Mass Transfer'!$D$111</definedName>
@@ -329,10 +354,12 @@
     <definedName name="V_gas_total" localSheetId="2">Electrochemistry!$D$25</definedName>
     <definedName name="V_H2_gen" localSheetId="2">Electrochemistry!$D$23</definedName>
     <definedName name="V_inserts" localSheetId="1">Geometry!$D$48</definedName>
+    <definedName name="V_L_m3" localSheetId="5">'Mass Transfer'!$D$141</definedName>
     <definedName name="V_max" localSheetId="1">Geometry!$D$23</definedName>
     <definedName name="V_O2_gen" localSheetId="2">Electrochemistry!$D$24</definedName>
     <definedName name="v_orifice" localSheetId="5">'Mass Transfer'!$D$62</definedName>
     <definedName name="V_vial_total" localSheetId="1">Geometry!$D$24</definedName>
+    <definedName name="vent_floor_chk" localSheetId="5">'Mass Transfer'!$D$163</definedName>
     <definedName name="ver_name_1" localSheetId="1">Geometry!$D$8</definedName>
     <definedName name="ver_name_2" localSheetId="1">Geometry!$D$9</definedName>
     <definedName name="vial_ID" localSheetId="1">Geometry!$D$20</definedName>
@@ -354,35 +381,8 @@
     <definedName name="z_e_H2" localSheetId="2">Electrochemistry!$D$16</definedName>
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$17</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
-    <definedName name="D_CO2" localSheetId="5">'Mass Transfer'!$D$138</definedName>
-    <definedName name="pCO2_air" localSheetId="5">'Mass Transfer'!$D$139</definedName>
-    <definedName name="headspace_V_m3" localSheetId="5">'Mass Transfer'!$D$140</definedName>
-    <definedName name="V_L_m3" localSheetId="5">'Mass Transfer'!$D$141</definedName>
-    <definedName name="Q_vent" localSheetId="5">'Mass Transfer'!$D$142</definedName>
-    <definedName name="k_vent" localSheetId="5">'Mass Transfer'!$D$143</definedName>
-    <definedName name="tau_hs" localSheetId="5">'Mass Transfer'!$D$144</definedName>
-    <definedName name="C_sat_CO2" localSheetId="5">'Mass Transfer'!$D$145</definedName>
-    <definedName name="C_air_CO2" localSheetId="5">'Mass Transfer'!$D$146</definedName>
-    <definedName name="sqrtD_CO2" localSheetId="5">'Mass Transfer'!$D$147</definedName>
-    <definedName name="kLa_CO2_off" localSheetId="5">'Mass Transfer'!$D$148</definedName>
-    <definedName name="tau_surf_floor" localSheetId="5">'Mass Transfer'!$D$149</definedName>
-    <definedName name="n_hs_gas" localSheetId="5">'Mass Transfer'!$D$150</definedName>
-    <definedName name="t_on_CO2" localSheetId="5">'Mass Transfer'!$D$151</definedName>
-    <definedName name="t_off_CO2" localSheetId="5">'Mass Transfer'!$D$152</definedName>
-    <definedName name="eon_CO2" localSheetId="5">'Mass Transfer'!$D$153</definedName>
-    <definedName name="e1_CO2" localSheetId="5">'Mass Transfer'!$D$154</definedName>
-    <definedName name="e2_CO2" localSheetId="5">'Mass Transfer'!$D$155</definedName>
-    <definedName name="coef_CO2" localSheetId="5">'Mass Transfer'!$D$156</definedName>
-    <definedName name="Ca_CO2" localSheetId="5">'Mass Transfer'!$D$157</definedName>
-    <definedName name="Cb_CO2" localSheetId="5">'Mass Transfer'!$D$158</definedName>
-    <definedName name="CO2_int_on" localSheetId="5">'Mass Transfer'!$D$159</definedName>
-    <definedName name="CO2_int_off" localSheetId="5">'Mass Transfer'!$D$160</definedName>
-    <definedName name="CO2_cyc_avg" localSheetId="5">'Mass Transfer'!$D$161</definedName>
-    <definedName name="CO2aqc_ss" localSheetId="5">'Mass Transfer'!$D$162</definedName>
-    <definedName name="vent_floor_chk" localSheetId="5">'Mass Transfer'!$D$163</definedName>
-    <definedName name="sched_valid" localSheetId="5">'Mass Transfer'!$D$164</definedName>
   </definedNames>
-  <calcPr calcMode="auto" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -400,7 +400,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="1249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="1259">
   <si>
     <t>CO₂ DOSING FLOWRATES</t>
   </si>
@@ -2985,9 +2985,6 @@
     <t>mol/L</t>
   </si>
   <si>
-    <t>→ Biology (CO2_diss / 1000)</t>
-  </si>
-  <si>
     <t>(import) Electrolysis current (Gerrit's Law)</t>
   </si>
   <si>
@@ -3924,229 +3921,262 @@
     <t>Override</t>
   </si>
   <si>
-    <t xml:space="preserve">Schedule → dissolved-CO₂ sawtooth model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limit-cycle dissolved CO₂ from the sparge pulse/gap schedule; feeds Chemistry CO2aqc (D5).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO₂ molecular diffusivity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D_CO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m²/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO₂ molecular diffusivity in water ~25°C, Cussler/Tamimi 1994. FLAG: scaled against the 30°C D_O2, ~3% bias on kLa, conservative.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atmospheric pCO₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pCO2_air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atmospheric pCO₂ ~400 ppm; between-pulse decay target; assumes ventilated headspace.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO₂ saturation (pure sparge)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C_sat_CO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mol/m³</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pure-CO₂ sparge saturation = pulse asymptote &amp; upper clamp ~29.28.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO₂ air-equilibrium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C_air_CO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mol/m³</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air-equilibrium = gap asymptote &amp; lower clamp ~0.0116.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diffusivity scaling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sqrtD_CO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penetration-theory diffusivity scaling kL~D^0.5.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kLa CO₂ during pulse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kLa_CO2_on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bubble-path CO₂ transfer during a pulse.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kLa CO₂ between pulses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kLa_CO2_off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surface-path CO₂ stripping between pulses.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pulse duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t_on_CO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pulse duration = in-use schedule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gap duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t_off_CO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUARD floored at 0; without it interval&lt;pulse drives the average negative and a more-than-full-sparge schedule wrongly reports the no-sparge pH.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pulse decay factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">saw_a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(-kLa_CO2_on*t_on_CO2); fraction of the saturation gap left at pulse end.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gap decay factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">saw_b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(-kLa_CO2_off*t_off_CO2); fraction of the air-eq gap left at gap end.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cycle-start CO₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO2_cyc_start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mol/m³</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Periodic limit-cycle concentration at the start of each pulse.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cycle-end CO₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO2_cyc_end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mol/m³</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentration at the end of each pulse (start of the gap).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pulse time-integral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO2_int_on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mol.s/m³</t>
-  </si>
-  <si>
-    <t xml:space="preserve">∫C dt over the pulse (analytic, first-order relaxation toward C_sat_CO2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gap time-integral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO2_int_off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mol.s/m³</t>
-  </si>
-  <si>
-    <t xml:space="preserve">∫C dt over the gap (analytic, first-order relaxation toward C_air_CO2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cycle-average CO₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO2_cyc_avg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mol/m³</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cycle time-average dissolved CO₂, schedule-dependent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steady dissolved CO₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO2aqc_ss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mol/L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bounded steady dissolved CO₂; the value Chemistry D5 is repointed to.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schedule validity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sched_valid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surfaces the duty&gt;1 misuse the guard absorbs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schedule-dependent steady-state dissolved CO₂ (sawtooth limit cycle, bounded air-eq..saturation) - was the fixed full-sparge worst case</t>
+    <t>Schedule → dissolved-CO₂ sawtooth model</t>
+  </si>
+  <si>
+    <t>Limit-cycle dissolved CO₂ from the sparge pulse/gap schedule; feeds Chemistry CO2aqc (D5).</t>
+  </si>
+  <si>
+    <t>CO₂ molecular diffusivity</t>
+  </si>
+  <si>
+    <t>D_CO2</t>
+  </si>
+  <si>
+    <t>pCO2_air</t>
+  </si>
+  <si>
+    <t>CO₂ saturation (pure sparge)</t>
+  </si>
+  <si>
+    <t>C_sat_CO2</t>
+  </si>
+  <si>
+    <t>CO₂ air-equilibrium</t>
+  </si>
+  <si>
+    <t>C_air_CO2</t>
+  </si>
+  <si>
+    <t>sqrtD_CO2</t>
+  </si>
+  <si>
+    <t>kLa_CO2_off</t>
+  </si>
+  <si>
+    <t>Pulse duration</t>
+  </si>
+  <si>
+    <t>t_on_CO2</t>
+  </si>
+  <si>
+    <t>Gap duration</t>
+  </si>
+  <si>
+    <t>t_off_CO2</t>
+  </si>
+  <si>
+    <t>CO2_int_on</t>
+  </si>
+  <si>
+    <t>mol.s/m³</t>
+  </si>
+  <si>
+    <t>CO2_int_off</t>
+  </si>
+  <si>
+    <t>Cycle-average CO₂</t>
+  </si>
+  <si>
+    <t>CO2_cyc_avg</t>
+  </si>
+  <si>
+    <t>Steady dissolved CO₂</t>
+  </si>
+  <si>
+    <t>CO2aqc_ss</t>
+  </si>
+  <si>
+    <t>Schedule validity</t>
+  </si>
+  <si>
+    <t>sched_valid</t>
+  </si>
+  <si>
+    <t>Schedule-dependent steady-state dissolved CO₂ (sawtooth limit cycle, bounded air-eq..saturation) - was the fixed full-sparge worst case</t>
+  </si>
+  <si>
+    <t>CO₂ diffusivity in water ~25°C, Cussler/Tamimi 1994.</t>
+  </si>
+  <si>
+    <t>Atmospheric CO₂ partial pressure</t>
+  </si>
+  <si>
+    <t>Atmospheric pCO₂ (~400 ppm).</t>
+  </si>
+  <si>
+    <t>Headspace volume (SI)</t>
+  </si>
+  <si>
+    <t>headspace_V_m3</t>
+  </si>
+  <si>
+    <t>m³</t>
+  </si>
+  <si>
+    <t>Geometry headspace volume converted mL→m³.</t>
+  </si>
+  <si>
+    <t>Liquid volume (SI)</t>
+  </si>
+  <si>
+    <t>V_L_m3</t>
+  </si>
+  <si>
+    <t>Charged liquid volume converted mL→m³.</t>
+  </si>
+  <si>
+    <t>Headspace vent bleed</t>
+  </si>
+  <si>
+    <t>Q_vent</t>
+  </si>
+  <si>
+    <t>Slow restricted vent bleed - dead-volume + tube + near-closed solenoid leak. KEY NEW UNCERTAIN PARAMETER - measure. NOT free membrane diffusion, which would clear in seconds and could not reproduce the run-2 acidification.</t>
+  </si>
+  <si>
+    <t>Headspace vent rate</t>
+  </si>
+  <si>
+    <t>k_vent</t>
+  </si>
+  <si>
+    <t>First-order headspace clearance from the vent volumetric bleed.</t>
+  </si>
+  <si>
+    <t>Headspace residence time</t>
+  </si>
+  <si>
+    <t>tau_hs</t>
+  </si>
+  <si>
+    <t>Time constant for the headspace to clear through the vent.</t>
+  </si>
+  <si>
+    <t>Henry-law dissolved CO₂ at pure-CO₂ saturation.</t>
+  </si>
+  <si>
+    <t>Henry-law dissolved CO₂ in equilibrium with room air.</t>
+  </si>
+  <si>
+    <t>Diffusivity scaling (CO₂/O₂)</t>
+  </si>
+  <si>
+    <t>Penetration-theory √(D_CO₂/D_O₂) scaling of the O₂ transfer coefficient.</t>
+  </si>
+  <si>
+    <t>CO₂ surface transfer coefficient</t>
+  </si>
+  <si>
+    <t>Surface kLa for CO₂ between pulses (surface path).</t>
+  </si>
+  <si>
+    <t>Surface-relaxation time</t>
+  </si>
+  <si>
+    <t>tau_surf_floor</t>
+  </si>
+  <si>
+    <t>Time constant for the liquid to relax to the headspace via the surface.</t>
+  </si>
+  <si>
+    <t>Headspace gas inventory</t>
+  </si>
+  <si>
+    <t>n_hs_gas</t>
+  </si>
+  <si>
+    <t>Moles of gas in the headspace at P_atm, T_K (ideal-gas).</t>
+  </si>
+  <si>
+    <t>Sparge pulse on-time from the schedule.</t>
+  </si>
+  <si>
+    <t>Time between pulses, guard-floored at 0.</t>
+  </si>
+  <si>
+    <t>On-phase surface decay</t>
+  </si>
+  <si>
+    <t>eon_CO2</t>
+  </si>
+  <si>
+    <t>Surface-path liquid decay factor over the pulse.</t>
+  </si>
+  <si>
+    <t>Off-phase surface decay</t>
+  </si>
+  <si>
+    <t>e1_CO2</t>
+  </si>
+  <si>
+    <t>Surface-path liquid decay factor over the gap.</t>
+  </si>
+  <si>
+    <t>Off-phase vent decay</t>
+  </si>
+  <si>
+    <t>e2_CO2</t>
+  </si>
+  <si>
+    <t>Headspace vent decay factor over the gap.</t>
+  </si>
+  <si>
+    <t>Two-compartment coupling coef</t>
+  </si>
+  <si>
+    <t>coef_CO2</t>
+  </si>
+  <si>
+    <t>Coupling coefficient linking the venting headspace to the liquid relaxation.</t>
+  </si>
+  <si>
+    <t>Cycle-start liquid CO₂</t>
+  </si>
+  <si>
+    <t>Ca_CO2</t>
+  </si>
+  <si>
+    <t>Closed-form limit-cycle dissolved CO₂ at the start of each pulse.</t>
+  </si>
+  <si>
+    <t>End-of-pulse liquid CO₂</t>
+  </si>
+  <si>
+    <t>Cb_CO2</t>
+  </si>
+  <si>
+    <t>Dissolved CO₂ at the end of the pulse (start of the gap).</t>
+  </si>
+  <si>
+    <t>On-phase CO₂ integral</t>
+  </si>
+  <si>
+    <t>Time-integral of dissolved CO₂ over the pulse.</t>
+  </si>
+  <si>
+    <t>Off-phase CO₂ integral</t>
+  </si>
+  <si>
+    <t>Time-integral of dissolved CO₂ over the gap, including the venting-headspace term.</t>
+  </si>
+  <si>
+    <t>Limit-cycle time-average dissolved CO₂ over one pulse+gap.</t>
+  </si>
+  <si>
+    <t>Bounded steady dissolved CO₂; the value Chemistry D5 is repointed to (two-compartment headspace model).</t>
+  </si>
+  <si>
+    <t>Vent-path sanity check</t>
+  </si>
+  <si>
+    <t>vent_floor_chk</t>
+  </si>
+  <si>
+    <t>Confirms the vent is the rate-limiting path; if the surface cleared faster, run 2 could not stay acidic.</t>
+  </si>
+  <si>
+    <t>Surfaces an interval&lt;pulse misconfiguration.</t>
   </si>
 </sst>
 </file>
@@ -4940,7 +4970,7 @@
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="31">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -5112,6 +5142,28 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
+          <bgColor theme="3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
+          <bgColor theme="3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
@@ -5164,14 +5216,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBDD7EE"/>
-          <bgColor rgb="FFBDD7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5535,7 +5579,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="105" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E5" s="20" t="s">
         <v>31</v>
@@ -5668,12 +5712,12 @@
         <v>29</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20" t="s">
@@ -5694,7 +5738,7 @@
     </row>
     <row r="14" spans="1:7" s="3" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20" t="s">
@@ -5730,7 +5774,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="28" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20" t="s">
@@ -6039,7 +6083,7 @@
     </row>
     <row r="34" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="90" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="95" t="str">
@@ -6051,43 +6095,43 @@
         <v>→ Biology</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="90" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="129">
         <f>Chemistry!$D$103</f>
-        <v>7.3834297974</v>
+        <v>7.0138967253152611</v>
       </c>
       <c r="E35" s="23" t="str">
         <f>HYPERLINK("#Chemistry!D103","→ Chemistry")</f>
         <v>→ Chemistry</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="90" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>104</v>
       </c>
       <c r="D36" s="129">
         <f>Chemistry!$D$145</f>
-        <v>0.6807516555</v>
+        <v>0</v>
       </c>
       <c r="E36" s="23" t="str">
         <f>HYPERLINK("#Chemistry!D139","→ Chemistry")</f>
         <v>→ Chemistry</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -6336,13 +6380,13 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="20" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B58" s="20" t="s">
         <v>1039</v>
       </c>
-      <c r="B58" s="20" t="s">
+      <c r="C58" s="20" t="s">
         <v>1040</v>
-      </c>
-      <c r="C58" s="20" t="s">
-        <v>1041</v>
       </c>
       <c r="D58" s="36" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/surface-kla.md","surface-kla.md →")</f>
@@ -6350,18 +6394,18 @@
       </c>
       <c r="E58" s="109"/>
       <c r="F58" s="21" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="20" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B59" s="20" t="s">
         <v>1043</v>
       </c>
-      <c r="B59" s="20" t="s">
+      <c r="C59" s="20" t="s">
         <v>1044</v>
-      </c>
-      <c r="C59" s="20" t="s">
-        <v>1045</v>
       </c>
       <c r="D59" s="36" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/vial-geometry.md","vial-geometry.md →")</f>
@@ -6369,18 +6413,18 @@
       </c>
       <c r="E59" s="109"/>
       <c r="F59" s="21" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="20" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B60" s="20" t="s">
         <v>1047</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c r="C60" s="20" t="s">
         <v>1048</v>
-      </c>
-      <c r="C60" s="20" t="s">
-        <v>1049</v>
       </c>
       <c r="D60" s="36" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/faradaic-efficiency.md","faradaic-efficiency.md →")</f>
@@ -6388,18 +6432,18 @@
       </c>
       <c r="E60" s="109"/>
       <c r="F60" s="21" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="20" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B61" s="20" t="s">
         <v>1051</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="C61" s="20" t="s">
         <v>1052</v>
-      </c>
-      <c r="C61" s="20" t="s">
-        <v>1053</v>
       </c>
       <c r="D61" s="36" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/knallgas-stoichiometry.md","knallgas-stoichiometry.md →")</f>
@@ -6407,18 +6451,18 @@
       </c>
       <c r="E61" s="109"/>
       <c r="F61" s="21" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="20" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B62" s="20" t="s">
         <v>1055</v>
       </c>
-      <c r="B62" s="20" t="s">
+      <c r="C62" s="20" t="s">
         <v>1056</v>
-      </c>
-      <c r="C62" s="20" t="s">
-        <v>1057</v>
       </c>
       <c r="D62" s="36" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/faradaic-efficiency.md","faradaic-efficiency.md →")</f>
@@ -6426,18 +6470,18 @@
       </c>
       <c r="E62" s="109"/>
       <c r="F62" s="21" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="20" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B63" s="20" t="s">
         <v>1059</v>
       </c>
-      <c r="B63" s="20" t="s">
+      <c r="C63" s="20" t="s">
         <v>1060</v>
-      </c>
-      <c r="C63" s="20" t="s">
-        <v>1061</v>
       </c>
       <c r="D63" s="36" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/vial-geometry.md","vial-geometry.md →")</f>
@@ -6445,18 +6489,18 @@
       </c>
       <c r="E63" s="109"/>
       <c r="F63" s="21" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="20" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B64" s="20" t="s">
         <v>1063</v>
       </c>
-      <c r="B64" s="20" t="s">
+      <c r="C64" s="20" t="s">
         <v>1064</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>1065</v>
       </c>
       <c r="D64" s="36" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/flow-calibration.md","flow-calibration.md →")</f>
@@ -6464,18 +6508,18 @@
       </c>
       <c r="E64" s="109"/>
       <c r="F64" s="21" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="20" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B65" s="20" t="s">
         <v>1067</v>
       </c>
-      <c r="B65" s="20" t="s">
+      <c r="C65" s="20" t="s">
         <v>1068</v>
-      </c>
-      <c r="C65" s="20" t="s">
-        <v>1069</v>
       </c>
       <c r="D65" s="36" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/dissolved-oxygen.md","dissolved-oxygen.md →")</f>
@@ -6483,18 +6527,18 @@
       </c>
       <c r="E65" s="109"/>
       <c r="F65" s="21" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B66" s="20" t="s">
         <v>1071</v>
       </c>
-      <c r="B66" s="20" t="s">
+      <c r="C66" s="20" t="s">
         <v>1072</v>
-      </c>
-      <c r="C66" s="20" t="s">
-        <v>1073</v>
       </c>
       <c r="D66" s="36" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/flow-calibration.md","flow-calibration.md →")</f>
@@ -6502,18 +6546,18 @@
       </c>
       <c r="E66" s="109"/>
       <c r="F66" s="21" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="20" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B67" s="20" t="s">
         <v>1075</v>
       </c>
-      <c r="B67" s="20" t="s">
+      <c r="C67" s="20" t="s">
         <v>1076</v>
-      </c>
-      <c r="C67" s="20" t="s">
-        <v>1077</v>
       </c>
       <c r="D67" s="36" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/sinter-porosity.md","sinter-porosity.md →")</f>
@@ -6521,18 +6565,18 @@
       </c>
       <c r="E67" s="109"/>
       <c r="F67" s="21" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="20" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B68" s="20" t="s">
         <v>1079</v>
       </c>
-      <c r="B68" s="20" t="s">
+      <c r="C68" s="20" t="s">
         <v>1080</v>
-      </c>
-      <c r="C68" s="20" t="s">
-        <v>1081</v>
       </c>
       <c r="D68" s="36" t="str">
         <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/README.md","README.md →")</f>
@@ -6540,7 +6584,7 @@
       </c>
       <c r="E68" s="109"/>
       <c r="F68" s="21" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
@@ -6568,73 +6612,73 @@
       <c r="F71" s="20"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B56:B68">
+    <cfRule type="expression" dxfId="30" priority="16" stopIfTrue="1">
+      <formula>EXACT(B56,"HIGH")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="17" stopIfTrue="1">
+      <formula>EXACT(B56,"MED")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="18" stopIfTrue="1">
+      <formula>EXACT(B56,"LOW")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C56:C68">
+    <cfRule type="expression" dxfId="27" priority="19" stopIfTrue="1">
+      <formula>EXACT(C56,"low")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="20" stopIfTrue="1">
+      <formula>EXACT(C56,"med")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="21" stopIfTrue="1">
+      <formula>EXACT(C56,"high")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13:D16">
+    <cfRule type="expression" dxfId="24" priority="15" stopIfTrue="1">
+      <formula>ISNUMBER(SEARCH("calibrate this",D13))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="29" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="1" stopIfTrue="1">
       <formula>AND(ISNUMBER($G$13),$G$13&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16">
-    <cfRule type="expression" dxfId="29" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="3" stopIfTrue="1">
       <formula>AND(ISNUMBER($G$15),$G$15&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B56:B68">
-    <cfRule type="expression" dxfId="28" priority="15" stopIfTrue="1">
-      <formula>EXACT(B56,"HIGH")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="16" stopIfTrue="1">
-      <formula>EXACT(B56,"MED")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="17" stopIfTrue="1">
-      <formula>EXACT(B56,"LOW")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C56:C68">
-    <cfRule type="expression" dxfId="25" priority="18" stopIfTrue="1">
-      <formula>EXACT(C56,"low")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="19" stopIfTrue="1">
-      <formula>EXACT(C56,"med")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="20" stopIfTrue="1">
-      <formula>EXACT(C56,"high")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D13:D16">
-    <cfRule type="expression" dxfId="22" priority="14" stopIfTrue="1">
-      <formula>ISNUMBER(SEARCH("calibrate this",D13))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D19:D36">
-    <cfRule type="expression" dxfId="21" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="12" stopIfTrue="1">
       <formula>OR(ISNUMBER(SEARCH("INCONSISTENT",D19)),ISNUMBER(SEARCH("OVER",D19)),ISNUMBER(SEARCH("BELOW",D19)),ISNUMBER(SEARCH("EXCEED",D19)),ISNUMBER(SEARCH("NO CALIB",D19)),ISNUMBER(SEARCH("calibrate this",D19)),ISNUMBER(SEARCH("RISK",D19)),ISNUMBER(SEARCH("EXPLOSIVE",D19)),ISNUMBER(SEARCH("OOR",D19)),ISNUMBER(SEARCH("insufficient",D19)),ISNUMBER(SEARCH("TIP SPEED",D19)),ISNUMBER(SEARCH("SHORTFALL",D19)),EXACT(D19,"OUT"),EXACT(D19,"LOW"),ISNUMBER(SEARCH("GAP",D19)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="13" stopIfTrue="1">
       <formula>OR(ISNUMBER(SEARCH("above optimum",D19)),ISNUMBER(SEARCH("watch",D19)),ISNUMBER(SEARCH("NEAREST",D19)),ISNUMBER(SEARCH("unknown",D19)),ISNUMBER(SEARCH("TIGHT",D19)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="14" stopIfTrue="1">
       <formula>OR(EXACT(D19,"OK"),ISNUMBER(SEARCH("calibrated:",D19)),ISNUMBER(SEARCH("optimum",D19)),ISNUMBER(SEARCH("above min",D19)),ISNUMBER(SEARCH("CARBON-limited",D19)),ISNUMBER(SEARCH("Static",D19)),ISNUMBER(SEARCH("Dynamic",D19)),ISNUMBER(SEARCH("present",D19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35">
-    <cfRule type="expression" dxfId="18" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="22" stopIfTrue="1">
       <formula>OR(D35&lt;6,D35&gt;8)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="23" stopIfTrue="1">
       <formula>OR(D35&lt;6.5,D35&gt;7.5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="24" stopIfTrue="1">
       <formula>ISNUMBER(D35)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D36">
-    <cfRule type="expression" dxfId="15" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="25" stopIfTrue="1">
       <formula>D36&gt;1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="26" stopIfTrue="1">
       <formula>D36&gt;0.1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="27" stopIfTrue="1">
       <formula>ISNUMBER(D36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9286,7 +9330,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="36" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>858</v>
       </c>
@@ -9298,111 +9342,111 @@
       </c>
       <c r="D5" s="64">
         <f>'Mass Transfer'!$D$162</f>
-        <v>8.724353186629647E-4</v>
+        <v>9.8009182872224013E-4</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>1248</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
+        <v>861</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>862</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>863</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>864</v>
       </c>
       <c r="D6" s="64">
         <f>Electrochemistry!$D$19</f>
         <v>5.6899999999999997E-3</v>
       </c>
       <c r="E6" s="51" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
+        <v>865</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>866</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>867</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>868</v>
       </c>
       <c r="D7" s="64">
         <f>Electrochemistry!$D$15</f>
         <v>96485.332120000006</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
+        <v>869</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>870</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>871</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>872</v>
       </c>
       <c r="D8" s="64">
         <f>Biology!$D$6/1000</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E8" s="51" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
+        <v>873</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>874</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>875</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>876</v>
       </c>
       <c r="D9" s="52">
         <v>8.3140000000000001</v>
       </c>
       <c r="E9" s="85" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="110" t="s">
+        <v>877</v>
+      </c>
+      <c r="F11" s="107" t="s">
         <v>878</v>
-      </c>
-      <c r="F11" s="107" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
+        <v>879</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>880</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="C12" s="16" t="s">
         <v>881</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="D12" s="16" t="s">
         <v>882</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="E12" s="16" t="s">
         <v>883</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B13" s="52">
         <v>4.4499999999999997E-7</v>
@@ -9415,12 +9459,12 @@
         <v>4.4499999999999997E-7</v>
       </c>
       <c r="E13" s="85" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B14" s="52">
         <v>4.6900000000000001E-11</v>
@@ -9433,12 +9477,12 @@
         <v>4.6900000000000001E-11</v>
       </c>
       <c r="E14" s="85" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B15" s="52">
         <v>7.1000000000000004E-3</v>
@@ -9451,12 +9495,12 @@
         <v>7.1000000000000004E-3</v>
       </c>
       <c r="E15" s="85" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B16" s="52">
         <v>6.3100000000000003E-8</v>
@@ -9469,12 +9513,12 @@
         <v>6.3100000000000003E-8</v>
       </c>
       <c r="E16" s="85" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B17" s="52">
         <v>4.1999999999999998E-13</v>
@@ -9487,12 +9531,12 @@
         <v>4.1999999999999998E-13</v>
       </c>
       <c r="E17" s="85" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B18" s="52">
         <v>5.6000000000000003E-10</v>
@@ -9505,12 +9549,12 @@
         <v>5.6000000000000003E-10</v>
       </c>
       <c r="E18" s="85" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B19" s="52">
         <v>1E-14</v>
@@ -9523,12 +9567,12 @@
         <v>1E-14</v>
       </c>
       <c r="E19" s="85" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B20" s="52">
         <v>2.8840315031266057E-8</v>
@@ -9541,55 +9585,55 @@
         <v>2.8840315031266057E-8</v>
       </c>
       <c r="E20" s="85" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
+        <v>892</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>893</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="C21" s="19" t="s">
         <v>894</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>895</v>
       </c>
       <c r="D21" s="62">
         <f>-LOG10(Ka_HOCl)</f>
         <v>7.54</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="110" t="s">
+        <v>896</v>
+      </c>
+      <c r="F23" s="107" t="s">
         <v>897</v>
-      </c>
-      <c r="F23" s="107" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
+        <v>900</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>901</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="C24" s="16" t="s">
         <v>902</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="D24" s="16" t="s">
         <v>903</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="E24" s="16" t="s">
         <v>904</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B25" s="52">
         <v>136.08600000000001</v>
@@ -9601,12 +9645,12 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="17" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B26" s="52">
         <v>141.96</v>
@@ -9618,12 +9662,12 @@
         <v>2.9</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="17" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B27" s="52">
         <v>156.01</v>
@@ -9635,12 +9679,12 @@
         <v>0</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="17" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B28" s="52">
         <v>84.007000000000005</v>
@@ -9652,12 +9696,12 @@
         <v>1.05</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="17" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B29" s="52">
         <v>174.26</v>
@@ -9669,12 +9713,12 @@
         <v>0</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B30" s="52">
         <v>172.17</v>
@@ -9686,12 +9730,12 @@
         <v>0</v>
       </c>
       <c r="E30" s="51" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="17" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B31" s="52">
         <v>246.48</v>
@@ -9703,12 +9747,12 @@
         <v>0.5</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="17" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B32" s="52">
         <v>132.13999999999999</v>
@@ -9720,12 +9764,12 @@
         <v>0.47</v>
       </c>
       <c r="E32" s="51" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="24" x14ac:dyDescent="0.2">
       <c r="A33" s="17" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B33" s="52">
         <v>110.98</v>
@@ -9737,234 +9781,234 @@
         <v>0.01</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
+        <v>914</v>
+      </c>
+      <c r="B35" s="18" t="s">
         <v>915</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="C35" s="19" t="s">
         <v>916</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>917</v>
       </c>
       <c r="D35" s="62">
         <f>mc_Na2HPO4/MW_Na2HPO4+mc_NaH2PO4_2H2O/MW_NaH2PO4_2H2O</f>
         <v>4.0007195769523628E-2</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="17" t="s">
+        <v>918</v>
+      </c>
+      <c r="B36" s="18" t="s">
         <v>919</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="C36" s="19" t="s">
         <v>920</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>921</v>
       </c>
       <c r="D36" s="62">
         <f>(2*mc_Na2HPO4/MW_Na2HPO4+mc_NaH2PO4_2H2O/MW_NaH2PO4_2H2O+2*mc_K2SO4/MW_K2SO4+2*mc_MgSO4_7H2O/MW_MgSO4_7H2O+2*mc_CaSO4_2H2O/MW_CaSO4_2H2O)-2*(mc_NH42SO4/MW_NH42SO4+mc_MgSO4_7H2O/MW_MgSO4_7H2O+mc_K2SO4/MW_K2SO4+mc_CaSO4_2H2O/MW_CaSO4_2H2O)</f>
         <v>4.6127523207276644E-2</v>
       </c>
       <c r="E36" s="51" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="B37" s="18" t="s">
         <v>923</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="C37" s="19" t="s">
         <v>924</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>925</v>
       </c>
       <c r="D37" s="62">
         <f>2*mc_NH42SO4/MW_NH42SO4</f>
         <v>1.4272741032238535E-2</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="17" t="s">
+        <v>926</v>
+      </c>
+      <c r="B38" s="18" t="s">
         <v>927</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="C38" s="19" t="s">
         <v>928</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>929</v>
       </c>
       <c r="D38" s="62">
         <f>0</f>
         <v>0</v>
       </c>
       <c r="E38" s="51" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="17" t="s">
+        <v>930</v>
+      </c>
+      <c r="B39" s="18" t="s">
         <v>931</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="C39" s="19" t="s">
         <v>932</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>933</v>
       </c>
       <c r="D39" s="62">
         <f>udg_KH2PO4/MW_KH2PO4+udg_Na2HPO4/MW_Na2HPO4</f>
         <v>3.7329366919026843E-2</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="17" t="s">
+        <v>934</v>
+      </c>
+      <c r="B40" s="18" t="s">
         <v>935</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="C40" s="19" t="s">
         <v>936</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>937</v>
       </c>
       <c r="D40" s="62">
         <f>(udg_NaHCO3/MW_NaHCO3+2*udg_Na2HPO4/MW_Na2HPO4+udg_KH2PO4/MW_KH2PO4+2*udg_MgSO4_7H2O/MW_MgSO4_7H2O+2*udg_CaCl2/MW_CaCl2)-(2*(udg_NH42SO4/MW_NH42SO4+udg_MgSO4_7H2O/MW_MgSO4_7H2O)+2*udg_CaCl2/MW_CaCl2)</f>
         <v>6.3142947675680683E-2</v>
       </c>
       <c r="E40" s="51" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="17" t="s">
+        <v>938</v>
+      </c>
+      <c r="B41" s="18" t="s">
         <v>939</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="C41" s="19" t="s">
         <v>940</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>941</v>
       </c>
       <c r="D41" s="62">
         <f>2*udg_NH42SO4/MW_NH42SO4</f>
         <v>7.1136673225367037E-3</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="B42" s="18" t="s">
         <v>943</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="C42" s="19" t="s">
         <v>944</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>945</v>
       </c>
       <c r="D42" s="62">
         <f>2*udg_CaCl2/MW_CaCl2</f>
         <v>1.8021265092809516E-4</v>
       </c>
       <c r="E42" s="51" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="17" t="s">
+        <v>946</v>
+      </c>
+      <c r="B44" s="18" t="s">
         <v>947</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="C44" s="19" t="s">
         <v>948</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>949</v>
       </c>
       <c r="D44" s="62">
         <f>IF(Summary!$D$5="MC02",SID_mc02,IF(Summary!$D$5="UdG phosphate",SID_udg,NA()))</f>
         <v>4.6127523207276644E-2</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="17" t="s">
+        <v>950</v>
+      </c>
+      <c r="B45" s="18" t="s">
         <v>951</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="C45" s="19" t="s">
         <v>952</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>953</v>
       </c>
       <c r="D45" s="62">
         <f>IF(Summary!$D$5="MC02",PT_mc02,IF(Summary!$D$5="UdG phosphate",PT_udg,NA()))</f>
         <v>4.0007195769523628E-2</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="17" t="s">
+        <v>954</v>
+      </c>
+      <c r="B46" s="18" t="s">
         <v>955</v>
       </c>
-      <c r="B46" s="18" t="s">
+      <c r="C46" s="19" t="s">
         <v>956</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>957</v>
       </c>
       <c r="D46" s="62">
         <f>IF(Summary!$D$5="MC02",NT_mc02,IF(Summary!$D$5="UdG phosphate",NT_udg,NA()))</f>
         <v>1.4272741032238535E-2</v>
       </c>
       <c r="E46" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="17" t="s">
+        <v>958</v>
+      </c>
+      <c r="B47" s="18" t="s">
         <v>959</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="C47" s="19" t="s">
         <v>960</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>961</v>
       </c>
       <c r="D47" s="62">
         <f>IF(Summary!$D$5="MC02",Cl_mc02,IF(Summary!$D$5="UdG phosphate",Cl_udg,NA()))</f>
         <v>0</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="16" t="s">
+        <v>962</v>
+      </c>
+      <c r="B49" s="16" t="s">
         <v>963</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="C49" s="16" t="s">
         <v>964</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -9973,7 +10017,7 @@
       </c>
       <c r="B50" s="64">
         <f t="shared" ref="B50:B81" si="1">pH_SID + pH_NT*(10^-A50)/((10^-A50)+Ka_NH4) + (10^-A50) - (pH_PT*Ka1p*(10^-A50)^2 + 2*pH_PT*Ka1p*Ka2p*(10^-A50) + 3*pH_PT*Ka1p*Ka2p*Ka3p)/((10^-A50)^3 + Ka1p*(10^-A50)^2 + Ka1p*Ka2p*(10^-A50) + Ka1p*Ka2p*Ka3p) - Ka1c*CO2aqc/(10^-A50) - 2*Ka1c*Ka2c*CO2aqc/(10^-A50)^2 - Kw_w/(10^-A50)</f>
-        <v>2.0874624062048423E-2</v>
+        <v>2.1019058551390035E-2</v>
       </c>
       <c r="C50" s="64">
         <f t="shared" ref="C50:C81" si="2">IF(AND(B50&gt;=0,B51&lt;0),A50+0.1*B50/(B50-B51),0)</f>
@@ -9986,7 +10030,7 @@
       </c>
       <c r="B51" s="64">
         <f t="shared" si="1"/>
-        <v>2.0695962665004713E-2</v>
+        <v>2.087779495813831E-2</v>
       </c>
       <c r="C51" s="64">
         <f t="shared" si="2"/>
@@ -9999,7 +10043,7 @@
       </c>
       <c r="B52" s="64">
         <f t="shared" si="1"/>
-        <v>2.0532645631821684E-2</v>
+        <v>2.0761558996324307E-2</v>
       </c>
       <c r="C52" s="64">
         <f t="shared" si="2"/>
@@ -10012,7 +10056,7 @@
       </c>
       <c r="B53" s="64">
         <f t="shared" si="1"/>
-        <v>2.0376266518924033E-2</v>
+        <v>2.0664451481525431E-2</v>
       </c>
       <c r="C53" s="64">
         <f t="shared" si="2"/>
@@ -10025,7 +10069,7 @@
       </c>
       <c r="B54" s="64">
         <f t="shared" si="1"/>
-        <v>2.0218684833030565E-2</v>
+        <v>2.0581488381558221E-2</v>
       </c>
       <c r="C54" s="64">
         <f t="shared" si="2"/>
@@ -10038,7 +10082,7 @@
       </c>
       <c r="B55" s="64">
         <f t="shared" si="1"/>
-        <v>2.0051631281345267E-2</v>
+        <v>2.0508374166718756E-2</v>
       </c>
       <c r="C55" s="64">
         <f t="shared" si="2"/>
@@ -10051,7 +10095,7 @@
       </c>
       <c r="B56" s="64">
         <f t="shared" si="1"/>
-        <v>1.9866292996637152E-2</v>
+        <v>2.0441298663309293E-2</v>
       </c>
       <c r="C56" s="64">
         <f t="shared" si="2"/>
@@ -10064,7 +10108,7 @@
       </c>
       <c r="B57" s="64">
         <f t="shared" si="1"/>
-        <v>1.9652861766555167E-2</v>
+        <v>2.0376751712173753E-2</v>
       </c>
       <c r="C57" s="64">
         <f t="shared" si="2"/>
@@ -10077,7 +10121,7 @@
       </c>
       <c r="B58" s="64">
         <f t="shared" si="1"/>
-        <v>1.9400024781889909E-2</v>
+        <v>2.0311349339068894E-2</v>
       </c>
       <c r="C58" s="64">
         <f t="shared" si="2"/>
@@ -10090,7 +10134,7 @@
       </c>
       <c r="B59" s="64">
         <f t="shared" si="1"/>
-        <v>1.9094373482848061E-2</v>
+        <v>2.0241664884390737E-2</v>
       </c>
       <c r="C59" s="64">
         <f t="shared" si="2"/>
@@ -10103,7 +10147,7 @@
       </c>
       <c r="B60" s="64">
         <f t="shared" si="1"/>
-        <v>1.8719701369951561E-2</v>
+        <v>2.0164058456515817E-2</v>
       </c>
       <c r="C60" s="64">
         <f t="shared" si="2"/>
@@ -10116,7 +10160,7 @@
       </c>
       <c r="B61" s="64">
         <f t="shared" si="1"/>
-        <v>1.8256155845531651E-2</v>
+        <v>2.0074498101705092E-2</v>
       </c>
       <c r="C61" s="64">
         <f t="shared" si="2"/>
@@ -10129,7 +10173,7 @@
       </c>
       <c r="B62" s="64">
         <f t="shared" si="1"/>
-        <v>1.767920197321712E-2</v>
+        <v>1.9968366246046778E-2</v>
       </c>
       <c r="C62" s="64">
         <f t="shared" si="2"/>
@@ -10142,7 +10186,7 @@
       </c>
       <c r="B63" s="64">
         <f t="shared" si="1"/>
-        <v>1.6958347204622286E-2</v>
+        <v>1.984024537243341E-2</v>
       </c>
       <c r="C63" s="64">
         <f t="shared" si="2"/>
@@ -10155,7 +10199,7 @@
       </c>
       <c r="B64" s="64">
         <f t="shared" si="1"/>
-        <v>1.6055565345378109E-2</v>
+        <v>1.9683677764218453E-2</v>
       </c>
       <c r="C64" s="64">
         <f t="shared" si="2"/>
@@ -10168,7 +10212,7 @@
       </c>
       <c r="B65" s="64">
         <f t="shared" si="1"/>
-        <v>1.4923345039105761E-2</v>
+        <v>1.9490895824322143E-2</v>
       </c>
       <c r="C65" s="64">
         <f t="shared" si="2"/>
@@ -10181,7 +10225,7 @@
       </c>
       <c r="B66" s="64">
         <f t="shared" si="1"/>
-        <v>1.3502272558642855E-2</v>
+        <v>1.9252522473739295E-2</v>
       </c>
       <c r="C66" s="64">
         <f t="shared" si="2"/>
@@ -10194,7 +10238,7 @@
       </c>
       <c r="B67" s="64">
         <f t="shared" si="1"/>
-        <v>1.1718040406093968E-2</v>
+        <v>1.8957246140313841E-2</v>
       </c>
       <c r="C67" s="64">
         <f t="shared" si="2"/>
@@ -10207,7 +10251,7 @@
       </c>
       <c r="B68" s="64">
         <f t="shared" si="1"/>
-        <v>9.4777517382294597E-3</v>
+        <v>1.859148272799048E-2</v>
       </c>
       <c r="C68" s="64">
         <f t="shared" si="2"/>
@@ -10220,7 +10264,7 @@
       </c>
       <c r="B69" s="64">
         <f t="shared" si="1"/>
-        <v>6.6653652728653565E-3</v>
+        <v>1.8139048623930128E-2</v>
       </c>
       <c r="C69" s="64">
         <f t="shared" si="2"/>
@@ -10233,11 +10277,11 @@
       </c>
       <c r="B70" s="64">
         <f t="shared" si="1"/>
-        <v>3.1360947436589025E-3</v>
+        <v>1.7580884924116733E-2</v>
       </c>
       <c r="C70" s="64">
         <f t="shared" si="2"/>
-        <v>6.0708472792648696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -10246,7 +10290,7 @@
       </c>
       <c r="B71" s="64">
         <f t="shared" si="1"/>
-        <v>-1.2904616127740953E-3</v>
+        <v>1.6894893432710553E-2</v>
       </c>
       <c r="C71" s="64">
         <f t="shared" si="2"/>
@@ -10259,7 +10303,7 @@
       </c>
       <c r="B72" s="64">
         <f t="shared" si="1"/>
-        <v>-6.8387380621257963E-3</v>
+        <v>1.6055967446511051E-2</v>
       </c>
       <c r="C72" s="64">
         <f t="shared" si="2"/>
@@ -10272,7 +10316,7 @@
       </c>
       <c r="B73" s="64">
         <f t="shared" si="1"/>
-        <v>-1.3787516718870499E-2</v>
+        <v>1.503631913895208E-2</v>
       </c>
       <c r="C73" s="64">
         <f t="shared" si="2"/>
@@ -10285,7 +10329,7 @@
       </c>
       <c r="B74" s="64">
         <f t="shared" si="1"/>
-        <v>-2.2482608132766504E-2</v>
+        <v>1.3806209412016438E-2</v>
       </c>
       <c r="C74" s="64">
         <f t="shared" si="2"/>
@@ -10298,7 +10342,7 @@
       </c>
       <c r="B75" s="64">
         <f t="shared" si="1"/>
-        <v>-3.3352543005210851E-2</v>
+        <v>1.2335157995106044E-2</v>
       </c>
       <c r="C75" s="64">
         <f t="shared" si="2"/>
@@ -10311,7 +10355,7 @@
       </c>
       <c r="B76" s="64">
         <f t="shared" si="1"/>
-        <v>-4.692819424853182E-2</v>
+        <v>1.059362973993507E-2</v>
       </c>
       <c r="C76" s="64">
         <f t="shared" si="2"/>
@@ -10324,7 +10368,7 @@
       </c>
       <c r="B77" s="64">
         <f t="shared" si="1"/>
-        <v>-6.386764531861687E-2</v>
+        <v>8.5550398269848369E-3</v>
       </c>
       <c r="C77" s="64">
         <f t="shared" si="2"/>
@@ -10337,7 +10381,7 @@
       </c>
       <c r="B78" s="64">
         <f t="shared" si="1"/>
-        <v>-8.4988153413295311E-2</v>
+        <v>6.1976982814282806E-3</v>
       </c>
       <c r="C78" s="64">
         <f t="shared" si="2"/>
@@ -10350,7 +10394,7 @@
       </c>
       <c r="B79" s="64">
         <f t="shared" si="1"/>
-        <v>-0.11130770165306031</v>
+        <v>3.5060654213823097E-3</v>
       </c>
       <c r="C79" s="64">
         <f t="shared" si="2"/>
@@ -10363,11 +10407,11 @@
       </c>
       <c r="B80" s="64">
         <f t="shared" si="1"/>
-        <v>-0.14409932493270913</v>
+        <v>4.705083533996436E-4</v>
       </c>
       <c r="C80" s="64">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.0138967253152611</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -10376,7 +10420,7 @@
       </c>
       <c r="B81" s="64">
         <f t="shared" si="1"/>
-        <v>-0.18496204030404337</v>
+        <v>-2.9152414741727248E-3</v>
       </c>
       <c r="C81" s="64">
         <f t="shared" si="2"/>
@@ -10389,7 +10433,7 @@
       </c>
       <c r="B82" s="64">
         <f t="shared" ref="B82:B100" si="3">pH_SID + pH_NT*(10^-A82)/((10^-A82)+Ka_NH4) + (10^-A82) - (pH_PT*Ka1p*(10^-A82)^2 + 2*pH_PT*Ka1p*Ka2p*(10^-A82) + 3*pH_PT*Ka1p*Ka2p*Ka3p)/((10^-A82)^3 + Ka1p*(10^-A82)^2 + Ka1p*Ka2p*(10^-A82) + Ka1p*Ka2p*Ka3p) - Ka1c*CO2aqc/(10^-A82) - 2*Ka1c*Ka2c*CO2aqc/(10^-A82)^2 - Kw_w/(10^-A82)</f>
-        <v>-0.23591277205629452</v>
+        <v>-6.659438935895547E-3</v>
       </c>
       <c r="C82" s="64">
         <f t="shared" ref="C82:C99" si="4">IF(AND(B82&gt;=0,B83&lt;0),A82+0.1*B82/(B82-B83),0)</f>
@@ -10402,7 +10446,7 @@
       </c>
       <c r="B83" s="64">
         <f t="shared" si="3"/>
-        <v>-0.29950422994063303</v>
+        <v>-1.0780453391272093E-2</v>
       </c>
       <c r="C83" s="64">
         <f t="shared" si="4"/>
@@ -10415,7 +10459,7 @@
       </c>
       <c r="B84" s="64">
         <f t="shared" si="3"/>
-        <v>-0.37897455836011895</v>
+        <v>-1.5317047274339206E-2</v>
       </c>
       <c r="C84" s="64">
         <f t="shared" si="4"/>
@@ -10428,7 +10472,7 @@
       </c>
       <c r="B85" s="64">
         <f t="shared" si="3"/>
-        <v>-0.47843613536450541</v>
+        <v>-2.0339810546031352E-2</v>
       </c>
       <c r="C85" s="64">
         <f t="shared" si="4"/>
@@ -10441,7 +10485,7 @@
       </c>
       <c r="B86" s="64">
         <f t="shared" si="3"/>
-        <v>-0.60311355724869076</v>
+        <v>-2.5962833613778116E-2</v>
       </c>
       <c r="C86" s="64">
         <f t="shared" si="4"/>
@@ -10454,7 +10498,7 @@
       </c>
       <c r="B87" s="64">
         <f t="shared" si="3"/>
-        <v>-0.75964486243394314</v>
+        <v>-3.2355230637624466E-2</v>
       </c>
       <c r="C87" s="64">
         <f t="shared" si="4"/>
@@ -10467,7 +10511,7 @@
       </c>
       <c r="B88" s="64">
         <f t="shared" si="3"/>
-        <v>-0.95646560365632072</v>
+        <v>-3.9752906997736523E-2</v>
       </c>
       <c r="C88" s="64">
         <f t="shared" si="4"/>
@@ -10480,7 +10524,7 @@
       </c>
       <c r="B89" s="64">
         <f t="shared" si="3"/>
-        <v>-1.2043027611486459</v>
+        <v>-4.8471734024719042E-2</v>
       </c>
       <c r="C89" s="64">
         <f t="shared" si="4"/>
@@ -10493,7 +10537,7 @@
       </c>
       <c r="B90" s="64">
         <f t="shared" si="3"/>
-        <v>-1.5168153664416366</v>
+        <v>-5.8923885427503334E-2</v>
       </c>
       <c r="C90" s="64">
         <f t="shared" si="4"/>
@@ -10506,7 +10550,7 @@
       </c>
       <c r="B91" s="64">
         <f t="shared" si="3"/>
-        <v>-1.9114323371204927</v>
+        <v>-7.1639511319352173E-2</v>
       </c>
       <c r="C91" s="64">
         <f t="shared" si="4"/>
@@ -10519,7 +10563,7 @@
       </c>
       <c r="B92" s="64">
         <f t="shared" si="3"/>
-        <v>-2.4104574606330629</v>
+        <v>-8.7296326026057247E-2</v>
       </c>
       <c r="C92" s="64">
         <f t="shared" si="4"/>
@@ -10532,7 +10576,7 @@
       </c>
       <c r="B93" s="64">
         <f t="shared" si="3"/>
-        <v>-3.0425398421007839</v>
+        <v>-0.1067602794936845</v>
       </c>
       <c r="C93" s="64">
         <f t="shared" si="4"/>
@@ -10545,7 +10589,7 @@
       </c>
       <c r="B94" s="64">
         <f t="shared" si="3"/>
-        <v>-3.8446501768470562</v>
+        <v>-0.13114150219427442</v>
       </c>
       <c r="C94" s="64">
         <f t="shared" si="4"/>
@@ -10558,7 +10602,7 @@
       </c>
       <c r="B95" s="64">
         <f t="shared" si="3"/>
-        <v>-4.8647661482019897</v>
+        <v>-0.16187141848680417</v>
       </c>
       <c r="C95" s="64">
         <f t="shared" si="4"/>
@@ -10571,7 +10615,7 @@
       </c>
       <c r="B96" s="64">
         <f t="shared" si="3"/>
-        <v>-6.1655652619170853</v>
+        <v>-0.20080965054365266</v>
       </c>
       <c r="C96" s="64">
         <f t="shared" si="4"/>
@@ -10584,7 +10628,7 @@
       </c>
       <c r="B97" s="64">
         <f t="shared" si="3"/>
-        <v>-7.8295679374291032</v>
+        <v>-0.25039358543571821</v>
       </c>
       <c r="C97" s="64">
         <f t="shared" si="4"/>
@@ -10597,7 +10641,7 @@
       </c>
       <c r="B98" s="64">
         <f t="shared" si="3"/>
-        <v>-9.9663949721734042</v>
+        <v>-0.31385003445265258</v>
       </c>
       <c r="C98" s="64">
         <f t="shared" si="4"/>
@@ -10610,7 +10654,7 @@
       </c>
       <c r="B99" s="64">
         <f t="shared" si="3"/>
-        <v>-12.723144417541558</v>
+        <v>-0.39549850835234002</v>
       </c>
       <c r="C99" s="64">
         <f t="shared" si="4"/>
@@ -10623,7 +10667,7 @@
       </c>
       <c r="B100" s="64">
         <f t="shared" si="3"/>
-        <v>-16.29942083120859</v>
+        <v>-0.50119120576268095</v>
       </c>
       <c r="C100" s="64">
         <f>0</f>
@@ -10653,210 +10697,210 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="17" t="s">
+        <v>965</v>
+      </c>
+      <c r="B103" s="18" t="s">
         <v>966</v>
       </c>
-      <c r="B103" s="18" t="s">
+      <c r="C103" s="19" t="s">
         <v>967</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>968</v>
       </c>
       <c r="D103" s="62">
         <f>IF(n_cross=1,SUM(C50:C100),NA())</f>
-        <v>7.3834297974</v>
+        <v>7.0138967253152611</v>
       </c>
       <c r="E103" s="51" t="s">
+        <v>968</v>
+      </c>
+      <c r="F103" s="107" t="s">
         <v>969</v>
-      </c>
-      <c r="F103" s="107" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="17" t="s">
+        <v>970</v>
+      </c>
+      <c r="B104" s="18" t="s">
         <v>971</v>
       </c>
-      <c r="B104" s="18" t="s">
+      <c r="C104" s="19" t="s">
         <v>972</v>
-      </c>
-      <c r="C104" s="19" t="s">
-        <v>973</v>
       </c>
       <c r="D104" s="62">
         <f>1/(1+10^(pH_op-pKa_HOCl))</f>
-        <v>0.5667723118</v>
+        <v>0.77054613735518007</v>
       </c>
       <c r="E104" s="51" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="36" x14ac:dyDescent="0.2">
       <c r="A105" s="17" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B105" s="18" t="s">
         <v>1029</v>
       </c>
-      <c r="B105" s="18" t="s">
+      <c r="C105" s="19" t="s">
         <v>1030</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>1031</v>
       </c>
       <c r="D105" s="62">
         <f>SUMPRODUCT((B50:B99&gt;=0)*(B51:B100&lt;0))</f>
         <v>1</v>
       </c>
       <c r="E105" s="51" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F105" s="20"/>
     </row>
     <row r="106" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A106" s="110" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G106" s="69" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="328" x14ac:dyDescent="0.2">
       <c r="A107" s="17" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B107" s="18" t="s">
+        <v>975</v>
+      </c>
+      <c r="C107" s="19" t="s">
         <v>976</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>977</v>
       </c>
       <c r="D107" s="62">
         <f>Iappc/(2*Fcc)*52460*3600/VLc</f>
         <v>371.24490544791416</v>
       </c>
       <c r="E107" s="51" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G107" s="69" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="284" x14ac:dyDescent="0.2">
       <c r="A108" s="17" t="s">
+        <v>977</v>
+      </c>
+      <c r="B108" s="18" t="s">
         <v>978</v>
       </c>
-      <c r="B108" s="18" t="s">
+      <c r="C108" s="19" t="s">
         <v>979</v>
-      </c>
-      <c r="C108" s="19" t="s">
-        <v>980</v>
       </c>
       <c r="D108" s="62">
         <f>1/(bleach_rate)*60</f>
         <v>0.16161837945657148</v>
       </c>
       <c r="E108" s="51" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G108" s="69" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="204" x14ac:dyDescent="0.2">
       <c r="A109" s="17" t="s">
+        <v>981</v>
+      </c>
+      <c r="B109" s="18" t="s">
         <v>982</v>
       </c>
-      <c r="B109" s="18" t="s">
+      <c r="C109" s="19" t="s">
         <v>983</v>
-      </c>
-      <c r="C109" s="19" t="s">
-        <v>984</v>
       </c>
       <c r="D109" s="64" t="str">
         <f>IF(C_eff&lt;Cl_onset,"negligible free chlorine ("&amp;TEXT(C_eff,"0.00")&amp;" mg/L &lt; onset)",IF(C_eff&lt;Cl_kill,"MILD sub-lethal penalty: "&amp;TEXT(C_eff,"0.00")&amp;" mg/L (chloride costs lag/growth — Sydow 2017; chloride-free avoids it)","SEVERE free chlorine: "&amp;TEXT(C_eff,"0.0")&amp;" mg/L → biofilm/electrode damage (Baek 2021)"))</f>
-        <v>MILD sub-lethal penalty: 0.68 mg/L (chloride costs lag/growth — Sydow 2017; chloride-free avoids it)</v>
+        <v>negligible free chlorine (0.00 mg/L &lt; onset)</v>
       </c>
       <c r="E109" s="51" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G109" s="69" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="328" x14ac:dyDescent="0.2">
       <c r="A110" s="17" t="s">
+        <v>984</v>
+      </c>
+      <c r="B110" s="18" t="s">
         <v>985</v>
       </c>
-      <c r="B110" s="18" t="s">
+      <c r="C110" s="19" t="s">
         <v>986</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>987</v>
       </c>
       <c r="D110" s="64" t="str">
         <f>IF(pH_op&lt;6.5,"pH BELOW HOB optimum (&lt;6.5) — reduce CO₂ dose",IF(pH_op&gt;7.5,"pH above optimum (&gt;7.5)","pH in HOB band 6.5–7.5"))</f>
-        <v>pH in HOB band 6.5-7.5</v>
+        <v>pH in HOB band 6.5–7.5</v>
       </c>
       <c r="E110" s="51" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G110" s="69" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="110" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="16" t="s">
+        <v>989</v>
+      </c>
+      <c r="B113" s="16" t="s">
         <v>990</v>
       </c>
-      <c r="B113" s="16" t="s">
+      <c r="C113" s="16" t="s">
         <v>991</v>
       </c>
-      <c r="C113" s="16" t="s">
+      <c r="D113" s="16" t="s">
         <v>992</v>
       </c>
-      <c r="D113" s="16" t="s">
+      <c r="E113" s="16" t="s">
         <v>993</v>
-      </c>
-      <c r="E113" s="16" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="20" t="s">
+        <v>994</v>
+      </c>
+      <c r="B114" s="20" t="s">
         <v>995</v>
-      </c>
-      <c r="B114" s="20" t="s">
-        <v>996</v>
       </c>
       <c r="C114" s="62">
         <f>PT_mc02*1000</f>
         <v>40.007195769523626</v>
       </c>
       <c r="D114" s="20" t="s">
+        <v>996</v>
+      </c>
+      <c r="E114" s="20" t="s">
         <v>997</v>
-      </c>
-      <c r="E114" s="20" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="20" t="s">
+        <v>998</v>
+      </c>
+      <c r="B115" s="20" t="s">
         <v>999</v>
-      </c>
-      <c r="B115" s="20" t="s">
-        <v>1000</v>
       </c>
       <c r="C115" s="62">
         <f>PT_udg*1000</f>
         <v>37.329366919026846</v>
       </c>
       <c r="D115" s="20" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E115" s="20" t="s">
         <v>1001</v>
-      </c>
-      <c r="E115" s="20" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -10864,375 +10908,375 @@
     </row>
     <row r="125" spans="1:5" ht="36" x14ac:dyDescent="0.2">
       <c r="A125" s="17" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B125" s="18" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C125" s="19" t="s">
         <v>1003</v>
-      </c>
-      <c r="C125" s="19" t="s">
-        <v>1004</v>
       </c>
       <c r="D125" s="62">
         <f>pH_Cl*pH_fHOCl*52460</f>
-        <v>5.3582403096</v>
+        <v>0</v>
       </c>
       <c r="E125" s="51" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="110" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A128" s="17" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B128" s="18" t="s">
         <v>1098</v>
       </c>
-      <c r="B128" s="18" t="s">
+      <c r="C128" s="19" t="s">
         <v>1099</v>
-      </c>
-      <c r="C128" s="19" t="s">
-        <v>1100</v>
       </c>
       <c r="D128" s="52">
         <v>0.5</v>
       </c>
       <c r="E128" s="51" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="24" x14ac:dyDescent="0.2">
       <c r="A129" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B129" s="18" t="s">
         <v>1102</v>
       </c>
-      <c r="B129" s="18" t="s">
+      <c r="C129" s="19" t="s">
         <v>1103</v>
-      </c>
-      <c r="C129" s="19" t="s">
-        <v>1104</v>
       </c>
       <c r="D129" s="52">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="E129" s="51" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="24" x14ac:dyDescent="0.2">
       <c r="A130" s="17" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B130" s="18" t="s">
         <v>1106</v>
       </c>
-      <c r="B130" s="18" t="s">
+      <c r="C130" s="19" t="s">
         <v>1107</v>
-      </c>
-      <c r="C130" s="19" t="s">
-        <v>1108</v>
       </c>
       <c r="D130" s="52">
         <v>5</v>
       </c>
       <c r="E130" s="51" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="17" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B131" s="18" t="s">
         <v>1110</v>
       </c>
-      <c r="B131" s="18" t="s">
+      <c r="C131" s="19" t="s">
         <v>1111</v>
-      </c>
-      <c r="C131" s="19" t="s">
-        <v>1112</v>
       </c>
       <c r="D131" s="62">
         <f>Iappc*FE_CER</f>
         <v>2.8449999999999999E-3</v>
       </c>
       <c r="E131" s="51" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="36" x14ac:dyDescent="0.2">
       <c r="A132" s="17" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B132" s="18" t="s">
         <v>1114</v>
       </c>
-      <c r="B132" s="18" t="s">
-        <v>1115</v>
-      </c>
       <c r="C132" s="19" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D132" s="62">
         <f>Fcc*km_Cl*(pH_Cl/1000)*A_anode</f>
         <v>0</v>
       </c>
       <c r="E132" s="51" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="17" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B133" s="18" t="s">
         <v>1117</v>
       </c>
-      <c r="B133" s="18" t="s">
-        <v>1118</v>
-      </c>
       <c r="C133" s="19" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D133" s="62">
         <f>MIN(I_Cl_FE,I_Cl_mt)</f>
         <v>0</v>
       </c>
       <c r="E133" s="51" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="17" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B134" s="18" t="s">
         <v>1120</v>
       </c>
-      <c r="B134" s="18" t="s">
+      <c r="C134" s="19" t="s">
         <v>1121</v>
-      </c>
-      <c r="C134" s="19" t="s">
-        <v>1122</v>
       </c>
       <c r="D134" s="62">
         <f>I_Cl/(2*Fcc*VLc)</f>
         <v>0</v>
       </c>
       <c r="E134" s="51" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="17" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B135" s="18" t="s">
         <v>1124</v>
       </c>
-      <c r="B135" s="18" t="s">
+      <c r="C135" s="19" t="s">
         <v>1125</v>
-      </c>
-      <c r="C135" s="19" t="s">
-        <v>1126</v>
       </c>
       <c r="D135" s="62">
         <f>pH_NT*14007</f>
         <v>199.91828363856516</v>
       </c>
       <c r="E135" s="51" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="36" x14ac:dyDescent="0.2">
       <c r="A136" s="17" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B136" s="18" t="s">
         <v>1128</v>
       </c>
-      <c r="B136" s="18" t="s">
+      <c r="C136" s="19" t="s">
         <v>1129</v>
-      </c>
-      <c r="C136" s="19" t="s">
-        <v>1130</v>
       </c>
       <c r="D136" s="52">
         <v>4200000</v>
       </c>
       <c r="E136" s="51" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="36" x14ac:dyDescent="0.2">
       <c r="A137" s="17" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B137" s="18" t="s">
         <v>1132</v>
       </c>
-      <c r="B137" s="18" t="s">
-        <v>1133</v>
-      </c>
       <c r="C137" s="19" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D137" s="52">
         <v>9.25</v>
       </c>
       <c r="E137" s="51" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="24" x14ac:dyDescent="0.2">
       <c r="A138" s="17" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B138" s="18" t="s">
         <v>1135</v>
       </c>
-      <c r="B138" s="18" t="s">
+      <c r="C138" s="19" t="s">
         <v>1136</v>
-      </c>
-      <c r="C138" s="19" t="s">
-        <v>1137</v>
       </c>
       <c r="D138" s="62">
         <f>pH_NT/(1+10^(pKa_NH4-pH_op))</f>
-        <v>9.542413029E-5</v>
+        <v>8.239289743160408E-5</v>
       </c>
       <c r="E138" s="51" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="24" x14ac:dyDescent="0.2">
       <c r="A139" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B139" s="18" t="s">
         <v>1139</v>
       </c>
-      <c r="B139" s="18" t="s">
-        <v>1140</v>
-      </c>
       <c r="C139" s="19" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D139" s="62">
         <f>P_HOCl/(k1_NH2Cl*NH3_free)</f>
-        <v>2.2482664447E-10</v>
+        <v>0</v>
       </c>
       <c r="E139" s="51" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="24" x14ac:dyDescent="0.2">
       <c r="A140" s="17" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B140" s="18" t="s">
         <v>1142</v>
       </c>
-      <c r="B140" s="18" t="s">
-        <v>1143</v>
-      </c>
       <c r="C140" s="19" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D140" s="62">
         <f>HOCl_ss*52460</f>
         <v>0</v>
       </c>
       <c r="E140" s="51" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A141" s="17" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B141" s="18" t="s">
         <v>1145</v>
       </c>
-      <c r="B141" s="18" t="s">
-        <v>1146</v>
-      </c>
       <c r="C141" s="19" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D141" s="52">
         <v>10</v>
       </c>
       <c r="E141" s="51" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="36" x14ac:dyDescent="0.2">
       <c r="A142" s="17" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B142" s="18" t="s">
         <v>1148</v>
       </c>
-      <c r="B142" s="18" t="s">
+      <c r="C142" s="19" t="s">
         <v>1149</v>
-      </c>
-      <c r="C142" s="19" t="s">
-        <v>1150</v>
       </c>
       <c r="D142" s="52">
         <v>1</v>
       </c>
       <c r="E142" s="51" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="36" x14ac:dyDescent="0.2">
       <c r="A143" s="17" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B143" s="18" t="s">
         <v>1152</v>
       </c>
-      <c r="B143" s="18" t="s">
-        <v>1153</v>
-      </c>
       <c r="C143" s="19" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D143" s="62">
         <f>MIN(P_HOCl*tau_NH2Cl*3600*52460,5.06*NH3_N)</f>
         <v>0</v>
       </c>
       <c r="E143" s="51" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="36" x14ac:dyDescent="0.2">
       <c r="A144" s="17" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B144" s="18" t="s">
         <v>1155</v>
       </c>
-      <c r="B144" s="18" t="s">
-        <v>1156</v>
-      </c>
       <c r="C144" s="19" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D144" s="52">
         <v>25</v>
       </c>
       <c r="E144" s="51" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="36" x14ac:dyDescent="0.2">
       <c r="A145" s="17" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B145" s="18" t="s">
         <v>1158</v>
       </c>
-      <c r="B145" s="18" t="s">
-        <v>1159</v>
-      </c>
       <c r="C145" s="19" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D145" s="62">
         <f>f_local*pH_fHOCl*HOCl_ss_mgL+NH2Cl_mgL/R_chloramine</f>
-        <v>0.6807516555</v>
+        <v>0</v>
       </c>
       <c r="E145" s="51" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="36" x14ac:dyDescent="0.2">
       <c r="A146" s="17" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B146" s="18" t="s">
         <v>1161</v>
       </c>
-      <c r="B146" s="18" t="s">
-        <v>1162</v>
-      </c>
       <c r="C146" s="19" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D146" s="52">
         <v>0.1</v>
       </c>
       <c r="E146" s="51" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="24" x14ac:dyDescent="0.2">
       <c r="A147" s="17" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B147" s="18" t="s">
         <v>1164</v>
       </c>
-      <c r="B147" s="18" t="s">
-        <v>1165</v>
-      </c>
       <c r="C147" s="19" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D147" s="52">
         <v>2</v>
       </c>
       <c r="E147" s="51" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
   </sheetData>
@@ -11764,7 +11808,7 @@
         <v>3.3E-4</v>
       </c>
       <c r="E29" s="67" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F29" s="20"/>
     </row>
@@ -11931,7 +11975,7 @@
         <v>7.7999999999999999E-6</v>
       </c>
       <c r="E38" s="67" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F38" s="20"/>
     </row>
@@ -13608,7 +13652,7 @@
         <v>2.6677872118283601E-4</v>
       </c>
       <c r="E70" s="69" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F70" s="20"/>
     </row>
@@ -13665,7 +13709,7 @@
         <v>1.5048188534755734E-4</v>
       </c>
       <c r="E73" s="69" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F73" s="20"/>
     </row>
@@ -13722,7 +13766,7 @@
         <v>405.2999999999999</v>
       </c>
       <c r="E76" s="69" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="F76" s="20"/>
     </row>
@@ -13816,7 +13860,7 @@
         <v>730</v>
       </c>
       <c r="E81" s="68" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="F81" s="20"/>
     </row>
@@ -13834,7 +13878,7 @@
         <v>1</v>
       </c>
       <c r="E82" s="68" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="F82" s="20"/>
     </row>
@@ -13852,7 +13896,7 @@
         <v>1</v>
       </c>
       <c r="E83" s="68" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="F83" s="20"/>
     </row>
@@ -13927,7 +13971,7 @@
         <v>1.5969906352431712E-3</v>
       </c>
       <c r="E87" s="101" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F87" s="20"/>
     </row>
@@ -13946,7 +13990,7 @@
         <v>1.5969906352431712E-3</v>
       </c>
       <c r="E88" s="69" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="F88" s="20"/>
     </row>
@@ -13965,7 +14009,7 @@
         <v>1.3984393971616449</v>
       </c>
       <c r="E89" s="101" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="F89" s="20"/>
     </row>
@@ -14003,7 +14047,7 @@
         <v>181.0677266956931</v>
       </c>
       <c r="E91" s="81" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="F91" s="20"/>
     </row>
@@ -14079,7 +14123,7 @@
         <v>OK</v>
       </c>
       <c r="E95" s="101" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="F95" s="20"/>
     </row>
@@ -14691,815 +14735,599 @@
     </row>
     <row r="132" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A132" s="17" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B132" s="18" t="s">
         <v>1010</v>
       </c>
-      <c r="B132" s="18" t="s">
+      <c r="C132" s="19" t="s">
         <v>1011</v>
-      </c>
-      <c r="C132" s="19" t="s">
-        <v>1012</v>
       </c>
       <c r="D132" s="28">
         <f>O2_net_gen</f>
         <v>5.3075424911539388E-5</v>
       </c>
       <c r="E132" s="69" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F132" s="20"/>
     </row>
     <row r="133" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A133" s="17" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B133" s="18" t="s">
         <v>1014</v>
       </c>
-      <c r="B133" s="18" t="s">
+      <c r="C133" s="19" t="s">
         <v>1015</v>
-      </c>
-      <c r="C133" s="19" t="s">
-        <v>1016</v>
       </c>
       <c r="D133" s="28">
         <f>O2_excess/(kLa_surf_used*3600*(V_charge/1000000))</f>
         <v>4.2885167873123194E-2</v>
       </c>
       <c r="E133" s="69" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F133" s="20"/>
     </row>
     <row r="134" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A134" s="20" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B134" s="20" t="s">
         <v>1018</v>
       </c>
-      <c r="B134" s="20" t="s">
+      <c r="C134" s="20" t="s">
         <v>1019</v>
-      </c>
-      <c r="C134" s="20" t="s">
-        <v>1020</v>
       </c>
       <c r="D134" s="28" t="str">
         <f>IF(DO_ss_sawtooth&lt;target_DO_frac*O2_ceil_C,"SURFACE-HELD","SPARGE-NEEDED")</f>
         <v>SURFACE-HELD</v>
       </c>
       <c r="E134" s="69" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F134" s="20"/>
     </row>
     <row r="135" spans="1:6" ht="36" x14ac:dyDescent="0.2">
       <c r="A135" s="20" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B135" s="20" t="s">
         <v>1022</v>
       </c>
-      <c r="B135" s="20" t="s">
+      <c r="C135" s="20" t="s">
         <v>1023</v>
-      </c>
-      <c r="C135" s="20" t="s">
-        <v>1024</v>
       </c>
       <c r="D135" s="28">
         <f>O2_net_gen/(kLa_surf_used*3600*(V_charge/1000000))</f>
         <v>0.12865550361936959</v>
       </c>
       <c r="E135" s="69" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="F135" s="20"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="20" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B137" s="20"/>
       <c r="C137" s="20"/>
       <c r="D137" s="20"/>
       <c r="E137" s="20" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F137" s="20"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" s="17" t="s">
         <v>1175</v>
       </c>
-      <c r="F137" s="20"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A138" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO₂ molecular diffusivity</t>
-        </is>
-      </c>
-      <c r="B138" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D_CO2</t>
-        </is>
-      </c>
-      <c r="C138" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">m²/s</t>
-        </is>
+      <c r="B138" s="18" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C138" s="19" t="s">
+        <v>584</v>
       </c>
       <c r="D138" s="124">
         <v>1.92E-9</v>
       </c>
-      <c r="E138" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO₂ diffusivity in water ~25°C, Cussler/Tamimi 1994.</t>
-        </is>
+      <c r="E138" s="67" t="s">
+        <v>1198</v>
       </c>
       <c r="F138" s="20"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A139" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atmospheric CO₂ partial pressure</t>
-        </is>
-      </c>
-      <c r="B139" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pCO2_air</t>
-        </is>
-      </c>
-      <c r="C139" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pa</t>
-        </is>
+      <c r="A139" s="17" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B139" s="18" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>64</v>
       </c>
       <c r="D139" s="124">
         <v>40</v>
       </c>
-      <c r="E139" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atmospheric pCO₂ (~400 ppm).</t>
-        </is>
+      <c r="E139" s="67" t="s">
+        <v>1200</v>
       </c>
       <c r="F139" s="20"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A140" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Headspace volume (SI)</t>
-        </is>
-      </c>
-      <c r="B140" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">headspace_V_m3</t>
-        </is>
-      </c>
-      <c r="C140" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">m³</t>
-        </is>
+      <c r="A140" s="17" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B140" s="18" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C140" s="19" t="s">
+        <v>1203</v>
       </c>
       <c r="D140" s="48">
         <f>headspace_V/1000000</f>
         <v>2.6124284559171357E-6</v>
       </c>
-      <c r="E140" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Geometry headspace volume converted mL→m³.</t>
-        </is>
+      <c r="E140" s="67" t="s">
+        <v>1204</v>
       </c>
       <c r="F140" s="20"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A141" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Liquid volume (SI)</t>
-        </is>
-      </c>
-      <c r="B141" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">V_L_m3</t>
-        </is>
-      </c>
-      <c r="C141" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">m³</t>
-        </is>
+      <c r="A141" s="17" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B141" s="18" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>1203</v>
       </c>
       <c r="D141" s="48">
         <f>V_charge/1000000</f>
         <v>1.5E-5</v>
       </c>
-      <c r="E141" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Charged liquid volume converted mL→m³.</t>
-        </is>
+      <c r="E141" s="67" t="s">
+        <v>1207</v>
       </c>
       <c r="F141" s="20"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A142" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Headspace vent bleed</t>
-        </is>
-      </c>
-      <c r="B142" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q_vent</t>
-        </is>
-      </c>
-      <c r="C142" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mL/min</t>
-        </is>
+    <row r="142" spans="1:6" ht="36" x14ac:dyDescent="0.2">
+      <c r="A142" s="17" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B142" s="18" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C142" s="19" t="s">
+        <v>364</v>
       </c>
       <c r="D142" s="124">
         <v>0.5</v>
       </c>
-      <c r="E142" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Slow restricted vent bleed - dead-volume + tube + near-closed solenoid leak. KEY NEW UNCERTAIN PARAMETER - measure. NOT free membrane diffusion, which would clear in seconds and could not reproduce the run-2 acidification.</t>
-        </is>
+      <c r="E142" s="69" t="s">
+        <v>1210</v>
       </c>
       <c r="F142" s="20"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A143" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Headspace vent rate</t>
-        </is>
-      </c>
-      <c r="B143" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">k_vent</t>
-        </is>
-      </c>
-      <c r="C143" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1/s</t>
-        </is>
+      <c r="A143" s="17" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B143" s="18" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>647</v>
       </c>
       <c r="D143" s="48">
         <f>(Q_vent/1000000/60)/headspace_V_m3</f>
-        <v>3.189880019281822E-3</v>
-      </c>
-      <c r="E143" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">First-order headspace clearance from the vent volumetric bleed.</t>
-        </is>
+        <v>3.1898800192818222E-3</v>
+      </c>
+      <c r="E143" s="67" t="s">
+        <v>1213</v>
       </c>
       <c r="F143" s="20"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A144" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Headspace residence time</t>
-        </is>
-      </c>
-      <c r="B144" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tau_hs</t>
-        </is>
-      </c>
-      <c r="C144" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">min</t>
-        </is>
+      <c r="A144" s="17" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B144" s="18" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C144" s="19" t="s">
+        <v>69</v>
       </c>
       <c r="D144" s="48">
         <f>headspace_V_m3/(Q_vent/1000000/60)/60</f>
-        <v>5.224856911834271</v>
-      </c>
-      <c r="E144" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time constant for the headspace to clear through the vent.</t>
-        </is>
+        <v>5.2248569118342711</v>
+      </c>
+      <c r="E144" s="67" t="s">
+        <v>1216</v>
       </c>
       <c r="F144" s="20"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO₂ saturation (pure sparge)</t>
-        </is>
-      </c>
-      <c r="B145" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C_sat_CO2</t>
-        </is>
-      </c>
-      <c r="C145" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mol/m³</t>
-        </is>
+      <c r="A145" s="17" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B145" s="18" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>465</v>
       </c>
       <c r="D145" s="48">
         <f>Biology!$D$31*P_atm</f>
-        <v>29.279978066256632</v>
-      </c>
-      <c r="E145" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Henry-law dissolved CO₂ at pure-CO₂ saturation.</t>
-        </is>
+        <v>33.437249999999999</v>
+      </c>
+      <c r="E145" s="67" t="s">
+        <v>1217</v>
       </c>
       <c r="F145" s="20"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A146" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO₂ air-equilibrium</t>
-        </is>
-      </c>
-      <c r="B146" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C_air_CO2</t>
-        </is>
-      </c>
-      <c r="C146" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mol/m³</t>
-        </is>
+      <c r="A146" s="17" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B146" s="18" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>465</v>
       </c>
       <c r="D146" s="48">
         <f>Biology!$D$31*pCO2_air</f>
-        <v>1.155883664100928E-2</v>
-      </c>
-      <c r="E146" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Henry-law dissolved CO₂ in equilibrium with room air.</t>
-        </is>
+        <v>1.32E-2</v>
+      </c>
+      <c r="E146" s="67" t="s">
+        <v>1218</v>
       </c>
       <c r="F146" s="20"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Diffusivity scaling (CO₂/O₂)</t>
-        </is>
-      </c>
-      <c r="B147" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sqrtD_CO2</t>
-        </is>
-      </c>
-      <c r="C147" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
+      <c r="A147" s="17" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B147" s="18" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>137</v>
       </c>
       <c r="D147" s="48">
         <f>SQRT(D_CO2/D_O2)</f>
-        <v>0.9239657792511647</v>
-      </c>
-      <c r="E147" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Penetration-theory √(D_CO₂/D_O₂) scaling of the O₂ transfer coefficient.</t>
-        </is>
+        <v>0.92396577925116474</v>
+      </c>
+      <c r="E147" s="67" t="s">
+        <v>1220</v>
       </c>
       <c r="F147" s="20"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A148" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO₂ surface transfer coefficient</t>
-        </is>
-      </c>
-      <c r="B148" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kLa_CO2_off</t>
-        </is>
-      </c>
-      <c r="C148" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1/s</t>
-        </is>
+      <c r="A148" s="17" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B148" s="18" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C148" s="19" t="s">
+        <v>647</v>
       </c>
       <c r="D148" s="48">
         <f>kLa_surf*sqrtD_CO2</f>
-        <v>4.991283516870223E-3</v>
-      </c>
-      <c r="E148" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surface kLa for CO₂ between pulses (surface path).</t>
-        </is>
+        <v>7.0587408432071473E-3</v>
+      </c>
+      <c r="E148" s="67" t="s">
+        <v>1222</v>
       </c>
       <c r="F148" s="20"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A149" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surface-relaxation time</t>
-        </is>
-      </c>
-      <c r="B149" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tau_surf_floor</t>
-        </is>
-      </c>
-      <c r="C149" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">min</t>
-        </is>
+      <c r="A149" s="17" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B149" s="18" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>69</v>
       </c>
       <c r="D149" s="48">
         <f>1/kLa_CO2_off/60</f>
-        <v>3.3391544700545235</v>
-      </c>
-      <c r="E149" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time constant for the liquid to relax to the headspace via the surface.</t>
-        </is>
+        <v>2.3611387692049264</v>
+      </c>
+      <c r="E149" s="67" t="s">
+        <v>1225</v>
       </c>
       <c r="F149" s="20"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A150" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Headspace gas inventory</t>
-        </is>
-      </c>
-      <c r="B150" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n_hs_gas</t>
-        </is>
-      </c>
-      <c r="C150" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mol</t>
-        </is>
+      <c r="A150" s="17" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B150" s="18" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C150" s="19" t="s">
+        <v>827</v>
       </c>
       <c r="D150" s="48">
         <f>P_atm*headspace_V_m3/(R_gas*T_K)</f>
-        <v>1.0501933416012095E-4</v>
-      </c>
-      <c r="E150" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Moles of gas in the headspace at P_atm, T_K (ideal-gas).</t>
-        </is>
+        <v>1.0678051702378222E-4</v>
+      </c>
+      <c r="E150" s="67" t="s">
+        <v>1228</v>
       </c>
       <c r="F150" s="20"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A151" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pulse duration</t>
-        </is>
-      </c>
-      <c r="B151" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">t_on_CO2</t>
-        </is>
-      </c>
-      <c r="C151" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
+      <c r="A151" s="17" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B151" s="18" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="D151" s="48">
         <f>spg_dur</f>
-        <v>0.7845130498249656</v>
-      </c>
-      <c r="E151" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sparge pulse on-time from the schedule.</t>
-        </is>
+        <v>0.78451304982496561</v>
+      </c>
+      <c r="E151" s="67" t="s">
+        <v>1229</v>
       </c>
       <c r="F151" s="20"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A152" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gap duration</t>
-        </is>
-      </c>
-      <c r="B152" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">t_off_CO2</t>
-        </is>
-      </c>
-      <c r="C152" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s</t>
-        </is>
+      <c r="A152" s="17" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B152" s="18" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C152" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="D152" s="48">
         <f>MAX(0,spg_int*60-spg_dur)</f>
-        <v>10684.092817840014</v>
-      </c>
-      <c r="E152" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time between pulses, guard-floored at 0.</t>
-        </is>
+        <v>10863.279088691761</v>
+      </c>
+      <c r="E152" s="67" t="s">
+        <v>1230</v>
       </c>
       <c r="F152" s="20"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A153" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On-phase surface decay</t>
-        </is>
-      </c>
-      <c r="B153" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eon_CO2</t>
-        </is>
-      </c>
-      <c r="C153" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
+      <c r="A153" s="17" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B153" s="18" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C153" s="19" t="s">
+        <v>137</v>
       </c>
       <c r="D153" s="48">
         <f>EXP(-kLa_CO2_off*t_on_CO2)</f>
-        <v>0.996091929408022</v>
-      </c>
-      <c r="E153" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surface-path liquid decay factor over the pulse.</t>
-        </is>
+        <v>0.99447763034777281</v>
+      </c>
+      <c r="E153" s="67" t="s">
+        <v>1233</v>
       </c>
       <c r="F153" s="20"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A154" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Off-phase surface decay</t>
-        </is>
-      </c>
-      <c r="B154" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">e1_CO2</t>
-        </is>
-      </c>
-      <c r="C154" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
+      <c r="A154" s="17" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B154" s="18" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C154" s="19" t="s">
+        <v>137</v>
       </c>
       <c r="D154" s="48">
         <f>EXP(-kLa_CO2_off*t_off_CO2)</f>
-        <v>6.922007698981812E-24</v>
-      </c>
-      <c r="E154" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surface-path liquid decay factor over the gap.</t>
-        </is>
+        <v>4.9869343751369273E-34</v>
+      </c>
+      <c r="E154" s="67" t="s">
+        <v>1236</v>
       </c>
       <c r="F154" s="20"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A155" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Off-phase vent decay</t>
-        </is>
-      </c>
-      <c r="B155" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">e2_CO2</t>
-        </is>
-      </c>
-      <c r="C155" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
+      <c r="A155" s="17" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B155" s="18" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C155" s="19" t="s">
+        <v>137</v>
       </c>
       <c r="D155" s="48">
         <f>EXP(-k_vent*t_off_CO2)</f>
-        <v>1.5805963161657336E-15</v>
-      </c>
-      <c r="E155" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Headspace vent decay factor over the gap.</t>
-        </is>
+        <v>8.9245381551518439E-16</v>
+      </c>
+      <c r="E155" s="67" t="s">
+        <v>1239</v>
       </c>
       <c r="F155" s="20"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A156" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two-compartment coupling coef</t>
-        </is>
-      </c>
-      <c r="B156" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coef_CO2</t>
-        </is>
-      </c>
-      <c r="C156" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mol/m³</t>
-        </is>
+      <c r="A156" s="17" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B156" s="18" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C156" s="19" t="s">
+        <v>465</v>
       </c>
       <c r="D156" s="48">
         <f>(C_sat_CO2-C_air_CO2)*kLa_CO2_off/(kLa_CO2_off-k_vent)</f>
-        <v>81.09620008021494</v>
-      </c>
-      <c r="E156" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coupling coefficient linking the venting headspace to the liquid relaxation.</t>
-        </is>
+        <v>60.982216114205634</v>
+      </c>
+      <c r="E156" s="67" t="s">
+        <v>1242</v>
       </c>
       <c r="F156" s="20"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A157" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cycle-start liquid CO₂</t>
-        </is>
-      </c>
-      <c r="B157" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ca_CO2</t>
-        </is>
-      </c>
-      <c r="C157" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mol/m³</t>
-        </is>
+      <c r="A157" s="17" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B157" s="18" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C157" s="19" t="s">
+        <v>465</v>
       </c>
       <c r="D157" s="48">
         <f>(e1_CO2*C_sat_CO2*(1-eon_CO2)+C_air_CO2*(1-e1_CO2)+coef_CO2*(e2_CO2-e1_CO2))/(1-e1_CO2*eon_CO2)</f>
-        <v>1.155883664113746E-2</v>
-      </c>
-      <c r="E157" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Closed-form limit-cycle dissolved CO₂ at the start of each pulse.</t>
-        </is>
+        <v>1.3200000000054423E-2</v>
+      </c>
+      <c r="E157" s="67" t="s">
+        <v>1245</v>
       </c>
       <c r="F157" s="20"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A158" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">End-of-pulse liquid CO₂</t>
-        </is>
-      </c>
-      <c r="B158" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cb_CO2</t>
-        </is>
-      </c>
-      <c r="C158" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mol/m³</t>
-        </is>
+      <c r="A158" s="17" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B158" s="18" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C158" s="19" t="s">
+        <v>465</v>
       </c>
       <c r="D158" s="48">
         <f>C_sat_CO2+(Ca_CO2-C_sat_CO2)*eon_CO2</f>
-        <v>0.1259418851060765</v>
-      </c>
-      <c r="E158" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dissolved CO₂ at the end of the pulse (start of the gap).</t>
-        </is>
+        <v>0.1977799593745786</v>
+      </c>
+      <c r="E158" s="67" t="s">
+        <v>1248</v>
       </c>
       <c r="F158" s="20"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A159" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On-phase CO₂ integral</t>
-        </is>
-      </c>
-      <c r="B159" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO2_int_on</t>
-        </is>
-      </c>
-      <c r="C159" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mol.s/m³</t>
-        </is>
+      <c r="A159" s="17" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B159" s="18" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C159" s="19" t="s">
+        <v>1189</v>
       </c>
       <c r="D159" s="48">
         <f>C_sat_CO2*t_on_CO2+(Ca_CO2-C_sat_CO2)/kLa_CO2_off*(1-eon_CO2)</f>
-        <v>5.3964836756566825E-2</v>
-      </c>
-      <c r="E159" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time-integral of dissolved CO₂ over the pulse.</t>
-        </is>
+        <v>8.2825089412320807E-2</v>
+      </c>
+      <c r="E159" s="67" t="s">
+        <v>1250</v>
       </c>
       <c r="F159" s="20"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A160" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Off-phase CO₂ integral</t>
-        </is>
-      </c>
-      <c r="B160" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO2_int_off</t>
-        </is>
-      </c>
-      <c r="C160" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mol.s/m³</t>
-        </is>
+      <c r="A160" s="17" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B160" s="18" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C160" s="19" t="s">
+        <v>1189</v>
       </c>
       <c r="D160" s="48">
         <f>C_air_CO2*t_off_CO2+(Cb_CO2-C_air_CO2)/kLa_CO2_off*(1-e1_CO2)+coef_CO2*((1-e2_CO2)/k_vent-(1-e1_CO2)/kLa_CO2_off)</f>
-        <v>9321.810394212807</v>
-      </c>
-      <c r="E160" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time-integral of dissolved CO₂ over the gap, including the venting-headspace term.</t>
-        </is>
+        <v>10647.697137696226</v>
+      </c>
+      <c r="E160" s="67" t="s">
+        <v>1252</v>
       </c>
       <c r="F160" s="20"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A161" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cycle-average CO₂</t>
-        </is>
-      </c>
-      <c r="B161" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO2_cyc_avg</t>
-        </is>
-      </c>
-      <c r="C161" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mol/m³</t>
-        </is>
+      <c r="A161" s="17" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B161" s="18" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C161" s="19" t="s">
+        <v>465</v>
       </c>
       <c r="D161" s="48">
         <f>(CO2_int_on+CO2_int_off)/(t_on_CO2+t_off_CO2)</f>
-        <v>0.8724353186629646</v>
-      </c>
-      <c r="E161" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Limit-cycle time-average dissolved CO₂ over one pulse+gap.</t>
-        </is>
+        <v>0.98009182872224021</v>
+      </c>
+      <c r="E161" s="67" t="s">
+        <v>1253</v>
       </c>
       <c r="F161" s="20"/>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Steady dissolved CO₂</t>
-        </is>
-      </c>
-      <c r="B162" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO2aqc_ss</t>
-        </is>
-      </c>
-      <c r="C162" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mol/L</t>
-        </is>
+    <row r="162" spans="1:6" ht="24" x14ac:dyDescent="0.2">
+      <c r="A162" s="17" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B162" s="18" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C162" s="19" t="s">
+        <v>492</v>
       </c>
       <c r="D162" s="48">
         <f>MIN(C_sat_CO2,MAX(C_air_CO2,CO2_cyc_avg))/1000</f>
-        <v>8.724353186629647E-4</v>
-      </c>
-      <c r="E162" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bounded steady dissolved CO₂; the value Chemistry D5 is repointed to (two-compartment headspace model).</t>
-        </is>
+        <v>9.8009182872224013E-4</v>
+      </c>
+      <c r="E162" s="67" t="s">
+        <v>1254</v>
       </c>
       <c r="F162" s="20"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vent-path sanity check</t>
-        </is>
-      </c>
-      <c r="B163" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vent_floor_chk</t>
-        </is>
-      </c>
-      <c r="C163" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
+      <c r="A163" s="17" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B163" s="18" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C163" s="19" t="s">
+        <v>137</v>
       </c>
       <c r="D163" s="48" t="str">
         <f>IF(tau_hs&gt;=tau_surf_floor,"vent is slow path - OK","WARNING: surface clears faster than vent - run2 cannot stay acidic")</f>
         <v>vent is slow path - OK</v>
       </c>
-      <c r="E163" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confirms the vent is the rate-limiting path; if the surface cleared faster, run 2 could not stay acidic.</t>
-        </is>
+      <c r="E163" s="67" t="s">
+        <v>1257</v>
       </c>
       <c r="F163" s="20"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A164" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Schedule validity</t>
-        </is>
-      </c>
-      <c r="B164" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sched_valid</t>
-        </is>
-      </c>
-      <c r="C164" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
+      <c r="A164" s="17" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B164" s="18" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C164" s="19" t="s">
+        <v>137</v>
       </c>
       <c r="D164" s="48" t="str">
         <f>IF(spg_int*60&gt;=spg_dur,"OK","INVALID: interval &lt; pulse")</f>
         <v>OK</v>
       </c>
-      <c r="E164" s="67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surfaces an interval&lt;pulse misconfiguration.</t>
-        </is>
+      <c r="E164" s="67" t="s">
+        <v>1258</v>
       </c>
       <c r="F164" s="20"/>
     </row>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martincurrie/andeye Dropbox/andeye/Projects/electroPioreactor/Media/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8775397F-2CA4-D643-B203-BF9035C146C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB5C439-CC84-1846-B800-B9224A2CB035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="580" windowWidth="25640" windowHeight="18060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,6 +36,8 @@
     <definedName name="bubble_regime" localSheetId="5">'Mass Transfer'!$D$64</definedName>
     <definedName name="C_air_CO2" localSheetId="5">'Mass Transfer'!$D$146</definedName>
     <definedName name="C_eff" localSheetId="3">Chemistry!$D$145</definedName>
+    <definedName name="C_eff_hi" localSheetId="3">Chemistry!$D$157</definedName>
+    <definedName name="C_eff_lo" localSheetId="3">Chemistry!$D$156</definedName>
     <definedName name="C_H2_sat" localSheetId="4">Biology!$D$41</definedName>
     <definedName name="C_sat_CO2" localSheetId="5">'Mass Transfer'!$D$145</definedName>
     <definedName name="Ca_CO2" localSheetId="5">'Mass Transfer'!$D$157</definedName>
@@ -46,6 +48,7 @@
     <definedName name="Cl_kill" localSheetId="3">Chemistry!$D$147</definedName>
     <definedName name="Cl_mc02" localSheetId="3">Chemistry!$D$38</definedName>
     <definedName name="Cl_onset" localSheetId="3">Chemistry!$D$146</definedName>
+    <definedName name="Cl_pool_mgL" localSheetId="3">Chemistry!$D$149</definedName>
     <definedName name="Cl_udg" localSheetId="3">Chemistry!$D$42</definedName>
     <definedName name="CO2_carbon_margin" localSheetId="4">Biology!$D$35</definedName>
     <definedName name="CO2_cons" localSheetId="4">Biology!$D$15</definedName>
@@ -60,6 +63,7 @@
     <definedName name="CO2aqc" localSheetId="3">Chemistry!$D$5</definedName>
     <definedName name="CO2aqc_ss" localSheetId="5">'Mass Transfer'!$D$162</definedName>
     <definedName name="coef_CO2" localSheetId="5">'Mass Transfer'!$D$156</definedName>
+    <definedName name="corr_I_frac" localSheetId="3">Chemistry!$D$158</definedName>
     <definedName name="d_bubble" localSheetId="5">'Mass Transfer'!$D$42</definedName>
     <definedName name="d_bubble_mm" localSheetId="5">'Mass Transfer'!$D$43</definedName>
     <definedName name="D_CO2" localSheetId="5">'Mass Transfer'!$D$138</definedName>
@@ -189,6 +193,11 @@
     <definedName name="media_volume" localSheetId="0">Summary!$D$9</definedName>
     <definedName name="mend_a" localSheetId="5">'Mass Transfer'!$D$44</definedName>
     <definedName name="mend_b" localSheetId="5">'Mass Transfer'!$D$45</definedName>
+    <definedName name="metal_flag" localSheetId="3">Chemistry!$D$163</definedName>
+    <definedName name="metal_leach_rate" localSheetId="3">Chemistry!$D$161</definedName>
+    <definedName name="metal_MW" localSheetId="3">Chemistry!$D$159</definedName>
+    <definedName name="metal_tox_thresh" localSheetId="3">Chemistry!$D$162</definedName>
+    <definedName name="metal_z" localSheetId="3">Chemistry!$D$160</definedName>
     <definedName name="min_sparge_cal" localSheetId="5">'Mass Transfer'!$D$118</definedName>
     <definedName name="MW_CaCl2" localSheetId="3">Chemistry!$B$33</definedName>
     <definedName name="MW_CaSO4_2H2O" localSheetId="3">Chemistry!$B$30</definedName>
@@ -200,9 +209,12 @@
     <definedName name="MW_NaHCO3" localSheetId="3">Chemistry!$B$28</definedName>
     <definedName name="MW_NH42SO4" localSheetId="3">Chemistry!$B$32</definedName>
     <definedName name="n_cross" localSheetId="3">Chemistry!$D$105</definedName>
+    <definedName name="n_e_Cl" localSheetId="3">Chemistry!$D$148</definedName>
     <definedName name="n_hs_gas" localSheetId="5">'Mass Transfer'!$D$150</definedName>
     <definedName name="n_pores_active" localSheetId="5">'Mass Transfer'!$D$61</definedName>
     <definedName name="nCO2_rate" localSheetId="5">'Mass Transfer'!$D$104</definedName>
+    <definedName name="NH2Cl_hi" localSheetId="3">Chemistry!$D$155</definedName>
+    <definedName name="NH2Cl_lo" localSheetId="3">Chemistry!$D$154</definedName>
     <definedName name="NH2Cl_mgL" localSheetId="3">Chemistry!$D$143</definedName>
     <definedName name="NH3_free" localSheetId="3">Chemistry!$D$138</definedName>
     <definedName name="NH3_N" localSheetId="3">Chemistry!$D$135</definedName>
@@ -264,6 +276,8 @@
     <definedName name="Q_CO2" localSheetId="5">'Mass Transfer'!$D$102</definedName>
     <definedName name="Q_vent" localSheetId="5">'Mass Transfer'!$D$142</definedName>
     <definedName name="R_chloramine" localSheetId="3">Chemistry!$D$144</definedName>
+    <definedName name="R_chloramine_hi" localSheetId="3">Chemistry!$D$153</definedName>
+    <definedName name="R_chloramine_lo" localSheetId="3">Chemistry!$D$152</definedName>
     <definedName name="R_gas" localSheetId="3">Chemistry!$D$9</definedName>
     <definedName name="R_gas" localSheetId="2">Electrochemistry!$D$7</definedName>
     <definedName name="R_gas" localSheetId="5">'Mass Transfer'!$D$101</definedName>
@@ -333,6 +347,8 @@
     <definedName name="target_DO_frac" localSheetId="5">'Mass Transfer'!$D$84</definedName>
     <definedName name="tau_hs" localSheetId="5">'Mass Transfer'!$D$144</definedName>
     <definedName name="tau_NH2Cl" localSheetId="3">Chemistry!$D$142</definedName>
+    <definedName name="tau_NH2Cl_hi" localSheetId="3">Chemistry!$D$151</definedName>
+    <definedName name="tau_NH2Cl_lo" localSheetId="3">Chemistry!$D$150</definedName>
     <definedName name="tau_surf_floor" localSheetId="5">'Mass Transfer'!$D$149</definedName>
     <definedName name="temp_C" localSheetId="0">Summary!$D$8</definedName>
     <definedName name="tip_speed" localSheetId="5">'Mass Transfer'!$D$68</definedName>
@@ -400,7 +416,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="1259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="1323">
   <si>
     <t>CO₂ DOSING FLOWRATES</t>
   </si>
@@ -4177,6 +4193,198 @@
   </si>
   <si>
     <t>Surfaces an interval&lt;pulse misconfiguration.</t>
+  </si>
+  <si>
+    <t>electrons per produced HOCl</t>
+  </si>
+  <si>
+    <t>n_e_Cl</t>
+  </si>
+  <si>
+    <t>e-/HOCl</t>
+  </si>
+  <si>
+    <t>n-electron count in the binding regime: 1 e-/Cl- when chloride-arrival-limited, 2 e-/Cl2 on the FE route</t>
+  </si>
+  <si>
+    <t>chloride-pool ceiling on chlorine</t>
+  </si>
+  <si>
+    <t>Cl_pool_mgL</t>
+  </si>
+  <si>
+    <t>mg/L</t>
+  </si>
+  <si>
+    <t>Total chloride pool as HOCl-equivalent; chlorine (free+combined) cannot exceed this. UdG CaCl2-derived (closed batch also depletes it)</t>
+  </si>
+  <si>
+    <t>monochloramine residence (low)</t>
+  </si>
+  <si>
+    <t>tau_NH2Cl_lo</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>Low bound of monochloramine residence (~1 min); weak estimate, swept for the C_eff band</t>
+  </si>
+  <si>
+    <t>monochloramine residence (high)</t>
+  </si>
+  <si>
+    <t>tau_NH2Cl_hi</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>High bound of monochloramine residence (5 h); weak estimate, swept for the C_eff band</t>
+  </si>
+  <si>
+    <t>chloramine potency divisor (low)</t>
+  </si>
+  <si>
+    <t>R_chloramine_lo</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Most-potent end of the monochloramine potency-divisor band (defensible)</t>
+  </si>
+  <si>
+    <t>chloramine potency divisor (high)</t>
+  </si>
+  <si>
+    <t>R_chloramine_hi</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Least-potent end of the monochloramine potency-divisor band</t>
+  </si>
+  <si>
+    <t>combined chlorine (low-tau)</t>
+  </si>
+  <si>
+    <t>NH2Cl_lo</t>
+  </si>
+  <si>
+    <t>mg/L</t>
+  </si>
+  <si>
+    <t>Combined chlorine at the low-tau bound, chloride-pool-capped</t>
+  </si>
+  <si>
+    <t>combined chlorine (high-tau)</t>
+  </si>
+  <si>
+    <t>NH2Cl_hi</t>
+  </si>
+  <si>
+    <t>mg/L</t>
+  </si>
+  <si>
+    <t>Combined chlorine at the high-tau bound, chloride-pool-capped</t>
+  </si>
+  <si>
+    <t>effective biocidal chlorine (low)</t>
+  </si>
+  <si>
+    <t>C_eff_lo</t>
+  </si>
+  <si>
+    <t>mg/L</t>
+  </si>
+  <si>
+    <t>Low bound of effective biocidal chlorine (least chlorine, least potent)</t>
+  </si>
+  <si>
+    <t>effective biocidal chlorine (high)</t>
+  </si>
+  <si>
+    <t>C_eff_hi</t>
+  </si>
+  <si>
+    <t>mg/L</t>
+  </si>
+  <si>
+    <t>High bound (most chlorine, most potent); the chloride-pool cap keeps it below the kill threshold in UdG</t>
+  </si>
+  <si>
+    <t>anodic charge to metal dissolution</t>
+  </si>
+  <si>
+    <t>corr_I_frac</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>DATA GAP - fraction of anodic charge going to electrode metal dissolution; measure (the green anode points to Cu/Ni ammine)</t>
+  </si>
+  <si>
+    <t>leached-metal molar mass</t>
+  </si>
+  <si>
+    <t>metal_MW</t>
+  </si>
+  <si>
+    <t>g/mol</t>
+  </si>
+  <si>
+    <t>Cu molar mass, representative leached transition metal</t>
+  </si>
+  <si>
+    <t>electrons per metal ion</t>
+  </si>
+  <si>
+    <t>metal_z</t>
+  </si>
+  <si>
+    <t>e-/ion</t>
+  </si>
+  <si>
+    <t>Electrons per dissolved divalent metal ion</t>
+  </si>
+  <si>
+    <t>dissolved-metal leach rate</t>
+  </si>
+  <si>
+    <t>metal_leach_rate</t>
+  </si>
+  <si>
+    <t>mg/L/h</t>
+  </si>
+  <si>
+    <t>Dissolved-metal accumulation rate; #N/A until corr_I_frac is measured</t>
+  </si>
+  <si>
+    <t>metal toxicity threshold</t>
+  </si>
+  <si>
+    <t>metal_tox_thresh</t>
+  </si>
+  <si>
+    <t>mg/L</t>
+  </si>
+  <si>
+    <t>Order-of-magnitude bactericidal Cu/Ni concentration for gram-negatives (literature)</t>
+  </si>
+  <si>
+    <t>electrode-corrosion verdict</t>
+  </si>
+  <si>
+    <t>metal_flag</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Verdict pointer: the unmodelled prime suspect for the Exp-2 death</t>
   </si>
 </sst>
 </file>
@@ -5561,7 +5769,7 @@
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="105" t="s">
-        <v>39</v>
+        <v>540</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>31</v>
@@ -5579,7 +5787,7 @@
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="105" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="E5" s="20" t="s">
         <v>31</v>
@@ -5855,7 +6063,7 @@
       <c r="C21" s="20"/>
       <c r="D21" s="91" t="str">
         <f>'Mass Transfer'!$D$109</f>
-        <v>at/under optimum</v>
+        <v>organism optimum unknown</v>
       </c>
       <c r="E21" s="23" t="str">
         <f>HYPERLINK("#'Mass Transfer'!D109","→ Mass")</f>
@@ -5891,7 +6099,7 @@
       <c r="C23" s="20"/>
       <c r="D23" s="91" t="str">
         <f>'Mass Transfer'!$D$113</f>
-        <v>Surface stripping holds DO under impairment - sparge is CARBON-limited (long interval); the O2-limited interval is the conservative fallback until kL_surf is measured</v>
+        <v>organism DO unknown</v>
       </c>
       <c r="E23" s="23" t="str">
         <f>HYPERLINK("#'Mass Transfer'!D113","→ Mass")</f>
@@ -6105,7 +6313,7 @@
       <c r="C35" s="20"/>
       <c r="D35" s="129">
         <f>Chemistry!$D$103</f>
-        <v>7.0138967253152611</v>
+        <v>7.3761471820171503</v>
       </c>
       <c r="E35" s="23" t="str">
         <f>HYPERLINK("#Chemistry!D103","→ Chemistry")</f>
@@ -6124,7 +6332,7 @@
       </c>
       <c r="D36" s="129">
         <f>Chemistry!$D$145</f>
-        <v>0</v>
+        <v>0.37839805023646339</v>
       </c>
       <c r="E36" s="23" t="str">
         <f>HYPERLINK("#Chemistry!D139","→ Chemistry")</f>
@@ -9275,7 +9483,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFC00"/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -9940,7 +10148,7 @@
       </c>
       <c r="D44" s="62">
         <f>IF(Summary!$D$5="MC02",SID_mc02,IF(Summary!$D$5="UdG phosphate",SID_udg,NA()))</f>
-        <v>4.6127523207276644E-2</v>
+        <v>6.3142947675680683E-2</v>
       </c>
       <c r="E44" s="51" t="s">
         <v>949</v>
@@ -9958,7 +10166,7 @@
       </c>
       <c r="D45" s="62">
         <f>IF(Summary!$D$5="MC02",PT_mc02,IF(Summary!$D$5="UdG phosphate",PT_udg,NA()))</f>
-        <v>4.0007195769523628E-2</v>
+        <v>3.7329366919026843E-2</v>
       </c>
       <c r="E45" s="51" t="s">
         <v>953</v>
@@ -9976,7 +10184,7 @@
       </c>
       <c r="D46" s="62">
         <f>IF(Summary!$D$5="MC02",NT_mc02,IF(Summary!$D$5="UdG phosphate",NT_udg,NA()))</f>
-        <v>1.4272741032238535E-2</v>
+        <v>7.1136673225367037E-3</v>
       </c>
       <c r="E46" s="51" t="s">
         <v>957</v>
@@ -9994,7 +10202,7 @@
       </c>
       <c r="D47" s="62">
         <f>IF(Summary!$D$5="MC02",Cl_mc02,IF(Summary!$D$5="UdG phosphate",Cl_udg,NA()))</f>
-        <v>0</v>
+        <v>1.8021265092809516E-4</v>
       </c>
       <c r="E47" s="51" t="s">
         <v>961</v>
@@ -10017,7 +10225,7 @@
       </c>
       <c r="B50" s="64">
         <f t="shared" ref="B50:B81" si="1">pH_SID + pH_NT*(10^-A50)/((10^-A50)+Ka_NH4) + (10^-A50) - (pH_PT*Ka1p*(10^-A50)^2 + 2*pH_PT*Ka1p*Ka2p*(10^-A50) + 3*pH_PT*Ka1p*Ka2p*Ka3p)/((10^-A50)^3 + Ka1p*(10^-A50)^2 + Ka1p*Ka2p*(10^-A50) + Ka1p*Ka2p*Ka3p) - Ka1c*CO2aqc/(10^-A50) - 2*Ka1c*Ka2c*CO2aqc/(10^-A50)^2 - Kw_w/(10^-A50)</f>
-        <v>2.1019058551390035E-2</v>
+        <v>3.3517774517338811E-2</v>
       </c>
       <c r="C50" s="64">
         <f t="shared" ref="C50:C81" si="2">IF(AND(B50&gt;=0,B51&lt;0),A50+0.1*B50/(B50-B51),0)</f>
@@ -10030,7 +10238,7 @@
       </c>
       <c r="B51" s="64">
         <f t="shared" si="1"/>
-        <v>2.087779495813831E-2</v>
+        <v>3.3384522985935881E-2</v>
       </c>
       <c r="C51" s="64">
         <f t="shared" si="2"/>
@@ -10043,7 +10251,7 @@
       </c>
       <c r="B52" s="64">
         <f t="shared" si="1"/>
-        <v>2.0761558996324307E-2</v>
+        <v>3.3274889786970713E-2</v>
       </c>
       <c r="C52" s="64">
         <f t="shared" si="2"/>
@@ -10056,7 +10264,7 @@
       </c>
       <c r="B53" s="64">
         <f t="shared" si="1"/>
-        <v>2.0664451481525431E-2</v>
+        <v>3.3183307892540218E-2</v>
       </c>
       <c r="C53" s="64">
         <f t="shared" si="2"/>
@@ -10069,7 +10277,7 @@
       </c>
       <c r="B54" s="64">
         <f t="shared" si="1"/>
-        <v>2.0581488381558221E-2</v>
+        <v>3.3105074993299691E-2</v>
       </c>
       <c r="C54" s="64">
         <f t="shared" si="2"/>
@@ -10082,7 +10290,7 @@
       </c>
       <c r="B55" s="64">
         <f t="shared" si="1"/>
-        <v>2.0508374166718756E-2</v>
+        <v>3.3036139256554423E-2</v>
       </c>
       <c r="C55" s="64">
         <f t="shared" si="2"/>
@@ -10095,7 +10303,7 @@
       </c>
       <c r="B56" s="64">
         <f t="shared" si="1"/>
-        <v>2.0441298663309293E-2</v>
+        <v>3.297290744358844E-2</v>
       </c>
       <c r="C56" s="64">
         <f t="shared" si="2"/>
@@ -10108,7 +10316,7 @@
       </c>
       <c r="B57" s="64">
         <f t="shared" si="1"/>
-        <v>2.0376751712173753E-2</v>
+        <v>3.291206994508325E-2</v>
       </c>
       <c r="C57" s="64">
         <f t="shared" si="2"/>
@@ -10121,7 +10329,7 @@
       </c>
       <c r="B58" s="64">
         <f t="shared" si="1"/>
-        <v>2.0311349339068894E-2</v>
+        <v>3.2850436754628849E-2</v>
       </c>
       <c r="C58" s="64">
         <f t="shared" si="2"/>
@@ -10134,7 +10342,7 @@
       </c>
       <c r="B59" s="64">
         <f t="shared" si="1"/>
-        <v>2.0241664884390737E-2</v>
+        <v>3.2784778168851753E-2</v>
       </c>
       <c r="C59" s="64">
         <f t="shared" si="2"/>
@@ -10147,7 +10355,7 @@
       </c>
       <c r="B60" s="64">
         <f t="shared" si="1"/>
-        <v>2.0164058456515817E-2</v>
+        <v>3.2711663930267844E-2</v>
       </c>
       <c r="C60" s="64">
         <f t="shared" si="2"/>
@@ -10160,7 +10368,7 @@
       </c>
       <c r="B61" s="64">
         <f t="shared" si="1"/>
-        <v>2.0074498101705092E-2</v>
+        <v>3.2627294556085151E-2</v>
       </c>
       <c r="C61" s="64">
         <f t="shared" si="2"/>
@@ -10173,7 +10381,7 @@
       </c>
       <c r="B62" s="64">
         <f t="shared" si="1"/>
-        <v>1.9968366246046778E-2</v>
+        <v>3.2527318743270667E-2</v>
       </c>
       <c r="C62" s="64">
         <f t="shared" si="2"/>
@@ -10186,7 +10394,7 @@
       </c>
       <c r="B63" s="64">
         <f t="shared" si="1"/>
-        <v>1.984024537243341E-2</v>
+        <v>3.2406631110720986E-2</v>
       </c>
       <c r="C63" s="64">
         <f t="shared" si="2"/>
@@ -10199,7 +10407,7 @@
       </c>
       <c r="B64" s="64">
         <f t="shared" si="1"/>
-        <v>1.9683677764218453E-2</v>
+        <v>3.2259145334480252E-2</v>
       </c>
       <c r="C64" s="64">
         <f t="shared" si="2"/>
@@ -10212,7 +10420,7 @@
       </c>
       <c r="B65" s="64">
         <f t="shared" si="1"/>
-        <v>1.9490895824322143E-2</v>
+        <v>3.207753927489275E-2</v>
       </c>
       <c r="C65" s="64">
         <f t="shared" si="2"/>
@@ -10225,7 +10433,7 @@
       </c>
       <c r="B66" s="64">
         <f t="shared" si="1"/>
-        <v>1.9252522473739295E-2</v>
+        <v>3.1852971459638446E-2</v>
       </c>
       <c r="C66" s="64">
         <f t="shared" si="2"/>
@@ -10238,7 +10446,7 @@
       </c>
       <c r="B67" s="64">
         <f t="shared" si="1"/>
-        <v>1.8957246140313841E-2</v>
+        <v>3.1574772919404664E-2</v>
       </c>
       <c r="C67" s="64">
         <f t="shared" si="2"/>
@@ -10251,7 +10459,7 @@
       </c>
       <c r="B68" s="64">
         <f t="shared" si="1"/>
-        <v>1.859148272799048E-2</v>
+        <v>3.1230125674441868E-2</v>
       </c>
       <c r="C68" s="64">
         <f t="shared" si="2"/>
@@ -10264,7 +10472,7 @@
       </c>
       <c r="B69" s="64">
         <f t="shared" si="1"/>
-        <v>1.8139048623930128E-2</v>
+        <v>3.0803749991778262E-2</v>
       </c>
       <c r="C69" s="64">
         <f t="shared" si="2"/>
@@ -10277,7 +10485,7 @@
       </c>
       <c r="B70" s="64">
         <f t="shared" si="1"/>
-        <v>1.7580884924116733E-2</v>
+        <v>3.0277637494317763E-2</v>
       </c>
       <c r="C70" s="64">
         <f t="shared" si="2"/>
@@ -10290,7 +10498,7 @@
       </c>
       <c r="B71" s="64">
         <f t="shared" si="1"/>
-        <v>1.6894893432710553E-2</v>
+        <v>2.9630886108782794E-2</v>
       </c>
       <c r="C71" s="64">
         <f t="shared" si="2"/>
@@ -10303,7 +10511,7 @@
       </c>
       <c r="B72" s="64">
         <f t="shared" si="1"/>
-        <v>1.6055967446511051E-2</v>
+        <v>2.8839713658810901E-2</v>
       </c>
       <c r="C72" s="64">
         <f t="shared" si="2"/>
@@ -10316,7 +10524,7 @@
       </c>
       <c r="B73" s="64">
         <f t="shared" si="1"/>
-        <v>1.503631913895208E-2</v>
+        <v>2.7877744284005988E-2</v>
       </c>
       <c r="C73" s="64">
         <f t="shared" si="2"/>
@@ -10329,7 +10537,7 @@
       </c>
       <c r="B74" s="64">
         <f t="shared" si="1"/>
-        <v>1.3806209412016438E-2</v>
+        <v>2.6716665431949674E-2</v>
       </c>
       <c r="C74" s="64">
         <f t="shared" si="2"/>
@@ -10342,7 +10550,7 @@
       </c>
       <c r="B75" s="64">
         <f t="shared" si="1"/>
-        <v>1.2335157995106044E-2</v>
+        <v>2.532732668498941E-2</v>
       </c>
       <c r="C75" s="64">
         <f t="shared" si="2"/>
@@ -10355,7 +10563,7 @@
       </c>
       <c r="B76" s="64">
         <f t="shared" si="1"/>
-        <v>1.059362973993507E-2</v>
+        <v>2.3681274978059403E-2</v>
       </c>
       <c r="C76" s="64">
         <f t="shared" si="2"/>
@@ -10368,7 +10576,7 @@
       </c>
       <c r="B77" s="64">
         <f t="shared" si="1"/>
-        <v>8.5550398269848369E-3</v>
+        <v>2.1752577334341151E-2</v>
       </c>
       <c r="C77" s="64">
         <f t="shared" si="2"/>
@@ -10381,7 +10589,7 @@
       </c>
       <c r="B78" s="64">
         <f t="shared" si="1"/>
-        <v>6.1976982814282806E-3</v>
+        <v>1.9519574225990561E-2</v>
       </c>
       <c r="C78" s="64">
         <f t="shared" si="2"/>
@@ -10394,7 +10602,7 @@
       </c>
       <c r="B79" s="64">
         <f t="shared" si="1"/>
-        <v>3.5060654213823097E-3</v>
+        <v>1.6965973789974383E-2</v>
       </c>
       <c r="C79" s="64">
         <f t="shared" si="2"/>
@@ -10407,11 +10615,11 @@
       </c>
       <c r="B80" s="64">
         <f t="shared" si="1"/>
-        <v>4.705083533996436E-4</v>
+        <v>1.4080526789693596E-2</v>
       </c>
       <c r="C80" s="64">
         <f t="shared" si="2"/>
-        <v>7.0138967253152611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -10420,7 +10628,7 @@
       </c>
       <c r="B81" s="64">
         <f t="shared" si="1"/>
-        <v>-2.9152414741727248E-3</v>
+        <v>1.0854530162518642E-2</v>
       </c>
       <c r="C81" s="64">
         <f t="shared" si="2"/>
@@ -10433,7 +10641,7 @@
       </c>
       <c r="B82" s="64">
         <f t="shared" ref="B82:B100" si="3">pH_SID + pH_NT*(10^-A82)/((10^-A82)+Ka_NH4) + (10^-A82) - (pH_PT*Ka1p*(10^-A82)^2 + 2*pH_PT*Ka1p*Ka2p*(10^-A82) + 3*pH_PT*Ka1p*Ka2p*Ka3p)/((10^-A82)^3 + Ka1p*(10^-A82)^2 + Ka1p*Ka2p*(10^-A82) + Ka1p*Ka2p*Ka3p) - Ka1c*CO2aqc/(10^-A82) - 2*Ka1c*Ka2c*CO2aqc/(10^-A82)^2 - Kw_w/(10^-A82)</f>
-        <v>-6.659438935895547E-3</v>
+        <v>7.276676554452138E-3</v>
       </c>
       <c r="C82" s="64">
         <f t="shared" ref="C82:C99" si="4">IF(AND(B82&gt;=0,B83&lt;0),A82+0.1*B82/(B82-B83),0)</f>
@@ -10446,11 +10654,11 @@
       </c>
       <c r="B83" s="64">
         <f t="shared" si="3"/>
-        <v>-1.0780453391272093E-2</v>
+        <v>3.3252688428751227E-3</v>
       </c>
       <c r="C83" s="64">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.3761471820171503</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -10459,7 +10667,7 @@
       </c>
       <c r="B84" s="64">
         <f t="shared" si="3"/>
-        <v>-1.5317047274339206E-2</v>
+        <v>-1.0416279414683588E-3</v>
       </c>
       <c r="C84" s="64">
         <f t="shared" si="4"/>
@@ -10472,7 +10680,7 @@
       </c>
       <c r="B85" s="64">
         <f t="shared" si="3"/>
-        <v>-2.0339810546031352E-2</v>
+        <v>-5.8971860782859728E-3</v>
       </c>
       <c r="C85" s="64">
         <f t="shared" si="4"/>
@@ -10485,7 +10693,7 @@
       </c>
       <c r="B86" s="64">
         <f t="shared" si="3"/>
-        <v>-2.5962833613778116E-2</v>
+        <v>-1.1357132390000149E-2</v>
       </c>
       <c r="C86" s="64">
         <f t="shared" si="4"/>
@@ -10498,7 +10706,7 @@
       </c>
       <c r="B87" s="64">
         <f t="shared" si="3"/>
-        <v>-3.2355230637624466E-2</v>
+        <v>-1.7591051221532129E-2</v>
       </c>
       <c r="C87" s="64">
         <f t="shared" si="4"/>
@@ -10511,7 +10719,7 @@
       </c>
       <c r="B88" s="64">
         <f t="shared" si="3"/>
-        <v>-3.9752906997736523E-2</v>
+        <v>-2.4834081383202963E-2</v>
       </c>
       <c r="C88" s="64">
         <f t="shared" si="4"/>
@@ -10524,7 +10732,7 @@
       </c>
       <c r="B89" s="64">
         <f t="shared" si="3"/>
-        <v>-4.8471734024719042E-2</v>
+        <v>-3.3400148091886857E-2</v>
       </c>
       <c r="C89" s="64">
         <f t="shared" si="4"/>
@@ -10537,7 +10745,7 @@
       </c>
       <c r="B90" s="64">
         <f t="shared" si="3"/>
-        <v>-5.8923885427503334E-2</v>
+        <v>-4.3698443776948967E-2</v>
       </c>
       <c r="C90" s="64">
         <f t="shared" si="4"/>
@@ -10550,7 +10758,7 @@
       </c>
       <c r="B91" s="64">
         <f t="shared" si="3"/>
-        <v>-7.1639511319352173E-2</v>
+        <v>-5.6255294638319062E-2</v>
       </c>
       <c r="C91" s="64">
         <f t="shared" si="4"/>
@@ -10563,7 +10771,7 @@
       </c>
       <c r="B92" s="64">
         <f t="shared" si="3"/>
-        <v>-8.7296326026057247E-2</v>
+        <v>-7.1743965497692963E-2</v>
       </c>
       <c r="C92" s="64">
         <f t="shared" si="4"/>
@@ -10576,7 +10784,7 @@
       </c>
       <c r="B93" s="64">
         <f t="shared" si="3"/>
-        <v>-0.1067602794936845</v>
+        <v>-9.1025569288744251E-2</v>
       </c>
       <c r="C93" s="64">
         <f t="shared" si="4"/>
@@ -10589,7 +10797,7 @@
       </c>
       <c r="B94" s="64">
         <f t="shared" si="3"/>
-        <v>-0.13114150219427442</v>
+        <v>-0.11520528483710941</v>
       </c>
       <c r="C94" s="64">
         <f t="shared" si="4"/>
@@ -10602,7 +10810,7 @@
       </c>
       <c r="B95" s="64">
         <f t="shared" si="3"/>
-        <v>-0.16187141848680417</v>
+        <v>-0.14570980052831864</v>
       </c>
       <c r="C95" s="64">
         <f t="shared" si="4"/>
@@ -10615,7 +10823,7 @@
       </c>
       <c r="B96" s="64">
         <f t="shared" si="3"/>
-        <v>-0.20080965054365266</v>
+        <v>-0.18439462545018237</v>
       </c>
       <c r="C96" s="64">
         <f t="shared" si="4"/>
@@ -10628,7 +10836,7 @@
       </c>
       <c r="B97" s="64">
         <f t="shared" si="3"/>
-        <v>-0.25039358543571821</v>
+        <v>-0.23369414228106924</v>
       </c>
       <c r="C97" s="64">
         <f t="shared" si="4"/>
@@ -10641,7 +10849,7 @@
       </c>
       <c r="B98" s="64">
         <f t="shared" si="3"/>
-        <v>-0.31385003445265258</v>
+        <v>-0.29683379986713238</v>
       </c>
       <c r="C98" s="64">
         <f t="shared" si="4"/>
@@ -10654,7 +10862,7 @@
       </c>
       <c r="B99" s="64">
         <f t="shared" si="3"/>
-        <v>-0.39549850835234002</v>
+        <v>-0.3781338949228632</v>
       </c>
       <c r="C99" s="64">
         <f t="shared" si="4"/>
@@ -10667,7 +10875,7 @@
       </c>
       <c r="B100" s="64">
         <f t="shared" si="3"/>
-        <v>-0.50119120576268095</v>
+        <v>-0.48344992527027159</v>
       </c>
       <c r="C100" s="64">
         <f>0</f>
@@ -10707,7 +10915,7 @@
       </c>
       <c r="D103" s="62">
         <f>IF(n_cross=1,SUM(C50:C100),NA())</f>
-        <v>7.0138967253152611</v>
+        <v>7.3761471820171503</v>
       </c>
       <c r="E103" s="51" t="s">
         <v>968</v>
@@ -10728,7 +10936,7 @@
       </c>
       <c r="D104" s="62">
         <f>1/(1+10^(pH_op-pKa_HOCl))</f>
-        <v>0.77054613735518007</v>
+        <v>0.59321812496000326</v>
       </c>
       <c r="E104" s="51" t="s">
         <v>973</v>
@@ -10814,8 +11022,8 @@
         <v>983</v>
       </c>
       <c r="D109" s="64" t="str">
-        <f>IF(C_eff&lt;Cl_onset,"negligible free chlorine ("&amp;TEXT(C_eff,"0.00")&amp;" mg/L &lt; onset)",IF(C_eff&lt;Cl_kill,"MILD sub-lethal penalty: "&amp;TEXT(C_eff,"0.00")&amp;" mg/L (chloride costs lag/growth — Sydow 2017; chloride-free avoids it)","SEVERE free chlorine: "&amp;TEXT(C_eff,"0.0")&amp;" mg/L → biofilm/electrode damage (Baek 2021)"))</f>
-        <v>negligible free chlorine (0.00 mg/L &lt; onset)</v>
+        <f>IF(C_eff&lt;Cl_onset,"negligible free chlorine ("&amp;TEXT(C_eff,"0.00")&amp;" mg/L &lt; onset); does NOT account for the Exp-2 death - see metal_flag",IF(C_eff&lt;Cl_kill,"sub-lethal "&amp;TEXT(C_eff,"0.00")&amp;" mg/L (band "&amp;TEXT(C_eff_lo,"0.00")&amp;"-"&amp;TEXT(C_eff_hi,"0.00")&amp;"); chloride-pool-bounded, cannot reach the kill threshold in this medium; does NOT explain the death - see metal_flag","SEVERE free chlorine: "&amp;TEXT(C_eff,"0.0")&amp;" mg/L biofilm/electrode damage (Baek 2021)"))</f>
+        <v>sub-lethal 0.38 mg/L (band 0.01-0.53); chloride-pool-bounded, cannot reach the kill threshold in this medium; does NOT explain the death - see metal_flag</v>
       </c>
       <c r="E109" s="51" t="s">
         <v>1166</v>
@@ -10918,7 +11126,7 @@
       </c>
       <c r="D125" s="62">
         <f>pH_Cl*pH_fHOCl*52460</f>
-        <v>0</v>
+        <v>5.6082578546407955</v>
       </c>
       <c r="E125" s="51" t="s">
         <v>1091</v>
@@ -11010,7 +11218,7 @@
       </c>
       <c r="D132" s="62">
         <f>Fcc*km_Cl*(pH_Cl/1000)*A_anode</f>
-        <v>0</v>
+        <v>2.6081816215534336E-4</v>
       </c>
       <c r="E132" s="51" t="s">
         <v>1115</v>
@@ -11028,7 +11236,7 @@
       </c>
       <c r="D133" s="62">
         <f>MIN(I_Cl_FE,I_Cl_mt)</f>
-        <v>0</v>
+        <v>2.6081816215534336E-4</v>
       </c>
       <c r="E133" s="51" t="s">
         <v>1118</v>
@@ -11045,8 +11253,8 @@
         <v>1121</v>
       </c>
       <c r="D134" s="62">
-        <f>I_Cl/(2*Fcc*VLc)</f>
-        <v>0</v>
+        <f>I_Cl/(n_e_Cl*Fcc*VLc)</f>
+        <v>1.8021265092809519E-7</v>
       </c>
       <c r="E134" s="51" t="s">
         <v>1122</v>
@@ -11064,7 +11272,7 @@
       </c>
       <c r="D135" s="62">
         <f>pH_NT*14007</f>
-        <v>199.91828363856516</v>
+        <v>99.641138186771613</v>
       </c>
       <c r="E135" s="51" t="s">
         <v>1126</v>
@@ -11116,7 +11324,7 @@
       </c>
       <c r="D138" s="62">
         <f>pH_NT/(1+10^(pKa_NH4-pH_op))</f>
-        <v>8.239289743160408E-5</v>
+        <v>9.3858256339933826E-5</v>
       </c>
       <c r="E138" s="51" t="s">
         <v>1137</v>
@@ -11134,7 +11342,7 @@
       </c>
       <c r="D139" s="62">
         <f>P_HOCl/(k1_NH2Cl*NH3_free)</f>
-        <v>0</v>
+        <v>4.5715503040133623E-10</v>
       </c>
       <c r="E139" s="51" t="s">
         <v>1140</v>
@@ -11152,7 +11360,7 @@
       </c>
       <c r="D140" s="62">
         <f>HOCl_ss*52460</f>
-        <v>0</v>
+        <v>2.3982352894854098E-5</v>
       </c>
       <c r="E140" s="51" t="s">
         <v>1143</v>
@@ -11203,8 +11411,8 @@
         <v>1125</v>
       </c>
       <c r="D143" s="62">
-        <f>MIN(P_HOCl*tau_NH2Cl*3600*52460,5.06*NH3_N)</f>
-        <v>0</v>
+        <f>MIN(P_HOCl*tau_NH2Cl*3600*52460,5.06*NH3_N,Cl_pool_mgL)</f>
+        <v>9.4539556676878718</v>
       </c>
       <c r="E143" s="51" t="s">
         <v>1153</v>
@@ -11238,8 +11446,8 @@
         <v>1125</v>
       </c>
       <c r="D145" s="62">
-        <f>f_local*pH_fHOCl*HOCl_ss_mgL+NH2Cl_mgL/R_chloramine</f>
-        <v>0</v>
+        <f>f_local*HOCl_ss_mgL+NH2Cl_mgL/R_chloramine</f>
+        <v>0.37839805023646339</v>
       </c>
       <c r="E145" s="51" t="s">
         <v>1159</v>
@@ -11277,6 +11485,284 @@
       </c>
       <c r="E147" s="51" t="s">
         <v>1165</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+      <c r="A148" s="17" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B148" s="18" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C148" s="19" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D148" s="62">
+        <f>IF(I_Cl_mt&lt;=I_Cl_FE,1,2)</f>
+        <v>1</v>
+      </c>
+      <c r="E148" s="51" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="36" x14ac:dyDescent="0.2">
+      <c r="A149" s="17" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B149" s="18" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D149" s="62">
+        <f>pH_Cl*52460</f>
+        <v>9.4539556676878718</v>
+      </c>
+      <c r="E149" s="51" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+      <c r="A150" s="17" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B150" s="18" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C150" s="19" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D150" s="52">
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="E150" s="75" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+      <c r="A151" s="17" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B151" s="18" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D151" s="52">
+        <v>5</v>
+      </c>
+      <c r="E151" s="75" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+      <c r="A152" s="17" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B152" s="18" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C152" s="19" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D152" s="52">
+        <v>18</v>
+      </c>
+      <c r="E152" s="75" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" s="17" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B153" s="18" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C153" s="19" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D153" s="52">
+        <v>70</v>
+      </c>
+      <c r="E153" s="75" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A154" s="17" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B154" s="18" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C154" s="19" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D154" s="62">
+        <f>MIN(P_HOCl*tau_NH2Cl_lo*3600*52460,5.06*NH3_N,Cl_pool_mgL)</f>
+        <v>0.56723734006127247</v>
+      </c>
+      <c r="E154" s="51" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155" s="17" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B155" s="18" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C155" s="19" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D155" s="62">
+        <f>MIN(P_HOCl*tau_NH2Cl_hi*3600*52460,5.06*NH3_N,Cl_pool_mgL)</f>
+        <v>9.4539556676878718</v>
+      </c>
+      <c r="E155" s="51" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156" s="17" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B156" s="18" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C156" s="19" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D156" s="62">
+        <f>f_local*HOCl_ss_mgL+NH2Cl_lo/R_chloramine_hi</f>
+        <v>8.3432141012524334E-3</v>
+      </c>
+      <c r="E156" s="51" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+      <c r="A157" s="17" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B157" s="18" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C157" s="19" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D157" s="62">
+        <f>f_local*HOCl_ss_mgL+NH2Cl_hi/R_chloramine_lo</f>
+        <v>0.52545958284494143</v>
+      </c>
+      <c r="E157" s="51" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+      <c r="A158" s="17" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B158" s="18" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C158" s="19" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D158" s="52"/>
+      <c r="E158" s="57" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A159" s="17" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B159" s="18" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C159" s="19" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D159" s="52">
+        <v>63.55</v>
+      </c>
+      <c r="E159" s="51" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A160" s="17" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B160" s="18" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C160" s="19" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D160" s="52">
+        <v>2</v>
+      </c>
+      <c r="E160" s="51" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+      <c r="A161" s="17" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B161" s="18" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C161" s="19" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D161" s="62" t="e">
+        <f>IF(ISNUMBER(corr_I_frac),corr_I_frac*Iappc/(metal_z*Fcc)*metal_MW*1000*3600/VLc,NA())</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E161" s="57" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+      <c r="A162" s="17" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B162" s="18" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C162" s="19" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D162" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="E162" s="51" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A163" s="17" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B163" s="18" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C163" s="19" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D163" s="64" t="str">
+        <f>IF(ISNUMBER(corr_I_frac),"metal leach "&amp;TEXT(metal_leach_rate,"0.00")&amp;" mg/L/h vs ~"&amp;TEXT(metal_tox_thresh,"0.0")&amp;" mg/L bactericidal threshold","DATA GAP - measure dissolved Cu/Ni/Fe in spent medium; the green anode implicates electrode corrosion / metal leaching as the unmodelled prime suspect for the Exp-2 death")</f>
+        <v>DATA GAP - measure dissolved Cu/Ni/Fe in spent medium; the green anode implicates electrode corrosion / metal leaching as the unmodelled prime suspect for the Exp-2 death</v>
+      </c>
+      <c r="E163" s="57" t="s">
+        <v>1322</v>
       </c>
     </row>
   </sheetData>
@@ -11407,7 +11893,7 @@
       <c r="C7" s="20"/>
       <c r="D7" s="38" t="str">
         <f>Summary!$D$4</f>
-        <v>Cupriavidus necator</v>
+        <v>UdG (mixed)</v>
       </c>
       <c r="E7" s="23" t="str">
         <f>HYPERLINK("#Summary!D5","→ Summary")</f>
@@ -11425,7 +11911,7 @@
       <c r="C8" s="20"/>
       <c r="D8" s="38" t="str">
         <f>Summary!$D$4</f>
-        <v>Cupriavidus necator</v>
+        <v>UdG (mixed)</v>
       </c>
       <c r="E8" s="23" t="str">
         <f>HYPERLINK("#Summary!D5","→ Summary")</f>
@@ -12121,9 +12607,9 @@
       <c r="C46" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="D46" s="24">
+      <c r="D46" s="24" t="e">
         <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE),NA())</f>
-        <v>2.6</v>
+        <v>#N/A</v>
       </c>
       <c r="E46" s="20"/>
       <c r="F46" s="20"/>
@@ -12138,9 +12624,9 @@
       <c r="C47" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="D47" s="24">
+      <c r="D47" s="24" t="e">
         <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE),NA())</f>
-        <v>3</v>
+        <v>#N/A</v>
       </c>
       <c r="E47" s="20"/>
       <c r="F47" s="20"/>
@@ -12155,9 +12641,9 @@
       <c r="C48" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="D48" s="24">
+      <c r="D48" s="24" t="e">
         <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE),NA())</f>
-        <v>11.5</v>
+        <v>#N/A</v>
       </c>
       <c r="E48" s="20"/>
       <c r="F48" s="20"/>
@@ -12766,9 +13252,9 @@
         <v>521</v>
       </c>
       <c r="C22" s="20"/>
-      <c r="D22" s="26">
+      <c r="D22" s="26" t="e">
         <f>Biology!$D$46</f>
-        <v>2.6</v>
+        <v>#N/A</v>
       </c>
       <c r="E22" s="23" t="str">
         <f>HYPERLINK("#Biology!D46","→ Biology")</f>
@@ -12784,9 +13270,9 @@
         <v>523</v>
       </c>
       <c r="C23" s="20"/>
-      <c r="D23" s="26">
+      <c r="D23" s="26" t="e">
         <f>Biology!$D$47</f>
-        <v>3</v>
+        <v>#N/A</v>
       </c>
       <c r="E23" s="23" t="str">
         <f>HYPERLINK("#Biology!D47","→ Biology")</f>
@@ -12802,9 +13288,9 @@
         <v>525</v>
       </c>
       <c r="C24" s="20"/>
-      <c r="D24" s="26">
+      <c r="D24" s="26" t="e">
         <f>Biology!$D$48</f>
-        <v>11.5</v>
+        <v>#N/A</v>
       </c>
       <c r="E24" s="23" t="str">
         <f>HYPERLINK("#Biology!D48","→ Biology")</f>
@@ -13912,7 +14398,7 @@
       </c>
       <c r="D84" s="80">
         <f>IF(AND(ISNUMBER(DO_opt),ISNUMBER(DO_toxic)),DO_opt/DO_toxic,0.5)</f>
-        <v>0.22608695652173913</v>
+        <v>0.5</v>
       </c>
       <c r="E84" s="68" t="s">
         <v>737</v>
@@ -13968,7 +14454,7 @@
       </c>
       <c r="D87" s="48">
         <f>O2_src_guard/(target_DO_frac*(O2_ceil_Pa/P_atm))/(nCO2_rate*3600)</f>
-        <v>1.5969906352431712E-3</v>
+        <v>7.2211750463169471E-4</v>
       </c>
       <c r="E87" s="101" t="s">
         <v>1095</v>
@@ -13987,7 +14473,7 @@
       </c>
       <c r="D88" s="48">
         <f>MAX(duty_carbon,duty_O2vent)</f>
-        <v>1.5969906352431712E-3</v>
+        <v>7.2211750463169471E-4</v>
       </c>
       <c r="E88" s="69" t="s">
         <v>1027</v>
@@ -14006,7 +14492,7 @@
       </c>
       <c r="D89" s="48">
         <f>target_DO_frac*O2_ceil_C*(V_charge/1000000)/O2_src_guard*60</f>
-        <v>1.3984393971616449</v>
+        <v>3.0927025129536387</v>
       </c>
       <c r="E89" s="101" t="s">
         <v>1094</v>
@@ -14369,7 +14855,7 @@
       <c r="C109" s="20"/>
       <c r="D109" s="24" t="str">
         <f>IF(ISNUMBER(DO_opt),IF(DO_ss&lt;=DO_opt,"at/under optimum",IF(DO_ss&lt;DO_impair,"above optimum, under impairment","OVER IMPAIRMENT - surface strip insufficient")),"organism optimum unknown")</f>
-        <v>at/under optimum</v>
+        <v>organism optimum unknown</v>
       </c>
       <c r="E109" s="20"/>
       <c r="F109" s="20"/>
@@ -14433,7 +14919,7 @@
       <c r="C113" s="20"/>
       <c r="D113" s="24" t="str">
         <f>IF(AND(ISNUMBER(DO_ss),ISNUMBER(DO_impair)),IF(DO_ss&lt;DO_impair,"Surface stripping holds DO under impairment - sparge is CARBON-limited (long interval); the O2-limited interval is the conservative fallback until kL_surf is measured","Surface stripping insufficient - sparge must vent O2 - use the O2-limited interval"),"organism DO unknown")</f>
-        <v>Surface stripping holds DO under impairment - sparge is CARBON-limited (long interval); the O2-limited interval is the conservative fallback until kL_surf is measured</v>
+        <v>organism DO unknown</v>
       </c>
       <c r="E113" s="83" t="s">
         <v>807</v>
@@ -14724,9 +15210,9 @@
       <c r="C131" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="D131" s="24">
+      <c r="D131" s="24" t="e">
         <f>IF(ISNUMBER(DO_impair),O2_excess*32/(DO_impair*3600*(V_charge/1000000)*a_surf),NA())</f>
-        <v>1.2203573592429917E-4</v>
+        <v>#N/A</v>
       </c>
       <c r="E131" s="107" t="s">
         <v>846</v>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Biology" sheetId="4" r:id="rId5"/>
     <sheet name="Mass Transfer" sheetId="5" r:id="rId6"/>
     <sheet name="CO2 flows" sheetId="6" r:id="rId7"/>
+    <sheet name="Calibrations" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="A_anode" localSheetId="3">Chemistry!$D$130</definedName>
@@ -424,8 +425,26 @@
     <definedName name="z_e_H2" localSheetId="2">Electrochemistry!$D$16</definedName>
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$17</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
+    <definedName name="cal_gerrit_slope">Calibrations!$D$16</definedName>
+    <definedName name="cal_gerrit_int">Calibrations!$D$17</definedName>
+    <definedName name="cal_etaF">Calibrations!$D$31</definedName>
+    <definedName name="cal_etaF_OER">Calibrations!$D$32</definedName>
+    <definedName name="cal_kLa">Calibrations!$D$46</definedName>
+    <definedName name="cal_flow">Calibrations!$D$60</definedName>
+    <definedName name="cal_Vtot">Calibrations!$D$74</definedName>
+    <definedName name="cal_Dint">Calibrations!$D$75</definedName>
+    <definedName name="cal_sinter">Calibrations!$D$89</definedName>
+    <definedName name="cal_DO_min">Calibrations!$D$103</definedName>
+    <definedName name="cal_DO_opt">Calibrations!$D$104</definedName>
+    <definedName name="cal_DO_impair">Calibrations!$D$105</definedName>
+    <definedName name="cal_DO_toxic">Calibrations!$D$106</definedName>
+    <definedName name="cal_knall_H2">Calibrations!$D$120</definedName>
+    <definedName name="cal_knall_O2">Calibrations!$D$121</definedName>
+    <definedName name="cal_knall_CO2">Calibrations!$D$122</definedName>
+    <definedName name="cal_j_opt">Calibrations!$D$136</definedName>
+    <definedName name="cal_j_ceiling">Calibrations!$D$137</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -7983,7 +8002,7 @@
         <v>146</v>
       </c>
       <c r="D22" s="44">
-        <f>VLOOKUP(rx_ver,$A$84:$I$87,4,FALSE)</f>
+        <f>IFERROR(cal_Dint,VLOOKUP(rx_ver,$A$84:$I$87,4,FALSE))</f>
         <v>55</v>
       </c>
       <c r="E22" s="101" t="s">
@@ -8027,7 +8046,7 @@
         <v>57</v>
       </c>
       <c r="D24" s="44">
-        <f>VLOOKUP(rx_ver,$A$84:$I$87,6,FALSE)</f>
+        <f>IFERROR(cal_Vtot,VLOOKUP(rx_ver,$A$84:$I$87,6,FALSE))</f>
         <v>20</v>
       </c>
       <c r="E24" s="101" t="s">
@@ -9487,6 +9506,7 @@
         <v>321</v>
       </c>
       <c r="D11" s="50">
+        <f>IFERROR(cal_gerrit_slope,1.03)</f>
         <v>1.03</v>
       </c>
       <c r="E11" s="115" t="s">
@@ -9508,6 +9528,7 @@
         <v>325</v>
       </c>
       <c r="D12" s="54">
+        <f>IFERROR(cal_gerrit_int,2.6)</f>
         <v>2.6</v>
       </c>
       <c r="E12" s="115" t="s">
@@ -9634,6 +9655,7 @@
         <v>135</v>
       </c>
       <c r="D18" s="114">
+        <f>IFERROR(cal_etaF,1)</f>
         <v>1</v>
       </c>
       <c r="E18" s="57" t="s">
@@ -9809,6 +9831,7 @@
         <v>135</v>
       </c>
       <c r="D26" s="114">
+        <f>IFERROR(cal_etaF_OER,1)</f>
         <v>1</v>
       </c>
       <c r="E26" s="122" t="s">
@@ -9925,7 +9948,7 @@
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="24">
-        <f>IF(ISNUMBER(VLOOKUP(electrode_sel,$A$35:$I$38,5,FALSE)),VLOOKUP(electrode_sel,$A$35:$I$38,5,FALSE),0)</f>
+        <f>IFERROR(cal_sinter,IF(ISNUMBER(VLOOKUP(electrode_sel,$A$35:$I$38,5,FALSE)),VLOOKUP(electrode_sel,$A$35:$I$38,5,FALSE),0))</f>
         <v>0</v>
       </c>
       <c r="E32" s="107" t="s">
@@ -10462,7 +10485,7 @@
         <v>1326</v>
       </c>
       <c r="D56" s="48">
-        <f>IFERROR(VLOOKUP(Summary!$D$4,$A$66:$E$71,2,FALSE),j_opt_default)</f>
+        <f>IFERROR(cal_j_opt,IFERROR(VLOOKUP(Summary!$D$4,$A$66:$E$71,2,FALSE),j_opt_default))</f>
         <v>2.14</v>
       </c>
       <c r="E56" s="101" t="s">
@@ -10480,7 +10503,7 @@
         <v>1326</v>
       </c>
       <c r="D57" s="48">
-        <f>IFERROR(VLOOKUP(Summary!$D$4,$A$66:$E$71,3,FALSE),j_ceiling_default)</f>
+        <f>IFERROR(cal_j_ceiling,IFERROR(VLOOKUP(Summary!$D$4,$A$66:$E$71,3,FALSE),j_ceiling_default))</f>
         <v>4.29</v>
       </c>
       <c r="E57" s="101" t="s">
@@ -13291,6 +13314,7 @@
         <v>135</v>
       </c>
       <c r="D10" s="111">
+        <f>IFERROR(cal_knall_H2,6)</f>
         <v>6</v>
       </c>
       <c r="E10" s="61" t="s">
@@ -13309,6 +13333,7 @@
         <v>135</v>
       </c>
       <c r="D11" s="111">
+        <f>IFERROR(cal_knall_O2,2)</f>
         <v>2</v>
       </c>
       <c r="E11" s="61" t="s">
@@ -13327,6 +13352,7 @@
         <v>135</v>
       </c>
       <c r="D12" s="111">
+        <f>IFERROR(cal_knall_CO2,1)</f>
         <v>1</v>
       </c>
       <c r="E12" s="61" t="s">
@@ -13943,8 +13969,8 @@
       <c r="C45" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="71" t="e">
-        <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE),NA())</f>
+      <c r="D45" s="71">
+        <f>IFERROR(cal_DO_min,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE),NA()))</f>
         <v>#N/A</v>
       </c>
       <c r="E45" s="20"/>
@@ -13960,8 +13986,8 @@
       <c r="C46" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D46" s="24" t="e">
-        <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE),NA())</f>
+      <c r="D46" s="24">
+        <f>IFERROR(cal_DO_opt,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE),NA()))</f>
         <v>#N/A</v>
       </c>
       <c r="E46" s="20"/>
@@ -13977,8 +14003,8 @@
       <c r="C47" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D47" s="24" t="e">
-        <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE),NA())</f>
+      <c r="D47" s="24">
+        <f>IFERROR(cal_DO_impair,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE),NA()))</f>
         <v>#N/A</v>
       </c>
       <c r="E47" s="20"/>
@@ -13994,8 +14020,8 @@
       <c r="C48" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D48" s="24" t="e">
-        <f>IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE),NA())</f>
+      <c r="D48" s="24">
+        <f>IFERROR(cal_DO_toxic,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE),NA()))</f>
         <v>#N/A</v>
       </c>
       <c r="E48" s="20"/>
@@ -15996,6 +16022,7 @@
         <v>510</v>
       </c>
       <c r="D97" s="124">
+        <f>IFERROR(cal_kLa,0)</f>
         <v>0</v>
       </c>
       <c r="E97" s="69" t="s">
@@ -19462,4 +19489,1902 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:N140"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CALIBRATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fill the white cells only: Researcher, Date, the key (Reactor or Organism) and the raw measurements. Grey cells are computed automatically. Set Include to y for rows the model should use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The value in use for each calibration follows the rule stated under its heading. If no rows are included yet, the model falls back to its built-in default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GERRIT CURRENT  (electrolysis current law)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use: least-squares fit of current vs intensity, averaged across all included runs for the active reactor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Researcher</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reactor</t>
+        </is>
+      </c>
+      <c r="D7" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intensity</t>
+        </is>
+      </c>
+      <c r="E7" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current</t>
+        </is>
+      </c>
+      <c r="F7" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type (auto)</t>
+        </is>
+      </c>
+      <c r="G7" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include?</t>
+        </is>
+      </c>
+      <c r="H7" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="53"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="48">
+        <f>IFERROR(VLOOKUP(C8,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="53"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="48">
+        <f>IFERROR(VLOOKUP(C9,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="53"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="48">
+        <f>IFERROR(VLOOKUP(C10,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="53"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="48">
+        <f>IFERROR(VLOOKUP(C11,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="53"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="48">
+        <f>IFERROR(VLOOKUP(C12,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="53"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="48">
+        <f>IFERROR(VLOOKUP(C13,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="53"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="48">
+        <f>IFERROR(VLOOKUP(C14,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="53"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="48">
+        <f>IFERROR(VLOOKUP(C15,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - slope</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mA/%</t>
+        </is>
+      </c>
+      <c r="D16" s="48">
+        <f>(COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*E8:E15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(E8:E15,C8:C15,Summary!$D$2,G8:G15,"y"))/(COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*D8:D15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - intercept</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mA</t>
+        </is>
+      </c>
+      <c r="D17" s="48">
+        <f>(SUMIFS(E8:E15,C8:C15,Summary!$D$2,G8:G15,"y")-((COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*E8:E15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(E8:E15,C8:C15,Summary!$D$2,G8:G15,"y"))/(COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*D8:D15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")))*SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y"))/COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FARADAIC EFFICIENCY  (cathodic etaF, anodic etaF_OER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use: average of the included runs for the active reactor, taken separately for the H2 (cathode) and O2 (anode) electrodes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Researcher</t>
+        </is>
+      </c>
+      <c r="B22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="C22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reactor</t>
+        </is>
+      </c>
+      <c r="D22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Charge Q</t>
+        </is>
+      </c>
+      <c r="E22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas volume</t>
+        </is>
+      </c>
+      <c r="F22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp</t>
+        </is>
+      </c>
+      <c r="G22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pressure</t>
+        </is>
+      </c>
+      <c r="H22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrode</t>
+        </is>
+      </c>
+      <c r="I22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etaF (computed)</t>
+        </is>
+      </c>
+      <c r="J22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type (auto)</t>
+        </is>
+      </c>
+      <c r="K22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include?</t>
+        </is>
+      </c>
+      <c r="L22" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="53"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="124"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="124"/>
+      <c r="I23" s="48">
+        <f>IFERROR((G23*(E23/1000000)/(8.314*(F23+273.15)))/(D23/(IF(H23="H2",2,4)*96485)),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="48">
+        <f>IFERROR(VLOOKUP(C23,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="53"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="124"/>
+      <c r="F24" s="124"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="124"/>
+      <c r="I24" s="48">
+        <f>IFERROR((G24*(E24/1000000)/(8.314*(F24+273.15)))/(D24/(IF(H24="H2",2,4)*96485)),"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="48">
+        <f>IFERROR(VLOOKUP(C24,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="53"/>
+      <c r="L24" s="53"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="53"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="124"/>
+      <c r="H25" s="124"/>
+      <c r="I25" s="48">
+        <f>IFERROR((G25*(E25/1000000)/(8.314*(F25+273.15)))/(D25/(IF(H25="H2",2,4)*96485)),"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="48">
+        <f>IFERROR(VLOOKUP(C25,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="53"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="124"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="124"/>
+      <c r="I26" s="48">
+        <f>IFERROR((G26*(E26/1000000)/(8.314*(F26+273.15)))/(D26/(IF(H26="H2",2,4)*96485)),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="48">
+        <f>IFERROR(VLOOKUP(C26,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="53"/>
+      <c r="B27" s="124"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="124"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="124"/>
+      <c r="G27" s="124"/>
+      <c r="H27" s="124"/>
+      <c r="I27" s="48">
+        <f>IFERROR((G27*(E27/1000000)/(8.314*(F27+273.15)))/(D27/(IF(H27="H2",2,4)*96485)),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="48">
+        <f>IFERROR(VLOOKUP(C27,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="53"/>
+      <c r="B28" s="124"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="124"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="124"/>
+      <c r="G28" s="124"/>
+      <c r="H28" s="124"/>
+      <c r="I28" s="48">
+        <f>IFERROR((G28*(E28/1000000)/(8.314*(F28+273.15)))/(D28/(IF(H28="H2",2,4)*96485)),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="48">
+        <f>IFERROR(VLOOKUP(C28,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="53"/>
+      <c r="B29" s="124"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="124"/>
+      <c r="E29" s="124"/>
+      <c r="F29" s="124"/>
+      <c r="G29" s="124"/>
+      <c r="H29" s="124"/>
+      <c r="I29" s="48">
+        <f>IFERROR((G29*(E29/1000000)/(8.314*(F29+273.15)))/(D29/(IF(H29="H2",2,4)*96485)),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="48">
+        <f>IFERROR(VLOOKUP(C29,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="53"/>
+      <c r="B30" s="124"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="124"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="124"/>
+      <c r="G30" s="124"/>
+      <c r="H30" s="124"/>
+      <c r="I30" s="48">
+        <f>IFERROR((G30*(E30/1000000)/(8.314*(F30+273.15)))/(D30/(IF(H30="H2",2,4)*96485)),"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="48">
+        <f>IFERROR(VLOOKUP(C30,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="K30" s="53"/>
+      <c r="L30" s="53"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - cathode (H2)</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D31" s="48">
+        <f>AVERAGEIFS(I23:I30,C23:C30,Summary!$D$2,K23:K30,"y",H23:H30,"H2")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - anode (O2)</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D32" s="48">
+        <f>AVERAGEIFS(I23:I30,C23:C30,Summary!$D$2,K23:K30,"y",H23:H30,"O2")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SURFACE kLa  (oxygen surface transfer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use: average of the included kLa runs for the active reactor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Researcher</t>
+        </is>
+      </c>
+      <c r="B37" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="C37" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reactor</t>
+        </is>
+      </c>
+      <c r="D37" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kLa</t>
+        </is>
+      </c>
+      <c r="E37" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type (auto)</t>
+        </is>
+      </c>
+      <c r="F37" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include?</t>
+        </is>
+      </c>
+      <c r="G37" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" s="53"/>
+      <c r="B38" s="124"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="124"/>
+      <c r="E38" s="48">
+        <f>IFERROR(VLOOKUP(C38,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" s="53"/>
+      <c r="B39" s="124"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="124"/>
+      <c r="E39" s="48">
+        <f>IFERROR(VLOOKUP(C39,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40" s="53"/>
+      <c r="B40" s="124"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="124"/>
+      <c r="E40" s="48">
+        <f>IFERROR(VLOOKUP(C40,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A41" s="53"/>
+      <c r="B41" s="124"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="124"/>
+      <c r="E41" s="48">
+        <f>IFERROR(VLOOKUP(C41,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A42" s="53"/>
+      <c r="B42" s="124"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="124"/>
+      <c r="E42" s="48">
+        <f>IFERROR(VLOOKUP(C42,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A43" s="53"/>
+      <c r="B43" s="124"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="124"/>
+      <c r="E43" s="48">
+        <f>IFERROR(VLOOKUP(C43,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A44" s="53"/>
+      <c r="B44" s="124"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="124"/>
+      <c r="E44" s="48">
+        <f>IFERROR(VLOOKUP(C44,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A45" s="53"/>
+      <c r="B45" s="124"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="124"/>
+      <c r="E45" s="48">
+        <f>IFERROR(VLOOKUP(C45,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="53"/>
+      <c r="G45" s="53"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - kLa</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/s</t>
+        </is>
+      </c>
+      <c r="D46" s="48">
+        <f>AVERAGEIFS(D38:D45,C38:C45,Summary!$D$2,F38:F45,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A49" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO2 FLOW  (dosing flow rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A50" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use: the most recent included measurement for the active reactor (a flow rate is a valve/hardware setting, so the latest reading replaces older ones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A51" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Researcher</t>
+        </is>
+      </c>
+      <c r="B51" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="C51" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reactor</t>
+        </is>
+      </c>
+      <c r="D51" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO2 volume</t>
+        </is>
+      </c>
+      <c r="E51" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time</t>
+        </is>
+      </c>
+      <c r="F51" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flow (computed)</t>
+        </is>
+      </c>
+      <c r="G51" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type (auto)</t>
+        </is>
+      </c>
+      <c r="H51" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include?</t>
+        </is>
+      </c>
+      <c r="I51" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A52" s="53"/>
+      <c r="B52" s="124"/>
+      <c r="C52" s="53"/>
+      <c r="D52" s="124"/>
+      <c r="E52" s="124"/>
+      <c r="F52" s="48">
+        <f>IFERROR(D52/E52,"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="48">
+        <f>IFERROR(VLOOKUP(C52,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A53" s="53"/>
+      <c r="B53" s="124"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="124"/>
+      <c r="E53" s="124"/>
+      <c r="F53" s="48">
+        <f>IFERROR(D53/E53,"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="48">
+        <f>IFERROR(VLOOKUP(C53,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="53"/>
+      <c r="I53" s="53"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A54" s="53"/>
+      <c r="B54" s="124"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="124"/>
+      <c r="E54" s="124"/>
+      <c r="F54" s="48">
+        <f>IFERROR(D54/E54,"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="48">
+        <f>IFERROR(VLOOKUP(C54,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A55" s="53"/>
+      <c r="B55" s="124"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="124"/>
+      <c r="E55" s="124"/>
+      <c r="F55" s="48">
+        <f>IFERROR(D55/E55,"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="48">
+        <f>IFERROR(VLOOKUP(C55,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A56" s="53"/>
+      <c r="B56" s="124"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="124"/>
+      <c r="E56" s="124"/>
+      <c r="F56" s="48">
+        <f>IFERROR(D56/E56,"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="48">
+        <f>IFERROR(VLOOKUP(C56,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A57" s="53"/>
+      <c r="B57" s="124"/>
+      <c r="C57" s="53"/>
+      <c r="D57" s="124"/>
+      <c r="E57" s="124"/>
+      <c r="F57" s="48">
+        <f>IFERROR(D57/E57,"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="48">
+        <f>IFERROR(VLOOKUP(C57,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="53"/>
+      <c r="I57" s="53"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A58" s="53"/>
+      <c r="B58" s="124"/>
+      <c r="C58" s="53"/>
+      <c r="D58" s="124"/>
+      <c r="E58" s="124"/>
+      <c r="F58" s="48">
+        <f>IFERROR(D58/E58,"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="48">
+        <f>IFERROR(VLOOKUP(C58,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="53"/>
+      <c r="I58" s="53"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A59" s="53"/>
+      <c r="B59" s="124"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="124"/>
+      <c r="E59" s="124"/>
+      <c r="F59" s="48">
+        <f>IFERROR(D59/E59,"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="48">
+        <f>IFERROR(VLOOKUP(C59,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="53"/>
+      <c r="I59" s="53"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - flow rate</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mL/s</t>
+        </is>
+      </c>
+      <c r="D60" s="48">
+        <f>AVERAGEIFS(F52:F59,C52:C59,Summary!$D$2,H52:H59,"y",B52:B59,MAXIFS(B52:B59,C52:C59,Summary!$D$2,H52:H59,"y"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A63" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIAL GEOMETRY  (true volume &amp; bore depth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A64" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use: average across included vials of the active reactor type (all vials of a type are nominally identical, so averaging improves the estimate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A65" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Researcher</t>
+        </is>
+      </c>
+      <c r="B65" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="C65" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reactor</t>
+        </is>
+      </c>
+      <c r="D65" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Headspace mass</t>
+        </is>
+      </c>
+      <c r="E65" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Body mass</t>
+        </is>
+      </c>
+      <c r="F65" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temp</t>
+        </is>
+      </c>
+      <c r="G65" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V total (computed)</t>
+        </is>
+      </c>
+      <c r="H65" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bore depth (computed)</t>
+        </is>
+      </c>
+      <c r="I65" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type (auto)</t>
+        </is>
+      </c>
+      <c r="J65" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include?</t>
+        </is>
+      </c>
+      <c r="K65" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A66" s="53"/>
+      <c r="B66" s="124"/>
+      <c r="C66" s="53"/>
+      <c r="D66" s="124"/>
+      <c r="E66" s="124"/>
+      <c r="F66" s="124"/>
+      <c r="G66" s="48">
+        <f>IFERROR(E66/(0.99705-0.00028*(F66-25)),"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="48">
+        <f>IFERROR((E66/(0.99705-0.00028*(F66-25)))*1000/Geometry!$D$21,"")</f>
+        <v/>
+      </c>
+      <c r="I66" s="48">
+        <f>IFERROR(VLOOKUP(C66,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J66" s="53"/>
+      <c r="K66" s="53"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A67" s="53"/>
+      <c r="B67" s="124"/>
+      <c r="C67" s="53"/>
+      <c r="D67" s="124"/>
+      <c r="E67" s="124"/>
+      <c r="F67" s="124"/>
+      <c r="G67" s="48">
+        <f>IFERROR(E67/(0.99705-0.00028*(F67-25)),"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="48">
+        <f>IFERROR((E67/(0.99705-0.00028*(F67-25)))*1000/Geometry!$D$21,"")</f>
+        <v/>
+      </c>
+      <c r="I67" s="48">
+        <f>IFERROR(VLOOKUP(C67,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J67" s="53"/>
+      <c r="K67" s="53"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A68" s="53"/>
+      <c r="B68" s="124"/>
+      <c r="C68" s="53"/>
+      <c r="D68" s="124"/>
+      <c r="E68" s="124"/>
+      <c r="F68" s="124"/>
+      <c r="G68" s="48">
+        <f>IFERROR(E68/(0.99705-0.00028*(F68-25)),"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="48">
+        <f>IFERROR((E68/(0.99705-0.00028*(F68-25)))*1000/Geometry!$D$21,"")</f>
+        <v/>
+      </c>
+      <c r="I68" s="48">
+        <f>IFERROR(VLOOKUP(C68,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J68" s="53"/>
+      <c r="K68" s="53"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A69" s="53"/>
+      <c r="B69" s="124"/>
+      <c r="C69" s="53"/>
+      <c r="D69" s="124"/>
+      <c r="E69" s="124"/>
+      <c r="F69" s="124"/>
+      <c r="G69" s="48">
+        <f>IFERROR(E69/(0.99705-0.00028*(F69-25)),"")</f>
+        <v/>
+      </c>
+      <c r="H69" s="48">
+        <f>IFERROR((E69/(0.99705-0.00028*(F69-25)))*1000/Geometry!$D$21,"")</f>
+        <v/>
+      </c>
+      <c r="I69" s="48">
+        <f>IFERROR(VLOOKUP(C69,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J69" s="53"/>
+      <c r="K69" s="53"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A70" s="53"/>
+      <c r="B70" s="124"/>
+      <c r="C70" s="53"/>
+      <c r="D70" s="124"/>
+      <c r="E70" s="124"/>
+      <c r="F70" s="124"/>
+      <c r="G70" s="48">
+        <f>IFERROR(E70/(0.99705-0.00028*(F70-25)),"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="48">
+        <f>IFERROR((E70/(0.99705-0.00028*(F70-25)))*1000/Geometry!$D$21,"")</f>
+        <v/>
+      </c>
+      <c r="I70" s="48">
+        <f>IFERROR(VLOOKUP(C70,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J70" s="53"/>
+      <c r="K70" s="53"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A71" s="53"/>
+      <c r="B71" s="124"/>
+      <c r="C71" s="53"/>
+      <c r="D71" s="124"/>
+      <c r="E71" s="124"/>
+      <c r="F71" s="124"/>
+      <c r="G71" s="48">
+        <f>IFERROR(E71/(0.99705-0.00028*(F71-25)),"")</f>
+        <v/>
+      </c>
+      <c r="H71" s="48">
+        <f>IFERROR((E71/(0.99705-0.00028*(F71-25)))*1000/Geometry!$D$21,"")</f>
+        <v/>
+      </c>
+      <c r="I71" s="48">
+        <f>IFERROR(VLOOKUP(C71,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J71" s="53"/>
+      <c r="K71" s="53"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A72" s="53"/>
+      <c r="B72" s="124"/>
+      <c r="C72" s="53"/>
+      <c r="D72" s="124"/>
+      <c r="E72" s="124"/>
+      <c r="F72" s="124"/>
+      <c r="G72" s="48">
+        <f>IFERROR(E72/(0.99705-0.00028*(F72-25)),"")</f>
+        <v/>
+      </c>
+      <c r="H72" s="48">
+        <f>IFERROR((E72/(0.99705-0.00028*(F72-25)))*1000/Geometry!$D$21,"")</f>
+        <v/>
+      </c>
+      <c r="I72" s="48">
+        <f>IFERROR(VLOOKUP(C72,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J72" s="53"/>
+      <c r="K72" s="53"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A73" s="53"/>
+      <c r="B73" s="124"/>
+      <c r="C73" s="53"/>
+      <c r="D73" s="124"/>
+      <c r="E73" s="124"/>
+      <c r="F73" s="124"/>
+      <c r="G73" s="48">
+        <f>IFERROR(E73/(0.99705-0.00028*(F73-25)),"")</f>
+        <v/>
+      </c>
+      <c r="H73" s="48">
+        <f>IFERROR((E73/(0.99705-0.00028*(F73-25)))*1000/Geometry!$D$21,"")</f>
+        <v/>
+      </c>
+      <c r="I73" s="48">
+        <f>IFERROR(VLOOKUP(C73,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="J73" s="53"/>
+      <c r="K73" s="53"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - total vial volume</t>
+        </is>
+      </c>
+      <c r="C74" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mL</t>
+        </is>
+      </c>
+      <c r="D74" s="48">
+        <f>AVERAGEIFS(G66:G73,I66:I73,Geometry!$D$51,J66:J73,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - usable depth</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mm</t>
+        </is>
+      </c>
+      <c r="D75" s="48">
+        <f>AVERAGEIFS(H66:H73,I66:I73,Geometry!$D$51,J66:J73,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A78" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SINTER POROSITY  (sparger frit grade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A79" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use: the most recent included measurement for the active reactor (the fitted frit is hardware, so the latest reading replaces older ones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A80" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Researcher</t>
+        </is>
+      </c>
+      <c r="B80" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="C80" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reactor</t>
+        </is>
+      </c>
+      <c r="D80" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bubble-point</t>
+        </is>
+      </c>
+      <c r="E80" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grade (computed)</t>
+        </is>
+      </c>
+      <c r="F80" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type (auto)</t>
+        </is>
+      </c>
+      <c r="G80" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include?</t>
+        </is>
+      </c>
+      <c r="H80" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A81" s="53"/>
+      <c r="B81" s="124"/>
+      <c r="C81" s="53"/>
+      <c r="D81" s="124"/>
+      <c r="E81" s="48">
+        <f>IFERROR(IF((291.2/D81)&gt;160,0,IF((291.2/D81)&gt;100,1,IF((291.2/D81)&gt;40,2,IF((291.2/D81)&gt;16,3,IF((291.2/D81)&gt;10,4,5))))),"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="48">
+        <f>IFERROR(VLOOKUP(C81,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G81" s="53"/>
+      <c r="H81" s="53"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A82" s="53"/>
+      <c r="B82" s="124"/>
+      <c r="C82" s="53"/>
+      <c r="D82" s="124"/>
+      <c r="E82" s="48">
+        <f>IFERROR(IF((291.2/D82)&gt;160,0,IF((291.2/D82)&gt;100,1,IF((291.2/D82)&gt;40,2,IF((291.2/D82)&gt;16,3,IF((291.2/D82)&gt;10,4,5))))),"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="48">
+        <f>IFERROR(VLOOKUP(C82,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G82" s="53"/>
+      <c r="H82" s="53"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A83" s="53"/>
+      <c r="B83" s="124"/>
+      <c r="C83" s="53"/>
+      <c r="D83" s="124"/>
+      <c r="E83" s="48">
+        <f>IFERROR(IF((291.2/D83)&gt;160,0,IF((291.2/D83)&gt;100,1,IF((291.2/D83)&gt;40,2,IF((291.2/D83)&gt;16,3,IF((291.2/D83)&gt;10,4,5))))),"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="48">
+        <f>IFERROR(VLOOKUP(C83,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G83" s="53"/>
+      <c r="H83" s="53"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A84" s="53"/>
+      <c r="B84" s="124"/>
+      <c r="C84" s="53"/>
+      <c r="D84" s="124"/>
+      <c r="E84" s="48">
+        <f>IFERROR(IF((291.2/D84)&gt;160,0,IF((291.2/D84)&gt;100,1,IF((291.2/D84)&gt;40,2,IF((291.2/D84)&gt;16,3,IF((291.2/D84)&gt;10,4,5))))),"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="48">
+        <f>IFERROR(VLOOKUP(C84,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G84" s="53"/>
+      <c r="H84" s="53"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A85" s="53"/>
+      <c r="B85" s="124"/>
+      <c r="C85" s="53"/>
+      <c r="D85" s="124"/>
+      <c r="E85" s="48">
+        <f>IFERROR(IF((291.2/D85)&gt;160,0,IF((291.2/D85)&gt;100,1,IF((291.2/D85)&gt;40,2,IF((291.2/D85)&gt;16,3,IF((291.2/D85)&gt;10,4,5))))),"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="48">
+        <f>IFERROR(VLOOKUP(C85,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G85" s="53"/>
+      <c r="H85" s="53"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A86" s="53"/>
+      <c r="B86" s="124"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="124"/>
+      <c r="E86" s="48">
+        <f>IFERROR(IF((291.2/D86)&gt;160,0,IF((291.2/D86)&gt;100,1,IF((291.2/D86)&gt;40,2,IF((291.2/D86)&gt;16,3,IF((291.2/D86)&gt;10,4,5))))),"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="48">
+        <f>IFERROR(VLOOKUP(C86,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G86" s="53"/>
+      <c r="H86" s="53"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A87" s="53"/>
+      <c r="B87" s="124"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="124"/>
+      <c r="E87" s="48">
+        <f>IFERROR(IF((291.2/D87)&gt;160,0,IF((291.2/D87)&gt;100,1,IF((291.2/D87)&gt;40,2,IF((291.2/D87)&gt;16,3,IF((291.2/D87)&gt;10,4,5))))),"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="48">
+        <f>IFERROR(VLOOKUP(C87,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G87" s="53"/>
+      <c r="H87" s="53"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A88" s="53"/>
+      <c r="B88" s="124"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="124"/>
+      <c r="E88" s="48">
+        <f>IFERROR(IF((291.2/D88)&gt;160,0,IF((291.2/D88)&gt;100,1,IF((291.2/D88)&gt;40,2,IF((291.2/D88)&gt;16,3,IF((291.2/D88)&gt;10,4,5))))),"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="48">
+        <f>IFERROR(VLOOKUP(C88,Geometry!$A$59:$B$80,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G88" s="53"/>
+      <c r="H88" s="53"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - porosity grade</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0-5</t>
+        </is>
+      </c>
+      <c r="D89" s="48">
+        <f>AVERAGEIFS(E81:E88,C81:C88,Summary!$D$2,G81:G88,"y",B81:B88,MAXIFS(B81:B88,C81:C88,Summary!$D$2,G81:G88,"y"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A92" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISSOLVED-OXYGEN THRESHOLDS  (per organism)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A93" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use: average of the included values for the active organism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A94" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Researcher</t>
+        </is>
+      </c>
+      <c r="B94" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="C94" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organism</t>
+        </is>
+      </c>
+      <c r="D94" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Min DO</t>
+        </is>
+      </c>
+      <c r="E94" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Optimum DO</t>
+        </is>
+      </c>
+      <c r="F94" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impairment DO</t>
+        </is>
+      </c>
+      <c r="G94" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toxic DO</t>
+        </is>
+      </c>
+      <c r="H94" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include?</t>
+        </is>
+      </c>
+      <c r="I94" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A95" s="53"/>
+      <c r="B95" s="124"/>
+      <c r="C95" s="53"/>
+      <c r="D95" s="124"/>
+      <c r="E95" s="124"/>
+      <c r="F95" s="124"/>
+      <c r="G95" s="124"/>
+      <c r="H95" s="53"/>
+      <c r="I95" s="53"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A96" s="53"/>
+      <c r="B96" s="124"/>
+      <c r="C96" s="53"/>
+      <c r="D96" s="124"/>
+      <c r="E96" s="124"/>
+      <c r="F96" s="124"/>
+      <c r="G96" s="124"/>
+      <c r="H96" s="53"/>
+      <c r="I96" s="53"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A97" s="53"/>
+      <c r="B97" s="124"/>
+      <c r="C97" s="53"/>
+      <c r="D97" s="124"/>
+      <c r="E97" s="124"/>
+      <c r="F97" s="124"/>
+      <c r="G97" s="124"/>
+      <c r="H97" s="53"/>
+      <c r="I97" s="53"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A98" s="53"/>
+      <c r="B98" s="124"/>
+      <c r="C98" s="53"/>
+      <c r="D98" s="124"/>
+      <c r="E98" s="124"/>
+      <c r="F98" s="124"/>
+      <c r="G98" s="124"/>
+      <c r="H98" s="53"/>
+      <c r="I98" s="53"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A99" s="53"/>
+      <c r="B99" s="124"/>
+      <c r="C99" s="53"/>
+      <c r="D99" s="124"/>
+      <c r="E99" s="124"/>
+      <c r="F99" s="124"/>
+      <c r="G99" s="124"/>
+      <c r="H99" s="53"/>
+      <c r="I99" s="53"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A100" s="53"/>
+      <c r="B100" s="124"/>
+      <c r="C100" s="53"/>
+      <c r="D100" s="124"/>
+      <c r="E100" s="124"/>
+      <c r="F100" s="124"/>
+      <c r="G100" s="124"/>
+      <c r="H100" s="53"/>
+      <c r="I100" s="53"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A101" s="53"/>
+      <c r="B101" s="124"/>
+      <c r="C101" s="53"/>
+      <c r="D101" s="124"/>
+      <c r="E101" s="124"/>
+      <c r="F101" s="124"/>
+      <c r="G101" s="124"/>
+      <c r="H101" s="53"/>
+      <c r="I101" s="53"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A102" s="53"/>
+      <c r="B102" s="124"/>
+      <c r="C102" s="53"/>
+      <c r="D102" s="124"/>
+      <c r="E102" s="124"/>
+      <c r="F102" s="124"/>
+      <c r="G102" s="124"/>
+      <c r="H102" s="53"/>
+      <c r="I102" s="53"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - minimum DO</t>
+        </is>
+      </c>
+      <c r="C103" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mg/L</t>
+        </is>
+      </c>
+      <c r="D103" s="48">
+        <f>AVERAGEIFS(D95:D102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A104" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - optimum DO</t>
+        </is>
+      </c>
+      <c r="C104" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mg/L</t>
+        </is>
+      </c>
+      <c r="D104" s="48">
+        <f>AVERAGEIFS(E95:E102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A105" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - impairment DO</t>
+        </is>
+      </c>
+      <c r="C105" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mg/L</t>
+        </is>
+      </c>
+      <c r="D105" s="48">
+        <f>AVERAGEIFS(F95:F102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - toxic DO</t>
+        </is>
+      </c>
+      <c r="C106" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mg/L</t>
+        </is>
+      </c>
+      <c r="D106" s="48">
+        <f>AVERAGEIFS(G95:G102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A109" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KNALLGAS UPTAKE RATIO  (per organism)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A110" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use: average of the included ratios for the active organism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A111" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Researcher</t>
+        </is>
+      </c>
+      <c r="B111" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="C111" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organism</t>
+        </is>
+      </c>
+      <c r="D111" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H2</t>
+        </is>
+      </c>
+      <c r="E111" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O2</t>
+        </is>
+      </c>
+      <c r="F111" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO2</t>
+        </is>
+      </c>
+      <c r="G111" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include?</t>
+        </is>
+      </c>
+      <c r="H111" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A112" s="53"/>
+      <c r="B112" s="124"/>
+      <c r="C112" s="53"/>
+      <c r="D112" s="124"/>
+      <c r="E112" s="124"/>
+      <c r="F112" s="124"/>
+      <c r="G112" s="53"/>
+      <c r="H112" s="53"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A113" s="53"/>
+      <c r="B113" s="124"/>
+      <c r="C113" s="53"/>
+      <c r="D113" s="124"/>
+      <c r="E113" s="124"/>
+      <c r="F113" s="124"/>
+      <c r="G113" s="53"/>
+      <c r="H113" s="53"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A114" s="53"/>
+      <c r="B114" s="124"/>
+      <c r="C114" s="53"/>
+      <c r="D114" s="124"/>
+      <c r="E114" s="124"/>
+      <c r="F114" s="124"/>
+      <c r="G114" s="53"/>
+      <c r="H114" s="53"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A115" s="53"/>
+      <c r="B115" s="124"/>
+      <c r="C115" s="53"/>
+      <c r="D115" s="124"/>
+      <c r="E115" s="124"/>
+      <c r="F115" s="124"/>
+      <c r="G115" s="53"/>
+      <c r="H115" s="53"/>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A116" s="53"/>
+      <c r="B116" s="124"/>
+      <c r="C116" s="53"/>
+      <c r="D116" s="124"/>
+      <c r="E116" s="124"/>
+      <c r="F116" s="124"/>
+      <c r="G116" s="53"/>
+      <c r="H116" s="53"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A117" s="53"/>
+      <c r="B117" s="124"/>
+      <c r="C117" s="53"/>
+      <c r="D117" s="124"/>
+      <c r="E117" s="124"/>
+      <c r="F117" s="124"/>
+      <c r="G117" s="53"/>
+      <c r="H117" s="53"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A118" s="53"/>
+      <c r="B118" s="124"/>
+      <c r="C118" s="53"/>
+      <c r="D118" s="124"/>
+      <c r="E118" s="124"/>
+      <c r="F118" s="124"/>
+      <c r="G118" s="53"/>
+      <c r="H118" s="53"/>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A119" s="53"/>
+      <c r="B119" s="124"/>
+      <c r="C119" s="53"/>
+      <c r="D119" s="124"/>
+      <c r="E119" s="124"/>
+      <c r="F119" s="124"/>
+      <c r="G119" s="53"/>
+      <c r="H119" s="53"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - H2</t>
+        </is>
+      </c>
+      <c r="C120" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parts</t>
+        </is>
+      </c>
+      <c r="D120" s="48">
+        <f>AVERAGEIFS(D112:D119,C112:C119,Summary!$D$4,G112:G119,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A121" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - O2</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parts</t>
+        </is>
+      </c>
+      <c r="D121" s="48">
+        <f>AVERAGEIFS(E112:E119,C112:C119,Summary!$D$4,G112:G119,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A122" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - CO2</t>
+        </is>
+      </c>
+      <c r="C122" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parts</t>
+        </is>
+      </c>
+      <c r="D122" s="48">
+        <f>AVERAGEIFS(F112:F119,C112:C119,Summary!$D$4,G112:G119,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A125" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CURRENT-DENSITY TOLERANCE  (per organism)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A126" s="51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use: average of the included screen results for the active organism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A127" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Researcher</t>
+        </is>
+      </c>
+      <c r="B127" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="C127" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organism</t>
+        </is>
+      </c>
+      <c r="D127" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j optimum</t>
+        </is>
+      </c>
+      <c r="E127" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j ceiling</t>
+        </is>
+      </c>
+      <c r="F127" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include?</t>
+        </is>
+      </c>
+      <c r="G127" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A128" s="53"/>
+      <c r="B128" s="124"/>
+      <c r="C128" s="53"/>
+      <c r="D128" s="124"/>
+      <c r="E128" s="124"/>
+      <c r="F128" s="53"/>
+      <c r="G128" s="53"/>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A129" s="53"/>
+      <c r="B129" s="124"/>
+      <c r="C129" s="53"/>
+      <c r="D129" s="124"/>
+      <c r="E129" s="124"/>
+      <c r="F129" s="53"/>
+      <c r="G129" s="53"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A130" s="53"/>
+      <c r="B130" s="124"/>
+      <c r="C130" s="53"/>
+      <c r="D130" s="124"/>
+      <c r="E130" s="124"/>
+      <c r="F130" s="53"/>
+      <c r="G130" s="53"/>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A131" s="53"/>
+      <c r="B131" s="124"/>
+      <c r="C131" s="53"/>
+      <c r="D131" s="124"/>
+      <c r="E131" s="124"/>
+      <c r="F131" s="53"/>
+      <c r="G131" s="53"/>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A132" s="53"/>
+      <c r="B132" s="124"/>
+      <c r="C132" s="53"/>
+      <c r="D132" s="124"/>
+      <c r="E132" s="124"/>
+      <c r="F132" s="53"/>
+      <c r="G132" s="53"/>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A133" s="53"/>
+      <c r="B133" s="124"/>
+      <c r="C133" s="53"/>
+      <c r="D133" s="124"/>
+      <c r="E133" s="124"/>
+      <c r="F133" s="53"/>
+      <c r="G133" s="53"/>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A134" s="53"/>
+      <c r="B134" s="124"/>
+      <c r="C134" s="53"/>
+      <c r="D134" s="124"/>
+      <c r="E134" s="124"/>
+      <c r="F134" s="53"/>
+      <c r="G134" s="53"/>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A135" s="53"/>
+      <c r="B135" s="124"/>
+      <c r="C135" s="53"/>
+      <c r="D135" s="124"/>
+      <c r="E135" s="124"/>
+      <c r="F135" s="53"/>
+      <c r="G135" s="53"/>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A136" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - optimum j</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mA/cm²</t>
+        </is>
+      </c>
+      <c r="D136" s="48">
+        <f>AVERAGEIFS(D128:D135,C128:C135,Summary!$D$4,F128:F135,"y")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A137" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value in use - ceiling j</t>
+        </is>
+      </c>
+      <c r="C137" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mA/cm²</t>
+        </is>
+      </c>
+      <c r="D137" s="48">
+        <f>AVERAGEIFS(E128:E135,C128:C135,Summary!$D$4,F128:F135,"y")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -8003,7 +8003,6 @@
       </c>
       <c r="D22" s="44">
         <f>IFERROR(cal_Dint,VLOOKUP(rx_ver,$A$84:$I$87,4,FALSE))</f>
-        <v>55</v>
       </c>
       <c r="E22" s="101" t="s">
         <v>176</v>
@@ -8047,7 +8046,6 @@
       </c>
       <c r="D24" s="44">
         <f>IFERROR(cal_Vtot,VLOOKUP(rx_ver,$A$84:$I$87,6,FALSE))</f>
-        <v>20</v>
       </c>
       <c r="E24" s="101" t="s">
         <v>176</v>
@@ -9507,7 +9505,6 @@
       </c>
       <c r="D11" s="50">
         <f>IFERROR(cal_gerrit_slope,1.03)</f>
-        <v>1.03</v>
       </c>
       <c r="E11" s="115" t="s">
         <v>322</v>
@@ -9529,7 +9526,6 @@
       </c>
       <c r="D12" s="54">
         <f>IFERROR(cal_gerrit_int,2.6)</f>
-        <v>2.6</v>
       </c>
       <c r="E12" s="115" t="s">
         <v>326</v>
@@ -9656,7 +9652,6 @@
       </c>
       <c r="D18" s="114">
         <f>IFERROR(cal_etaF,1)</f>
-        <v>1</v>
       </c>
       <c r="E18" s="57" t="s">
         <v>345</v>
@@ -9832,7 +9827,6 @@
       </c>
       <c r="D26" s="114">
         <f>IFERROR(cal_etaF_OER,1)</f>
-        <v>1</v>
       </c>
       <c r="E26" s="122" t="s">
         <v>372</v>
@@ -9949,7 +9943,6 @@
       <c r="C32" s="20"/>
       <c r="D32" s="24">
         <f>IFERROR(cal_sinter,IF(ISNUMBER(VLOOKUP(electrode_sel,$A$35:$I$38,5,FALSE)),VLOOKUP(electrode_sel,$A$35:$I$38,5,FALSE),0))</f>
-        <v>0</v>
       </c>
       <c r="E32" s="107" t="s">
         <v>387</v>
@@ -10486,7 +10479,6 @@
       </c>
       <c r="D56" s="48">
         <f>IFERROR(cal_j_opt,IFERROR(VLOOKUP(Summary!$D$4,$A$66:$E$71,2,FALSE),j_opt_default))</f>
-        <v>2.14</v>
       </c>
       <c r="E56" s="101" t="s">
         <v>1396</v>
@@ -10504,7 +10496,6 @@
       </c>
       <c r="D57" s="48">
         <f>IFERROR(cal_j_ceiling,IFERROR(VLOOKUP(Summary!$D$4,$A$66:$E$71,3,FALSE),j_ceiling_default))</f>
-        <v>4.29</v>
       </c>
       <c r="E57" s="101" t="s">
         <v>1399</v>
@@ -13315,7 +13306,6 @@
       </c>
       <c r="D10" s="111">
         <f>IFERROR(cal_knall_H2,6)</f>
-        <v>6</v>
       </c>
       <c r="E10" s="61" t="s">
         <v>411</v>
@@ -13334,7 +13324,6 @@
       </c>
       <c r="D11" s="111">
         <f>IFERROR(cal_knall_O2,2)</f>
-        <v>2</v>
       </c>
       <c r="E11" s="61" t="s">
         <v>414</v>
@@ -13353,7 +13342,6 @@
       </c>
       <c r="D12" s="111">
         <f>IFERROR(cal_knall_CO2,1)</f>
-        <v>1</v>
       </c>
       <c r="E12" s="61" t="s">
         <v>417</v>
@@ -13971,7 +13959,6 @@
       </c>
       <c r="D45" s="71">
         <f>IFERROR(cal_DO_min,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE),NA()))</f>
-        <v>#N/A</v>
       </c>
       <c r="E45" s="20"/>
       <c r="F45" s="20"/>
@@ -13988,7 +13975,6 @@
       </c>
       <c r="D46" s="24">
         <f>IFERROR(cal_DO_opt,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE),NA()))</f>
-        <v>#N/A</v>
       </c>
       <c r="E46" s="20"/>
       <c r="F46" s="20"/>
@@ -14005,7 +13991,6 @@
       </c>
       <c r="D47" s="24">
         <f>IFERROR(cal_DO_impair,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE),NA()))</f>
-        <v>#N/A</v>
       </c>
       <c r="E47" s="20"/>
       <c r="F47" s="20"/>
@@ -14022,7 +14007,6 @@
       </c>
       <c r="D48" s="24">
         <f>IFERROR(cal_DO_toxic,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE),NA()))</f>
-        <v>#N/A</v>
       </c>
       <c r="E48" s="20"/>
       <c r="F48" s="20"/>
@@ -16023,7 +16007,6 @@
       </c>
       <c r="D97" s="124">
         <f>IFERROR(cal_kLa,0)</f>
-        <v>0</v>
       </c>
       <c r="E97" s="69" t="s">
         <v>769</v>
@@ -19581,7 +19564,6 @@
       <c r="E8" s="124"/>
       <c r="F8" s="48">
         <f>IFERROR(VLOOKUP(C8,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G8" s="53"/>
       <c r="H8" s="53"/>
@@ -19594,7 +19576,6 @@
       <c r="E9" s="124"/>
       <c r="F9" s="48">
         <f>IFERROR(VLOOKUP(C9,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G9" s="53"/>
       <c r="H9" s="53"/>
@@ -19607,7 +19588,6 @@
       <c r="E10" s="124"/>
       <c r="F10" s="48">
         <f>IFERROR(VLOOKUP(C10,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G10" s="53"/>
       <c r="H10" s="53"/>
@@ -19620,7 +19600,6 @@
       <c r="E11" s="124"/>
       <c r="F11" s="48">
         <f>IFERROR(VLOOKUP(C11,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G11" s="53"/>
       <c r="H11" s="53"/>
@@ -19633,7 +19612,6 @@
       <c r="E12" s="124"/>
       <c r="F12" s="48">
         <f>IFERROR(VLOOKUP(C12,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G12" s="53"/>
       <c r="H12" s="53"/>
@@ -19646,7 +19624,6 @@
       <c r="E13" s="124"/>
       <c r="F13" s="48">
         <f>IFERROR(VLOOKUP(C13,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G13" s="53"/>
       <c r="H13" s="53"/>
@@ -19659,7 +19636,6 @@
       <c r="E14" s="124"/>
       <c r="F14" s="48">
         <f>IFERROR(VLOOKUP(C14,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G14" s="53"/>
       <c r="H14" s="53"/>
@@ -19672,7 +19648,6 @@
       <c r="E15" s="124"/>
       <c r="F15" s="48">
         <f>IFERROR(VLOOKUP(C15,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G15" s="53"/>
       <c r="H15" s="53"/>
@@ -19690,7 +19665,6 @@
       </c>
       <c r="D16" s="48">
         <f>(COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*E8:E15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(E8:E15,C8:C15,Summary!$D$2,G8:G15,"y"))/(COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*D8:D15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y"))</f>
-        <v/>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -19706,7 +19680,6 @@
       </c>
       <c r="D17" s="48">
         <f>(SUMIFS(E8:E15,C8:C15,Summary!$D$2,G8:G15,"y")-((COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*E8:E15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(E8:E15,C8:C15,Summary!$D$2,G8:G15,"y"))/(COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*D8:D15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")))*SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y"))/COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -19796,11 +19769,9 @@
       <c r="H23" s="124"/>
       <c r="I23" s="48">
         <f>IFERROR((G23*(E23/1000000)/(8.314*(F23+273.15)))/(D23/(IF(H23="H2",2,4)*96485)),"")</f>
-        <v/>
       </c>
       <c r="J23" s="48">
         <f>IFERROR(VLOOKUP(C23,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="K23" s="53"/>
       <c r="L23" s="53"/>
@@ -19816,11 +19787,9 @@
       <c r="H24" s="124"/>
       <c r="I24" s="48">
         <f>IFERROR((G24*(E24/1000000)/(8.314*(F24+273.15)))/(D24/(IF(H24="H2",2,4)*96485)),"")</f>
-        <v/>
       </c>
       <c r="J24" s="48">
         <f>IFERROR(VLOOKUP(C24,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="K24" s="53"/>
       <c r="L24" s="53"/>
@@ -19836,11 +19805,9 @@
       <c r="H25" s="124"/>
       <c r="I25" s="48">
         <f>IFERROR((G25*(E25/1000000)/(8.314*(F25+273.15)))/(D25/(IF(H25="H2",2,4)*96485)),"")</f>
-        <v/>
       </c>
       <c r="J25" s="48">
         <f>IFERROR(VLOOKUP(C25,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="K25" s="53"/>
       <c r="L25" s="53"/>
@@ -19856,11 +19823,9 @@
       <c r="H26" s="124"/>
       <c r="I26" s="48">
         <f>IFERROR((G26*(E26/1000000)/(8.314*(F26+273.15)))/(D26/(IF(H26="H2",2,4)*96485)),"")</f>
-        <v/>
       </c>
       <c r="J26" s="48">
         <f>IFERROR(VLOOKUP(C26,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="K26" s="53"/>
       <c r="L26" s="53"/>
@@ -19876,11 +19841,9 @@
       <c r="H27" s="124"/>
       <c r="I27" s="48">
         <f>IFERROR((G27*(E27/1000000)/(8.314*(F27+273.15)))/(D27/(IF(H27="H2",2,4)*96485)),"")</f>
-        <v/>
       </c>
       <c r="J27" s="48">
         <f>IFERROR(VLOOKUP(C27,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="K27" s="53"/>
       <c r="L27" s="53"/>
@@ -19896,11 +19859,9 @@
       <c r="H28" s="124"/>
       <c r="I28" s="48">
         <f>IFERROR((G28*(E28/1000000)/(8.314*(F28+273.15)))/(D28/(IF(H28="H2",2,4)*96485)),"")</f>
-        <v/>
       </c>
       <c r="J28" s="48">
         <f>IFERROR(VLOOKUP(C28,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="K28" s="53"/>
       <c r="L28" s="53"/>
@@ -19916,11 +19877,9 @@
       <c r="H29" s="124"/>
       <c r="I29" s="48">
         <f>IFERROR((G29*(E29/1000000)/(8.314*(F29+273.15)))/(D29/(IF(H29="H2",2,4)*96485)),"")</f>
-        <v/>
       </c>
       <c r="J29" s="48">
         <f>IFERROR(VLOOKUP(C29,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="K29" s="53"/>
       <c r="L29" s="53"/>
@@ -19936,11 +19895,9 @@
       <c r="H30" s="124"/>
       <c r="I30" s="48">
         <f>IFERROR((G30*(E30/1000000)/(8.314*(F30+273.15)))/(D30/(IF(H30="H2",2,4)*96485)),"")</f>
-        <v/>
       </c>
       <c r="J30" s="48">
         <f>IFERROR(VLOOKUP(C30,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="K30" s="53"/>
       <c r="L30" s="53"/>
@@ -19958,7 +19915,6 @@
       </c>
       <c r="D31" s="48">
         <f>AVERAGEIFS(I23:I30,C23:C30,Summary!$D$2,K23:K30,"y",H23:H30,"H2")</f>
-        <v/>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
@@ -19974,7 +19930,6 @@
       </c>
       <c r="D32" s="48">
         <f>AVERAGEIFS(I23:I30,C23:C30,Summary!$D$2,K23:K30,"y",H23:H30,"O2")</f>
-        <v/>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -20035,7 +19990,6 @@
       <c r="D38" s="124"/>
       <c r="E38" s="48">
         <f>IFERROR(VLOOKUP(C38,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="F38" s="53"/>
       <c r="G38" s="53"/>
@@ -20047,7 +20001,6 @@
       <c r="D39" s="124"/>
       <c r="E39" s="48">
         <f>IFERROR(VLOOKUP(C39,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="F39" s="53"/>
       <c r="G39" s="53"/>
@@ -20059,7 +20012,6 @@
       <c r="D40" s="124"/>
       <c r="E40" s="48">
         <f>IFERROR(VLOOKUP(C40,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="F40" s="53"/>
       <c r="G40" s="53"/>
@@ -20071,7 +20023,6 @@
       <c r="D41" s="124"/>
       <c r="E41" s="48">
         <f>IFERROR(VLOOKUP(C41,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="F41" s="53"/>
       <c r="G41" s="53"/>
@@ -20083,7 +20034,6 @@
       <c r="D42" s="124"/>
       <c r="E42" s="48">
         <f>IFERROR(VLOOKUP(C42,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="F42" s="53"/>
       <c r="G42" s="53"/>
@@ -20095,7 +20045,6 @@
       <c r="D43" s="124"/>
       <c r="E43" s="48">
         <f>IFERROR(VLOOKUP(C43,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="F43" s="53"/>
       <c r="G43" s="53"/>
@@ -20107,7 +20056,6 @@
       <c r="D44" s="124"/>
       <c r="E44" s="48">
         <f>IFERROR(VLOOKUP(C44,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="F44" s="53"/>
       <c r="G44" s="53"/>
@@ -20119,7 +20067,6 @@
       <c r="D45" s="124"/>
       <c r="E45" s="48">
         <f>IFERROR(VLOOKUP(C45,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="F45" s="53"/>
       <c r="G45" s="53"/>
@@ -20137,7 +20084,6 @@
       </c>
       <c r="D46" s="48">
         <f>AVERAGEIFS(D38:D45,C38:C45,Summary!$D$2,F38:F45,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
@@ -20209,11 +20155,9 @@
       <c r="E52" s="124"/>
       <c r="F52" s="48">
         <f>IFERROR(D52/E52,"")</f>
-        <v/>
       </c>
       <c r="G52" s="48">
         <f>IFERROR(VLOOKUP(C52,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="H52" s="53"/>
       <c r="I52" s="53"/>
@@ -20226,11 +20170,9 @@
       <c r="E53" s="124"/>
       <c r="F53" s="48">
         <f>IFERROR(D53/E53,"")</f>
-        <v/>
       </c>
       <c r="G53" s="48">
         <f>IFERROR(VLOOKUP(C53,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="H53" s="53"/>
       <c r="I53" s="53"/>
@@ -20243,11 +20185,9 @@
       <c r="E54" s="124"/>
       <c r="F54" s="48">
         <f>IFERROR(D54/E54,"")</f>
-        <v/>
       </c>
       <c r="G54" s="48">
         <f>IFERROR(VLOOKUP(C54,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="H54" s="53"/>
       <c r="I54" s="53"/>
@@ -20260,11 +20200,9 @@
       <c r="E55" s="124"/>
       <c r="F55" s="48">
         <f>IFERROR(D55/E55,"")</f>
-        <v/>
       </c>
       <c r="G55" s="48">
         <f>IFERROR(VLOOKUP(C55,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="H55" s="53"/>
       <c r="I55" s="53"/>
@@ -20277,11 +20215,9 @@
       <c r="E56" s="124"/>
       <c r="F56" s="48">
         <f>IFERROR(D56/E56,"")</f>
-        <v/>
       </c>
       <c r="G56" s="48">
         <f>IFERROR(VLOOKUP(C56,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="H56" s="53"/>
       <c r="I56" s="53"/>
@@ -20294,11 +20230,9 @@
       <c r="E57" s="124"/>
       <c r="F57" s="48">
         <f>IFERROR(D57/E57,"")</f>
-        <v/>
       </c>
       <c r="G57" s="48">
         <f>IFERROR(VLOOKUP(C57,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="H57" s="53"/>
       <c r="I57" s="53"/>
@@ -20311,11 +20245,9 @@
       <c r="E58" s="124"/>
       <c r="F58" s="48">
         <f>IFERROR(D58/E58,"")</f>
-        <v/>
       </c>
       <c r="G58" s="48">
         <f>IFERROR(VLOOKUP(C58,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="H58" s="53"/>
       <c r="I58" s="53"/>
@@ -20328,11 +20260,9 @@
       <c r="E59" s="124"/>
       <c r="F59" s="48">
         <f>IFERROR(D59/E59,"")</f>
-        <v/>
       </c>
       <c r="G59" s="48">
         <f>IFERROR(VLOOKUP(C59,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="H59" s="53"/>
       <c r="I59" s="53"/>
@@ -20350,7 +20280,6 @@
       </c>
       <c r="D60" s="48">
         <f>AVERAGEIFS(F52:F59,C52:C59,Summary!$D$2,H52:H59,"y",B52:B59,MAXIFS(B52:B59,C52:C59,Summary!$D$2,H52:H59,"y"))</f>
-        <v/>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
@@ -20433,15 +20362,12 @@
       <c r="F66" s="124"/>
       <c r="G66" s="48">
         <f>IFERROR(E66/(0.99705-0.00028*(F66-25)),"")</f>
-        <v/>
       </c>
       <c r="H66" s="48">
         <f>IFERROR((E66/(0.99705-0.00028*(F66-25)))*1000/Geometry!$D$21,"")</f>
-        <v/>
       </c>
       <c r="I66" s="48">
         <f>IFERROR(VLOOKUP(C66,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="J66" s="53"/>
       <c r="K66" s="53"/>
@@ -20455,15 +20381,12 @@
       <c r="F67" s="124"/>
       <c r="G67" s="48">
         <f>IFERROR(E67/(0.99705-0.00028*(F67-25)),"")</f>
-        <v/>
       </c>
       <c r="H67" s="48">
         <f>IFERROR((E67/(0.99705-0.00028*(F67-25)))*1000/Geometry!$D$21,"")</f>
-        <v/>
       </c>
       <c r="I67" s="48">
         <f>IFERROR(VLOOKUP(C67,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="J67" s="53"/>
       <c r="K67" s="53"/>
@@ -20477,15 +20400,12 @@
       <c r="F68" s="124"/>
       <c r="G68" s="48">
         <f>IFERROR(E68/(0.99705-0.00028*(F68-25)),"")</f>
-        <v/>
       </c>
       <c r="H68" s="48">
         <f>IFERROR((E68/(0.99705-0.00028*(F68-25)))*1000/Geometry!$D$21,"")</f>
-        <v/>
       </c>
       <c r="I68" s="48">
         <f>IFERROR(VLOOKUP(C68,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="J68" s="53"/>
       <c r="K68" s="53"/>
@@ -20499,15 +20419,12 @@
       <c r="F69" s="124"/>
       <c r="G69" s="48">
         <f>IFERROR(E69/(0.99705-0.00028*(F69-25)),"")</f>
-        <v/>
       </c>
       <c r="H69" s="48">
         <f>IFERROR((E69/(0.99705-0.00028*(F69-25)))*1000/Geometry!$D$21,"")</f>
-        <v/>
       </c>
       <c r="I69" s="48">
         <f>IFERROR(VLOOKUP(C69,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="J69" s="53"/>
       <c r="K69" s="53"/>
@@ -20521,15 +20438,12 @@
       <c r="F70" s="124"/>
       <c r="G70" s="48">
         <f>IFERROR(E70/(0.99705-0.00028*(F70-25)),"")</f>
-        <v/>
       </c>
       <c r="H70" s="48">
         <f>IFERROR((E70/(0.99705-0.00028*(F70-25)))*1000/Geometry!$D$21,"")</f>
-        <v/>
       </c>
       <c r="I70" s="48">
         <f>IFERROR(VLOOKUP(C70,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="J70" s="53"/>
       <c r="K70" s="53"/>
@@ -20543,15 +20457,12 @@
       <c r="F71" s="124"/>
       <c r="G71" s="48">
         <f>IFERROR(E71/(0.99705-0.00028*(F71-25)),"")</f>
-        <v/>
       </c>
       <c r="H71" s="48">
         <f>IFERROR((E71/(0.99705-0.00028*(F71-25)))*1000/Geometry!$D$21,"")</f>
-        <v/>
       </c>
       <c r="I71" s="48">
         <f>IFERROR(VLOOKUP(C71,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="J71" s="53"/>
       <c r="K71" s="53"/>
@@ -20565,15 +20476,12 @@
       <c r="F72" s="124"/>
       <c r="G72" s="48">
         <f>IFERROR(E72/(0.99705-0.00028*(F72-25)),"")</f>
-        <v/>
       </c>
       <c r="H72" s="48">
         <f>IFERROR((E72/(0.99705-0.00028*(F72-25)))*1000/Geometry!$D$21,"")</f>
-        <v/>
       </c>
       <c r="I72" s="48">
         <f>IFERROR(VLOOKUP(C72,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="J72" s="53"/>
       <c r="K72" s="53"/>
@@ -20587,15 +20495,12 @@
       <c r="F73" s="124"/>
       <c r="G73" s="48">
         <f>IFERROR(E73/(0.99705-0.00028*(F73-25)),"")</f>
-        <v/>
       </c>
       <c r="H73" s="48">
         <f>IFERROR((E73/(0.99705-0.00028*(F73-25)))*1000/Geometry!$D$21,"")</f>
-        <v/>
       </c>
       <c r="I73" s="48">
         <f>IFERROR(VLOOKUP(C73,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="J73" s="53"/>
       <c r="K73" s="53"/>
@@ -20613,7 +20518,6 @@
       </c>
       <c r="D74" s="48">
         <f>AVERAGEIFS(G66:G73,I66:I73,Geometry!$D$51,J66:J73,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
@@ -20629,7 +20533,6 @@
       </c>
       <c r="D75" s="48">
         <f>AVERAGEIFS(H66:H73,I66:I73,Geometry!$D$51,J66:J73,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
@@ -20695,11 +20598,9 @@
       <c r="D81" s="124"/>
       <c r="E81" s="48">
         <f>IFERROR(IF((291.2/D81)&gt;160,0,IF((291.2/D81)&gt;100,1,IF((291.2/D81)&gt;40,2,IF((291.2/D81)&gt;16,3,IF((291.2/D81)&gt;10,4,5))))),"")</f>
-        <v/>
       </c>
       <c r="F81" s="48">
         <f>IFERROR(VLOOKUP(C81,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G81" s="53"/>
       <c r="H81" s="53"/>
@@ -20711,11 +20612,9 @@
       <c r="D82" s="124"/>
       <c r="E82" s="48">
         <f>IFERROR(IF((291.2/D82)&gt;160,0,IF((291.2/D82)&gt;100,1,IF((291.2/D82)&gt;40,2,IF((291.2/D82)&gt;16,3,IF((291.2/D82)&gt;10,4,5))))),"")</f>
-        <v/>
       </c>
       <c r="F82" s="48">
         <f>IFERROR(VLOOKUP(C82,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G82" s="53"/>
       <c r="H82" s="53"/>
@@ -20727,11 +20626,9 @@
       <c r="D83" s="124"/>
       <c r="E83" s="48">
         <f>IFERROR(IF((291.2/D83)&gt;160,0,IF((291.2/D83)&gt;100,1,IF((291.2/D83)&gt;40,2,IF((291.2/D83)&gt;16,3,IF((291.2/D83)&gt;10,4,5))))),"")</f>
-        <v/>
       </c>
       <c r="F83" s="48">
         <f>IFERROR(VLOOKUP(C83,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G83" s="53"/>
       <c r="H83" s="53"/>
@@ -20743,11 +20640,9 @@
       <c r="D84" s="124"/>
       <c r="E84" s="48">
         <f>IFERROR(IF((291.2/D84)&gt;160,0,IF((291.2/D84)&gt;100,1,IF((291.2/D84)&gt;40,2,IF((291.2/D84)&gt;16,3,IF((291.2/D84)&gt;10,4,5))))),"")</f>
-        <v/>
       </c>
       <c r="F84" s="48">
         <f>IFERROR(VLOOKUP(C84,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G84" s="53"/>
       <c r="H84" s="53"/>
@@ -20759,11 +20654,9 @@
       <c r="D85" s="124"/>
       <c r="E85" s="48">
         <f>IFERROR(IF((291.2/D85)&gt;160,0,IF((291.2/D85)&gt;100,1,IF((291.2/D85)&gt;40,2,IF((291.2/D85)&gt;16,3,IF((291.2/D85)&gt;10,4,5))))),"")</f>
-        <v/>
       </c>
       <c r="F85" s="48">
         <f>IFERROR(VLOOKUP(C85,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G85" s="53"/>
       <c r="H85" s="53"/>
@@ -20775,11 +20668,9 @@
       <c r="D86" s="124"/>
       <c r="E86" s="48">
         <f>IFERROR(IF((291.2/D86)&gt;160,0,IF((291.2/D86)&gt;100,1,IF((291.2/D86)&gt;40,2,IF((291.2/D86)&gt;16,3,IF((291.2/D86)&gt;10,4,5))))),"")</f>
-        <v/>
       </c>
       <c r="F86" s="48">
         <f>IFERROR(VLOOKUP(C86,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G86" s="53"/>
       <c r="H86" s="53"/>
@@ -20791,11 +20682,9 @@
       <c r="D87" s="124"/>
       <c r="E87" s="48">
         <f>IFERROR(IF((291.2/D87)&gt;160,0,IF((291.2/D87)&gt;100,1,IF((291.2/D87)&gt;40,2,IF((291.2/D87)&gt;16,3,IF((291.2/D87)&gt;10,4,5))))),"")</f>
-        <v/>
       </c>
       <c r="F87" s="48">
         <f>IFERROR(VLOOKUP(C87,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G87" s="53"/>
       <c r="H87" s="53"/>
@@ -20807,11 +20696,9 @@
       <c r="D88" s="124"/>
       <c r="E88" s="48">
         <f>IFERROR(IF((291.2/D88)&gt;160,0,IF((291.2/D88)&gt;100,1,IF((291.2/D88)&gt;40,2,IF((291.2/D88)&gt;16,3,IF((291.2/D88)&gt;10,4,5))))),"")</f>
-        <v/>
       </c>
       <c r="F88" s="48">
         <f>IFERROR(VLOOKUP(C88,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-        <v/>
       </c>
       <c r="G88" s="53"/>
       <c r="H88" s="53"/>
@@ -20829,7 +20716,6 @@
       </c>
       <c r="D89" s="48">
         <f>AVERAGEIFS(E81:E88,C81:C88,Summary!$D$2,G81:G88,"y",B81:B88,MAXIFS(B81:B88,C81:C88,Summary!$D$2,G81:G88,"y"))</f>
-        <v/>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
@@ -20994,7 +20880,6 @@
       </c>
       <c r="D103" s="48">
         <f>AVERAGEIFS(D95:D102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
@@ -21010,7 +20895,6 @@
       </c>
       <c r="D104" s="48">
         <f>AVERAGEIFS(E95:E102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
@@ -21026,7 +20910,6 @@
       </c>
       <c r="D105" s="48">
         <f>AVERAGEIFS(F95:F102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
@@ -21042,7 +20925,6 @@
       </c>
       <c r="D106" s="48">
         <f>AVERAGEIFS(G95:G102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
@@ -21194,7 +21076,6 @@
       </c>
       <c r="D120" s="48">
         <f>AVERAGEIFS(D112:D119,C112:C119,Summary!$D$4,G112:G119,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
@@ -21210,7 +21091,6 @@
       </c>
       <c r="D121" s="48">
         <f>AVERAGEIFS(E112:E119,C112:C119,Summary!$D$4,G112:G119,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
@@ -21226,7 +21106,6 @@
       </c>
       <c r="D122" s="48">
         <f>AVERAGEIFS(F112:F119,C112:C119,Summary!$D$4,G112:G119,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
@@ -21365,7 +21244,6 @@
       </c>
       <c r="D136" s="48">
         <f>AVERAGEIFS(D128:D135,C128:C135,Summary!$D$4,F128:F135,"y")</f>
-        <v/>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
@@ -21381,7 +21259,6 @@
       </c>
       <c r="D137" s="48">
         <f>AVERAGEIFS(E128:E135,C128:C135,Summary!$D$4,F128:F135,"y")</f>
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/Media/electroPioreactorGasModel.xlsx
+++ b/Media/electroPioreactorGasModel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martincurrie/andeye Dropbox/andeye/Projects/electroPioreactor/Media/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00290DCA-E4FD-0C4F-9B5E-A39CAEAD2AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F77307-233A-1A48-BEA2-E097B7E9FC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="580" windowWidth="25640" windowHeight="18060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="580" windowWidth="25140" windowHeight="18060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Biology" sheetId="4" r:id="rId5"/>
     <sheet name="Mass Transfer" sheetId="5" r:id="rId6"/>
     <sheet name="CO2 flows" sheetId="6" r:id="rId7"/>
-    <sheet name="Calibrations" sheetId="8" r:id="rId12"/>
+    <sheet name="Calibrations" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="A_anode" localSheetId="3">Chemistry!$D$130</definedName>
@@ -49,6 +49,24 @@
     <definedName name="C_H2_sat" localSheetId="4">Biology!$D$41</definedName>
     <definedName name="C_sat_CO2" localSheetId="5">'Mass Transfer'!$D$145</definedName>
     <definedName name="Ca_CO2" localSheetId="5">'Mass Transfer'!$D$157</definedName>
+    <definedName name="cal_Dint">Calibrations!$D$75</definedName>
+    <definedName name="cal_DO_impair">Calibrations!$D$105</definedName>
+    <definedName name="cal_DO_min">Calibrations!$D$103</definedName>
+    <definedName name="cal_DO_opt">Calibrations!$D$104</definedName>
+    <definedName name="cal_DO_toxic">Calibrations!$D$106</definedName>
+    <definedName name="cal_etaF">Calibrations!$D$31</definedName>
+    <definedName name="cal_etaF_OER">Calibrations!$D$32</definedName>
+    <definedName name="cal_flow">Calibrations!$D$60</definedName>
+    <definedName name="cal_gerrit_int">Calibrations!$D$17</definedName>
+    <definedName name="cal_gerrit_slope">Calibrations!$D$16</definedName>
+    <definedName name="cal_j_ceiling">Calibrations!$D$137</definedName>
+    <definedName name="cal_j_opt">Calibrations!$D$136</definedName>
+    <definedName name="cal_kLa">Calibrations!$D$46</definedName>
+    <definedName name="cal_knall_CO2">Calibrations!$D$122</definedName>
+    <definedName name="cal_knall_H2">Calibrations!$D$120</definedName>
+    <definedName name="cal_knall_O2">Calibrations!$D$121</definedName>
+    <definedName name="cal_sinter">Calibrations!$D$89</definedName>
+    <definedName name="cal_Vtot">Calibrations!$D$74</definedName>
     <definedName name="cal_warning" localSheetId="5">'Mass Transfer'!$D$120</definedName>
     <definedName name="carbon_margin_min" localSheetId="5">'Mass Transfer'!$D$85</definedName>
     <definedName name="carry_flag" localSheetId="5">'Mass Transfer'!$D$59</definedName>
@@ -268,6 +286,7 @@
     <definedName name="opt_binding" localSheetId="5">'Mass Transfer'!$D$94</definedName>
     <definedName name="organism_sel" localSheetId="4">Biology!$D$7</definedName>
     <definedName name="organism_sel" localSheetId="0">Summary!$D$4</definedName>
+    <definedName name="OrganismList">Biology!$A$52:$A$57</definedName>
     <definedName name="P_atm" localSheetId="4">Biology!$D$19</definedName>
     <definedName name="P_atm" localSheetId="2">Electrochemistry!$D$6</definedName>
     <definedName name="P_atm" localSheetId="5">'Mass Transfer'!$D$9</definedName>
@@ -312,6 +331,7 @@
     <definedName name="Reactor" localSheetId="5">'Mass Transfer'!$D$115</definedName>
     <definedName name="reactor_sel" localSheetId="1">Geometry!$D$5</definedName>
     <definedName name="Reactor_sel" localSheetId="0">Summary!$D$2</definedName>
+    <definedName name="ReactorList">Geometry!$A$59:$A$70</definedName>
     <definedName name="rH2_gen" localSheetId="4">Biology!$D$4</definedName>
     <definedName name="rH2_gen" localSheetId="2">Electrochemistry!$D$21</definedName>
     <definedName name="rho_CO2" localSheetId="5">'Mass Transfer'!$D$60</definedName>
@@ -425,26 +445,8 @@
     <definedName name="z_e_H2" localSheetId="2">Electrochemistry!$D$16</definedName>
     <definedName name="z_e_O2" localSheetId="2">Electrochemistry!$D$17</definedName>
     <definedName name="z_e_ORR" localSheetId="2">Electrochemistry!$D$27</definedName>
-    <definedName name="cal_gerrit_slope">Calibrations!$D$16</definedName>
-    <definedName name="cal_gerrit_int">Calibrations!$D$17</definedName>
-    <definedName name="cal_etaF">Calibrations!$D$31</definedName>
-    <definedName name="cal_etaF_OER">Calibrations!$D$32</definedName>
-    <definedName name="cal_kLa">Calibrations!$D$46</definedName>
-    <definedName name="cal_flow">Calibrations!$D$60</definedName>
-    <definedName name="cal_Vtot">Calibrations!$D$74</definedName>
-    <definedName name="cal_Dint">Calibrations!$D$75</definedName>
-    <definedName name="cal_sinter">Calibrations!$D$89</definedName>
-    <definedName name="cal_DO_min">Calibrations!$D$103</definedName>
-    <definedName name="cal_DO_opt">Calibrations!$D$104</definedName>
-    <definedName name="cal_DO_impair">Calibrations!$D$105</definedName>
-    <definedName name="cal_DO_toxic">Calibrations!$D$106</definedName>
-    <definedName name="cal_knall_H2">Calibrations!$D$120</definedName>
-    <definedName name="cal_knall_O2">Calibrations!$D$121</definedName>
-    <definedName name="cal_knall_CO2">Calibrations!$D$122</definedName>
-    <definedName name="cal_j_opt">Calibrations!$D$136</definedName>
-    <definedName name="cal_j_ceiling">Calibrations!$D$137</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -461,8 +463,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="1438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="1501">
   <si>
     <t>CO₂ DOSING FLOWRATES</t>
   </si>
@@ -4776,6 +4800,195 @@
   </si>
   <si>
     <t>Computed from the shape-aware wetted area (Electrochemistry A_anode_wet); tracks reactor &amp; electrode.</t>
+  </si>
+  <si>
+    <t>CALIBRATIONS</t>
+  </si>
+  <si>
+    <t>Fill the white cells only: Researcher, Date, the key (Reactor or Organism) and the raw measurements. Grey cells are computed automatically. Set Include to y for rows the model should use.</t>
+  </si>
+  <si>
+    <t>The value in use for each calibration follows the rule stated under its heading. If no rows are included yet, the model falls back to its built-in default.</t>
+  </si>
+  <si>
+    <t>Value in use: least-squares fit of current vs intensity, averaged across all included runs for the active reactor.</t>
+  </si>
+  <si>
+    <t>Researcher</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Intensity</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Type (auto)</t>
+  </si>
+  <si>
+    <t>Include?</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Value in use - slope</t>
+  </si>
+  <si>
+    <t>Value in use - intercept</t>
+  </si>
+  <si>
+    <t>Value in use: average of the included runs for the active reactor, taken separately for the H2 (cathode) and O2 (anode) electrodes.</t>
+  </si>
+  <si>
+    <t>Charge Q</t>
+  </si>
+  <si>
+    <t>Gas volume</t>
+  </si>
+  <si>
+    <t>Temp</t>
+  </si>
+  <si>
+    <t>Pressure</t>
+  </si>
+  <si>
+    <t>etaF (computed)</t>
+  </si>
+  <si>
+    <t>Value in use - cathode (H2)</t>
+  </si>
+  <si>
+    <t>Value in use - anode (O2)</t>
+  </si>
+  <si>
+    <t>Value in use: average of the included kLa runs for the active reactor.</t>
+  </si>
+  <si>
+    <t>kLa</t>
+  </si>
+  <si>
+    <t>Value in use - kLa</t>
+  </si>
+  <si>
+    <t>Value in use: the most recent included measurement for the active reactor (a flow rate is a valve/hardware setting, so the latest reading replaces older ones).</t>
+  </si>
+  <si>
+    <t>CO2 volume</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Flow (computed)</t>
+  </si>
+  <si>
+    <t>Value in use - flow rate</t>
+  </si>
+  <si>
+    <t>mL/s</t>
+  </si>
+  <si>
+    <t>Value in use: average across included vials of the active reactor type (all vials of a type are nominally identical, so averaging improves the estimate).</t>
+  </si>
+  <si>
+    <t>Headspace mass</t>
+  </si>
+  <si>
+    <t>Body mass</t>
+  </si>
+  <si>
+    <t>V total (computed)</t>
+  </si>
+  <si>
+    <t>Bore depth (computed)</t>
+  </si>
+  <si>
+    <t>Value in use - total vial volume</t>
+  </si>
+  <si>
+    <t>Value in use - usable depth</t>
+  </si>
+  <si>
+    <t>Value in use: the most recent included measurement for the active reactor (the fitted frit is hardware, so the latest reading replaces older ones).</t>
+  </si>
+  <si>
+    <t>Bubble-point</t>
+  </si>
+  <si>
+    <t>Grade (computed)</t>
+  </si>
+  <si>
+    <t>Value in use - porosity grade</t>
+  </si>
+  <si>
+    <t>Value in use: average of the included values for the active organism.</t>
+  </si>
+  <si>
+    <t>Min DO</t>
+  </si>
+  <si>
+    <t>Optimum DO</t>
+  </si>
+  <si>
+    <t>Impairment DO</t>
+  </si>
+  <si>
+    <t>Toxic DO</t>
+  </si>
+  <si>
+    <t>Value in use - minimum DO</t>
+  </si>
+  <si>
+    <t>Value in use - optimum DO</t>
+  </si>
+  <si>
+    <t>Value in use - impairment DO</t>
+  </si>
+  <si>
+    <t>Value in use - toxic DO</t>
+  </si>
+  <si>
+    <t>Value in use: average of the included ratios for the active organism.</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>O2</t>
+  </si>
+  <si>
+    <t>CO2</t>
+  </si>
+  <si>
+    <t>Value in use - H2</t>
+  </si>
+  <si>
+    <t>parts</t>
+  </si>
+  <si>
+    <t>Value in use - O2</t>
+  </si>
+  <si>
+    <t>Value in use - CO2</t>
+  </si>
+  <si>
+    <t>Value in use: average of the included screen results for the active organism.</t>
+  </si>
+  <si>
+    <t>j optimum</t>
+  </si>
+  <si>
+    <t>j ceiling</t>
+  </si>
+  <si>
+    <t>Value in use - optimum j</t>
+  </si>
+  <si>
+    <t>Value in use - ceiling j</t>
   </si>
 </sst>
 </file>
@@ -5050,7 +5263,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5153,6 +5366,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5380,7 +5599,7 @@
     <xf numFmtId="0" fontId="28" fillId="10" borderId="11"/>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="11"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -5562,6 +5781,15 @@
     <xf numFmtId="170" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="32" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="25" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="39" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="26" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -8003,6 +8231,7 @@
       </c>
       <c r="D22" s="44">
         <f>IFERROR(cal_Dint,VLOOKUP(rx_ver,$A$84:$I$87,4,FALSE))</f>
+        <v>55</v>
       </c>
       <c r="E22" s="101" t="s">
         <v>176</v>
@@ -8046,6 +8275,7 @@
       </c>
       <c r="D24" s="44">
         <f>IFERROR(cal_Vtot,VLOOKUP(rx_ver,$A$84:$I$87,6,FALSE))</f>
+        <v>20</v>
       </c>
       <c r="E24" s="101" t="s">
         <v>176</v>
@@ -9295,6 +9525,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -9505,6 +9736,7 @@
       </c>
       <c r="D11" s="50">
         <f>IFERROR(cal_gerrit_slope,1.03)</f>
+        <v>1.03</v>
       </c>
       <c r="E11" s="115" t="s">
         <v>322</v>
@@ -9526,6 +9758,7 @@
       </c>
       <c r="D12" s="54">
         <f>IFERROR(cal_gerrit_int,2.6)</f>
+        <v>2.6</v>
       </c>
       <c r="E12" s="115" t="s">
         <v>326</v>
@@ -9652,6 +9885,7 @@
       </c>
       <c r="D18" s="114">
         <f>IFERROR(cal_etaF,1)</f>
+        <v>1</v>
       </c>
       <c r="E18" s="57" t="s">
         <v>345</v>
@@ -9827,6 +10061,7 @@
       </c>
       <c r="D26" s="114">
         <f>IFERROR(cal_etaF_OER,1)</f>
+        <v>1</v>
       </c>
       <c r="E26" s="122" t="s">
         <v>372</v>
@@ -9942,7 +10177,8 @@
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="24">
-        <f>IFERROR(cal_sinter,IF(ISNUMBER(VLOOKUP(electrode_sel,$A$35:$I$38,5,FALSE)),VLOOKUP(electrode_sel,$A$35:$I$38,5,FALSE),0))</f>
+        <f ca="1">IFERROR(cal_sinter,IF(ISNUMBER(VLOOKUP(electrode_sel,$A$35:$I$38,5,FALSE)),VLOOKUP(electrode_sel,$A$35:$I$38,5,FALSE),0))</f>
+        <v>0</v>
       </c>
       <c r="E32" s="107" t="s">
         <v>387</v>
@@ -10479,6 +10715,7 @@
       </c>
       <c r="D56" s="48">
         <f>IFERROR(cal_j_opt,IFERROR(VLOOKUP(Summary!$D$4,$A$66:$E$71,2,FALSE),j_opt_default))</f>
+        <v>2.14</v>
       </c>
       <c r="E56" s="101" t="s">
         <v>1396</v>
@@ -10496,6 +10733,7 @@
       </c>
       <c r="D57" s="48">
         <f>IFERROR(cal_j_ceiling,IFERROR(VLOOKUP(Summary!$D$4,$A$66:$E$71,3,FALSE),j_ceiling_default))</f>
+        <v>4.29</v>
       </c>
       <c r="E57" s="101" t="s">
         <v>1399</v>
@@ -13306,6 +13544,7 @@
       </c>
       <c r="D10" s="111">
         <f>IFERROR(cal_knall_H2,6)</f>
+        <v>6</v>
       </c>
       <c r="E10" s="61" t="s">
         <v>411</v>
@@ -13324,6 +13563,7 @@
       </c>
       <c r="D11" s="111">
         <f>IFERROR(cal_knall_O2,2)</f>
+        <v>2</v>
       </c>
       <c r="E11" s="61" t="s">
         <v>414</v>
@@ -13342,6 +13582,7 @@
       </c>
       <c r="D12" s="111">
         <f>IFERROR(cal_knall_CO2,1)</f>
+        <v>1</v>
       </c>
       <c r="E12" s="61" t="s">
         <v>417</v>
@@ -13957,8 +14198,9 @@
       <c r="C45" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="71">
+      <c r="D45" s="71" t="e">
         <f>IFERROR(cal_DO_min,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,2,FALSE),NA()))</f>
+        <v>#N/A</v>
       </c>
       <c r="E45" s="20"/>
       <c r="F45" s="20"/>
@@ -13973,8 +14215,9 @@
       <c r="C46" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D46" s="24">
+      <c r="D46" s="24" t="e">
         <f>IFERROR(cal_DO_opt,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,3,FALSE),NA()))</f>
+        <v>#N/A</v>
       </c>
       <c r="E46" s="20"/>
       <c r="F46" s="20"/>
@@ -13989,8 +14232,9 @@
       <c r="C47" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D47" s="24">
+      <c r="D47" s="24" t="e">
         <f>IFERROR(cal_DO_impair,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,4,FALSE),NA()))</f>
+        <v>#N/A</v>
       </c>
       <c r="E47" s="20"/>
       <c r="F47" s="20"/>
@@ -14005,8 +14249,9 @@
       <c r="C48" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D48" s="24">
+      <c r="D48" s="24" t="e">
         <f>IFERROR(cal_DO_toxic,IF(ISNUMBER(VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE)),VLOOKUP(organism_sel,$A$52:$F$57,5,FALSE),NA()))</f>
+        <v>#N/A</v>
       </c>
       <c r="E48" s="20"/>
       <c r="F48" s="20"/>
@@ -14578,7 +14823,7 @@
         <v>556</v>
       </c>
       <c r="D20" s="27">
-        <f>Electrochemistry!$D$32</f>
+        <f ca="1">Electrochemistry!$D$32</f>
         <v>0</v>
       </c>
       <c r="E20" s="23" t="str">
@@ -14914,7 +15159,7 @@
         <v>605</v>
       </c>
       <c r="D39" s="77">
-        <f>CHOOSE(por_grade+1,por0_um,por1_um,por2_um,por3_um,por4_um,por5_um)/1000000</f>
+        <f ca="1">CHOOSE(por_grade+1,por0_um,por1_um,por2_um,por3_um,por4_um,por5_um)/1000000</f>
         <v>2.05E-4</v>
       </c>
       <c r="E39" s="101" t="s">
@@ -16007,6 +16252,7 @@
       </c>
       <c r="D97" s="124">
         <f>IFERROR(cal_kLa,0)</f>
+        <v>0</v>
       </c>
       <c r="E97" s="69" t="s">
         <v>769</v>
@@ -19476,1792 +19722,2517 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:N140"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M139"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16" width="12" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CALIBRATIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fill the white cells only: Researcher, Date, the key (Reactor or Organism) and the raw measurements. Grey cells are computed automatically. Set Include to y for rows the model should use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The value in use for each calibration follows the rule stated under its heading. If no rows are included yet, the model falls back to its built-in default.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GERRIT CURRENT  (electrolysis current law)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use: least-squares fit of current vs intensity, averaged across all included runs for the active reactor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Researcher</t>
-        </is>
-      </c>
-      <c r="B7" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="C7" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reactor</t>
-        </is>
-      </c>
-      <c r="D7" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intensity</t>
-        </is>
-      </c>
-      <c r="E7" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Current</t>
-        </is>
-      </c>
-      <c r="F7" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type (auto)</t>
-        </is>
-      </c>
-      <c r="G7" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Include?</t>
-        </is>
-      </c>
-      <c r="H7" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="53"/>
-      <c r="B8" s="124"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="48">
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/gerrit-current.md","ELECTROLYSIS CURRENT")</f>
+        <v>ELECTROLYSIS CURRENT</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="131"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="138" t="str">
         <f>IFERROR(VLOOKUP(C8,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="53"/>
-      <c r="B9" s="124"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="124"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="48">
+        <v/>
+      </c>
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="131"/>
+      <c r="B9" s="132"/>
+      <c r="C9" s="131"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="138" t="str">
         <f>IFERROR(VLOOKUP(C9,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="53"/>
-      <c r="B10" s="124"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="48">
+        <v/>
+      </c>
+      <c r="G9" s="131"/>
+      <c r="H9" s="131"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="131"/>
+      <c r="B10" s="132"/>
+      <c r="C10" s="131"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="138" t="str">
         <f>IFERROR(VLOOKUP(C10,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="53"/>
-      <c r="B11" s="124"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="48">
+        <v/>
+      </c>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="131"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="138" t="str">
         <f>IFERROR(VLOOKUP(C11,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="53"/>
-      <c r="B12" s="124"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="48">
+        <v/>
+      </c>
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="131"/>
+      <c r="B12" s="132"/>
+      <c r="C12" s="131"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="138" t="str">
         <f>IFERROR(VLOOKUP(C12,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="53"/>
-      <c r="B13" s="124"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="48">
+        <v/>
+      </c>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="131"/>
+      <c r="B13" s="132"/>
+      <c r="C13" s="131"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="138" t="str">
         <f>IFERROR(VLOOKUP(C13,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="53"/>
-      <c r="B14" s="124"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="48">
+        <v/>
+      </c>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="131"/>
+      <c r="B14" s="132"/>
+      <c r="C14" s="131"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="138" t="str">
         <f>IFERROR(VLOOKUP(C14,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="53"/>
-      <c r="B15" s="124"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="124"/>
-      <c r="E15" s="124"/>
-      <c r="F15" s="48">
+        <v/>
+      </c>
+      <c r="G14" s="131"/>
+      <c r="H14" s="131"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="131"/>
+      <c r="B15" s="132"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="138" t="str">
         <f>IFERROR(VLOOKUP(C15,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - slope</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mA/%</t>
-        </is>
-      </c>
-      <c r="D16" s="48">
-        <f>(COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*E8:E15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(E8:E15,C8:C15,Summary!$D$2,G8:G15,"y"))/(COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*D8:D15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y"))</f>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - intercept</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mA</t>
-        </is>
-      </c>
-      <c r="D17" s="48">
+        <v/>
+      </c>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="17" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="D16" s="48" t="e" cm="1">
+        <f t="array" ref="D16">(COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*E8:E15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(E8:E15,C8:C15,Summary!$D$2,G8:G15,"y"))/(COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*D8:D15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y"))</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="D17" s="48" t="e">
         <f>(SUMIFS(E8:E15,C8:C15,Summary!$D$2,G8:G15,"y")-((COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*E8:E15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(E8:E15,C8:C15,Summary!$D$2,G8:G15,"y"))/(COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")*SUMPRODUCT((C8:C15=Summary!$D$2)*(G8:G15="y")*D8:D15*D8:D15)-SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")*SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y")))*SUMIFS(D8:D15,C8:C15,Summary!$D$2,G8:G15,"y"))/COUNTIFS(C8:C15,Summary!$D$2,G8:G15,"y")</f>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FARADAIC EFFICIENCY  (cathodic etaF, anodic etaF_OER)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use: average of the included runs for the active reactor, taken separately for the H2 (cathode) and O2 (anode) electrodes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Researcher</t>
-        </is>
-      </c>
-      <c r="B22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="C22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reactor</t>
-        </is>
-      </c>
-      <c r="D22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Charge Q</t>
-        </is>
-      </c>
-      <c r="E22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gas volume</t>
-        </is>
-      </c>
-      <c r="F22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Temp</t>
-        </is>
-      </c>
-      <c r="G22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pressure</t>
-        </is>
-      </c>
-      <c r="H22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrode</t>
-        </is>
-      </c>
-      <c r="I22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">etaF (computed)</t>
-        </is>
-      </c>
-      <c r="J22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type (auto)</t>
-        </is>
-      </c>
-      <c r="K22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Include?</t>
-        </is>
-      </c>
-      <c r="L22" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="53"/>
-      <c r="B23" s="124"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="124"/>
-      <c r="I23" s="48">
-        <f>IFERROR((G23*(E23/1000000)/(8.314*(F23+273.15)))/(D23/(IF(H23="H2",2,4)*96485)),"")</f>
-      </c>
-      <c r="J23" s="48">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/faradaic-efficiency.md","FARADAIC EFFICIENCY  (cathodic etaF, anodic etaF_OER)")</f>
+        <v>FARADAIC EFFICIENCY  (cathodic etaF, anodic etaF_OER)</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="16" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>1456</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>1446</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>1447</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="131"/>
+      <c r="B23" s="132"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="132"/>
+      <c r="I23" s="138" t="str">
+        <f t="shared" ref="I23:I30" si="0">IFERROR((G23*(E23/1000000)/(8.314*(F23+273.15)))/(D23/(IF(H23="H2",2,4)*96485)),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="138" t="str">
         <f>IFERROR(VLOOKUP(C23,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="53"/>
-      <c r="B24" s="124"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="124"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124"/>
-      <c r="I24" s="48">
-        <f>IFERROR((G24*(E24/1000000)/(8.314*(F24+273.15)))/(D24/(IF(H24="H2",2,4)*96485)),"")</f>
-      </c>
-      <c r="J24" s="48">
+        <v/>
+      </c>
+      <c r="K23" s="131"/>
+      <c r="L23" s="131"/>
+      <c r="M23" s="98"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="131"/>
+      <c r="B24" s="132"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="132"/>
+      <c r="E24" s="132"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="132"/>
+      <c r="H24" s="132"/>
+      <c r="I24" s="138" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J24" s="138" t="str">
         <f>IFERROR(VLOOKUP(C24,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="53"/>
-      <c r="B25" s="124"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="124"/>
-      <c r="E25" s="124"/>
-      <c r="F25" s="124"/>
-      <c r="G25" s="124"/>
-      <c r="H25" s="124"/>
-      <c r="I25" s="48">
-        <f>IFERROR((G25*(E25/1000000)/(8.314*(F25+273.15)))/(D25/(IF(H25="H2",2,4)*96485)),"")</f>
-      </c>
-      <c r="J25" s="48">
+        <v/>
+      </c>
+      <c r="K24" s="131"/>
+      <c r="L24" s="131"/>
+      <c r="M24" s="98"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="131"/>
+      <c r="B25" s="132"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="132"/>
+      <c r="I25" s="138" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J25" s="138" t="str">
         <f>IFERROR(VLOOKUP(C25,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="53"/>
-      <c r="B26" s="124"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="124"/>
-      <c r="E26" s="124"/>
-      <c r="F26" s="124"/>
-      <c r="G26" s="124"/>
-      <c r="H26" s="124"/>
-      <c r="I26" s="48">
-        <f>IFERROR((G26*(E26/1000000)/(8.314*(F26+273.15)))/(D26/(IF(H26="H2",2,4)*96485)),"")</f>
-      </c>
-      <c r="J26" s="48">
+        <v/>
+      </c>
+      <c r="K25" s="131"/>
+      <c r="L25" s="131"/>
+      <c r="M25" s="98"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="131"/>
+      <c r="B26" s="132"/>
+      <c r="C26" s="131"/>
+      <c r="D26" s="132"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="132"/>
+      <c r="H26" s="132"/>
+      <c r="I26" s="138" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J26" s="138" t="str">
         <f>IFERROR(VLOOKUP(C26,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="53"/>
-      <c r="B27" s="124"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="124"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="124"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="124"/>
-      <c r="I27" s="48">
-        <f>IFERROR((G27*(E27/1000000)/(8.314*(F27+273.15)))/(D27/(IF(H27="H2",2,4)*96485)),"")</f>
-      </c>
-      <c r="J27" s="48">
+        <v/>
+      </c>
+      <c r="K26" s="131"/>
+      <c r="L26" s="131"/>
+      <c r="M26" s="98"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" s="131"/>
+      <c r="B27" s="132"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="138" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J27" s="138" t="str">
         <f>IFERROR(VLOOKUP(C27,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="53"/>
-      <c r="B28" s="124"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="124"/>
-      <c r="E28" s="124"/>
-      <c r="F28" s="124"/>
-      <c r="G28" s="124"/>
-      <c r="H28" s="124"/>
-      <c r="I28" s="48">
-        <f>IFERROR((G28*(E28/1000000)/(8.314*(F28+273.15)))/(D28/(IF(H28="H2",2,4)*96485)),"")</f>
-      </c>
-      <c r="J28" s="48">
+        <v/>
+      </c>
+      <c r="K27" s="131"/>
+      <c r="L27" s="131"/>
+      <c r="M27" s="98"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28" s="131"/>
+      <c r="B28" s="132"/>
+      <c r="C28" s="131"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="138" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J28" s="138" t="str">
         <f>IFERROR(VLOOKUP(C28,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="53"/>
-      <c r="B29" s="124"/>
-      <c r="C29" s="53"/>
-      <c r="D29" s="124"/>
-      <c r="E29" s="124"/>
-      <c r="F29" s="124"/>
-      <c r="G29" s="124"/>
-      <c r="H29" s="124"/>
-      <c r="I29" s="48">
-        <f>IFERROR((G29*(E29/1000000)/(8.314*(F29+273.15)))/(D29/(IF(H29="H2",2,4)*96485)),"")</f>
-      </c>
-      <c r="J29" s="48">
+        <v/>
+      </c>
+      <c r="K28" s="131"/>
+      <c r="L28" s="131"/>
+      <c r="M28" s="98"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29" s="131"/>
+      <c r="B29" s="132"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="132"/>
+      <c r="H29" s="132"/>
+      <c r="I29" s="138" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J29" s="138" t="str">
         <f>IFERROR(VLOOKUP(C29,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="K29" s="53"/>
-      <c r="L29" s="53"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="53"/>
-      <c r="B30" s="124"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="124"/>
-      <c r="E30" s="124"/>
-      <c r="F30" s="124"/>
-      <c r="G30" s="124"/>
-      <c r="H30" s="124"/>
-      <c r="I30" s="48">
-        <f>IFERROR((G30*(E30/1000000)/(8.314*(F30+273.15)))/(D30/(IF(H30="H2",2,4)*96485)),"")</f>
-      </c>
-      <c r="J30" s="48">
+        <v/>
+      </c>
+      <c r="K29" s="131"/>
+      <c r="L29" s="131"/>
+      <c r="M29" s="98"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30" s="131"/>
+      <c r="B30" s="132"/>
+      <c r="C30" s="131"/>
+      <c r="D30" s="132"/>
+      <c r="E30" s="132"/>
+      <c r="F30" s="132"/>
+      <c r="G30" s="132"/>
+      <c r="H30" s="132"/>
+      <c r="I30" s="138" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J30" s="138" t="str">
         <f>IFERROR(VLOOKUP(C30,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="K30" s="53"/>
-      <c r="L30" s="53"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - cathode (H2)</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="D31" s="48">
+        <v/>
+      </c>
+      <c r="K30" s="131"/>
+      <c r="L30" s="131"/>
+      <c r="M30" s="98"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31" s="134" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B31" s="98"/>
+      <c r="C31" s="135" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="133" t="e">
         <f>AVERAGEIFS(I23:I30,C23:C30,Summary!$D$2,K23:K30,"y",H23:H30,"H2")</f>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - anode (O2)</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="D32" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="98"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="98"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A32" s="134" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B32" s="98"/>
+      <c r="C32" s="135" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="133" t="e">
         <f>AVERAGEIFS(I23:I30,C23:C30,Summary!$D$2,K23:K30,"y",H23:H30,"O2")</f>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SURFACE kLa  (oxygen surface transfer)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use: average of the included kLa runs for the active reactor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Researcher</t>
-        </is>
-      </c>
-      <c r="B37" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="C37" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reactor</t>
-        </is>
-      </c>
-      <c r="D37" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kLa</t>
-        </is>
-      </c>
-      <c r="E37" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type (auto)</t>
-        </is>
-      </c>
-      <c r="F37" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Include?</t>
-        </is>
-      </c>
-      <c r="G37" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="53"/>
-      <c r="B38" s="124"/>
-      <c r="C38" s="53"/>
-      <c r="D38" s="124"/>
-      <c r="E38" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98"/>
+      <c r="H32" s="98"/>
+      <c r="I32" s="98"/>
+      <c r="J32" s="98"/>
+      <c r="K32" s="98"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="98"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" s="98"/>
+      <c r="B33" s="98"/>
+      <c r="C33" s="98"/>
+      <c r="D33" s="98"/>
+      <c r="E33" s="98"/>
+      <c r="F33" s="98"/>
+      <c r="G33" s="98"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="98"/>
+      <c r="J33" s="98"/>
+      <c r="K33" s="98"/>
+      <c r="L33" s="98"/>
+      <c r="M33" s="98"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" s="98"/>
+      <c r="B34" s="98"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="98"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="98"/>
+    </row>
+    <row r="35" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="136" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/surface-kla.md","SURFACE kLa  (oxygen surface transfer)")</f>
+        <v>SURFACE kLa  (oxygen surface transfer)</v>
+      </c>
+      <c r="B35" s="98"/>
+      <c r="C35" s="98"/>
+      <c r="D35" s="98"/>
+      <c r="E35" s="98"/>
+      <c r="F35" s="98"/>
+      <c r="G35" s="98"/>
+      <c r="H35" s="98"/>
+      <c r="I35" s="98"/>
+      <c r="J35" s="98"/>
+      <c r="K35" s="98"/>
+      <c r="L35" s="98"/>
+      <c r="M35" s="98"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" s="98" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B36" s="98"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="98"/>
+      <c r="E36" s="98"/>
+      <c r="F36" s="98"/>
+      <c r="G36" s="98"/>
+      <c r="H36" s="98"/>
+      <c r="I36" s="98"/>
+      <c r="J36" s="98"/>
+      <c r="K36" s="98"/>
+      <c r="L36" s="98"/>
+      <c r="M36" s="98"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" s="137" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B37" s="137" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C37" s="137" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="137" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E37" s="137" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F37" s="137" t="s">
+        <v>1447</v>
+      </c>
+      <c r="G37" s="137" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H37" s="98"/>
+      <c r="I37" s="98"/>
+      <c r="J37" s="98"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="98"/>
+      <c r="M37" s="98"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" s="131"/>
+      <c r="B38" s="132"/>
+      <c r="C38" s="131"/>
+      <c r="D38" s="132"/>
+      <c r="E38" s="138" t="str">
         <f>IFERROR(VLOOKUP(C38,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="F38" s="53"/>
-      <c r="G38" s="53"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39" s="53"/>
-      <c r="B39" s="124"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="124"/>
-      <c r="E39" s="48">
+        <v/>
+      </c>
+      <c r="F38" s="131"/>
+      <c r="G38" s="131"/>
+      <c r="H38" s="98"/>
+      <c r="I38" s="98"/>
+      <c r="J38" s="98"/>
+      <c r="K38" s="98"/>
+      <c r="L38" s="98"/>
+      <c r="M38" s="98"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A39" s="131"/>
+      <c r="B39" s="132"/>
+      <c r="C39" s="131"/>
+      <c r="D39" s="132"/>
+      <c r="E39" s="138" t="str">
         <f>IFERROR(VLOOKUP(C39,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40" s="53"/>
-      <c r="B40" s="124"/>
-      <c r="C40" s="53"/>
-      <c r="D40" s="124"/>
-      <c r="E40" s="48">
+        <v/>
+      </c>
+      <c r="F39" s="131"/>
+      <c r="G39" s="131"/>
+      <c r="H39" s="98"/>
+      <c r="I39" s="98"/>
+      <c r="J39" s="98"/>
+      <c r="K39" s="98"/>
+      <c r="L39" s="98"/>
+      <c r="M39" s="98"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A40" s="131"/>
+      <c r="B40" s="132"/>
+      <c r="C40" s="131"/>
+      <c r="D40" s="132"/>
+      <c r="E40" s="138" t="str">
         <f>IFERROR(VLOOKUP(C40,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="F40" s="53"/>
-      <c r="G40" s="53"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="53"/>
-      <c r="B41" s="124"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="124"/>
-      <c r="E41" s="48">
+        <v/>
+      </c>
+      <c r="F40" s="131"/>
+      <c r="G40" s="131"/>
+      <c r="H40" s="98"/>
+      <c r="I40" s="98"/>
+      <c r="J40" s="98"/>
+      <c r="K40" s="98"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="98"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A41" s="131"/>
+      <c r="B41" s="132"/>
+      <c r="C41" s="131"/>
+      <c r="D41" s="132"/>
+      <c r="E41" s="138" t="str">
         <f>IFERROR(VLOOKUP(C41,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="F41" s="53"/>
-      <c r="G41" s="53"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42" s="53"/>
-      <c r="B42" s="124"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="124"/>
-      <c r="E42" s="48">
+        <v/>
+      </c>
+      <c r="F41" s="131"/>
+      <c r="G41" s="131"/>
+      <c r="H41" s="98"/>
+      <c r="I41" s="98"/>
+      <c r="J41" s="98"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="98"/>
+      <c r="M41" s="98"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A42" s="131"/>
+      <c r="B42" s="132"/>
+      <c r="C42" s="131"/>
+      <c r="D42" s="132"/>
+      <c r="E42" s="138" t="str">
         <f>IFERROR(VLOOKUP(C42,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" s="53"/>
-      <c r="B43" s="124"/>
-      <c r="C43" s="53"/>
-      <c r="D43" s="124"/>
-      <c r="E43" s="48">
+        <v/>
+      </c>
+      <c r="F42" s="131"/>
+      <c r="G42" s="131"/>
+      <c r="H42" s="98"/>
+      <c r="I42" s="98"/>
+      <c r="J42" s="98"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="98"/>
+      <c r="M42" s="98"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A43" s="131"/>
+      <c r="B43" s="132"/>
+      <c r="C43" s="131"/>
+      <c r="D43" s="132"/>
+      <c r="E43" s="138" t="str">
         <f>IFERROR(VLOOKUP(C43,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="F43" s="53"/>
-      <c r="G43" s="53"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" s="53"/>
-      <c r="B44" s="124"/>
-      <c r="C44" s="53"/>
-      <c r="D44" s="124"/>
-      <c r="E44" s="48">
+        <v/>
+      </c>
+      <c r="F43" s="131"/>
+      <c r="G43" s="131"/>
+      <c r="H43" s="98"/>
+      <c r="I43" s="98"/>
+      <c r="J43" s="98"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="98"/>
+      <c r="M43" s="98"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A44" s="131"/>
+      <c r="B44" s="132"/>
+      <c r="C44" s="131"/>
+      <c r="D44" s="132"/>
+      <c r="E44" s="138" t="str">
         <f>IFERROR(VLOOKUP(C44,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="F44" s="53"/>
-      <c r="G44" s="53"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A45" s="53"/>
-      <c r="B45" s="124"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="124"/>
-      <c r="E45" s="48">
+        <v/>
+      </c>
+      <c r="F44" s="131"/>
+      <c r="G44" s="131"/>
+      <c r="H44" s="98"/>
+      <c r="I44" s="98"/>
+      <c r="J44" s="98"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="98"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A45" s="131"/>
+      <c r="B45" s="132"/>
+      <c r="C45" s="131"/>
+      <c r="D45" s="132"/>
+      <c r="E45" s="138" t="str">
         <f>IFERROR(VLOOKUP(C45,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="F45" s="53"/>
-      <c r="G45" s="53"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - kLa</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1/s</t>
-        </is>
-      </c>
-      <c r="D46" s="48">
+        <v/>
+      </c>
+      <c r="F45" s="131"/>
+      <c r="G45" s="131"/>
+      <c r="H45" s="98"/>
+      <c r="I45" s="98"/>
+      <c r="J45" s="98"/>
+      <c r="K45" s="98"/>
+      <c r="L45" s="98"/>
+      <c r="M45" s="98"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A46" s="134" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B46" s="98"/>
+      <c r="C46" s="135" t="s">
+        <v>645</v>
+      </c>
+      <c r="D46" s="133" t="e">
         <f>AVERAGEIFS(D38:D45,C38:C45,Summary!$D$2,F38:F45,"y")</f>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO2 FLOW  (dosing flow rate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use: the most recent included measurement for the active reactor (a flow rate is a valve/hardware setting, so the latest reading replaces older ones).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Researcher</t>
-        </is>
-      </c>
-      <c r="B51" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="C51" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reactor</t>
-        </is>
-      </c>
-      <c r="D51" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO2 volume</t>
-        </is>
-      </c>
-      <c r="E51" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time</t>
-        </is>
-      </c>
-      <c r="F51" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Flow (computed)</t>
-        </is>
-      </c>
-      <c r="G51" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type (auto)</t>
-        </is>
-      </c>
-      <c r="H51" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Include?</t>
-        </is>
-      </c>
-      <c r="I51" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" s="53"/>
-      <c r="B52" s="124"/>
-      <c r="C52" s="53"/>
-      <c r="D52" s="124"/>
-      <c r="E52" s="124"/>
-      <c r="F52" s="48">
-        <f>IFERROR(D52/E52,"")</f>
-      </c>
-      <c r="G52" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E46" s="98"/>
+      <c r="F46" s="98"/>
+      <c r="G46" s="98"/>
+      <c r="H46" s="98"/>
+      <c r="I46" s="98"/>
+      <c r="J46" s="98"/>
+      <c r="K46" s="98"/>
+      <c r="L46" s="98"/>
+      <c r="M46" s="98"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A47" s="98"/>
+      <c r="B47" s="98"/>
+      <c r="C47" s="98"/>
+      <c r="D47" s="98"/>
+      <c r="E47" s="98"/>
+      <c r="F47" s="98"/>
+      <c r="G47" s="98"/>
+      <c r="H47" s="98"/>
+      <c r="I47" s="98"/>
+      <c r="J47" s="98"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="98"/>
+      <c r="M47" s="98"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A48" s="98"/>
+      <c r="B48" s="98"/>
+      <c r="C48" s="98"/>
+      <c r="D48" s="98"/>
+      <c r="E48" s="98"/>
+      <c r="F48" s="98"/>
+      <c r="G48" s="98"/>
+      <c r="H48" s="98"/>
+      <c r="I48" s="98"/>
+      <c r="J48" s="98"/>
+      <c r="K48" s="98"/>
+      <c r="L48" s="98"/>
+      <c r="M48" s="98"/>
+    </row>
+    <row r="49" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="136" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/flow-calibration.md","CO2 FLOW  (dosing flow rate)")</f>
+        <v>CO2 FLOW  (dosing flow rate)</v>
+      </c>
+      <c r="B49" s="98"/>
+      <c r="C49" s="98"/>
+      <c r="D49" s="98"/>
+      <c r="E49" s="98"/>
+      <c r="F49" s="98"/>
+      <c r="G49" s="98"/>
+      <c r="H49" s="98"/>
+      <c r="I49" s="98"/>
+      <c r="J49" s="98"/>
+      <c r="K49" s="98"/>
+      <c r="L49" s="98"/>
+      <c r="M49" s="98"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A50" s="98" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B50" s="98"/>
+      <c r="C50" s="98"/>
+      <c r="D50" s="98"/>
+      <c r="E50" s="98"/>
+      <c r="F50" s="98"/>
+      <c r="G50" s="98"/>
+      <c r="H50" s="98"/>
+      <c r="I50" s="98"/>
+      <c r="J50" s="98"/>
+      <c r="K50" s="98"/>
+      <c r="L50" s="98"/>
+      <c r="M50" s="98"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A51" s="137" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B51" s="137" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C51" s="137" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="137" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E51" s="137" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F51" s="137" t="s">
+        <v>1465</v>
+      </c>
+      <c r="G51" s="137" t="s">
+        <v>1446</v>
+      </c>
+      <c r="H51" s="137" t="s">
+        <v>1447</v>
+      </c>
+      <c r="I51" s="137" t="s">
+        <v>1448</v>
+      </c>
+      <c r="J51" s="98"/>
+      <c r="K51" s="98"/>
+      <c r="L51" s="98"/>
+      <c r="M51" s="98"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A52" s="131"/>
+      <c r="B52" s="132"/>
+      <c r="C52" s="131"/>
+      <c r="D52" s="132"/>
+      <c r="E52" s="132"/>
+      <c r="F52" s="138" t="str">
+        <f t="shared" ref="F52:F59" si="1">IFERROR(D52/E52,"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="138" t="str">
         <f>IFERROR(VLOOKUP(C52,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="H52" s="53"/>
-      <c r="I52" s="53"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A53" s="53"/>
-      <c r="B53" s="124"/>
-      <c r="C53" s="53"/>
-      <c r="D53" s="124"/>
-      <c r="E53" s="124"/>
-      <c r="F53" s="48">
-        <f>IFERROR(D53/E53,"")</f>
-      </c>
-      <c r="G53" s="48">
+        <v/>
+      </c>
+      <c r="H52" s="131"/>
+      <c r="I52" s="131"/>
+      <c r="J52" s="98"/>
+      <c r="K52" s="98"/>
+      <c r="L52" s="98"/>
+      <c r="M52" s="98"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A53" s="131"/>
+      <c r="B53" s="132"/>
+      <c r="C53" s="131"/>
+      <c r="D53" s="132"/>
+      <c r="E53" s="132"/>
+      <c r="F53" s="138" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G53" s="138" t="str">
         <f>IFERROR(VLOOKUP(C53,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="H53" s="53"/>
-      <c r="I53" s="53"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" s="53"/>
-      <c r="B54" s="124"/>
-      <c r="C54" s="53"/>
-      <c r="D54" s="124"/>
-      <c r="E54" s="124"/>
-      <c r="F54" s="48">
-        <f>IFERROR(D54/E54,"")</f>
-      </c>
-      <c r="G54" s="48">
+        <v/>
+      </c>
+      <c r="H53" s="131"/>
+      <c r="I53" s="131"/>
+      <c r="J53" s="98"/>
+      <c r="K53" s="98"/>
+      <c r="L53" s="98"/>
+      <c r="M53" s="98"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A54" s="131"/>
+      <c r="B54" s="132"/>
+      <c r="C54" s="131"/>
+      <c r="D54" s="132"/>
+      <c r="E54" s="132"/>
+      <c r="F54" s="138" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G54" s="138" t="str">
         <f>IFERROR(VLOOKUP(C54,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="H54" s="53"/>
-      <c r="I54" s="53"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" s="53"/>
-      <c r="B55" s="124"/>
-      <c r="C55" s="53"/>
-      <c r="D55" s="124"/>
-      <c r="E55" s="124"/>
-      <c r="F55" s="48">
-        <f>IFERROR(D55/E55,"")</f>
-      </c>
-      <c r="G55" s="48">
+        <v/>
+      </c>
+      <c r="H54" s="131"/>
+      <c r="I54" s="131"/>
+      <c r="J54" s="98"/>
+      <c r="K54" s="98"/>
+      <c r="L54" s="98"/>
+      <c r="M54" s="98"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A55" s="131"/>
+      <c r="B55" s="132"/>
+      <c r="C55" s="131"/>
+      <c r="D55" s="132"/>
+      <c r="E55" s="132"/>
+      <c r="F55" s="138" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G55" s="138" t="str">
         <f>IFERROR(VLOOKUP(C55,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="H55" s="53"/>
-      <c r="I55" s="53"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A56" s="53"/>
-      <c r="B56" s="124"/>
-      <c r="C56" s="53"/>
-      <c r="D56" s="124"/>
-      <c r="E56" s="124"/>
-      <c r="F56" s="48">
-        <f>IFERROR(D56/E56,"")</f>
-      </c>
-      <c r="G56" s="48">
+        <v/>
+      </c>
+      <c r="H55" s="131"/>
+      <c r="I55" s="131"/>
+      <c r="J55" s="98"/>
+      <c r="K55" s="98"/>
+      <c r="L55" s="98"/>
+      <c r="M55" s="98"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A56" s="131"/>
+      <c r="B56" s="132"/>
+      <c r="C56" s="131"/>
+      <c r="D56" s="132"/>
+      <c r="E56" s="132"/>
+      <c r="F56" s="138" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G56" s="138" t="str">
         <f>IFERROR(VLOOKUP(C56,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="H56" s="53"/>
-      <c r="I56" s="53"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A57" s="53"/>
-      <c r="B57" s="124"/>
-      <c r="C57" s="53"/>
-      <c r="D57" s="124"/>
-      <c r="E57" s="124"/>
-      <c r="F57" s="48">
-        <f>IFERROR(D57/E57,"")</f>
-      </c>
-      <c r="G57" s="48">
+        <v/>
+      </c>
+      <c r="H56" s="131"/>
+      <c r="I56" s="131"/>
+      <c r="J56" s="98"/>
+      <c r="K56" s="98"/>
+      <c r="L56" s="98"/>
+      <c r="M56" s="98"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A57" s="131"/>
+      <c r="B57" s="132"/>
+      <c r="C57" s="131"/>
+      <c r="D57" s="132"/>
+      <c r="E57" s="132"/>
+      <c r="F57" s="138" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G57" s="138" t="str">
         <f>IFERROR(VLOOKUP(C57,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="H57" s="53"/>
-      <c r="I57" s="53"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58" s="53"/>
-      <c r="B58" s="124"/>
-      <c r="C58" s="53"/>
-      <c r="D58" s="124"/>
-      <c r="E58" s="124"/>
-      <c r="F58" s="48">
-        <f>IFERROR(D58/E58,"")</f>
-      </c>
-      <c r="G58" s="48">
+        <v/>
+      </c>
+      <c r="H57" s="131"/>
+      <c r="I57" s="131"/>
+      <c r="J57" s="98"/>
+      <c r="K57" s="98"/>
+      <c r="L57" s="98"/>
+      <c r="M57" s="98"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A58" s="131"/>
+      <c r="B58" s="132"/>
+      <c r="C58" s="131"/>
+      <c r="D58" s="132"/>
+      <c r="E58" s="132"/>
+      <c r="F58" s="138" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G58" s="138" t="str">
         <f>IFERROR(VLOOKUP(C58,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="H58" s="53"/>
-      <c r="I58" s="53"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A59" s="53"/>
-      <c r="B59" s="124"/>
-      <c r="C59" s="53"/>
-      <c r="D59" s="124"/>
-      <c r="E59" s="124"/>
-      <c r="F59" s="48">
-        <f>IFERROR(D59/E59,"")</f>
-      </c>
-      <c r="G59" s="48">
+        <v/>
+      </c>
+      <c r="H58" s="131"/>
+      <c r="I58" s="131"/>
+      <c r="J58" s="98"/>
+      <c r="K58" s="98"/>
+      <c r="L58" s="98"/>
+      <c r="M58" s="98"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A59" s="131"/>
+      <c r="B59" s="132"/>
+      <c r="C59" s="131"/>
+      <c r="D59" s="132"/>
+      <c r="E59" s="132"/>
+      <c r="F59" s="138" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G59" s="138" t="str">
         <f>IFERROR(VLOOKUP(C59,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="H59" s="53"/>
-      <c r="I59" s="53"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A60" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - flow rate</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mL/s</t>
-        </is>
-      </c>
-      <c r="D60" s="48">
-        <f>AVERAGEIFS(F52:F59,C52:C59,Summary!$D$2,H52:H59,"y",B52:B59,MAXIFS(B52:B59,C52:C59,Summary!$D$2,H52:H59,"y"))</f>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A63" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIAL GEOMETRY  (true volume &amp; bore depth)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A64" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use: average across included vials of the active reactor type (all vials of a type are nominally identical, so averaging improves the estimate).</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Researcher</t>
-        </is>
-      </c>
-      <c r="B65" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="C65" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reactor</t>
-        </is>
-      </c>
-      <c r="D65" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Headspace mass</t>
-        </is>
-      </c>
-      <c r="E65" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Body mass</t>
-        </is>
-      </c>
-      <c r="F65" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Temp</t>
-        </is>
-      </c>
-      <c r="G65" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">V total (computed)</t>
-        </is>
-      </c>
-      <c r="H65" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bore depth (computed)</t>
-        </is>
-      </c>
-      <c r="I65" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type (auto)</t>
-        </is>
-      </c>
-      <c r="J65" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Include?</t>
-        </is>
-      </c>
-      <c r="K65" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" s="53"/>
-      <c r="B66" s="124"/>
-      <c r="C66" s="53"/>
-      <c r="D66" s="124"/>
-      <c r="E66" s="124"/>
-      <c r="F66" s="124"/>
-      <c r="G66" s="48">
-        <f>IFERROR(E66/(0.99705-0.00028*(F66-25)),"")</f>
-      </c>
-      <c r="H66" s="48">
+        <v/>
+      </c>
+      <c r="H59" s="131"/>
+      <c r="I59" s="131"/>
+      <c r="J59" s="98"/>
+      <c r="K59" s="98"/>
+      <c r="L59" s="98"/>
+      <c r="M59" s="98"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A60" s="134" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B60" s="98"/>
+      <c r="C60" s="135" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D60" s="133" t="e">
+        <f ca="1">AVERAGEIFS(F52:F59,C52:C59,Summary!$D$2,H52:H59,"y",B52:B59,_xludf.MAXIFS(B52:B59,C52:C59,Summary!$D$2,H52:H59,"y"))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E60" s="98"/>
+      <c r="F60" s="98"/>
+      <c r="G60" s="98"/>
+      <c r="H60" s="98"/>
+      <c r="I60" s="98"/>
+      <c r="J60" s="98"/>
+      <c r="K60" s="98"/>
+      <c r="L60" s="98"/>
+      <c r="M60" s="98"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A61" s="98"/>
+      <c r="B61" s="98"/>
+      <c r="C61" s="98"/>
+      <c r="D61" s="98"/>
+      <c r="E61" s="98"/>
+      <c r="F61" s="98"/>
+      <c r="G61" s="98"/>
+      <c r="H61" s="98"/>
+      <c r="I61" s="98"/>
+      <c r="J61" s="98"/>
+      <c r="K61" s="98"/>
+      <c r="L61" s="98"/>
+      <c r="M61" s="98"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A62" s="98"/>
+      <c r="B62" s="98"/>
+      <c r="C62" s="98"/>
+      <c r="D62" s="98"/>
+      <c r="E62" s="98"/>
+      <c r="F62" s="98"/>
+      <c r="G62" s="98"/>
+      <c r="H62" s="98"/>
+      <c r="I62" s="98"/>
+      <c r="J62" s="98"/>
+      <c r="K62" s="98"/>
+      <c r="L62" s="98"/>
+      <c r="M62" s="98"/>
+    </row>
+    <row r="63" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A63" s="136" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/vial-geometry.md","VIAL GEOMETRY  (true volume &amp; bore depth)")</f>
+        <v>VIAL GEOMETRY  (true volume &amp; bore depth)</v>
+      </c>
+      <c r="B63" s="98"/>
+      <c r="C63" s="98"/>
+      <c r="D63" s="98"/>
+      <c r="E63" s="98"/>
+      <c r="F63" s="98"/>
+      <c r="G63" s="98"/>
+      <c r="H63" s="98"/>
+      <c r="I63" s="98"/>
+      <c r="J63" s="98"/>
+      <c r="K63" s="98"/>
+      <c r="L63" s="98"/>
+      <c r="M63" s="98"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A64" s="98" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B64" s="98"/>
+      <c r="C64" s="98"/>
+      <c r="D64" s="98"/>
+      <c r="E64" s="98"/>
+      <c r="F64" s="98"/>
+      <c r="G64" s="98"/>
+      <c r="H64" s="98"/>
+      <c r="I64" s="98"/>
+      <c r="J64" s="98"/>
+      <c r="K64" s="98"/>
+      <c r="L64" s="98"/>
+      <c r="M64" s="98"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A65" s="137" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B65" s="137" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C65" s="137" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="137" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E65" s="137" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F65" s="137" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G65" s="137" t="s">
+        <v>1471</v>
+      </c>
+      <c r="H65" s="137" t="s">
+        <v>1472</v>
+      </c>
+      <c r="I65" s="137" t="s">
+        <v>1446</v>
+      </c>
+      <c r="J65" s="137" t="s">
+        <v>1447</v>
+      </c>
+      <c r="K65" s="137" t="s">
+        <v>1448</v>
+      </c>
+      <c r="L65" s="98"/>
+      <c r="M65" s="98"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A66" s="131"/>
+      <c r="B66" s="132"/>
+      <c r="C66" s="131"/>
+      <c r="D66" s="132"/>
+      <c r="E66" s="132"/>
+      <c r="F66" s="132"/>
+      <c r="G66" s="138">
+        <f t="shared" ref="G66:G73" si="2">IFERROR(E66/(0.99705-0.00028*(F66-25)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="H66" s="138">
         <f>IFERROR((E66/(0.99705-0.00028*(F66-25)))*1000/Geometry!$D$21,"")</f>
-      </c>
-      <c r="I66" s="48">
+        <v>0</v>
+      </c>
+      <c r="I66" s="138" t="str">
         <f>IFERROR(VLOOKUP(C66,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="J66" s="53"/>
-      <c r="K66" s="53"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" s="53"/>
-      <c r="B67" s="124"/>
-      <c r="C67" s="53"/>
-      <c r="D67" s="124"/>
-      <c r="E67" s="124"/>
-      <c r="F67" s="124"/>
-      <c r="G67" s="48">
-        <f>IFERROR(E67/(0.99705-0.00028*(F67-25)),"")</f>
-      </c>
-      <c r="H67" s="48">
+        <v/>
+      </c>
+      <c r="J66" s="131"/>
+      <c r="K66" s="131"/>
+      <c r="L66" s="98"/>
+      <c r="M66" s="98"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A67" s="131"/>
+      <c r="B67" s="132"/>
+      <c r="C67" s="131"/>
+      <c r="D67" s="132"/>
+      <c r="E67" s="132"/>
+      <c r="F67" s="132"/>
+      <c r="G67" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H67" s="138">
         <f>IFERROR((E67/(0.99705-0.00028*(F67-25)))*1000/Geometry!$D$21,"")</f>
-      </c>
-      <c r="I67" s="48">
+        <v>0</v>
+      </c>
+      <c r="I67" s="138" t="str">
         <f>IFERROR(VLOOKUP(C67,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="J67" s="53"/>
-      <c r="K67" s="53"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68" s="53"/>
-      <c r="B68" s="124"/>
-      <c r="C68" s="53"/>
-      <c r="D68" s="124"/>
-      <c r="E68" s="124"/>
-      <c r="F68" s="124"/>
-      <c r="G68" s="48">
-        <f>IFERROR(E68/(0.99705-0.00028*(F68-25)),"")</f>
-      </c>
-      <c r="H68" s="48">
+        <v/>
+      </c>
+      <c r="J67" s="131"/>
+      <c r="K67" s="131"/>
+      <c r="L67" s="98"/>
+      <c r="M67" s="98"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A68" s="131"/>
+      <c r="B68" s="132"/>
+      <c r="C68" s="131"/>
+      <c r="D68" s="132"/>
+      <c r="E68" s="132"/>
+      <c r="F68" s="132"/>
+      <c r="G68" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H68" s="138">
         <f>IFERROR((E68/(0.99705-0.00028*(F68-25)))*1000/Geometry!$D$21,"")</f>
-      </c>
-      <c r="I68" s="48">
+        <v>0</v>
+      </c>
+      <c r="I68" s="138" t="str">
         <f>IFERROR(VLOOKUP(C68,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="J68" s="53"/>
-      <c r="K68" s="53"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A69" s="53"/>
-      <c r="B69" s="124"/>
-      <c r="C69" s="53"/>
-      <c r="D69" s="124"/>
-      <c r="E69" s="124"/>
-      <c r="F69" s="124"/>
-      <c r="G69" s="48">
-        <f>IFERROR(E69/(0.99705-0.00028*(F69-25)),"")</f>
-      </c>
-      <c r="H69" s="48">
+        <v/>
+      </c>
+      <c r="J68" s="131"/>
+      <c r="K68" s="131"/>
+      <c r="L68" s="98"/>
+      <c r="M68" s="98"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A69" s="131"/>
+      <c r="B69" s="132"/>
+      <c r="C69" s="131"/>
+      <c r="D69" s="132"/>
+      <c r="E69" s="132"/>
+      <c r="F69" s="132"/>
+      <c r="G69" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H69" s="138">
         <f>IFERROR((E69/(0.99705-0.00028*(F69-25)))*1000/Geometry!$D$21,"")</f>
-      </c>
-      <c r="I69" s="48">
+        <v>0</v>
+      </c>
+      <c r="I69" s="138" t="str">
         <f>IFERROR(VLOOKUP(C69,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="J69" s="53"/>
-      <c r="K69" s="53"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A70" s="53"/>
-      <c r="B70" s="124"/>
-      <c r="C70" s="53"/>
-      <c r="D70" s="124"/>
-      <c r="E70" s="124"/>
-      <c r="F70" s="124"/>
-      <c r="G70" s="48">
-        <f>IFERROR(E70/(0.99705-0.00028*(F70-25)),"")</f>
-      </c>
-      <c r="H70" s="48">
+        <v/>
+      </c>
+      <c r="J69" s="131"/>
+      <c r="K69" s="131"/>
+      <c r="L69" s="98"/>
+      <c r="M69" s="98"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A70" s="131"/>
+      <c r="B70" s="132"/>
+      <c r="C70" s="131"/>
+      <c r="D70" s="132"/>
+      <c r="E70" s="132"/>
+      <c r="F70" s="132"/>
+      <c r="G70" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H70" s="138">
         <f>IFERROR((E70/(0.99705-0.00028*(F70-25)))*1000/Geometry!$D$21,"")</f>
-      </c>
-      <c r="I70" s="48">
+        <v>0</v>
+      </c>
+      <c r="I70" s="138" t="str">
         <f>IFERROR(VLOOKUP(C70,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="J70" s="53"/>
-      <c r="K70" s="53"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A71" s="53"/>
-      <c r="B71" s="124"/>
-      <c r="C71" s="53"/>
-      <c r="D71" s="124"/>
-      <c r="E71" s="124"/>
-      <c r="F71" s="124"/>
-      <c r="G71" s="48">
-        <f>IFERROR(E71/(0.99705-0.00028*(F71-25)),"")</f>
-      </c>
-      <c r="H71" s="48">
+        <v/>
+      </c>
+      <c r="J70" s="131"/>
+      <c r="K70" s="131"/>
+      <c r="L70" s="98"/>
+      <c r="M70" s="98"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A71" s="131"/>
+      <c r="B71" s="132"/>
+      <c r="C71" s="131"/>
+      <c r="D71" s="132"/>
+      <c r="E71" s="132"/>
+      <c r="F71" s="132"/>
+      <c r="G71" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H71" s="138">
         <f>IFERROR((E71/(0.99705-0.00028*(F71-25)))*1000/Geometry!$D$21,"")</f>
-      </c>
-      <c r="I71" s="48">
+        <v>0</v>
+      </c>
+      <c r="I71" s="138" t="str">
         <f>IFERROR(VLOOKUP(C71,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="J71" s="53"/>
-      <c r="K71" s="53"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A72" s="53"/>
-      <c r="B72" s="124"/>
-      <c r="C72" s="53"/>
-      <c r="D72" s="124"/>
-      <c r="E72" s="124"/>
-      <c r="F72" s="124"/>
-      <c r="G72" s="48">
-        <f>IFERROR(E72/(0.99705-0.00028*(F72-25)),"")</f>
-      </c>
-      <c r="H72" s="48">
+        <v/>
+      </c>
+      <c r="J71" s="131"/>
+      <c r="K71" s="131"/>
+      <c r="L71" s="98"/>
+      <c r="M71" s="98"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A72" s="131"/>
+      <c r="B72" s="132"/>
+      <c r="C72" s="131"/>
+      <c r="D72" s="132"/>
+      <c r="E72" s="132"/>
+      <c r="F72" s="132"/>
+      <c r="G72" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H72" s="138">
         <f>IFERROR((E72/(0.99705-0.00028*(F72-25)))*1000/Geometry!$D$21,"")</f>
-      </c>
-      <c r="I72" s="48">
+        <v>0</v>
+      </c>
+      <c r="I72" s="138" t="str">
         <f>IFERROR(VLOOKUP(C72,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="J72" s="53"/>
-      <c r="K72" s="53"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A73" s="53"/>
-      <c r="B73" s="124"/>
-      <c r="C73" s="53"/>
-      <c r="D73" s="124"/>
-      <c r="E73" s="124"/>
-      <c r="F73" s="124"/>
-      <c r="G73" s="48">
-        <f>IFERROR(E73/(0.99705-0.00028*(F73-25)),"")</f>
-      </c>
-      <c r="H73" s="48">
+        <v/>
+      </c>
+      <c r="J72" s="131"/>
+      <c r="K72" s="131"/>
+      <c r="L72" s="98"/>
+      <c r="M72" s="98"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A73" s="131"/>
+      <c r="B73" s="132"/>
+      <c r="C73" s="131"/>
+      <c r="D73" s="132"/>
+      <c r="E73" s="132"/>
+      <c r="F73" s="132"/>
+      <c r="G73" s="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H73" s="138">
         <f>IFERROR((E73/(0.99705-0.00028*(F73-25)))*1000/Geometry!$D$21,"")</f>
-      </c>
-      <c r="I73" s="48">
+        <v>0</v>
+      </c>
+      <c r="I73" s="138" t="str">
         <f>IFERROR(VLOOKUP(C73,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="J73" s="53"/>
-      <c r="K73" s="53"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A74" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - total vial volume</t>
-        </is>
-      </c>
-      <c r="C74" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mL</t>
-        </is>
-      </c>
-      <c r="D74" s="48">
+        <v/>
+      </c>
+      <c r="J73" s="131"/>
+      <c r="K73" s="131"/>
+      <c r="L73" s="98"/>
+      <c r="M73" s="98"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A74" s="134" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B74" s="98"/>
+      <c r="C74" s="135" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" s="133" t="e">
         <f>AVERAGEIFS(G66:G73,I66:I73,Geometry!$D$51,J66:J73,"y")</f>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A75" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - usable depth</t>
-        </is>
-      </c>
-      <c r="C75" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mm</t>
-        </is>
-      </c>
-      <c r="D75" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E74" s="98"/>
+      <c r="F74" s="98"/>
+      <c r="G74" s="98"/>
+      <c r="H74" s="98"/>
+      <c r="I74" s="98"/>
+      <c r="J74" s="98"/>
+      <c r="K74" s="98"/>
+      <c r="L74" s="98"/>
+      <c r="M74" s="98"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A75" s="134" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B75" s="98"/>
+      <c r="C75" s="135" t="s">
+        <v>146</v>
+      </c>
+      <c r="D75" s="133" t="e">
         <f>AVERAGEIFS(H66:H73,I66:I73,Geometry!$D$51,J66:J73,"y")</f>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A78" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SINTER POROSITY  (sparger frit grade)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A79" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use: the most recent included measurement for the active reactor (the fitted frit is hardware, so the latest reading replaces older ones).</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A80" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Researcher</t>
-        </is>
-      </c>
-      <c r="B80" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="C80" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reactor</t>
-        </is>
-      </c>
-      <c r="D80" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bubble-point</t>
-        </is>
-      </c>
-      <c r="E80" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Grade (computed)</t>
-        </is>
-      </c>
-      <c r="F80" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Type (auto)</t>
-        </is>
-      </c>
-      <c r="G80" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Include?</t>
-        </is>
-      </c>
-      <c r="H80" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A81" s="53"/>
-      <c r="B81" s="124"/>
-      <c r="C81" s="53"/>
-      <c r="D81" s="124"/>
-      <c r="E81" s="48">
-        <f>IFERROR(IF((291.2/D81)&gt;160,0,IF((291.2/D81)&gt;100,1,IF((291.2/D81)&gt;40,2,IF((291.2/D81)&gt;16,3,IF((291.2/D81)&gt;10,4,5))))),"")</f>
-      </c>
-      <c r="F81" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E75" s="98"/>
+      <c r="F75" s="98"/>
+      <c r="G75" s="98"/>
+      <c r="H75" s="98"/>
+      <c r="I75" s="98"/>
+      <c r="J75" s="98"/>
+      <c r="K75" s="98"/>
+      <c r="L75" s="98"/>
+      <c r="M75" s="98"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A76" s="98"/>
+      <c r="B76" s="98"/>
+      <c r="C76" s="98"/>
+      <c r="D76" s="98"/>
+      <c r="E76" s="98"/>
+      <c r="F76" s="98"/>
+      <c r="G76" s="98"/>
+      <c r="H76" s="98"/>
+      <c r="I76" s="98"/>
+      <c r="J76" s="98"/>
+      <c r="K76" s="98"/>
+      <c r="L76" s="98"/>
+      <c r="M76" s="98"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A77" s="98"/>
+      <c r="B77" s="98"/>
+      <c r="C77" s="98"/>
+      <c r="D77" s="98"/>
+      <c r="E77" s="98"/>
+      <c r="F77" s="98"/>
+      <c r="G77" s="98"/>
+      <c r="H77" s="98"/>
+      <c r="I77" s="98"/>
+      <c r="J77" s="98"/>
+      <c r="K77" s="98"/>
+      <c r="L77" s="98"/>
+      <c r="M77" s="98"/>
+    </row>
+    <row r="78" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A78" s="136" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/sinter-porosity.md","SINTER POROSITY  (sparger frit grade)")</f>
+        <v>SINTER POROSITY  (sparger frit grade)</v>
+      </c>
+      <c r="B78" s="98"/>
+      <c r="C78" s="98"/>
+      <c r="D78" s="98"/>
+      <c r="E78" s="98"/>
+      <c r="F78" s="98"/>
+      <c r="G78" s="98"/>
+      <c r="H78" s="98"/>
+      <c r="I78" s="98"/>
+      <c r="J78" s="98"/>
+      <c r="K78" s="98"/>
+      <c r="L78" s="98"/>
+      <c r="M78" s="98"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A79" s="98" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B79" s="98"/>
+      <c r="C79" s="98"/>
+      <c r="D79" s="98"/>
+      <c r="E79" s="98"/>
+      <c r="F79" s="132"/>
+      <c r="G79" s="98"/>
+      <c r="H79" s="98"/>
+      <c r="I79" s="98"/>
+      <c r="J79" s="98"/>
+      <c r="K79" s="98"/>
+      <c r="L79" s="98"/>
+      <c r="M79" s="98"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A80" s="137" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B80" s="137" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C80" s="137" t="s">
+        <v>1</v>
+      </c>
+      <c r="D80" s="137" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E80" s="137" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F80" s="137" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G80" s="137" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H80" s="137" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I80" s="98"/>
+      <c r="J80" s="98"/>
+      <c r="K80" s="98"/>
+      <c r="L80" s="98"/>
+      <c r="M80" s="98"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A81" s="131"/>
+      <c r="B81" s="132"/>
+      <c r="C81" s="131"/>
+      <c r="D81" s="132"/>
+      <c r="E81" s="138" t="str">
+        <f t="shared" ref="E81:E88" si="3">IFERROR(IF((291.2/D81)&gt;160,0,IF((291.2/D81)&gt;100,1,IF((291.2/D81)&gt;40,2,IF((291.2/D81)&gt;16,3,IF((291.2/D81)&gt;10,4,5))))),"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="138" t="str">
         <f>IFERROR(VLOOKUP(C81,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G81" s="53"/>
-      <c r="H81" s="53"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A82" s="53"/>
-      <c r="B82" s="124"/>
-      <c r="C82" s="53"/>
-      <c r="D82" s="124"/>
-      <c r="E82" s="48">
-        <f>IFERROR(IF((291.2/D82)&gt;160,0,IF((291.2/D82)&gt;100,1,IF((291.2/D82)&gt;40,2,IF((291.2/D82)&gt;16,3,IF((291.2/D82)&gt;10,4,5))))),"")</f>
-      </c>
-      <c r="F82" s="48">
+        <v/>
+      </c>
+      <c r="G81" s="131"/>
+      <c r="H81" s="131"/>
+      <c r="I81" s="98"/>
+      <c r="J81" s="98"/>
+      <c r="K81" s="98"/>
+      <c r="L81" s="98"/>
+      <c r="M81" s="98"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A82" s="131"/>
+      <c r="B82" s="132"/>
+      <c r="C82" s="131"/>
+      <c r="D82" s="132"/>
+      <c r="E82" s="138" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="F82" s="139" t="str">
         <f>IFERROR(VLOOKUP(C82,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G82" s="53"/>
-      <c r="H82" s="53"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A83" s="53"/>
-      <c r="B83" s="124"/>
-      <c r="C83" s="53"/>
-      <c r="D83" s="124"/>
-      <c r="E83" s="48">
-        <f>IFERROR(IF((291.2/D83)&gt;160,0,IF((291.2/D83)&gt;100,1,IF((291.2/D83)&gt;40,2,IF((291.2/D83)&gt;16,3,IF((291.2/D83)&gt;10,4,5))))),"")</f>
-      </c>
-      <c r="F83" s="48">
+        <v/>
+      </c>
+      <c r="G82" s="131"/>
+      <c r="H82" s="131"/>
+      <c r="I82" s="98"/>
+      <c r="J82" s="98"/>
+      <c r="K82" s="98"/>
+      <c r="L82" s="98"/>
+      <c r="M82" s="98"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A83" s="131"/>
+      <c r="B83" s="132"/>
+      <c r="C83" s="131"/>
+      <c r="D83" s="132"/>
+      <c r="E83" s="138" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="F83" s="139" t="str">
         <f>IFERROR(VLOOKUP(C83,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G83" s="53"/>
-      <c r="H83" s="53"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A84" s="53"/>
-      <c r="B84" s="124"/>
-      <c r="C84" s="53"/>
-      <c r="D84" s="124"/>
-      <c r="E84" s="48">
-        <f>IFERROR(IF((291.2/D84)&gt;160,0,IF((291.2/D84)&gt;100,1,IF((291.2/D84)&gt;40,2,IF((291.2/D84)&gt;16,3,IF((291.2/D84)&gt;10,4,5))))),"")</f>
-      </c>
-      <c r="F84" s="48">
+        <v/>
+      </c>
+      <c r="G83" s="131"/>
+      <c r="H83" s="131"/>
+      <c r="I83" s="98"/>
+      <c r="J83" s="98"/>
+      <c r="K83" s="98"/>
+      <c r="L83" s="98"/>
+      <c r="M83" s="98"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A84" s="131"/>
+      <c r="B84" s="132"/>
+      <c r="C84" s="131"/>
+      <c r="D84" s="132"/>
+      <c r="E84" s="138" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="F84" s="139" t="str">
         <f>IFERROR(VLOOKUP(C84,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G84" s="53"/>
-      <c r="H84" s="53"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A85" s="53"/>
-      <c r="B85" s="124"/>
-      <c r="C85" s="53"/>
-      <c r="D85" s="124"/>
-      <c r="E85" s="48">
-        <f>IFERROR(IF((291.2/D85)&gt;160,0,IF((291.2/D85)&gt;100,1,IF((291.2/D85)&gt;40,2,IF((291.2/D85)&gt;16,3,IF((291.2/D85)&gt;10,4,5))))),"")</f>
-      </c>
-      <c r="F85" s="48">
+        <v/>
+      </c>
+      <c r="G84" s="131"/>
+      <c r="H84" s="131"/>
+      <c r="I84" s="98"/>
+      <c r="J84" s="98"/>
+      <c r="K84" s="98"/>
+      <c r="L84" s="98"/>
+      <c r="M84" s="98"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A85" s="131"/>
+      <c r="B85" s="132"/>
+      <c r="C85" s="131"/>
+      <c r="D85" s="132"/>
+      <c r="E85" s="138" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="F85" s="139" t="str">
         <f>IFERROR(VLOOKUP(C85,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G85" s="53"/>
-      <c r="H85" s="53"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A86" s="53"/>
-      <c r="B86" s="124"/>
-      <c r="C86" s="53"/>
-      <c r="D86" s="124"/>
-      <c r="E86" s="48">
-        <f>IFERROR(IF((291.2/D86)&gt;160,0,IF((291.2/D86)&gt;100,1,IF((291.2/D86)&gt;40,2,IF((291.2/D86)&gt;16,3,IF((291.2/D86)&gt;10,4,5))))),"")</f>
-      </c>
-      <c r="F86" s="48">
+        <v/>
+      </c>
+      <c r="G85" s="131"/>
+      <c r="H85" s="131"/>
+      <c r="I85" s="98"/>
+      <c r="J85" s="98"/>
+      <c r="K85" s="98"/>
+      <c r="L85" s="98"/>
+      <c r="M85" s="98"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A86" s="131"/>
+      <c r="B86" s="132"/>
+      <c r="C86" s="131"/>
+      <c r="D86" s="132"/>
+      <c r="E86" s="138" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="F86" s="138" t="str">
         <f>IFERROR(VLOOKUP(C86,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G86" s="53"/>
-      <c r="H86" s="53"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A87" s="53"/>
-      <c r="B87" s="124"/>
-      <c r="C87" s="53"/>
-      <c r="D87" s="124"/>
-      <c r="E87" s="48">
-        <f>IFERROR(IF((291.2/D87)&gt;160,0,IF((291.2/D87)&gt;100,1,IF((291.2/D87)&gt;40,2,IF((291.2/D87)&gt;16,3,IF((291.2/D87)&gt;10,4,5))))),"")</f>
-      </c>
-      <c r="F87" s="48">
+        <v/>
+      </c>
+      <c r="G86" s="131"/>
+      <c r="H86" s="131"/>
+      <c r="I86" s="98"/>
+      <c r="J86" s="98"/>
+      <c r="K86" s="98"/>
+      <c r="L86" s="98"/>
+      <c r="M86" s="98"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A87" s="131"/>
+      <c r="B87" s="132"/>
+      <c r="C87" s="131"/>
+      <c r="D87" s="132"/>
+      <c r="E87" s="138" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="F87" s="138" t="str">
         <f>IFERROR(VLOOKUP(C87,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G87" s="53"/>
-      <c r="H87" s="53"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A88" s="53"/>
-      <c r="B88" s="124"/>
-      <c r="C88" s="53"/>
-      <c r="D88" s="124"/>
-      <c r="E88" s="48">
-        <f>IFERROR(IF((291.2/D88)&gt;160,0,IF((291.2/D88)&gt;100,1,IF((291.2/D88)&gt;40,2,IF((291.2/D88)&gt;16,3,IF((291.2/D88)&gt;10,4,5))))),"")</f>
-      </c>
-      <c r="F88" s="48">
+        <v/>
+      </c>
+      <c r="G87" s="131"/>
+      <c r="H87" s="131"/>
+      <c r="I87" s="98"/>
+      <c r="J87" s="98"/>
+      <c r="K87" s="98"/>
+      <c r="L87" s="98"/>
+      <c r="M87" s="98"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A88" s="131"/>
+      <c r="B88" s="132"/>
+      <c r="C88" s="131"/>
+      <c r="D88" s="132"/>
+      <c r="E88" s="138" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="F88" s="138" t="str">
         <f>IFERROR(VLOOKUP(C88,Geometry!$A$59:$B$80,2,FALSE),"")</f>
-      </c>
-      <c r="G88" s="53"/>
-      <c r="H88" s="53"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A89" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - porosity grade</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0-5</t>
-        </is>
-      </c>
-      <c r="D89" s="48">
-        <f>AVERAGEIFS(E81:E88,C81:C88,Summary!$D$2,G81:G88,"y",B81:B88,MAXIFS(B81:B88,C81:C88,Summary!$D$2,G81:G88,"y"))</f>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A92" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DISSOLVED-OXYGEN THRESHOLDS  (per organism)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A93" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use: average of the included values for the active organism.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A94" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Researcher</t>
-        </is>
-      </c>
-      <c r="B94" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="C94" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Organism</t>
-        </is>
-      </c>
-      <c r="D94" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Min DO</t>
-        </is>
-      </c>
-      <c r="E94" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Optimum DO</t>
-        </is>
-      </c>
-      <c r="F94" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Impairment DO</t>
-        </is>
-      </c>
-      <c r="G94" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Toxic DO</t>
-        </is>
-      </c>
-      <c r="H94" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Include?</t>
-        </is>
-      </c>
-      <c r="I94" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A95" s="53"/>
-      <c r="B95" s="124"/>
-      <c r="C95" s="53"/>
-      <c r="D95" s="124"/>
-      <c r="E95" s="124"/>
-      <c r="F95" s="124"/>
-      <c r="G95" s="124"/>
-      <c r="H95" s="53"/>
-      <c r="I95" s="53"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A96" s="53"/>
-      <c r="B96" s="124"/>
-      <c r="C96" s="53"/>
-      <c r="D96" s="124"/>
-      <c r="E96" s="124"/>
-      <c r="F96" s="124"/>
-      <c r="G96" s="124"/>
-      <c r="H96" s="53"/>
-      <c r="I96" s="53"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A97" s="53"/>
-      <c r="B97" s="124"/>
-      <c r="C97" s="53"/>
-      <c r="D97" s="124"/>
-      <c r="E97" s="124"/>
-      <c r="F97" s="124"/>
-      <c r="G97" s="124"/>
-      <c r="H97" s="53"/>
-      <c r="I97" s="53"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A98" s="53"/>
-      <c r="B98" s="124"/>
-      <c r="C98" s="53"/>
-      <c r="D98" s="124"/>
-      <c r="E98" s="124"/>
-      <c r="F98" s="124"/>
-      <c r="G98" s="124"/>
-      <c r="H98" s="53"/>
-      <c r="I98" s="53"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A99" s="53"/>
-      <c r="B99" s="124"/>
-      <c r="C99" s="53"/>
-      <c r="D99" s="124"/>
-      <c r="E99" s="124"/>
-      <c r="F99" s="124"/>
-      <c r="G99" s="124"/>
-      <c r="H99" s="53"/>
-      <c r="I99" s="53"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A100" s="53"/>
-      <c r="B100" s="124"/>
-      <c r="C100" s="53"/>
-      <c r="D100" s="124"/>
-      <c r="E100" s="124"/>
-      <c r="F100" s="124"/>
-      <c r="G100" s="124"/>
-      <c r="H100" s="53"/>
-      <c r="I100" s="53"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A101" s="53"/>
-      <c r="B101" s="124"/>
-      <c r="C101" s="53"/>
-      <c r="D101" s="124"/>
-      <c r="E101" s="124"/>
-      <c r="F101" s="124"/>
-      <c r="G101" s="124"/>
-      <c r="H101" s="53"/>
-      <c r="I101" s="53"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A102" s="53"/>
-      <c r="B102" s="124"/>
-      <c r="C102" s="53"/>
-      <c r="D102" s="124"/>
-      <c r="E102" s="124"/>
-      <c r="F102" s="124"/>
-      <c r="G102" s="124"/>
-      <c r="H102" s="53"/>
-      <c r="I102" s="53"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A103" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - minimum DO</t>
-        </is>
-      </c>
-      <c r="C103" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mg/L</t>
-        </is>
-      </c>
-      <c r="D103" s="48">
+        <v/>
+      </c>
+      <c r="G88" s="131"/>
+      <c r="H88" s="131"/>
+      <c r="I88" s="98"/>
+      <c r="J88" s="98"/>
+      <c r="K88" s="98"/>
+      <c r="L88" s="98"/>
+      <c r="M88" s="98"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A89" s="134" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B89" s="98"/>
+      <c r="C89" s="135" t="s">
+        <v>556</v>
+      </c>
+      <c r="D89" s="133" t="e">
+        <f ca="1">AVERAGEIFS(E81:E88,C81:C88,Summary!$D$2,G81:G88,"y",B81:B88,_xludf.MAXIFS(B81:B88,C81:C88,Summary!$D$2,G81:G88,"y"))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E89" s="98"/>
+      <c r="F89" s="98"/>
+      <c r="G89" s="98"/>
+      <c r="H89" s="98"/>
+      <c r="I89" s="98"/>
+      <c r="J89" s="98"/>
+      <c r="K89" s="98"/>
+      <c r="L89" s="98"/>
+      <c r="M89" s="98"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A90" s="98"/>
+      <c r="B90" s="98"/>
+      <c r="C90" s="98"/>
+      <c r="D90" s="98"/>
+      <c r="E90" s="98"/>
+      <c r="F90" s="98"/>
+      <c r="G90" s="98"/>
+      <c r="H90" s="98"/>
+      <c r="I90" s="98"/>
+      <c r="J90" s="98"/>
+      <c r="K90" s="98"/>
+      <c r="L90" s="98"/>
+      <c r="M90" s="98"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A91" s="98"/>
+      <c r="B91" s="98"/>
+      <c r="C91" s="98"/>
+      <c r="D91" s="98"/>
+      <c r="E91" s="98"/>
+      <c r="F91" s="98"/>
+      <c r="G91" s="98"/>
+      <c r="H91" s="98"/>
+      <c r="I91" s="98"/>
+      <c r="J91" s="98"/>
+      <c r="K91" s="98"/>
+      <c r="L91" s="98"/>
+      <c r="M91" s="98"/>
+    </row>
+    <row r="92" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A92" s="136" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/dissolved-oxygen.md","DISSOLVED-OXYGEN THRESHOLDS  (per organism)")</f>
+        <v>DISSOLVED-OXYGEN THRESHOLDS  (per organism)</v>
+      </c>
+      <c r="B92" s="98"/>
+      <c r="C92" s="98"/>
+      <c r="D92" s="98"/>
+      <c r="E92" s="98"/>
+      <c r="F92" s="98"/>
+      <c r="G92" s="98"/>
+      <c r="H92" s="98"/>
+      <c r="I92" s="98"/>
+      <c r="J92" s="98"/>
+      <c r="K92" s="98"/>
+      <c r="L92" s="98"/>
+      <c r="M92" s="98"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A93" s="98" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B93" s="98"/>
+      <c r="C93" s="98"/>
+      <c r="D93" s="98"/>
+      <c r="E93" s="98"/>
+      <c r="F93" s="98"/>
+      <c r="G93" s="98"/>
+      <c r="H93" s="98"/>
+      <c r="I93" s="98"/>
+      <c r="J93" s="98"/>
+      <c r="K93" s="98"/>
+      <c r="L93" s="98"/>
+      <c r="M93" s="98"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A94" s="137" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B94" s="137" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C94" s="137" t="s">
+        <v>525</v>
+      </c>
+      <c r="D94" s="137" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E94" s="137" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F94" s="137" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G94" s="137" t="s">
+        <v>1483</v>
+      </c>
+      <c r="H94" s="137" t="s">
+        <v>1447</v>
+      </c>
+      <c r="I94" s="137" t="s">
+        <v>1448</v>
+      </c>
+      <c r="J94" s="98"/>
+      <c r="K94" s="98"/>
+      <c r="L94" s="98"/>
+      <c r="M94" s="98"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A95" s="131"/>
+      <c r="B95" s="132"/>
+      <c r="C95" s="131"/>
+      <c r="D95" s="132"/>
+      <c r="E95" s="132"/>
+      <c r="F95" s="132"/>
+      <c r="G95" s="132"/>
+      <c r="H95" s="131"/>
+      <c r="I95" s="131"/>
+      <c r="J95" s="98"/>
+      <c r="K95" s="98"/>
+      <c r="L95" s="98"/>
+      <c r="M95" s="98"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A96" s="131"/>
+      <c r="B96" s="132"/>
+      <c r="C96" s="131"/>
+      <c r="D96" s="132"/>
+      <c r="E96" s="132"/>
+      <c r="F96" s="132"/>
+      <c r="G96" s="132"/>
+      <c r="H96" s="131"/>
+      <c r="I96" s="131"/>
+      <c r="J96" s="98"/>
+      <c r="K96" s="98"/>
+      <c r="L96" s="98"/>
+      <c r="M96" s="98"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A97" s="131"/>
+      <c r="B97" s="132"/>
+      <c r="C97" s="131"/>
+      <c r="D97" s="132"/>
+      <c r="E97" s="132"/>
+      <c r="F97" s="132"/>
+      <c r="G97" s="132"/>
+      <c r="H97" s="131"/>
+      <c r="I97" s="131"/>
+      <c r="J97" s="98"/>
+      <c r="K97" s="98"/>
+      <c r="L97" s="98"/>
+      <c r="M97" s="98"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A98" s="131"/>
+      <c r="B98" s="132"/>
+      <c r="C98" s="131"/>
+      <c r="D98" s="132"/>
+      <c r="E98" s="132"/>
+      <c r="F98" s="132"/>
+      <c r="G98" s="132"/>
+      <c r="H98" s="131"/>
+      <c r="I98" s="131"/>
+      <c r="J98" s="98"/>
+      <c r="K98" s="98"/>
+      <c r="L98" s="98"/>
+      <c r="M98" s="98"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A99" s="131"/>
+      <c r="B99" s="132"/>
+      <c r="C99" s="131"/>
+      <c r="D99" s="132"/>
+      <c r="E99" s="132"/>
+      <c r="F99" s="132"/>
+      <c r="G99" s="132"/>
+      <c r="H99" s="131"/>
+      <c r="I99" s="131"/>
+      <c r="J99" s="98"/>
+      <c r="K99" s="98"/>
+      <c r="L99" s="98"/>
+      <c r="M99" s="98"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A100" s="131"/>
+      <c r="B100" s="132"/>
+      <c r="C100" s="131"/>
+      <c r="D100" s="132"/>
+      <c r="E100" s="132"/>
+      <c r="F100" s="132"/>
+      <c r="G100" s="132"/>
+      <c r="H100" s="131"/>
+      <c r="I100" s="131"/>
+      <c r="J100" s="98"/>
+      <c r="K100" s="98"/>
+      <c r="L100" s="98"/>
+      <c r="M100" s="98"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A101" s="131"/>
+      <c r="B101" s="132"/>
+      <c r="C101" s="131"/>
+      <c r="D101" s="132"/>
+      <c r="E101" s="132"/>
+      <c r="F101" s="132"/>
+      <c r="G101" s="132"/>
+      <c r="H101" s="131"/>
+      <c r="I101" s="131"/>
+      <c r="J101" s="98"/>
+      <c r="K101" s="98"/>
+      <c r="L101" s="98"/>
+      <c r="M101" s="98"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A102" s="131"/>
+      <c r="B102" s="132"/>
+      <c r="C102" s="131"/>
+      <c r="D102" s="132"/>
+      <c r="E102" s="132"/>
+      <c r="F102" s="132"/>
+      <c r="G102" s="132"/>
+      <c r="H102" s="131"/>
+      <c r="I102" s="131"/>
+      <c r="J102" s="98"/>
+      <c r="K102" s="98"/>
+      <c r="L102" s="98"/>
+      <c r="M102" s="98"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A103" s="134" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B103" s="98"/>
+      <c r="C103" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="D103" s="133" t="e">
         <f>AVERAGEIFS(D95:D102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
-      </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A104" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - optimum DO</t>
-        </is>
-      </c>
-      <c r="C104" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mg/L</t>
-        </is>
-      </c>
-      <c r="D104" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E103" s="98"/>
+      <c r="F103" s="98"/>
+      <c r="G103" s="98"/>
+      <c r="H103" s="98"/>
+      <c r="I103" s="98"/>
+      <c r="J103" s="98"/>
+      <c r="K103" s="98"/>
+      <c r="L103" s="98"/>
+      <c r="M103" s="98"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A104" s="134" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B104" s="98"/>
+      <c r="C104" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="D104" s="133" t="e">
         <f>AVERAGEIFS(E95:E102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
-      </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A105" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - impairment DO</t>
-        </is>
-      </c>
-      <c r="C105" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mg/L</t>
-        </is>
-      </c>
-      <c r="D105" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E104" s="98"/>
+      <c r="F104" s="98"/>
+      <c r="G104" s="98"/>
+      <c r="H104" s="98"/>
+      <c r="I104" s="98"/>
+      <c r="J104" s="98"/>
+      <c r="K104" s="98"/>
+      <c r="L104" s="98"/>
+      <c r="M104" s="98"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A105" s="134" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B105" s="98"/>
+      <c r="C105" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="D105" s="133" t="e">
         <f>AVERAGEIFS(F95:F102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
-      </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A106" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - toxic DO</t>
-        </is>
-      </c>
-      <c r="C106" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mg/L</t>
-        </is>
-      </c>
-      <c r="D106" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E105" s="98"/>
+      <c r="F105" s="98"/>
+      <c r="G105" s="98"/>
+      <c r="H105" s="98"/>
+      <c r="I105" s="98"/>
+      <c r="J105" s="98"/>
+      <c r="K105" s="98"/>
+      <c r="L105" s="98"/>
+      <c r="M105" s="98"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A106" s="134" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B106" s="98"/>
+      <c r="C106" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="D106" s="133" t="e">
         <f>AVERAGEIFS(G95:G102,C95:C102,Summary!$D$4,H95:H102,"y")</f>
-      </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A109" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KNALLGAS UPTAKE RATIO  (per organism)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A110" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use: average of the included ratios for the active organism.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A111" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Researcher</t>
-        </is>
-      </c>
-      <c r="B111" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="C111" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Organism</t>
-        </is>
-      </c>
-      <c r="D111" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H2</t>
-        </is>
-      </c>
-      <c r="E111" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O2</t>
-        </is>
-      </c>
-      <c r="F111" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CO2</t>
-        </is>
-      </c>
-      <c r="G111" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Include?</t>
-        </is>
-      </c>
-      <c r="H111" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A112" s="53"/>
-      <c r="B112" s="124"/>
-      <c r="C112" s="53"/>
-      <c r="D112" s="124"/>
-      <c r="E112" s="124"/>
-      <c r="F112" s="124"/>
-      <c r="G112" s="53"/>
-      <c r="H112" s="53"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A113" s="53"/>
-      <c r="B113" s="124"/>
-      <c r="C113" s="53"/>
-      <c r="D113" s="124"/>
-      <c r="E113" s="124"/>
-      <c r="F113" s="124"/>
-      <c r="G113" s="53"/>
-      <c r="H113" s="53"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A114" s="53"/>
-      <c r="B114" s="124"/>
-      <c r="C114" s="53"/>
-      <c r="D114" s="124"/>
-      <c r="E114" s="124"/>
-      <c r="F114" s="124"/>
-      <c r="G114" s="53"/>
-      <c r="H114" s="53"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A115" s="53"/>
-      <c r="B115" s="124"/>
-      <c r="C115" s="53"/>
-      <c r="D115" s="124"/>
-      <c r="E115" s="124"/>
-      <c r="F115" s="124"/>
-      <c r="G115" s="53"/>
-      <c r="H115" s="53"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A116" s="53"/>
-      <c r="B116" s="124"/>
-      <c r="C116" s="53"/>
-      <c r="D116" s="124"/>
-      <c r="E116" s="124"/>
-      <c r="F116" s="124"/>
-      <c r="G116" s="53"/>
-      <c r="H116" s="53"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A117" s="53"/>
-      <c r="B117" s="124"/>
-      <c r="C117" s="53"/>
-      <c r="D117" s="124"/>
-      <c r="E117" s="124"/>
-      <c r="F117" s="124"/>
-      <c r="G117" s="53"/>
-      <c r="H117" s="53"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A118" s="53"/>
-      <c r="B118" s="124"/>
-      <c r="C118" s="53"/>
-      <c r="D118" s="124"/>
-      <c r="E118" s="124"/>
-      <c r="F118" s="124"/>
-      <c r="G118" s="53"/>
-      <c r="H118" s="53"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A119" s="53"/>
-      <c r="B119" s="124"/>
-      <c r="C119" s="53"/>
-      <c r="D119" s="124"/>
-      <c r="E119" s="124"/>
-      <c r="F119" s="124"/>
-      <c r="G119" s="53"/>
-      <c r="H119" s="53"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A120" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - H2</t>
-        </is>
-      </c>
-      <c r="C120" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parts</t>
-        </is>
-      </c>
-      <c r="D120" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E106" s="98"/>
+      <c r="F106" s="98"/>
+      <c r="G106" s="98"/>
+      <c r="H106" s="98"/>
+      <c r="I106" s="98"/>
+      <c r="J106" s="98"/>
+      <c r="K106" s="98"/>
+      <c r="L106" s="98"/>
+      <c r="M106" s="98"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A107" s="98"/>
+      <c r="B107" s="98"/>
+      <c r="C107" s="98"/>
+      <c r="D107" s="98"/>
+      <c r="E107" s="98"/>
+      <c r="F107" s="98"/>
+      <c r="G107" s="98"/>
+      <c r="H107" s="98"/>
+      <c r="I107" s="98"/>
+      <c r="J107" s="98"/>
+      <c r="K107" s="98"/>
+      <c r="L107" s="98"/>
+      <c r="M107" s="98"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A108" s="98"/>
+      <c r="B108" s="98"/>
+      <c r="C108" s="98"/>
+      <c r="D108" s="98"/>
+      <c r="E108" s="98"/>
+      <c r="F108" s="98"/>
+      <c r="G108" s="98"/>
+      <c r="H108" s="98"/>
+      <c r="I108" s="98"/>
+      <c r="J108" s="98"/>
+      <c r="K108" s="98"/>
+      <c r="L108" s="98"/>
+      <c r="M108" s="98"/>
+    </row>
+    <row r="109" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A109" s="136" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/knallgas-stoichiometry.md","KNALLGAS UPTAKE RATIO  (per organism)")</f>
+        <v>KNALLGAS UPTAKE RATIO  (per organism)</v>
+      </c>
+      <c r="B109" s="98"/>
+      <c r="C109" s="98"/>
+      <c r="D109" s="98"/>
+      <c r="E109" s="98"/>
+      <c r="F109" s="98"/>
+      <c r="G109" s="98"/>
+      <c r="H109" s="98"/>
+      <c r="I109" s="98"/>
+      <c r="J109" s="98"/>
+      <c r="K109" s="98"/>
+      <c r="L109" s="98"/>
+      <c r="M109" s="98"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A110" s="98" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B110" s="98"/>
+      <c r="C110" s="98"/>
+      <c r="D110" s="98"/>
+      <c r="E110" s="98"/>
+      <c r="F110" s="98"/>
+      <c r="G110" s="98"/>
+      <c r="H110" s="98"/>
+      <c r="I110" s="98"/>
+      <c r="J110" s="98"/>
+      <c r="K110" s="98"/>
+      <c r="L110" s="98"/>
+      <c r="M110" s="98"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A111" s="137" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B111" s="137" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C111" s="137" t="s">
+        <v>525</v>
+      </c>
+      <c r="D111" s="137" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E111" s="137" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F111" s="137" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G111" s="137" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H111" s="137" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I111" s="98"/>
+      <c r="J111" s="98"/>
+      <c r="K111" s="98"/>
+      <c r="L111" s="98"/>
+      <c r="M111" s="98"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A112" s="131"/>
+      <c r="B112" s="132"/>
+      <c r="C112" s="131"/>
+      <c r="D112" s="132"/>
+      <c r="E112" s="132"/>
+      <c r="F112" s="132"/>
+      <c r="G112" s="131"/>
+      <c r="H112" s="131"/>
+      <c r="I112" s="98"/>
+      <c r="J112" s="98"/>
+      <c r="K112" s="98"/>
+      <c r="L112" s="98"/>
+      <c r="M112" s="98"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A113" s="131"/>
+      <c r="B113" s="132"/>
+      <c r="C113" s="131"/>
+      <c r="D113" s="132"/>
+      <c r="E113" s="132"/>
+      <c r="F113" s="132"/>
+      <c r="G113" s="131"/>
+      <c r="H113" s="131"/>
+      <c r="I113" s="98"/>
+      <c r="J113" s="98"/>
+      <c r="K113" s="98"/>
+      <c r="L113" s="98"/>
+      <c r="M113" s="98"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A114" s="131"/>
+      <c r="B114" s="132"/>
+      <c r="C114" s="131"/>
+      <c r="D114" s="132"/>
+      <c r="E114" s="132"/>
+      <c r="F114" s="132"/>
+      <c r="G114" s="131"/>
+      <c r="H114" s="131"/>
+      <c r="I114" s="98"/>
+      <c r="J114" s="98"/>
+      <c r="K114" s="98"/>
+      <c r="L114" s="98"/>
+      <c r="M114" s="98"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A115" s="131"/>
+      <c r="B115" s="132"/>
+      <c r="C115" s="131"/>
+      <c r="D115" s="132"/>
+      <c r="E115" s="132"/>
+      <c r="F115" s="132"/>
+      <c r="G115" s="131"/>
+      <c r="H115" s="131"/>
+      <c r="I115" s="98"/>
+      <c r="J115" s="98"/>
+      <c r="K115" s="98"/>
+      <c r="L115" s="98"/>
+      <c r="M115" s="98"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A116" s="131"/>
+      <c r="B116" s="132"/>
+      <c r="C116" s="131"/>
+      <c r="D116" s="132"/>
+      <c r="E116" s="132"/>
+      <c r="F116" s="132"/>
+      <c r="G116" s="131"/>
+      <c r="H116" s="131"/>
+      <c r="I116" s="98"/>
+      <c r="J116" s="98"/>
+      <c r="K116" s="98"/>
+      <c r="L116" s="98"/>
+      <c r="M116" s="98"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A117" s="131"/>
+      <c r="B117" s="132"/>
+      <c r="C117" s="131"/>
+      <c r="D117" s="132"/>
+      <c r="E117" s="132"/>
+      <c r="F117" s="132"/>
+      <c r="G117" s="131"/>
+      <c r="H117" s="131"/>
+      <c r="I117" s="98"/>
+      <c r="J117" s="98"/>
+      <c r="K117" s="98"/>
+      <c r="L117" s="98"/>
+      <c r="M117" s="98"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A118" s="131"/>
+      <c r="B118" s="132"/>
+      <c r="C118" s="131"/>
+      <c r="D118" s="132"/>
+      <c r="E118" s="132"/>
+      <c r="F118" s="132"/>
+      <c r="G118" s="131"/>
+      <c r="H118" s="131"/>
+      <c r="I118" s="98"/>
+      <c r="J118" s="98"/>
+      <c r="K118" s="98"/>
+      <c r="L118" s="98"/>
+      <c r="M118" s="98"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A119" s="131"/>
+      <c r="B119" s="132"/>
+      <c r="C119" s="131"/>
+      <c r="D119" s="132"/>
+      <c r="E119" s="132"/>
+      <c r="F119" s="132"/>
+      <c r="G119" s="131"/>
+      <c r="H119" s="131"/>
+      <c r="I119" s="98"/>
+      <c r="J119" s="98"/>
+      <c r="K119" s="98"/>
+      <c r="L119" s="98"/>
+      <c r="M119" s="98"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A120" s="134" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B120" s="98"/>
+      <c r="C120" s="135" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D120" s="133" t="e">
         <f>AVERAGEIFS(D112:D119,C112:C119,Summary!$D$4,G112:G119,"y")</f>
-      </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A121" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - O2</t>
-        </is>
-      </c>
-      <c r="C121" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parts</t>
-        </is>
-      </c>
-      <c r="D121" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E120" s="98"/>
+      <c r="F120" s="98"/>
+      <c r="G120" s="98"/>
+      <c r="H120" s="98"/>
+      <c r="I120" s="98"/>
+      <c r="J120" s="98"/>
+      <c r="K120" s="98"/>
+      <c r="L120" s="98"/>
+      <c r="M120" s="98"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A121" s="134" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B121" s="98"/>
+      <c r="C121" s="135" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D121" s="133" t="e">
         <f>AVERAGEIFS(E112:E119,C112:C119,Summary!$D$4,G112:G119,"y")</f>
-      </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A122" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - CO2</t>
-        </is>
-      </c>
-      <c r="C122" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parts</t>
-        </is>
-      </c>
-      <c r="D122" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E121" s="98"/>
+      <c r="F121" s="98"/>
+      <c r="G121" s="98"/>
+      <c r="H121" s="98"/>
+      <c r="I121" s="98"/>
+      <c r="J121" s="98"/>
+      <c r="K121" s="98"/>
+      <c r="L121" s="98"/>
+      <c r="M121" s="98"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A122" s="134" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B122" s="98"/>
+      <c r="C122" s="135" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D122" s="133" t="e">
         <f>AVERAGEIFS(F112:F119,C112:C119,Summary!$D$4,G112:G119,"y")</f>
-      </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A125" s="110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CURRENT-DENSITY TOLERANCE  (per organism)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A126" s="51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use: average of the included screen results for the active organism.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A127" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Researcher</t>
-        </is>
-      </c>
-      <c r="B127" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="C127" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Organism</t>
-        </is>
-      </c>
-      <c r="D127" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j optimum</t>
-        </is>
-      </c>
-      <c r="E127" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j ceiling</t>
-        </is>
-      </c>
-      <c r="F127" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Include?</t>
-        </is>
-      </c>
-      <c r="G127" s="109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A128" s="53"/>
-      <c r="B128" s="124"/>
-      <c r="C128" s="53"/>
-      <c r="D128" s="124"/>
-      <c r="E128" s="124"/>
-      <c r="F128" s="53"/>
-      <c r="G128" s="53"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A129" s="53"/>
-      <c r="B129" s="124"/>
-      <c r="C129" s="53"/>
-      <c r="D129" s="124"/>
-      <c r="E129" s="124"/>
-      <c r="F129" s="53"/>
-      <c r="G129" s="53"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A130" s="53"/>
-      <c r="B130" s="124"/>
-      <c r="C130" s="53"/>
-      <c r="D130" s="124"/>
-      <c r="E130" s="124"/>
-      <c r="F130" s="53"/>
-      <c r="G130" s="53"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A131" s="53"/>
-      <c r="B131" s="124"/>
-      <c r="C131" s="53"/>
-      <c r="D131" s="124"/>
-      <c r="E131" s="124"/>
-      <c r="F131" s="53"/>
-      <c r="G131" s="53"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A132" s="53"/>
-      <c r="B132" s="124"/>
-      <c r="C132" s="53"/>
-      <c r="D132" s="124"/>
-      <c r="E132" s="124"/>
-      <c r="F132" s="53"/>
-      <c r="G132" s="53"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A133" s="53"/>
-      <c r="B133" s="124"/>
-      <c r="C133" s="53"/>
-      <c r="D133" s="124"/>
-      <c r="E133" s="124"/>
-      <c r="F133" s="53"/>
-      <c r="G133" s="53"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A134" s="53"/>
-      <c r="B134" s="124"/>
-      <c r="C134" s="53"/>
-      <c r="D134" s="124"/>
-      <c r="E134" s="124"/>
-      <c r="F134" s="53"/>
-      <c r="G134" s="53"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A135" s="53"/>
-      <c r="B135" s="124"/>
-      <c r="C135" s="53"/>
-      <c r="D135" s="124"/>
-      <c r="E135" s="124"/>
-      <c r="F135" s="53"/>
-      <c r="G135" s="53"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A136" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - optimum j</t>
-        </is>
-      </c>
-      <c r="C136" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mA/cm²</t>
-        </is>
-      </c>
-      <c r="D136" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E122" s="98"/>
+      <c r="F122" s="98"/>
+      <c r="G122" s="98"/>
+      <c r="H122" s="98"/>
+      <c r="I122" s="98"/>
+      <c r="J122" s="98"/>
+      <c r="K122" s="98"/>
+      <c r="L122" s="98"/>
+      <c r="M122" s="98"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A123" s="98"/>
+      <c r="B123" s="98"/>
+      <c r="C123" s="98"/>
+      <c r="D123" s="98"/>
+      <c r="E123" s="98"/>
+      <c r="F123" s="98"/>
+      <c r="G123" s="98"/>
+      <c r="H123" s="98"/>
+      <c r="I123" s="98"/>
+      <c r="J123" s="98"/>
+      <c r="K123" s="98"/>
+      <c r="L123" s="98"/>
+      <c r="M123" s="98"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A124" s="98"/>
+      <c r="B124" s="98"/>
+      <c r="C124" s="98"/>
+      <c r="D124" s="98"/>
+      <c r="E124" s="98"/>
+      <c r="F124" s="98"/>
+      <c r="G124" s="98"/>
+      <c r="H124" s="98"/>
+      <c r="I124" s="98"/>
+      <c r="J124" s="98"/>
+      <c r="K124" s="98"/>
+      <c r="L124" s="98"/>
+      <c r="M124" s="98"/>
+    </row>
+    <row r="125" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A125" s="136" t="str">
+        <f>HYPERLINK("https://github.com/amy-bo/electroPioreactor/blob/CO2-modular/Media/protocols/current-density-screen.md","CURRENT-DENSITY TOLERANCE  (per organism)")</f>
+        <v>CURRENT-DENSITY TOLERANCE  (per organism)</v>
+      </c>
+      <c r="B125" s="98"/>
+      <c r="C125" s="98"/>
+      <c r="D125" s="98"/>
+      <c r="E125" s="98"/>
+      <c r="F125" s="98"/>
+      <c r="G125" s="98"/>
+      <c r="H125" s="98"/>
+      <c r="I125" s="98"/>
+      <c r="J125" s="98"/>
+      <c r="K125" s="98"/>
+      <c r="L125" s="98"/>
+      <c r="M125" s="98"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A126" s="98" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B126" s="98"/>
+      <c r="C126" s="98"/>
+      <c r="D126" s="98"/>
+      <c r="E126" s="98"/>
+      <c r="F126" s="98"/>
+      <c r="G126" s="98"/>
+      <c r="H126" s="98"/>
+      <c r="I126" s="98"/>
+      <c r="J126" s="98"/>
+      <c r="K126" s="98"/>
+      <c r="L126" s="98"/>
+      <c r="M126" s="98"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A127" s="137" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B127" s="137" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C127" s="137" t="s">
+        <v>525</v>
+      </c>
+      <c r="D127" s="137" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E127" s="137" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F127" s="137" t="s">
+        <v>1447</v>
+      </c>
+      <c r="G127" s="137" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H127" s="98"/>
+      <c r="I127" s="98"/>
+      <c r="J127" s="98"/>
+      <c r="K127" s="98"/>
+      <c r="L127" s="98"/>
+      <c r="M127" s="98"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A128" s="131"/>
+      <c r="B128" s="132"/>
+      <c r="C128" s="131"/>
+      <c r="D128" s="132"/>
+      <c r="E128" s="132"/>
+      <c r="F128" s="131"/>
+      <c r="G128" s="131"/>
+      <c r="H128" s="98"/>
+      <c r="I128" s="98"/>
+      <c r="J128" s="98"/>
+      <c r="K128" s="98"/>
+      <c r="L128" s="98"/>
+      <c r="M128" s="98"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A129" s="131"/>
+      <c r="B129" s="132"/>
+      <c r="C129" s="131"/>
+      <c r="D129" s="132"/>
+      <c r="E129" s="132"/>
+      <c r="F129" s="131"/>
+      <c r="G129" s="131"/>
+      <c r="H129" s="98"/>
+      <c r="I129" s="98"/>
+      <c r="J129" s="98"/>
+      <c r="K129" s="98"/>
+      <c r="L129" s="98"/>
+      <c r="M129" s="98"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A130" s="131"/>
+      <c r="B130" s="132"/>
+      <c r="C130" s="131"/>
+      <c r="D130" s="132"/>
+      <c r="E130" s="132"/>
+      <c r="F130" s="131"/>
+      <c r="G130" s="131"/>
+      <c r="H130" s="98"/>
+      <c r="I130" s="98"/>
+      <c r="J130" s="98"/>
+      <c r="K130" s="98"/>
+      <c r="L130" s="98"/>
+      <c r="M130" s="98"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A131" s="131"/>
+      <c r="B131" s="132"/>
+      <c r="C131" s="131"/>
+      <c r="D131" s="132"/>
+      <c r="E131" s="132"/>
+      <c r="F131" s="131"/>
+      <c r="G131" s="131"/>
+      <c r="H131" s="98"/>
+      <c r="I131" s="98"/>
+      <c r="J131" s="98"/>
+      <c r="K131" s="98"/>
+      <c r="L131" s="98"/>
+      <c r="M131" s="98"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A132" s="131"/>
+      <c r="B132" s="132"/>
+      <c r="C132" s="131"/>
+      <c r="D132" s="132"/>
+      <c r="E132" s="132"/>
+      <c r="F132" s="131"/>
+      <c r="G132" s="131"/>
+      <c r="H132" s="98"/>
+      <c r="I132" s="98"/>
+      <c r="J132" s="98"/>
+      <c r="K132" s="98"/>
+      <c r="L132" s="98"/>
+      <c r="M132" s="98"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A133" s="131"/>
+      <c r="B133" s="132"/>
+      <c r="C133" s="131"/>
+      <c r="D133" s="132"/>
+      <c r="E133" s="132"/>
+      <c r="F133" s="131"/>
+      <c r="G133" s="131"/>
+      <c r="H133" s="98"/>
+      <c r="I133" s="98"/>
+      <c r="J133" s="98"/>
+      <c r="K133" s="98"/>
+      <c r="L133" s="98"/>
+      <c r="M133" s="98"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A134" s="131"/>
+      <c r="B134" s="132"/>
+      <c r="C134" s="131"/>
+      <c r="D134" s="132"/>
+      <c r="E134" s="132"/>
+      <c r="F134" s="131"/>
+      <c r="G134" s="131"/>
+      <c r="H134" s="98"/>
+      <c r="I134" s="98"/>
+      <c r="J134" s="98"/>
+      <c r="K134" s="98"/>
+      <c r="L134" s="98"/>
+      <c r="M134" s="98"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A135" s="131"/>
+      <c r="B135" s="132"/>
+      <c r="C135" s="131"/>
+      <c r="D135" s="132"/>
+      <c r="E135" s="132"/>
+      <c r="F135" s="131"/>
+      <c r="G135" s="131"/>
+      <c r="H135" s="98"/>
+      <c r="I135" s="98"/>
+      <c r="J135" s="98"/>
+      <c r="K135" s="98"/>
+      <c r="L135" s="98"/>
+      <c r="M135" s="98"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A136" s="134" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B136" s="98"/>
+      <c r="C136" s="135" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D136" s="133" t="e">
         <f>AVERAGEIFS(D128:D135,C128:C135,Summary!$D$4,F128:F135,"y")</f>
-      </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A137" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Value in use - ceiling j</t>
-        </is>
-      </c>
-      <c r="C137" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mA/cm²</t>
-        </is>
-      </c>
-      <c r="D137" s="48">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E136" s="98"/>
+      <c r="F136" s="98"/>
+      <c r="G136" s="98"/>
+      <c r="H136" s="98"/>
+      <c r="I136" s="98"/>
+      <c r="J136" s="98"/>
+      <c r="K136" s="98"/>
+      <c r="L136" s="98"/>
+      <c r="M136" s="98"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A137" s="134" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B137" s="98"/>
+      <c r="C137" s="135" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D137" s="133" t="e">
         <f>AVERAGEIFS(E128:E135,C128:C135,Summary!$D$4,F128:F135,"y")</f>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E137" s="98"/>
+      <c r="F137" s="98"/>
+      <c r="G137" s="98"/>
+      <c r="H137" s="98"/>
+      <c r="I137" s="98"/>
+      <c r="J137" s="98"/>
+      <c r="K137" s="98"/>
+      <c r="L137" s="98"/>
+      <c r="M137" s="98"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A138" s="98"/>
+      <c r="B138" s="98"/>
+      <c r="C138" s="98"/>
+      <c r="D138" s="98"/>
+      <c r="E138" s="98"/>
+      <c r="F138" s="98"/>
+      <c r="G138" s="98"/>
+      <c r="H138" s="98"/>
+      <c r="I138" s="98"/>
+      <c r="J138" s="98"/>
+      <c r="K138" s="98"/>
+      <c r="L138" s="98"/>
+      <c r="M138" s="98"/>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A139" s="98"/>
+      <c r="B139" s="98"/>
+      <c r="C139" s="98"/>
+      <c r="D139" s="98"/>
+      <c r="E139" s="98"/>
+      <c r="F139" s="98"/>
+      <c r="G139" s="98"/>
+      <c r="H139" s="98"/>
+      <c r="I139" s="98"/>
+      <c r="J139" s="98"/>
+      <c r="K139" s="98"/>
+      <c r="L139" s="98"/>
+      <c r="M139" s="98"/>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8:C15 C81:C88 C66:C73 C52:C59 C38:C45 C23:C30" xr:uid="{00000000-0002-0000-0700-000000000000}">
+      <formula1>ReactorList</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8:G15 F128:F135 G112:G119 H95:H102 G81:G88 J66:J73 H52:H59 F38:F45 K23:K30" xr:uid="{00000000-0002-0000-0700-000001000000}">
+      <formula1>"y,n"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23:H30" xr:uid="{00000000-0002-0000-0700-000004000000}">
+      <formula1>"H2,O2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C95:C102 C128:C135 C112:C119" xr:uid="{00000000-0002-0000-0700-00000D000000}">
+      <formula1>OrganismList</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>